--- a/translations/translations.xlsx
+++ b/translations/translations.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/russell/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/russell/Projects/GPS-Sample/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD391444-E80D-654F-8444-B7107247E594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20DB9F89-9A3C-6346-AA8A-EFF711C1B8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19160" yWindow="3960" windowWidth="29040" windowHeight="15720" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
+    <workbookView xWindow="35920" yWindow="4420" windowWidth="29040" windowHeight="15720" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4750" uniqueCount="4400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4758" uniqueCount="4408">
   <si>
     <t>app_name</t>
   </si>
@@ -13300,6 +13300,30 @@
   </si>
   <si>
     <t>GPSSample enregistre votre itinéraire (fil d\'Ariane) lorsque vous vous déplacez entre les foyers et cartographiez les foyers.\n\nL\'enregistrement ne commence que lorsque vous appuyez sur le bouton ENREGISTRER dans l\'application et s\'arrête lorsque vous appuyez sur le bouton ARRÊTER.\n\nLa localisation est collectée en continu pendant l\'enregistrement, même si l\'application est en arrière-plan ou si votre appareil est verrouillé.\n\nVos données de localisation sont stockées en toute sécurité sur votre appareil et ne sont exportées que si vous le souhaitez.\n\nVous pouvez révoquer l\'accès à la localisation en arrière-plan à tout moment dans les paramètres Android.</t>
+  </si>
+  <si>
+    <t>password_error</t>
+  </si>
+  <si>
+    <t>duplicate_import</t>
+  </si>
+  <si>
+    <t>enumerator_import_error</t>
+  </si>
+  <si>
+    <t>proximity_warning_value</t>
+  </si>
+  <si>
+    <t>The password entered is incorrect.</t>
+  </si>
+  <si>
+    <t>The selected GeoJson file appears to have already been imported. Would you like to continue with this import?</t>
+  </si>
+  <si>
+    <t>This configuration does not have an enumeration team associated with it.</t>
+  </si>
+  <si>
+    <t>Proximity warning value?</t>
   </si>
 </sst>
 </file>
@@ -13518,7 +13542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -13570,6 +13594,11 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13677,8 +13706,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}" name="Table1" displayName="Table1" ref="A1:J475" totalsRowShown="0" headerRowDxfId="5">
-  <autoFilter ref="A1:J475" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}" name="Table1" displayName="Table1" ref="A1:J479" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="A1:J479" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{DE67F62A-9DCA-4DFE-8C98-83B024E5D946}" name="app_name" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{BCDA3AB5-7BB5-4A21-ABBB-4186B52D559D}" name="GPSSample::en" dataDxfId="3"/>
@@ -29219,20 +29248,68 @@
       </c>
     </row>
     <row r="476" spans="1:10">
-      <c r="I476" s="32"/>
-      <c r="J476" s="32"/>
+      <c r="A476" s="37" t="s">
+        <v>4400</v>
+      </c>
+      <c r="B476" s="14" t="s">
+        <v>4404</v>
+      </c>
+      <c r="C476" s="38"/>
+      <c r="D476" s="38"/>
+      <c r="E476" s="38"/>
+      <c r="F476" s="38"/>
+      <c r="G476" s="26"/>
+      <c r="H476" s="38"/>
+      <c r="I476" s="39"/>
+      <c r="J476" s="39"/>
     </row>
     <row r="477" spans="1:10">
-      <c r="I477" s="32"/>
-      <c r="J477" s="32"/>
+      <c r="A477" s="37" t="s">
+        <v>4401</v>
+      </c>
+      <c r="B477" s="14" t="s">
+        <v>4405</v>
+      </c>
+      <c r="C477" s="38"/>
+      <c r="D477" s="38"/>
+      <c r="E477" s="38"/>
+      <c r="F477" s="38"/>
+      <c r="G477" s="26"/>
+      <c r="H477" s="38"/>
+      <c r="I477" s="39"/>
+      <c r="J477" s="39"/>
     </row>
     <row r="478" spans="1:10">
-      <c r="I478" s="32"/>
-      <c r="J478" s="32"/>
+      <c r="A478" s="37" t="s">
+        <v>4402</v>
+      </c>
+      <c r="B478" s="14" t="s">
+        <v>4406</v>
+      </c>
+      <c r="C478" s="38"/>
+      <c r="D478" s="38"/>
+      <c r="E478" s="38"/>
+      <c r="F478" s="38"/>
+      <c r="G478" s="26"/>
+      <c r="H478" s="38"/>
+      <c r="I478" s="39"/>
+      <c r="J478" s="39"/>
     </row>
     <row r="479" spans="1:10">
-      <c r="I479" s="32"/>
-      <c r="J479" s="32"/>
+      <c r="A479" s="37" t="s">
+        <v>4403</v>
+      </c>
+      <c r="B479" s="14" t="s">
+        <v>4407</v>
+      </c>
+      <c r="C479" s="38"/>
+      <c r="D479" s="38"/>
+      <c r="E479" s="38"/>
+      <c r="F479" s="38"/>
+      <c r="G479" s="26"/>
+      <c r="H479" s="38"/>
+      <c r="I479" s="39"/>
+      <c r="J479" s="39"/>
     </row>
     <row r="480" spans="1:10">
       <c r="I480" s="32"/>
@@ -29294,6 +29371,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e0cf07b-8188-4b76-8f54-3cda03d37414" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="43e153a8-5ef1-4f65-aac7-dc4685f18eaa">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F12BE0DB4A3DF641BF113FBF1C7EA261" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c6b4b409d6b6c81c2874e5a51d11715e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="43e153a8-5ef1-4f65-aac7-dc4685f18eaa" xmlns:ns3="6e0cf07b-8188-4b76-8f54-3cda03d37414" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0521fade2ab7bf037697e8e8677cb864" ns2:_="" ns3:_="">
     <xsd:import namespace="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
@@ -29534,27 +29631,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E20926E-9EFB-4B7E-90D4-905B08F8E59C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e0cf07b-8188-4b76-8f54-3cda03d37414" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="43e153a8-5ef1-4f65-aac7-dc4685f18eaa">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6201EF1-2938-4925-833A-11BB4654F7B4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -29571,29 +29673,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E20926E-9EFB-4B7E-90D4-905B08F8E59C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/translations/translations.xlsx
+++ b/translations/translations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/russell/Projects/GPS-Sample/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C17420-C501-E840-B64E-19FB5AFF5FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18ABA0B9-D8A4-3742-B2B5-1C6AD3475189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16660" yWindow="2880" windowWidth="29040" windowHeight="15720" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
+    <workbookView xWindow="32040" yWindow="720" windowWidth="35760" windowHeight="24320" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4970" uniqueCount="4620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4996" uniqueCount="4646">
   <si>
     <t>app_name</t>
   </si>
@@ -13964,12 +13964,90 @@
   <si>
     <t>Halaga ng babala sa proximity?</t>
   </si>
+  <si>
+    <t>menu_team_review_show</t>
+  </si>
+  <si>
+    <t>menu_team_review_hide</t>
+  </si>
+  <si>
+    <t>continue_button</t>
+  </si>
+  <si>
+    <t>help_button</t>
+  </si>
+  <si>
+    <t>hide_breadcrumbs</t>
+  </si>
+  <si>
+    <t>stop_recording</t>
+  </si>
+  <si>
+    <t>primary_sample</t>
+  </si>
+  <si>
+    <t>strata_sample</t>
+  </si>
+  <si>
+    <t>subset_sample</t>
+  </si>
+  <si>
+    <t>subset_name</t>
+  </si>
+  <si>
+    <t>enable_subset_sample</t>
+  </si>
+  <si>
+    <t>enable_subset_sample_description</t>
+  </si>
+  <si>
+    <t>details</t>
+  </si>
+  <si>
+    <t>Show Walked Path</t>
+  </si>
+  <si>
+    <t>Hide Walked Path</t>
+  </si>
+  <si>
+    <t>Continue</t>
+  </si>
+  <si>
+    <t>Help</t>
+  </si>
+  <si>
+    <t>Hide the walked path</t>
+  </si>
+  <si>
+    <t>Stop recording the walked path</t>
+  </si>
+  <si>
+    <t>Primary Sample</t>
+  </si>
+  <si>
+    <t>Strata Sample</t>
+  </si>
+  <si>
+    <t>Subset Sample</t>
+  </si>
+  <si>
+    <t>Subset Name</t>
+  </si>
+  <si>
+    <t>Enable Subset Sample</t>
+  </si>
+  <si>
+    <t>Placeholder for the Enable Subset Sampling CheckBox description</t>
+  </si>
+  <si>
+    <t>Details</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -14063,6 +14141,12 @@
       <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF080808"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -14144,7 +14228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -14206,6 +14290,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14395,8 +14486,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}" name="Table1" displayName="Table1" ref="A1:J497" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J497" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}" name="Table1" displayName="Table1" ref="A1:J510" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J510" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{DE67F62A-9DCA-4DFE-8C98-83B024E5D946}" name="app_name" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{BCDA3AB5-7BB5-4A21-ABBB-4186B52D559D}" name="GPSSample::en" dataDxfId="8"/>
@@ -14722,7 +14813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD3E6CC-854C-5841-9577-D3ADD2982DB6}">
-  <dimension ref="A1:J497"/>
+  <dimension ref="A1:J510"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="28.33203125" customWidth="1"/>
@@ -30640,6 +30731,214 @@
         <v>4613</v>
       </c>
     </row>
+    <row r="498" spans="1:10">
+      <c r="A498" s="37" t="s">
+        <v>4620</v>
+      </c>
+      <c r="B498" s="41" t="s">
+        <v>4633</v>
+      </c>
+      <c r="C498" s="39"/>
+      <c r="D498" s="39"/>
+      <c r="E498" s="39"/>
+      <c r="F498" s="39"/>
+      <c r="G498" s="6"/>
+      <c r="H498" s="39"/>
+      <c r="I498" s="40"/>
+      <c r="J498" s="40"/>
+    </row>
+    <row r="499" spans="1:10">
+      <c r="A499" s="37" t="s">
+        <v>4621</v>
+      </c>
+      <c r="B499" s="41" t="s">
+        <v>4634</v>
+      </c>
+      <c r="C499" s="39"/>
+      <c r="D499" s="39"/>
+      <c r="E499" s="39"/>
+      <c r="F499" s="39"/>
+      <c r="G499" s="6"/>
+      <c r="H499" s="39"/>
+      <c r="I499" s="40"/>
+      <c r="J499" s="40"/>
+    </row>
+    <row r="500" spans="1:10">
+      <c r="A500" s="37" t="s">
+        <v>4622</v>
+      </c>
+      <c r="B500" s="38" t="s">
+        <v>4635</v>
+      </c>
+      <c r="C500" s="39"/>
+      <c r="D500" s="39"/>
+      <c r="E500" s="39"/>
+      <c r="F500" s="39"/>
+      <c r="G500" s="6"/>
+      <c r="H500" s="39"/>
+      <c r="I500" s="40"/>
+      <c r="J500" s="40"/>
+    </row>
+    <row r="501" spans="1:10">
+      <c r="A501" s="37" t="s">
+        <v>4623</v>
+      </c>
+      <c r="B501" s="41" t="s">
+        <v>4636</v>
+      </c>
+      <c r="C501" s="39"/>
+      <c r="D501" s="39"/>
+      <c r="E501" s="39"/>
+      <c r="F501" s="39"/>
+      <c r="G501" s="6"/>
+      <c r="H501" s="39"/>
+      <c r="I501" s="40"/>
+      <c r="J501" s="40"/>
+    </row>
+    <row r="502" spans="1:10">
+      <c r="A502" s="37" t="s">
+        <v>4624</v>
+      </c>
+      <c r="B502" s="41" t="s">
+        <v>4637</v>
+      </c>
+      <c r="C502" s="39"/>
+      <c r="D502" s="39"/>
+      <c r="E502" s="39"/>
+      <c r="F502" s="39"/>
+      <c r="G502" s="6"/>
+      <c r="H502" s="39"/>
+      <c r="I502" s="40"/>
+      <c r="J502" s="40"/>
+    </row>
+    <row r="503" spans="1:10">
+      <c r="A503" s="37" t="s">
+        <v>4625</v>
+      </c>
+      <c r="B503" s="41" t="s">
+        <v>4638</v>
+      </c>
+      <c r="C503" s="39"/>
+      <c r="D503" s="39"/>
+      <c r="E503" s="39"/>
+      <c r="F503" s="39"/>
+      <c r="G503" s="6"/>
+      <c r="H503" s="39"/>
+      <c r="I503" s="40"/>
+      <c r="J503" s="40"/>
+    </row>
+    <row r="504" spans="1:10">
+      <c r="A504" s="37" t="s">
+        <v>4626</v>
+      </c>
+      <c r="B504" s="41" t="s">
+        <v>4639</v>
+      </c>
+      <c r="C504" s="39"/>
+      <c r="D504" s="39"/>
+      <c r="E504" s="39"/>
+      <c r="F504" s="39"/>
+      <c r="G504" s="6"/>
+      <c r="H504" s="39"/>
+      <c r="I504" s="40"/>
+      <c r="J504" s="40"/>
+    </row>
+    <row r="505" spans="1:10">
+      <c r="A505" s="37" t="s">
+        <v>4627</v>
+      </c>
+      <c r="B505" s="41" t="s">
+        <v>4640</v>
+      </c>
+      <c r="C505" s="39"/>
+      <c r="D505" s="39"/>
+      <c r="E505" s="39"/>
+      <c r="F505" s="39"/>
+      <c r="G505" s="6"/>
+      <c r="H505" s="39"/>
+      <c r="I505" s="40"/>
+      <c r="J505" s="40"/>
+    </row>
+    <row r="506" spans="1:10">
+      <c r="A506" s="37" t="s">
+        <v>4628</v>
+      </c>
+      <c r="B506" s="41" t="s">
+        <v>4641</v>
+      </c>
+      <c r="C506" s="39"/>
+      <c r="D506" s="39"/>
+      <c r="E506" s="39"/>
+      <c r="F506" s="39"/>
+      <c r="G506" s="6"/>
+      <c r="H506" s="39"/>
+      <c r="I506" s="40"/>
+      <c r="J506" s="40"/>
+    </row>
+    <row r="507" spans="1:10">
+      <c r="A507" s="37" t="s">
+        <v>4629</v>
+      </c>
+      <c r="B507" s="41" t="s">
+        <v>4642</v>
+      </c>
+      <c r="C507" s="39"/>
+      <c r="D507" s="39"/>
+      <c r="E507" s="39"/>
+      <c r="F507" s="39"/>
+      <c r="G507" s="6"/>
+      <c r="H507" s="39"/>
+      <c r="I507" s="40"/>
+      <c r="J507" s="40"/>
+    </row>
+    <row r="508" spans="1:10">
+      <c r="A508" s="37" t="s">
+        <v>4630</v>
+      </c>
+      <c r="B508" s="38" t="s">
+        <v>4643</v>
+      </c>
+      <c r="C508" s="39"/>
+      <c r="D508" s="39"/>
+      <c r="E508" s="39"/>
+      <c r="F508" s="39"/>
+      <c r="G508" s="6"/>
+      <c r="H508" s="39"/>
+      <c r="I508" s="40"/>
+      <c r="J508" s="40"/>
+    </row>
+    <row r="509" spans="1:10">
+      <c r="A509" s="37" t="s">
+        <v>4631</v>
+      </c>
+      <c r="B509" s="38" t="s">
+        <v>4644</v>
+      </c>
+      <c r="C509" s="39"/>
+      <c r="D509" s="39"/>
+      <c r="E509" s="39"/>
+      <c r="F509" s="39"/>
+      <c r="G509" s="6"/>
+      <c r="H509" s="39"/>
+      <c r="I509" s="40"/>
+      <c r="J509" s="40"/>
+    </row>
+    <row r="510" spans="1:10">
+      <c r="A510" s="37" t="s">
+        <v>4632</v>
+      </c>
+      <c r="B510" s="41" t="s">
+        <v>4645</v>
+      </c>
+      <c r="C510" s="39"/>
+      <c r="D510" s="39"/>
+      <c r="E510" s="39"/>
+      <c r="F510" s="39"/>
+      <c r="G510" s="6"/>
+      <c r="H510" s="39"/>
+      <c r="I510" s="40"/>
+      <c r="J510" s="40"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30652,26 +30951,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e0cf07b-8188-4b76-8f54-3cda03d37414" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="43e153a8-5ef1-4f65-aac7-dc4685f18eaa">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F12BE0DB4A3DF641BF113FBF1C7EA261" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c6b4b409d6b6c81c2874e5a51d11715e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="43e153a8-5ef1-4f65-aac7-dc4685f18eaa" xmlns:ns3="6e0cf07b-8188-4b76-8f54-3cda03d37414" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0521fade2ab7bf037697e8e8677cb864" ns2:_="" ns3:_="">
     <xsd:import namespace="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
@@ -30912,10 +31191,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e0cf07b-8188-4b76-8f54-3cda03d37414" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="43e153a8-5ef1-4f65-aac7-dc4685f18eaa">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6201EF1-2938-4925-833A-11BB4654F7B4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
+    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -30938,20 +31248,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6201EF1-2938-4925-833A-11BB4654F7B4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
-    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/translations/translations.xlsx
+++ b/translations/translations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/russell/Projects/GPS-Sample/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2413F2-C830-B34A-9142-04AC67087426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE9ECBF-98C1-2940-B27E-36707EB3B85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18400" yWindow="2240" windowWidth="45160" windowHeight="22480" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5083" uniqueCount="4726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5074" uniqueCount="4717">
   <si>
     <t>app_name</t>
   </si>
@@ -10257,9 +10257,6 @@
     <t>Autorisation de localisation en arrière-plan</t>
   </si>
   <si>
-    <t>Activer la localisation en arrière-plan : \nTOUJOURS AUTORISER</t>
-  </si>
-  <si>
     <t>Permiso de ubicación en segundo plano</t>
   </si>
   <si>
@@ -10290,10 +10287,6 @@
     <t>Nanti: fitur pelacakan tidak akan berfungsi</t>
   </si>
   <si>
-    <t>Aktifkan Lokasi Latar Belakang:
-IZINKAN SEPANJANG WAKTU</t>
-  </si>
-  <si>
     <t>GPSSample merekam rute Anda (jejak perjalanan) saat Anda bepergian antar rumah tangga dan memetakan rumah tangga.\n\nPerekaman hanya dimulai saat Anda mengetuk tombol REKAM di aplikasi dan berhenti merekam saat Anda mengetuk tombol BERHENTI.\n\nLokasi dikumpulkan terus menerus selama perekaman, bahkan jika aplikasi berada di latar belakang atau perangkat Anda terkunci.\n\nData lokasi Anda disimpan dengan aman di perangkat Anda dan hanya diekspor jika Anda memilih untuk melakukannya.\n\nAnda dapat mencabut akses lokasi latar belakang kapan saja di Pengaturan Android.</t>
   </si>
   <si>
@@ -12976,47 +12969,15 @@
     <t>ایا تاسو ډاډه یاست چې غواړئ نقشه پاکه کړئ؟</t>
   </si>
   <si>
-    <t>د شاليد موقعيت فعال کړئ:\nتل اجازه ورکړئ</t>
-  </si>
-  <si>
-    <t>1. د تنظیماتو پرانیزئ (OPEN SETTINGS) تڼۍ ووهئ\n
-2. په لست کې GPSSample ومومئ.\n
-3. د شالید فعالیت اجازه (ALLOW BACKGROUND ACTIVITY) فعاله کړئ.\n
-4. بېرته دې اپلېکېشن ته راستانه شئ.</t>
-  </si>
-  <si>
     <t>اوس نه:\nتعقیب به کار ونه کړي</t>
   </si>
   <si>
-    <t>GPSSample ستاسو د تګ لاره ثبتوي کله چې تاسو د کورونو ترمنځ ګرځئ او کورونه په نقشه کې نښه کوئ.\n\n
-ثبت هغه وخت پیل کېږي کله چې تاسو د ثبت تڼۍ ووهئ، او هغه وخت بندېږي کله چې د بندولو تڼۍ ووهئ.\n\n
-کله چې ثبت روان وي، موقعیت تل اخیستل کېږي، حتی که اپلېکېشن په شالید کې وي یا موبایل لاک وي.\n\n
-ستاسو د موقعیت معلومات ستاسو په موبایل کې په خوندي ډول ساتل کېږي او یوازې ستاسو په اجازه لېږدول کېږي.\n\n
-تاسو کولی شئ د شالید موقعیت اجازه هر وخت د Android له تنظیماتو څخه بنده کړئ.</t>
-  </si>
-  <si>
-    <t>1. دکمه تنظیمات را لمس کنید\n
-2. GPSSample را در فهرست پیدا کنید.\n
-3. اجازه فعالیت در پس‌زمینه را فعال کنید.\n
-4. دوباره به این برنامه برگردید.</t>
-  </si>
-  <si>
     <t>مجوز موقعیت مکانی پس‌زمینه</t>
   </si>
   <si>
     <t>فعلاً نه:\nویژگی ردیابی کار نخواهد کرد</t>
   </si>
   <si>
-    <t>فعال‌سازی موقعیت در پس‌زمینه:\nهمیشه اجازه بده</t>
-  </si>
-  <si>
-    <t>GPSSample راه رفتن شما را ثبت می‌کند وقتی که بین خانه‌ها می‌روید و خانه‌ها را در نقشه نشان می‌دهید.\n\n
-ثبت زمانی شروع می‌شود که دکمه ثبت را لمس می‌کنید و زمانی پایان می‌یابد که دکمه توقف را لمس می‌کنید.\n\n
-وقتی ثبت روشن است، موقعیت شما همیشه گرفته می‌شود، حتی اگر برنامه باز نباشد یا تلفن قفل باشد.\n\n
-اطلاعات موقعیت شما به‌صورت امن در تلفن شما نگه‌داری می‌شود و فقط با اجازه شما انتقال داده می‌شود.\n\n
-شما می‌توانید اجازه موقعیت در پس‌زمینه را هر وقت از تنظیمات اندروید خاموش کنید.</t>
-  </si>
-  <si>
     <t>note</t>
   </si>
   <si>
@@ -13578,10 +13539,6 @@
     <t>دا ساحه د PII په توګه نښه کړئ که دا کولی شي یو ځانګړی فرد وپیژني. مثالونه: بشپړ نوم، د تلیفون شمېره، د ملي پېژندپاڼې شمېره.</t>
   </si>
   <si>
-    <t xml:space="preserve">
-د دې شمېرې پر بنسټ د پوښتنو د یوې ټولګې د تکرار لپاره د فیلډ بلاک وکاروئ. بېلګه: که دا فیلډ د ماشومانو شمېر ثبتوي، په بلاک کې پوښتنې به د هر ماشوم لپاره یو ځل وپوښتل شي. په ډله کې وروستۍ پوښتنه د End Field Block سره نښه کړئ.</t>
-  </si>
-  <si>
     <t>د خپلې مراجعې لپاره دې قانون ته یو لنډ تشریحي نوم ورکړئ (د بېلګې په توګه، '12-23 میاشتني ماشوم لري'، 'یو کور دی' کیدای شي child_household وي). دا نوم د فلټر تنظیم کولو په ګام کې ښکاري چیرې چې اصول سره یوځای کیږي.</t>
   </si>
   <si>
@@ -13598,9 +13555,6 @@
   </si>
   <si>
     <t>این فیلد را در صورتی که بتواند یک فرد خاص را شناسایی کند، به عنوان PII (اطلاعات شخصی قابل شناسایی) علامت‌گذاری کنید. مثال‌ها: نام کامل، شماره تلفن، شماره شناسایی ملی.</t>
-  </si>
-  <si>
-    <t>برای تکرار مجموعه‌ای از سؤالات بر اساس این شماره، از یک بلوک فیلد استفاده کنید. مثال: اگر این فیلد تعداد فرزندان را ثبت می‌کند، سؤالات موجود در بلوک به ازای هر فرزند یک بار پرسیده می‌شوند. آخرین سؤال در این گروه را با End Field Block علامت بزنید.</t>
   </si>
   <si>
     <t>برای ارجاع خود، یک نام توصیفی کوتاه به این قاعده بدهید (مثلاً، «دارای فرزند ۱۲-۲۳ ماهه»، «یک خانوار» می‌تواند child_household باشد). این نام در مرحله تنظیم فیلتر که در آن قواعد با هم ترکیب می‌شوند، ظاهر می‌گردد.</t>
@@ -14278,8 +14232,10 @@
     <t>Method descriptions:\n\nSimple Random Sample:\nEach household has an equal chance of being selected.\n\nCluster Sample (# of households):\nSelect a fixed number of households from each cluster.\n\nCluster Sample (% of households):\nSelect a percentage of households from each cluster.</t>
   </si>
   <si>
-    <t xml:space="preserve">
-</t>
+    <t>Activer la localisation en arrière-plan :\nTOUJOURS AUTORISER</t>
+  </si>
+  <si>
+    <t>Aktifkan Lokasi Latar Belakang:&amp;#10;IZINKAN SEPANJANG WAKTU</t>
   </si>
 </sst>
 </file>
@@ -15053,7 +15009,7 @@
     <col min="5" max="5" width="26.6640625" customWidth="1"/>
     <col min="6" max="6" width="29.1640625" customWidth="1"/>
     <col min="7" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="34.5" customWidth="1"/>
+    <col min="8" max="8" width="70.83203125" customWidth="1"/>
     <col min="9" max="9" width="74.83203125" customWidth="1"/>
     <col min="10" max="10" width="40.33203125" customWidth="1"/>
   </cols>
@@ -15084,10 +15040,10 @@
         <v>2884</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>4396</v>
+        <v>4388</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>4397</v>
+        <v>4389</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -15116,10 +15072,10 @@
         <v>2885</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>3432</v>
+        <v>3430</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>3432</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -15148,10 +15104,10 @@
         <v>2886</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>3433</v>
+        <v>3431</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>3875</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -15180,10 +15136,10 @@
         <v>2887</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>3434</v>
+        <v>3432</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>3876</v>
+        <v>3874</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -15212,10 +15168,10 @@
         <v>2888</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>3435</v>
+        <v>3433</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>3877</v>
+        <v>3875</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -15244,10 +15200,10 @@
         <v>33</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>3436</v>
+        <v>3434</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>3436</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -15276,10 +15232,10 @@
         <v>2889</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>3437</v>
+        <v>3435</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>3878</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -15308,10 +15264,10 @@
         <v>2890</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>3438</v>
+        <v>3436</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>3879</v>
+        <v>3877</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -15340,10 +15296,10 @@
         <v>2891</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>3439</v>
+        <v>3437</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>3883</v>
+        <v>3881</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -15372,10 +15328,10 @@
         <v>2892</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>3440</v>
+        <v>3438</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>3882</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -15404,10 +15360,10 @@
         <v>2893</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>3441</v>
+        <v>3439</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>3880</v>
+        <v>3878</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -15436,10 +15392,10 @@
         <v>2894</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>3442</v>
+        <v>3440</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>3881</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -15468,10 +15424,10 @@
         <v>2895</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>3443</v>
+        <v>3441</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>3912</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -15500,10 +15456,10 @@
         <v>2896</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>3444</v>
+        <v>3442</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>3913</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -15532,10 +15488,10 @@
         <v>2897</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>3445</v>
+        <v>3443</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>3914</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -15564,10 +15520,10 @@
         <v>2898</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>3446</v>
+        <v>3444</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>3915</v>
+        <v>3913</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -15596,10 +15552,10 @@
         <v>2899</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>3447</v>
+        <v>3445</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>3916</v>
+        <v>3914</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -15628,10 +15584,10 @@
         <v>2900</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>3448</v>
+        <v>3446</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>3917</v>
+        <v>3915</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -15660,10 +15616,10 @@
         <v>2901</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>3449</v>
+        <v>3447</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>3918</v>
+        <v>3916</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -15692,10 +15648,10 @@
         <v>2902</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>3450</v>
+        <v>3448</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>3919</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -15724,10 +15680,10 @@
         <v>2903</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>3451</v>
+        <v>3449</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>3920</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -15756,10 +15712,10 @@
         <v>2904</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>3452</v>
+        <v>3450</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>3925</v>
+        <v>3923</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -15788,10 +15744,10 @@
         <v>2905</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>3453</v>
+        <v>3451</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>3924</v>
+        <v>3922</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -15820,10 +15776,10 @@
         <v>2906</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>3454</v>
+        <v>3452</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>3923</v>
+        <v>3921</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -15852,10 +15808,10 @@
         <v>2907</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>3455</v>
+        <v>3453</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>3922</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -15884,10 +15840,10 @@
         <v>2908</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>3456</v>
+        <v>3454</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>3921</v>
+        <v>3919</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -15916,10 +15872,10 @@
         <v>2909</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>3457</v>
+        <v>3455</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>3908</v>
+        <v>3906</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -15948,10 +15904,10 @@
         <v>2910</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>3458</v>
+        <v>3456</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>3909</v>
+        <v>3907</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -15980,10 +15936,10 @@
         <v>175</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>3459</v>
+        <v>3457</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>3910</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -16012,10 +15968,10 @@
         <v>2911</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -16044,10 +16000,10 @@
         <v>2912</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>3461</v>
+        <v>3459</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>3911</v>
+        <v>3909</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -16076,10 +16032,10 @@
         <v>190</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>3462</v>
+        <v>3460</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>3884</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -16108,10 +16064,10 @@
         <v>196</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>3463</v>
+        <v>3461</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>3885</v>
+        <v>3883</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -16140,10 +16096,10 @@
         <v>2913</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>3464</v>
+        <v>3462</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>3886</v>
+        <v>3884</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -16172,10 +16128,10 @@
         <v>2914</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>3465</v>
+        <v>3463</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>3887</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -16204,10 +16160,10 @@
         <v>2916</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>3888</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -16236,10 +16192,10 @@
         <v>2915</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>3467</v>
+        <v>3465</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>3889</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -16268,10 +16224,10 @@
         <v>2917</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>3468</v>
+        <v>3466</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>3890</v>
+        <v>3888</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -16300,10 +16256,10 @@
         <v>2918</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>3469</v>
+        <v>3467</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>3891</v>
+        <v>3889</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -16332,10 +16288,10 @@
         <v>238</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>3470</v>
+        <v>3468</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>3470</v>
+        <v>3468</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -16364,10 +16320,10 @@
         <v>2919</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>3471</v>
+        <v>3469</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>3471</v>
+        <v>3469</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -16396,10 +16352,10 @@
         <v>249</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>3472</v>
+        <v>3470</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>3892</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -16428,10 +16384,10 @@
         <v>255</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>3473</v>
+        <v>3471</v>
       </c>
       <c r="J43" s="14" t="s">
-        <v>3893</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -16460,10 +16416,10 @@
         <v>2920</v>
       </c>
       <c r="I44" s="14" t="s">
-        <v>3474</v>
+        <v>3472</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>3894</v>
+        <v>3892</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -16492,10 +16448,10 @@
         <v>267</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J45" s="14" t="s">
-        <v>3895</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -16524,10 +16480,10 @@
         <v>2921</v>
       </c>
       <c r="I46" s="14" t="s">
-        <v>3436</v>
+        <v>3434</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>3436</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -16556,10 +16512,10 @@
         <v>2922</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>3476</v>
+        <v>3474</v>
       </c>
       <c r="J47" s="14" t="s">
-        <v>3896</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -16588,10 +16544,10 @@
         <v>284</v>
       </c>
       <c r="I48" s="14" t="s">
-        <v>3477</v>
+        <v>3475</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>3897</v>
+        <v>3895</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -16620,10 +16576,10 @@
         <v>289</v>
       </c>
       <c r="I49" s="14" t="s">
-        <v>3478</v>
+        <v>3476</v>
       </c>
       <c r="J49" s="14" t="s">
-        <v>3898</v>
+        <v>3896</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -16652,10 +16608,10 @@
         <v>2923</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>3479</v>
+        <v>3477</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>3432</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -16684,10 +16640,10 @@
         <v>2924</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>3480</v>
+        <v>3478</v>
       </c>
       <c r="J51" s="14" t="s">
-        <v>3899</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -16716,10 +16672,10 @@
         <v>2925</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>3481</v>
+        <v>3479</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>3900</v>
+        <v>3898</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -16748,10 +16704,10 @@
         <v>314</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>3482</v>
+        <v>3480</v>
       </c>
       <c r="J53" s="14" t="s">
-        <v>3901</v>
+        <v>3899</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -16780,10 +16736,10 @@
         <v>2926</v>
       </c>
       <c r="I54" s="14" t="s">
-        <v>3483</v>
+        <v>3481</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>3902</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -16812,10 +16768,10 @@
         <v>2927</v>
       </c>
       <c r="I55" s="14" t="s">
-        <v>3484</v>
+        <v>3482</v>
       </c>
       <c r="J55" s="14" t="s">
-        <v>3903</v>
+        <v>3901</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -16844,10 +16800,10 @@
         <v>2928</v>
       </c>
       <c r="I56" s="14" t="s">
-        <v>3485</v>
+        <v>3483</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>3904</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -16876,10 +16832,10 @@
         <v>2929</v>
       </c>
       <c r="I57" s="14" t="s">
-        <v>3486</v>
+        <v>3484</v>
       </c>
       <c r="J57" s="14" t="s">
-        <v>3905</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -16908,10 +16864,10 @@
         <v>2930</v>
       </c>
       <c r="I58" s="14" t="s">
-        <v>3487</v>
+        <v>3485</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>3906</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -16940,10 +16896,10 @@
         <v>2931</v>
       </c>
       <c r="I59" s="14" t="s">
-        <v>3488</v>
+        <v>3486</v>
       </c>
       <c r="J59" s="14" t="s">
-        <v>3907</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -16972,10 +16928,10 @@
         <v>2932</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>3489</v>
+        <v>3487</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>3984</v>
+        <v>3982</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -17004,10 +16960,10 @@
         <v>2933</v>
       </c>
       <c r="I61" s="14" t="s">
-        <v>3490</v>
+        <v>3488</v>
       </c>
       <c r="J61" s="14" t="s">
-        <v>3985</v>
+        <v>3983</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -17036,10 +16992,10 @@
         <v>2934</v>
       </c>
       <c r="I62" s="14" t="s">
-        <v>3491</v>
+        <v>3489</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>3986</v>
+        <v>3984</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -17068,10 +17024,10 @@
         <v>2935</v>
       </c>
       <c r="I63" s="14" t="s">
-        <v>3492</v>
+        <v>3490</v>
       </c>
       <c r="J63" s="14" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -17085,7 +17041,7 @@
         <v>372</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>4555</v>
+        <v>4545</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>373</v>
@@ -17100,10 +17056,10 @@
         <v>2936</v>
       </c>
       <c r="I64" s="14" t="s">
-        <v>3493</v>
+        <v>3491</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>3988</v>
+        <v>3986</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -17132,10 +17088,10 @@
         <v>2937</v>
       </c>
       <c r="I65" s="14" t="s">
-        <v>3494</v>
+        <v>3492</v>
       </c>
       <c r="J65" s="14" t="s">
-        <v>3989</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -17164,10 +17120,10 @@
         <v>2939</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="J66" s="14" t="s">
-        <v>3990</v>
+        <v>3988</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -17196,10 +17152,10 @@
         <v>2938</v>
       </c>
       <c r="I67" s="14" t="s">
-        <v>3496</v>
+        <v>3494</v>
       </c>
       <c r="J67" s="14" t="s">
-        <v>3991</v>
+        <v>3989</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -17228,10 +17184,10 @@
         <v>2940</v>
       </c>
       <c r="I68" s="14" t="s">
-        <v>3497</v>
+        <v>3495</v>
       </c>
       <c r="J68" s="14" t="s">
-        <v>3992</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -17260,10 +17216,10 @@
         <v>2941</v>
       </c>
       <c r="I69" s="14" t="s">
-        <v>3498</v>
+        <v>3496</v>
       </c>
       <c r="J69" s="14" t="s">
-        <v>3993</v>
+        <v>3991</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -17292,10 +17248,10 @@
         <v>2942</v>
       </c>
       <c r="I70" s="14" t="s">
-        <v>3499</v>
+        <v>3497</v>
       </c>
       <c r="J70" s="14" t="s">
-        <v>3994</v>
+        <v>3992</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -17324,10 +17280,10 @@
         <v>2943</v>
       </c>
       <c r="I71" s="14" t="s">
-        <v>3500</v>
+        <v>3498</v>
       </c>
       <c r="J71" s="14" t="s">
-        <v>3995</v>
+        <v>3993</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -17356,10 +17312,10 @@
         <v>2944</v>
       </c>
       <c r="I72" s="14" t="s">
-        <v>3501</v>
+        <v>3499</v>
       </c>
       <c r="J72" s="14" t="s">
-        <v>3968</v>
+        <v>3966</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -17388,10 +17344,10 @@
         <v>2946</v>
       </c>
       <c r="I73" s="14" t="s">
-        <v>3502</v>
+        <v>3500</v>
       </c>
       <c r="J73" s="14" t="s">
-        <v>3969</v>
+        <v>3967</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -17420,10 +17376,10 @@
         <v>2945</v>
       </c>
       <c r="I74" s="14" t="s">
-        <v>3433</v>
+        <v>3431</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>3875</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -17452,10 +17408,10 @@
         <v>2947</v>
       </c>
       <c r="I75" s="14" t="s">
-        <v>3503</v>
+        <v>3501</v>
       </c>
       <c r="J75" s="14" t="s">
-        <v>3970</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -17484,10 +17440,10 @@
         <v>2948</v>
       </c>
       <c r="I76" s="14" t="s">
-        <v>3504</v>
+        <v>3502</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>3971</v>
+        <v>3969</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -17516,10 +17472,10 @@
         <v>2949</v>
       </c>
       <c r="I77" s="14" t="s">
-        <v>3505</v>
+        <v>3503</v>
       </c>
       <c r="J77" s="14" t="s">
-        <v>3972</v>
+        <v>3970</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -17548,10 +17504,10 @@
         <v>450</v>
       </c>
       <c r="I78" s="14" t="s">
-        <v>3506</v>
+        <v>3504</v>
       </c>
       <c r="J78" s="14" t="s">
-        <v>3973</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -17580,10 +17536,10 @@
         <v>2950</v>
       </c>
       <c r="I79" s="14" t="s">
-        <v>3507</v>
+        <v>3505</v>
       </c>
       <c r="J79" s="14" t="s">
-        <v>3974</v>
+        <v>3972</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -17612,10 +17568,10 @@
         <v>2951</v>
       </c>
       <c r="I80" s="14" t="s">
-        <v>3508</v>
+        <v>3506</v>
       </c>
       <c r="J80" s="14" t="s">
-        <v>3975</v>
+        <v>3973</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -17644,10 +17600,10 @@
         <v>2952</v>
       </c>
       <c r="I81" s="14" t="s">
-        <v>3509</v>
+        <v>3507</v>
       </c>
       <c r="J81" s="14" t="s">
-        <v>3976</v>
+        <v>3974</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -17676,10 +17632,10 @@
         <v>2953</v>
       </c>
       <c r="I82" s="14" t="s">
-        <v>3510</v>
+        <v>3508</v>
       </c>
       <c r="J82" s="14" t="s">
-        <v>3977</v>
+        <v>3975</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -17708,10 +17664,10 @@
         <v>2954</v>
       </c>
       <c r="I83" s="14" t="s">
-        <v>3511</v>
+        <v>3509</v>
       </c>
       <c r="J83" s="14" t="s">
-        <v>3978</v>
+        <v>3976</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -17740,10 +17696,10 @@
         <v>2955</v>
       </c>
       <c r="I84" s="14" t="s">
-        <v>3512</v>
+        <v>3510</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>3979</v>
+        <v>3977</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -17772,10 +17728,10 @@
         <v>2956</v>
       </c>
       <c r="I85" s="14" t="s">
-        <v>3513</v>
+        <v>3511</v>
       </c>
       <c r="J85" s="14" t="s">
-        <v>3980</v>
+        <v>3978</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -17804,10 +17760,10 @@
         <v>2957</v>
       </c>
       <c r="I86" s="14" t="s">
-        <v>3514</v>
+        <v>3512</v>
       </c>
       <c r="J86" s="14" t="s">
-        <v>3981</v>
+        <v>3979</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -17836,10 +17792,10 @@
         <v>2958</v>
       </c>
       <c r="I87" s="14" t="s">
-        <v>3515</v>
+        <v>3513</v>
       </c>
       <c r="J87" s="14" t="s">
-        <v>3982</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -17868,10 +17824,10 @@
         <v>2959</v>
       </c>
       <c r="I88" s="14" t="s">
-        <v>3516</v>
+        <v>3514</v>
       </c>
       <c r="J88" s="14" t="s">
-        <v>3983</v>
+        <v>3981</v>
       </c>
     </row>
     <row r="89" spans="1:10">
@@ -17900,10 +17856,10 @@
         <v>2960</v>
       </c>
       <c r="I89" s="14" t="s">
-        <v>3517</v>
+        <v>3515</v>
       </c>
       <c r="J89" s="14" t="s">
-        <v>4041</v>
+        <v>4039</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -17932,10 +17888,10 @@
         <v>2961</v>
       </c>
       <c r="I90" s="14" t="s">
-        <v>3518</v>
+        <v>3516</v>
       </c>
       <c r="J90" s="14" t="s">
-        <v>4042</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -17964,10 +17920,10 @@
         <v>2962</v>
       </c>
       <c r="I91" s="14" t="s">
-        <v>3519</v>
+        <v>3517</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>4043</v>
+        <v>4041</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -17996,10 +17952,10 @@
         <v>2963</v>
       </c>
       <c r="I92" s="14" t="s">
-        <v>3520</v>
+        <v>3518</v>
       </c>
       <c r="J92" s="14" t="s">
-        <v>4044</v>
+        <v>4042</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -18028,10 +17984,10 @@
         <v>2964</v>
       </c>
       <c r="I93" s="14" t="s">
-        <v>3521</v>
+        <v>3519</v>
       </c>
       <c r="J93" s="14" t="s">
-        <v>4038</v>
+        <v>4036</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -18060,10 +18016,10 @@
         <v>2965</v>
       </c>
       <c r="I94" s="14" t="s">
-        <v>3522</v>
+        <v>3520</v>
       </c>
       <c r="J94" s="14" t="s">
-        <v>4039</v>
+        <v>4037</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -18092,10 +18048,10 @@
         <v>2966</v>
       </c>
       <c r="I95" s="14" t="s">
-        <v>3523</v>
+        <v>3521</v>
       </c>
       <c r="J95" s="14" t="s">
-        <v>4040</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -18124,10 +18080,10 @@
         <v>2967</v>
       </c>
       <c r="I96" s="14" t="s">
-        <v>3524</v>
+        <v>3522</v>
       </c>
       <c r="J96" s="14" t="s">
-        <v>4037</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -18156,10 +18112,10 @@
         <v>2968</v>
       </c>
       <c r="I97" s="14" t="s">
-        <v>3525</v>
+        <v>3523</v>
       </c>
       <c r="J97" s="14" t="s">
-        <v>4035</v>
+        <v>4033</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -18188,10 +18144,10 @@
         <v>2969</v>
       </c>
       <c r="I98" s="14" t="s">
-        <v>3526</v>
+        <v>3524</v>
       </c>
       <c r="J98" s="14" t="s">
-        <v>4036</v>
+        <v>4034</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -18220,10 +18176,10 @@
         <v>2970</v>
       </c>
       <c r="I99" s="14" t="s">
-        <v>3527</v>
+        <v>3525</v>
       </c>
       <c r="J99" s="14" t="s">
-        <v>4034</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -18252,10 +18208,10 @@
         <v>2971</v>
       </c>
       <c r="I100" s="14" t="s">
-        <v>3528</v>
+        <v>3526</v>
       </c>
       <c r="J100" s="14" t="s">
-        <v>4033</v>
+        <v>4031</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -18284,10 +18240,10 @@
         <v>2972</v>
       </c>
       <c r="I101" s="14" t="s">
-        <v>3529</v>
+        <v>3527</v>
       </c>
       <c r="J101" s="14" t="s">
-        <v>4031</v>
+        <v>4029</v>
       </c>
     </row>
     <row r="102" spans="1:10">
@@ -18316,10 +18272,10 @@
         <v>2973</v>
       </c>
       <c r="I102" s="14" t="s">
-        <v>3530</v>
+        <v>3528</v>
       </c>
       <c r="J102" s="14" t="s">
-        <v>4032</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -18348,10 +18304,10 @@
         <v>2974</v>
       </c>
       <c r="I103" s="14" t="s">
-        <v>3531</v>
+        <v>3529</v>
       </c>
       <c r="J103" s="14" t="s">
-        <v>4045</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="104" spans="1:10">
@@ -18380,10 +18336,10 @@
         <v>2975</v>
       </c>
       <c r="I104" s="14" t="s">
-        <v>3532</v>
+        <v>3530</v>
       </c>
       <c r="J104" s="14" t="s">
-        <v>4046</v>
+        <v>4044</v>
       </c>
     </row>
     <row r="105" spans="1:10">
@@ -18412,10 +18368,10 @@
         <v>2976</v>
       </c>
       <c r="I105" s="14" t="s">
-        <v>3533</v>
+        <v>3531</v>
       </c>
       <c r="J105" s="14" t="s">
-        <v>4047</v>
+        <v>4045</v>
       </c>
     </row>
     <row r="106" spans="1:10">
@@ -18444,10 +18400,10 @@
         <v>2977</v>
       </c>
       <c r="I106" s="14" t="s">
-        <v>3534</v>
+        <v>3532</v>
       </c>
       <c r="J106" s="14" t="s">
-        <v>4048</v>
+        <v>4046</v>
       </c>
     </row>
     <row r="107" spans="1:10">
@@ -18476,10 +18432,10 @@
         <v>2978</v>
       </c>
       <c r="I107" s="14" t="s">
-        <v>3535</v>
+        <v>3533</v>
       </c>
       <c r="J107" s="14" t="s">
-        <v>4049</v>
+        <v>4047</v>
       </c>
     </row>
     <row r="108" spans="1:10">
@@ -18508,10 +18464,10 @@
         <v>2979</v>
       </c>
       <c r="I108" s="14" t="s">
-        <v>3536</v>
+        <v>3534</v>
       </c>
       <c r="J108" s="14" t="s">
-        <v>3536</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="109" spans="1:10">
@@ -18540,10 +18496,10 @@
         <v>2980</v>
       </c>
       <c r="I109" s="14" t="s">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="J109" s="14" t="s">
-        <v>4117</v>
+        <v>4115</v>
       </c>
     </row>
     <row r="110" spans="1:10">
@@ -18572,10 +18528,10 @@
         <v>2981</v>
       </c>
       <c r="I110" s="14" t="s">
-        <v>3538</v>
+        <v>3536</v>
       </c>
       <c r="J110" s="14" t="s">
-        <v>4118</v>
+        <v>4116</v>
       </c>
     </row>
     <row r="111" spans="1:10">
@@ -18604,10 +18560,10 @@
         <v>2982</v>
       </c>
       <c r="I111" s="14" t="s">
-        <v>3539</v>
+        <v>3537</v>
       </c>
       <c r="J111" s="14" t="s">
-        <v>4119</v>
+        <v>4117</v>
       </c>
     </row>
     <row r="112" spans="1:10">
@@ -18636,10 +18592,10 @@
         <v>2983</v>
       </c>
       <c r="I112" s="14" t="s">
-        <v>3540</v>
+        <v>3538</v>
       </c>
       <c r="J112" s="14" t="s">
-        <v>4120</v>
+        <v>4118</v>
       </c>
     </row>
     <row r="113" spans="1:10">
@@ -18668,10 +18624,10 @@
         <v>2984</v>
       </c>
       <c r="I113" s="14" t="s">
-        <v>3541</v>
+        <v>3539</v>
       </c>
       <c r="J113" s="14" t="s">
-        <v>4121</v>
+        <v>4119</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -18700,10 +18656,10 @@
         <v>2985</v>
       </c>
       <c r="I114" s="14" t="s">
-        <v>3432</v>
+        <v>3430</v>
       </c>
       <c r="J114" s="14" t="s">
-        <v>3432</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="115" spans="1:10">
@@ -18732,10 +18688,10 @@
         <v>2986</v>
       </c>
       <c r="I115" s="14" t="s">
-        <v>3542</v>
+        <v>3540</v>
       </c>
       <c r="J115" s="14" t="s">
-        <v>4169</v>
+        <v>4167</v>
       </c>
     </row>
     <row r="116" spans="1:10">
@@ -18764,10 +18720,10 @@
         <v>2987</v>
       </c>
       <c r="I116" s="14" t="s">
-        <v>3543</v>
+        <v>3541</v>
       </c>
       <c r="J116" s="14" t="s">
-        <v>4170</v>
+        <v>4168</v>
       </c>
     </row>
     <row r="117" spans="1:10">
@@ -18796,10 +18752,10 @@
         <v>2988</v>
       </c>
       <c r="I117" s="14" t="s">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="J117" s="14" t="s">
-        <v>4171</v>
+        <v>4169</v>
       </c>
     </row>
     <row r="118" spans="1:10">
@@ -18828,10 +18784,10 @@
         <v>2989</v>
       </c>
       <c r="I118" s="14" t="s">
-        <v>3545</v>
+        <v>3543</v>
       </c>
       <c r="J118" s="14" t="s">
-        <v>4172</v>
+        <v>4170</v>
       </c>
     </row>
     <row r="119" spans="1:10">
@@ -18860,10 +18816,10 @@
         <v>2990</v>
       </c>
       <c r="I119" s="14" t="s">
-        <v>3546</v>
+        <v>3544</v>
       </c>
       <c r="J119" s="14" t="s">
-        <v>4173</v>
+        <v>4171</v>
       </c>
     </row>
     <row r="120" spans="1:10">
@@ -18892,10 +18848,10 @@
         <v>2991</v>
       </c>
       <c r="I120" s="14" t="s">
-        <v>3547</v>
+        <v>3545</v>
       </c>
       <c r="J120" s="14" t="s">
-        <v>4174</v>
+        <v>4172</v>
       </c>
     </row>
     <row r="121" spans="1:10">
@@ -18924,10 +18880,10 @@
         <v>2992</v>
       </c>
       <c r="I121" s="14" t="s">
-        <v>3548</v>
+        <v>3546</v>
       </c>
       <c r="J121" s="14" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
     </row>
     <row r="122" spans="1:10">
@@ -18956,10 +18912,10 @@
         <v>2993</v>
       </c>
       <c r="I122" s="14" t="s">
-        <v>3549</v>
+        <v>3547</v>
       </c>
       <c r="J122" s="14" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
     </row>
     <row r="123" spans="1:10">
@@ -18988,10 +18944,10 @@
         <v>3004</v>
       </c>
       <c r="I123" s="14" t="s">
-        <v>3550</v>
+        <v>3548</v>
       </c>
       <c r="J123" s="14" t="s">
-        <v>4177</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -19020,10 +18976,10 @@
         <v>3005</v>
       </c>
       <c r="I124" s="14" t="s">
-        <v>3551</v>
+        <v>3549</v>
       </c>
       <c r="J124" s="14" t="s">
-        <v>4178</v>
+        <v>4176</v>
       </c>
     </row>
     <row r="125" spans="1:10">
@@ -19052,10 +19008,10 @@
         <v>3006</v>
       </c>
       <c r="I125" s="14" t="s">
-        <v>3552</v>
+        <v>3550</v>
       </c>
       <c r="J125" s="14" t="s">
-        <v>4178</v>
+        <v>4176</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -19084,10 +19040,10 @@
         <v>3007</v>
       </c>
       <c r="I126" s="14" t="s">
-        <v>3553</v>
+        <v>3551</v>
       </c>
       <c r="J126" s="14" t="s">
-        <v>3880</v>
+        <v>3878</v>
       </c>
     </row>
     <row r="127" spans="1:10">
@@ -19116,10 +19072,10 @@
         <v>3000</v>
       </c>
       <c r="I127" s="14" t="s">
-        <v>3554</v>
+        <v>3552</v>
       </c>
       <c r="J127" s="14" t="s">
-        <v>4179</v>
+        <v>4177</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -19148,10 +19104,10 @@
         <v>3001</v>
       </c>
       <c r="I128" s="14" t="s">
-        <v>3555</v>
+        <v>3553</v>
       </c>
       <c r="J128" s="14" t="s">
-        <v>4180</v>
+        <v>4178</v>
       </c>
     </row>
     <row r="129" spans="1:10">
@@ -19180,10 +19136,10 @@
         <v>3002</v>
       </c>
       <c r="I129" s="14" t="s">
-        <v>3556</v>
+        <v>3554</v>
       </c>
       <c r="J129" s="14" t="s">
-        <v>4181</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -19212,10 +19168,10 @@
         <v>3003</v>
       </c>
       <c r="I130" s="14" t="s">
-        <v>3557</v>
+        <v>3555</v>
       </c>
       <c r="J130" s="14" t="s">
-        <v>4182</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="131" spans="1:10">
@@ -19244,10 +19200,10 @@
         <v>785</v>
       </c>
       <c r="I131" s="14" t="s">
-        <v>3558</v>
+        <v>3556</v>
       </c>
       <c r="J131" s="14" t="s">
-        <v>4199</v>
+        <v>4197</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -19276,10 +19232,10 @@
         <v>2994</v>
       </c>
       <c r="I132" s="14" t="s">
-        <v>3559</v>
+        <v>3557</v>
       </c>
       <c r="J132" s="14" t="s">
-        <v>4200</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="133" spans="1:10">
@@ -19308,10 +19264,10 @@
         <v>2995</v>
       </c>
       <c r="I133" s="14" t="s">
-        <v>3560</v>
+        <v>3558</v>
       </c>
       <c r="J133" s="14" t="s">
-        <v>4201</v>
+        <v>4199</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -19340,10 +19296,10 @@
         <v>2996</v>
       </c>
       <c r="I134" s="14" t="s">
-        <v>3561</v>
+        <v>3559</v>
       </c>
       <c r="J134" s="14" t="s">
-        <v>4202</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -19372,10 +19328,10 @@
         <v>2997</v>
       </c>
       <c r="I135" s="14" t="s">
-        <v>3562</v>
+        <v>3560</v>
       </c>
       <c r="J135" s="14" t="s">
-        <v>4203</v>
+        <v>4201</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -19404,10 +19360,10 @@
         <v>2998</v>
       </c>
       <c r="I136" s="14" t="s">
-        <v>3563</v>
+        <v>3561</v>
       </c>
       <c r="J136" s="14" t="s">
-        <v>4187</v>
+        <v>4185</v>
       </c>
     </row>
     <row r="137" spans="1:10">
@@ -19436,10 +19392,10 @@
         <v>2999</v>
       </c>
       <c r="I137" s="14" t="s">
-        <v>3564</v>
+        <v>3562</v>
       </c>
       <c r="J137" s="14" t="s">
-        <v>4188</v>
+        <v>4186</v>
       </c>
     </row>
     <row r="138" spans="1:10">
@@ -19468,10 +19424,10 @@
         <v>3010</v>
       </c>
       <c r="I138" s="14" t="s">
-        <v>3565</v>
+        <v>3563</v>
       </c>
       <c r="J138" s="14" t="s">
-        <v>4189</v>
+        <v>4187</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -19500,10 +19456,10 @@
         <v>3009</v>
       </c>
       <c r="I139" s="14" t="s">
-        <v>3566</v>
+        <v>3564</v>
       </c>
       <c r="J139" s="14" t="s">
-        <v>4190</v>
+        <v>4188</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -19532,10 +19488,10 @@
         <v>3008</v>
       </c>
       <c r="I140" s="14" t="s">
-        <v>3567</v>
+        <v>3565</v>
       </c>
       <c r="J140" s="14" t="s">
-        <v>4191</v>
+        <v>4189</v>
       </c>
     </row>
     <row r="141" spans="1:10">
@@ -19564,10 +19520,10 @@
         <v>3014</v>
       </c>
       <c r="I141" s="14" t="s">
-        <v>3568</v>
+        <v>3566</v>
       </c>
       <c r="J141" s="14" t="s">
-        <v>4192</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -19596,10 +19552,10 @@
         <v>3004</v>
       </c>
       <c r="I142" s="14" t="s">
-        <v>3569</v>
+        <v>3567</v>
       </c>
       <c r="J142" s="14" t="s">
-        <v>4193</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="143" spans="1:10">
@@ -19628,10 +19584,10 @@
         <v>3013</v>
       </c>
       <c r="I143" s="14" t="s">
-        <v>3570</v>
+        <v>3568</v>
       </c>
       <c r="J143" s="14" t="s">
-        <v>4194</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="144" spans="1:10">
@@ -19660,10 +19616,10 @@
         <v>3012</v>
       </c>
       <c r="I144" s="14" t="s">
-        <v>3571</v>
+        <v>3569</v>
       </c>
       <c r="J144" s="14" t="s">
-        <v>4195</v>
+        <v>4193</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -19692,10 +19648,10 @@
         <v>3011</v>
       </c>
       <c r="I145" s="14" t="s">
-        <v>3572</v>
+        <v>3570</v>
       </c>
       <c r="J145" s="14" t="s">
-        <v>4196</v>
+        <v>4194</v>
       </c>
     </row>
     <row r="146" spans="1:10">
@@ -19724,10 +19680,10 @@
         <v>3015</v>
       </c>
       <c r="I146" s="14" t="s">
-        <v>3573</v>
+        <v>3571</v>
       </c>
       <c r="J146" s="14" t="s">
-        <v>4197</v>
+        <v>4195</v>
       </c>
     </row>
     <row r="147" spans="1:10">
@@ -19756,10 +19712,10 @@
         <v>3017</v>
       </c>
       <c r="I147" s="14" t="s">
-        <v>3574</v>
+        <v>3572</v>
       </c>
       <c r="J147" s="14" t="s">
-        <v>4198</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="148" spans="1:10">
@@ -19788,10 +19744,10 @@
         <v>3016</v>
       </c>
       <c r="I148" s="14" t="s">
-        <v>3575</v>
+        <v>3573</v>
       </c>
       <c r="J148" s="14" t="s">
-        <v>4183</v>
+        <v>4181</v>
       </c>
     </row>
     <row r="149" spans="1:10">
@@ -19820,10 +19776,10 @@
         <v>3018</v>
       </c>
       <c r="I149" s="14" t="s">
-        <v>3576</v>
+        <v>3574</v>
       </c>
       <c r="J149" s="14" t="s">
-        <v>4184</v>
+        <v>4182</v>
       </c>
     </row>
     <row r="150" spans="1:10">
@@ -19852,10 +19808,10 @@
         <v>3019</v>
       </c>
       <c r="I150" s="14" t="s">
-        <v>3577</v>
+        <v>3575</v>
       </c>
       <c r="J150" s="14" t="s">
-        <v>4185</v>
+        <v>4183</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -19884,10 +19840,10 @@
         <v>3020</v>
       </c>
       <c r="I151" s="14" t="s">
-        <v>3578</v>
+        <v>3576</v>
       </c>
       <c r="J151" s="14" t="s">
-        <v>4186</v>
+        <v>4184</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -19916,10 +19872,10 @@
         <v>3027</v>
       </c>
       <c r="I152" s="14" t="s">
-        <v>3579</v>
+        <v>3577</v>
       </c>
       <c r="J152" s="14" t="s">
-        <v>4122</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -19948,10 +19904,10 @@
         <v>3028</v>
       </c>
       <c r="I153" s="14" t="s">
-        <v>3580</v>
+        <v>3578</v>
       </c>
       <c r="J153" s="14" t="s">
-        <v>4123</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="154" spans="1:10">
@@ -19980,10 +19936,10 @@
         <v>3029</v>
       </c>
       <c r="I154" s="14" t="s">
-        <v>3581</v>
+        <v>3579</v>
       </c>
       <c r="J154" s="14" t="s">
-        <v>4124</v>
+        <v>4122</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -20012,10 +19968,10 @@
         <v>3030</v>
       </c>
       <c r="I155" s="14" t="s">
-        <v>3582</v>
+        <v>3580</v>
       </c>
       <c r="J155" s="14" t="s">
-        <v>4125</v>
+        <v>4123</v>
       </c>
     </row>
     <row r="156" spans="1:10">
@@ -20044,10 +20000,10 @@
         <v>3031</v>
       </c>
       <c r="I156" s="14" t="s">
-        <v>3583</v>
+        <v>3581</v>
       </c>
       <c r="J156" s="14" t="s">
-        <v>4126</v>
+        <v>4124</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -20076,10 +20032,10 @@
         <v>3032</v>
       </c>
       <c r="I157" s="14" t="s">
-        <v>3584</v>
+        <v>3582</v>
       </c>
       <c r="J157" s="14" t="s">
-        <v>4127</v>
+        <v>4125</v>
       </c>
     </row>
     <row r="158" spans="1:10">
@@ -20108,10 +20064,10 @@
         <v>3033</v>
       </c>
       <c r="I158" s="14" t="s">
-        <v>3585</v>
+        <v>3583</v>
       </c>
       <c r="J158" s="14" t="s">
-        <v>4128</v>
+        <v>4126</v>
       </c>
     </row>
     <row r="159" spans="1:10">
@@ -20140,10 +20096,10 @@
         <v>3034</v>
       </c>
       <c r="I159" s="14" t="s">
-        <v>3586</v>
+        <v>3584</v>
       </c>
       <c r="J159" s="14" t="s">
-        <v>4129</v>
+        <v>4127</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -20172,10 +20128,10 @@
         <v>3035</v>
       </c>
       <c r="I160" s="14" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="J160" s="14" t="s">
-        <v>4130</v>
+        <v>4128</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -20204,10 +20160,10 @@
         <v>3036</v>
       </c>
       <c r="I161" s="14" t="s">
-        <v>3588</v>
+        <v>3586</v>
       </c>
       <c r="J161" s="14" t="s">
-        <v>4131</v>
+        <v>4129</v>
       </c>
     </row>
     <row r="162" spans="1:10">
@@ -20236,10 +20192,10 @@
         <v>3037</v>
       </c>
       <c r="I162" s="14" t="s">
-        <v>3589</v>
+        <v>3587</v>
       </c>
       <c r="J162" s="14" t="s">
-        <v>4132</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -20268,10 +20224,10 @@
         <v>3038</v>
       </c>
       <c r="I163" s="14" t="s">
-        <v>3590</v>
+        <v>3588</v>
       </c>
       <c r="J163" s="14" t="s">
-        <v>4133</v>
+        <v>4131</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -20300,10 +20256,10 @@
         <v>3039</v>
       </c>
       <c r="I164" s="14" t="s">
-        <v>3591</v>
+        <v>3589</v>
       </c>
       <c r="J164" s="14" t="s">
-        <v>4099</v>
+        <v>4097</v>
       </c>
     </row>
     <row r="165" spans="1:10">
@@ -20332,10 +20288,10 @@
         <v>3040</v>
       </c>
       <c r="I165" s="14" t="s">
-        <v>3592</v>
+        <v>3590</v>
       </c>
       <c r="J165" s="14" t="s">
-        <v>4134</v>
+        <v>4132</v>
       </c>
     </row>
     <row r="166" spans="1:10">
@@ -20364,10 +20320,10 @@
         <v>3041</v>
       </c>
       <c r="I166" s="14" t="s">
-        <v>3593</v>
+        <v>3591</v>
       </c>
       <c r="J166" s="14" t="s">
-        <v>4135</v>
+        <v>4133</v>
       </c>
     </row>
     <row r="167" spans="1:10">
@@ -20396,10 +20352,10 @@
         <v>3026</v>
       </c>
       <c r="I167" s="14" t="s">
-        <v>3594</v>
+        <v>3592</v>
       </c>
       <c r="J167" s="14" t="s">
-        <v>4136</v>
+        <v>4134</v>
       </c>
     </row>
     <row r="168" spans="1:10">
@@ -20428,10 +20384,10 @@
         <v>3025</v>
       </c>
       <c r="I168" s="14" t="s">
-        <v>3595</v>
+        <v>3593</v>
       </c>
       <c r="J168" s="14" t="s">
-        <v>4137</v>
+        <v>4135</v>
       </c>
     </row>
     <row r="169" spans="1:10">
@@ -20460,10 +20416,10 @@
         <v>3024</v>
       </c>
       <c r="I169" s="14" t="s">
-        <v>3596</v>
+        <v>3594</v>
       </c>
       <c r="J169" s="14" t="s">
-        <v>4050</v>
+        <v>4048</v>
       </c>
     </row>
     <row r="170" spans="1:10">
@@ -20492,10 +20448,10 @@
         <v>3023</v>
       </c>
       <c r="I170" s="14" t="s">
-        <v>3597</v>
+        <v>3595</v>
       </c>
       <c r="J170" s="14" t="s">
-        <v>3471</v>
+        <v>3469</v>
       </c>
     </row>
     <row r="171" spans="1:10">
@@ -20524,10 +20480,10 @@
         <v>1045</v>
       </c>
       <c r="I171" s="14" t="s">
-        <v>3598</v>
+        <v>3596</v>
       </c>
       <c r="J171" s="14" t="s">
-        <v>4051</v>
+        <v>4049</v>
       </c>
     </row>
     <row r="172" spans="1:10">
@@ -20556,10 +20512,10 @@
         <v>1051</v>
       </c>
       <c r="I172" s="14" t="s">
-        <v>3599</v>
+        <v>3597</v>
       </c>
       <c r="J172" s="14" t="s">
-        <v>4052</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="173" spans="1:10">
@@ -20588,10 +20544,10 @@
         <v>1057</v>
       </c>
       <c r="I173" s="14" t="s">
-        <v>3600</v>
+        <v>3598</v>
       </c>
       <c r="J173" s="14" t="s">
-        <v>4053</v>
+        <v>4051</v>
       </c>
     </row>
     <row r="174" spans="1:10">
@@ -20620,10 +20576,10 @@
         <v>3022</v>
       </c>
       <c r="I174" s="14" t="s">
-        <v>3601</v>
+        <v>3599</v>
       </c>
       <c r="J174" s="14" t="s">
-        <v>4054</v>
+        <v>4052</v>
       </c>
     </row>
     <row r="175" spans="1:10">
@@ -20652,10 +20608,10 @@
         <v>3021</v>
       </c>
       <c r="I175" s="14" t="s">
-        <v>3602</v>
+        <v>3600</v>
       </c>
       <c r="J175" s="14" t="s">
-        <v>4138</v>
+        <v>4136</v>
       </c>
     </row>
     <row r="176" spans="1:10">
@@ -20684,10 +20640,10 @@
         <v>3042</v>
       </c>
       <c r="I176" s="14" t="s">
-        <v>3603</v>
+        <v>3601</v>
       </c>
       <c r="J176" s="14" t="s">
-        <v>4139</v>
+        <v>4137</v>
       </c>
     </row>
     <row r="177" spans="1:10">
@@ -20716,10 +20672,10 @@
         <v>3043</v>
       </c>
       <c r="I177" s="14" t="s">
-        <v>3604</v>
+        <v>3602</v>
       </c>
       <c r="J177" s="14" t="s">
-        <v>4140</v>
+        <v>4138</v>
       </c>
     </row>
     <row r="178" spans="1:10">
@@ -20748,10 +20704,10 @@
         <v>3035</v>
       </c>
       <c r="I178" s="14" t="s">
-        <v>3587</v>
+        <v>3585</v>
       </c>
       <c r="J178" s="14" t="s">
-        <v>4130</v>
+        <v>4128</v>
       </c>
     </row>
     <row r="179" spans="1:10">
@@ -20780,10 +20736,10 @@
         <v>3044</v>
       </c>
       <c r="I179" s="14" t="s">
-        <v>3636</v>
+        <v>3634</v>
       </c>
       <c r="J179" s="14" t="s">
-        <v>4141</v>
+        <v>4139</v>
       </c>
     </row>
     <row r="180" spans="1:10">
@@ -20812,10 +20768,10 @@
         <v>3045</v>
       </c>
       <c r="I180" s="14" t="s">
-        <v>3637</v>
+        <v>3635</v>
       </c>
       <c r="J180" s="14" t="s">
-        <v>4142</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="181" spans="1:10">
@@ -20844,10 +20800,10 @@
         <v>3046</v>
       </c>
       <c r="I181" s="14" t="s">
-        <v>3638</v>
+        <v>3636</v>
       </c>
       <c r="J181" s="14" t="s">
-        <v>4143</v>
+        <v>4141</v>
       </c>
     </row>
     <row r="182" spans="1:10">
@@ -20876,10 +20832,10 @@
         <v>3047</v>
       </c>
       <c r="I182" s="14" t="s">
-        <v>3639</v>
+        <v>3637</v>
       </c>
       <c r="J182" s="14" t="s">
-        <v>4144</v>
+        <v>4142</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -20908,10 +20864,10 @@
         <v>3048</v>
       </c>
       <c r="I183" s="14" t="s">
-        <v>3640</v>
+        <v>3638</v>
       </c>
       <c r="J183" s="14" t="s">
-        <v>4145</v>
+        <v>4143</v>
       </c>
     </row>
     <row r="184" spans="1:10">
@@ -20940,10 +20896,10 @@
         <v>3049</v>
       </c>
       <c r="I184" s="14" t="s">
-        <v>3642</v>
+        <v>3640</v>
       </c>
       <c r="J184" s="14" t="s">
-        <v>4055</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="185" spans="1:10">
@@ -20972,10 +20928,10 @@
         <v>3050</v>
       </c>
       <c r="I185" s="14" t="s">
-        <v>3643</v>
+        <v>3641</v>
       </c>
       <c r="J185" s="14" t="s">
-        <v>4056</v>
+        <v>4054</v>
       </c>
     </row>
     <row r="186" spans="1:10">
@@ -21004,10 +20960,10 @@
         <v>3051</v>
       </c>
       <c r="I186" s="14" t="s">
-        <v>3641</v>
+        <v>3639</v>
       </c>
       <c r="J186" s="14" t="s">
-        <v>4057</v>
+        <v>4055</v>
       </c>
     </row>
     <row r="187" spans="1:10">
@@ -21036,10 +20992,10 @@
         <v>3052</v>
       </c>
       <c r="I187" s="14" t="s">
-        <v>3688</v>
+        <v>3686</v>
       </c>
       <c r="J187" s="14" t="s">
-        <v>4059</v>
+        <v>4057</v>
       </c>
     </row>
     <row r="188" spans="1:10">
@@ -21068,10 +21024,10 @@
         <v>3069</v>
       </c>
       <c r="I188" s="14" t="s">
-        <v>3689</v>
+        <v>3687</v>
       </c>
       <c r="J188" s="14" t="s">
-        <v>4058</v>
+        <v>4056</v>
       </c>
     </row>
     <row r="189" spans="1:10">
@@ -21100,10 +21056,10 @@
         <v>3068</v>
       </c>
       <c r="I189" s="14" t="s">
-        <v>3690</v>
+        <v>3688</v>
       </c>
       <c r="J189" s="14" t="s">
-        <v>4060</v>
+        <v>4058</v>
       </c>
     </row>
     <row r="190" spans="1:10">
@@ -21132,10 +21088,10 @@
         <v>3070</v>
       </c>
       <c r="I190" s="14" t="s">
-        <v>3691</v>
+        <v>3689</v>
       </c>
       <c r="J190" s="14" t="s">
-        <v>4061</v>
+        <v>4059</v>
       </c>
     </row>
     <row r="191" spans="1:10">
@@ -21164,10 +21120,10 @@
         <v>2906</v>
       </c>
       <c r="I191" s="14" t="s">
-        <v>3692</v>
+        <v>3690</v>
       </c>
       <c r="J191" s="14" t="s">
-        <v>4062</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="192" spans="1:10">
@@ -21196,10 +21152,10 @@
         <v>3071</v>
       </c>
       <c r="I192" s="14" t="s">
-        <v>3693</v>
+        <v>3691</v>
       </c>
       <c r="J192" s="14" t="s">
-        <v>4063</v>
+        <v>4061</v>
       </c>
     </row>
     <row r="193" spans="1:10">
@@ -21228,10 +21184,10 @@
         <v>3072</v>
       </c>
       <c r="I193" s="14" t="s">
-        <v>3694</v>
+        <v>3692</v>
       </c>
       <c r="J193" s="14" t="s">
-        <v>4064</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="194" spans="1:10">
@@ -21260,10 +21216,10 @@
         <v>3073</v>
       </c>
       <c r="I194" s="14" t="s">
-        <v>3695</v>
+        <v>3693</v>
       </c>
       <c r="J194" s="14" t="s">
-        <v>4065</v>
+        <v>4063</v>
       </c>
     </row>
     <row r="195" spans="1:10">
@@ -21292,10 +21248,10 @@
         <v>3074</v>
       </c>
       <c r="I195" s="14" t="s">
-        <v>3696</v>
+        <v>3694</v>
       </c>
       <c r="J195" s="14" t="s">
-        <v>4066</v>
+        <v>4064</v>
       </c>
     </row>
     <row r="196" spans="1:10">
@@ -21324,10 +21280,10 @@
         <v>3053</v>
       </c>
       <c r="I196" s="14" t="s">
-        <v>3697</v>
+        <v>3695</v>
       </c>
       <c r="J196" s="14" t="s">
-        <v>4067</v>
+        <v>4065</v>
       </c>
     </row>
     <row r="197" spans="1:10">
@@ -21356,10 +21312,10 @@
         <v>3054</v>
       </c>
       <c r="I197" s="14" t="s">
-        <v>3698</v>
+        <v>3696</v>
       </c>
       <c r="J197" s="14" t="s">
-        <v>4068</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="198" spans="1:10">
@@ -21388,10 +21344,10 @@
         <v>1206</v>
       </c>
       <c r="I198" s="14" t="s">
-        <v>3699</v>
+        <v>3697</v>
       </c>
       <c r="J198" s="14" t="s">
-        <v>4069</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="199" spans="1:10">
@@ -21420,10 +21376,10 @@
         <v>3055</v>
       </c>
       <c r="I199" s="14" t="s">
-        <v>3700</v>
+        <v>3698</v>
       </c>
       <c r="J199" s="14" t="s">
-        <v>4070</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="200" spans="1:10">
@@ -21452,10 +21408,10 @@
         <v>3056</v>
       </c>
       <c r="I200" s="14" t="s">
-        <v>3701</v>
+        <v>3699</v>
       </c>
       <c r="J200" s="14" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="201" spans="1:10">
@@ -21484,10 +21440,10 @@
         <v>3057</v>
       </c>
       <c r="I201" s="14" t="s">
-        <v>3702</v>
+        <v>3700</v>
       </c>
       <c r="J201" s="14" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="202" spans="1:10">
@@ -21516,10 +21472,10 @@
         <v>3058</v>
       </c>
       <c r="I202" s="14" t="s">
-        <v>3609</v>
+        <v>3607</v>
       </c>
       <c r="J202" s="14" t="s">
-        <v>3935</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="203" spans="1:10">
@@ -21548,10 +21504,10 @@
         <v>3059</v>
       </c>
       <c r="I203" s="14" t="s">
-        <v>3703</v>
+        <v>3701</v>
       </c>
       <c r="J203" s="14" t="s">
-        <v>4073</v>
+        <v>4071</v>
       </c>
     </row>
     <row r="204" spans="1:10">
@@ -21580,10 +21536,10 @@
         <v>3060</v>
       </c>
       <c r="I204" s="14" t="s">
-        <v>3704</v>
+        <v>3702</v>
       </c>
       <c r="J204" s="14" t="s">
-        <v>4074</v>
+        <v>4072</v>
       </c>
     </row>
     <row r="205" spans="1:10">
@@ -21612,10 +21568,10 @@
         <v>3061</v>
       </c>
       <c r="I205" s="14" t="s">
-        <v>3705</v>
+        <v>3703</v>
       </c>
       <c r="J205" s="14" t="s">
-        <v>4075</v>
+        <v>4073</v>
       </c>
     </row>
     <row r="206" spans="1:10">
@@ -21644,10 +21600,10 @@
         <v>1256</v>
       </c>
       <c r="I206" s="14" t="s">
-        <v>3706</v>
+        <v>3704</v>
       </c>
       <c r="J206" s="14" t="s">
-        <v>3706</v>
+        <v>3704</v>
       </c>
     </row>
     <row r="207" spans="1:10">
@@ -21676,10 +21632,10 @@
         <v>3067</v>
       </c>
       <c r="I207" s="14" t="s">
-        <v>3707</v>
+        <v>3705</v>
       </c>
       <c r="J207" s="14" t="s">
-        <v>4076</v>
+        <v>4074</v>
       </c>
     </row>
     <row r="208" spans="1:10">
@@ -21708,10 +21664,10 @@
         <v>2911</v>
       </c>
       <c r="I208" s="14" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
       <c r="J208" s="14" t="s">
-        <v>3460</v>
+        <v>3458</v>
       </c>
     </row>
     <row r="209" spans="1:10">
@@ -21740,10 +21696,10 @@
         <v>175</v>
       </c>
       <c r="I209" s="14" t="s">
-        <v>3708</v>
+        <v>3706</v>
       </c>
       <c r="J209" s="14" t="s">
-        <v>3459</v>
+        <v>3457</v>
       </c>
     </row>
     <row r="210" spans="1:10">
@@ -21772,10 +21728,10 @@
         <v>190</v>
       </c>
       <c r="I210" s="14" t="s">
-        <v>3709</v>
+        <v>3707</v>
       </c>
       <c r="J210" s="14" t="s">
-        <v>3884</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="211" spans="1:10">
@@ -21804,10 +21760,10 @@
         <v>3066</v>
       </c>
       <c r="I211" s="14" t="s">
-        <v>3711</v>
+        <v>3709</v>
       </c>
       <c r="J211" s="14" t="s">
-        <v>4077</v>
+        <v>4075</v>
       </c>
     </row>
     <row r="212" spans="1:10">
@@ -21836,10 +21792,10 @@
         <v>3065</v>
       </c>
       <c r="I212" s="14" t="s">
-        <v>3712</v>
+        <v>3710</v>
       </c>
       <c r="J212" s="14" t="s">
-        <v>4078</v>
+        <v>4076</v>
       </c>
     </row>
     <row r="213" spans="1:10">
@@ -21868,10 +21824,10 @@
         <v>3064</v>
       </c>
       <c r="I213" s="14" t="s">
-        <v>3713</v>
+        <v>3711</v>
       </c>
       <c r="J213" s="14" t="s">
-        <v>4079</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="214" spans="1:10">
@@ -21900,10 +21856,10 @@
         <v>3063</v>
       </c>
       <c r="I214" s="14" t="s">
-        <v>3710</v>
+        <v>3708</v>
       </c>
       <c r="J214" s="14" t="s">
-        <v>4148</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="215" spans="1:10">
@@ -21932,10 +21888,10 @@
         <v>3062</v>
       </c>
       <c r="I215" s="14" t="s">
-        <v>3714</v>
+        <v>3712</v>
       </c>
       <c r="J215" s="14" t="s">
-        <v>4149</v>
+        <v>4147</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -21964,10 +21920,10 @@
         <v>3217</v>
       </c>
       <c r="I216" s="14" t="s">
-        <v>3715</v>
+        <v>3713</v>
       </c>
       <c r="J216" s="14" t="s">
-        <v>4150</v>
+        <v>4148</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -21996,10 +21952,10 @@
         <v>3218</v>
       </c>
       <c r="I217" s="14" t="s">
-        <v>3716</v>
+        <v>3714</v>
       </c>
       <c r="J217" s="14" t="s">
-        <v>4151</v>
+        <v>4149</v>
       </c>
     </row>
     <row r="218" spans="1:10">
@@ -22028,10 +21984,10 @@
         <v>2912</v>
       </c>
       <c r="I218" s="14" t="s">
-        <v>3461</v>
+        <v>3459</v>
       </c>
       <c r="J218" s="14" t="s">
-        <v>3911</v>
+        <v>3909</v>
       </c>
     </row>
     <row r="219" spans="1:10">
@@ -22060,10 +22016,10 @@
         <v>196</v>
       </c>
       <c r="I219" s="14" t="s">
-        <v>3717</v>
+        <v>3715</v>
       </c>
       <c r="J219" s="14" t="s">
-        <v>4152</v>
+        <v>4150</v>
       </c>
     </row>
     <row r="220" spans="1:10">
@@ -22092,10 +22048,10 @@
         <v>3219</v>
       </c>
       <c r="I220" s="14" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
       <c r="J220" s="14" t="s">
-        <v>4153</v>
+        <v>4151</v>
       </c>
     </row>
     <row r="221" spans="1:10">
@@ -22124,10 +22080,10 @@
         <v>3220</v>
       </c>
       <c r="I221" s="14" t="s">
-        <v>3719</v>
+        <v>3717</v>
       </c>
       <c r="J221" s="14" t="s">
-        <v>3719</v>
+        <v>3717</v>
       </c>
     </row>
     <row r="222" spans="1:10">
@@ -22156,10 +22112,10 @@
         <v>249</v>
       </c>
       <c r="I222" s="14" t="s">
-        <v>3472</v>
+        <v>3470</v>
       </c>
       <c r="J222" s="14" t="s">
-        <v>3892</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="223" spans="1:10">
@@ -22188,10 +22144,10 @@
         <v>255</v>
       </c>
       <c r="I223" s="14" t="s">
-        <v>3473</v>
+        <v>3471</v>
       </c>
       <c r="J223" s="14" t="s">
-        <v>3893</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="224" spans="1:10">
@@ -22220,10 +22176,10 @@
         <v>2920</v>
       </c>
       <c r="I224" s="14" t="s">
-        <v>3474</v>
+        <v>3472</v>
       </c>
       <c r="J224" s="14" t="s">
-        <v>4146</v>
+        <v>4144</v>
       </c>
     </row>
     <row r="225" spans="1:10">
@@ -22252,10 +22208,10 @@
         <v>267</v>
       </c>
       <c r="I225" s="14" t="s">
-        <v>3475</v>
+        <v>3473</v>
       </c>
       <c r="J225" s="14" t="s">
-        <v>4147</v>
+        <v>4145</v>
       </c>
     </row>
     <row r="226" spans="1:10">
@@ -22284,10 +22240,10 @@
         <v>3231</v>
       </c>
       <c r="I226" s="14" t="s">
-        <v>3720</v>
+        <v>3718</v>
       </c>
       <c r="J226" s="14" t="s">
-        <v>4080</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="227" spans="1:10">
@@ -22316,10 +22272,10 @@
         <v>3232</v>
       </c>
       <c r="I227" s="14" t="s">
-        <v>3721</v>
+        <v>3719</v>
       </c>
       <c r="J227" s="14" t="s">
-        <v>4081</v>
+        <v>4079</v>
       </c>
     </row>
     <row r="228" spans="1:10">
@@ -22348,10 +22304,10 @@
         <v>3233</v>
       </c>
       <c r="I228" s="14" t="s">
-        <v>3722</v>
+        <v>3720</v>
       </c>
       <c r="J228" s="14" t="s">
-        <v>4082</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="229" spans="1:10">
@@ -22380,10 +22336,10 @@
         <v>2913</v>
       </c>
       <c r="I229" s="14" t="s">
-        <v>3723</v>
+        <v>3721</v>
       </c>
       <c r="J229" s="14" t="s">
-        <v>3886</v>
+        <v>3884</v>
       </c>
     </row>
     <row r="230" spans="1:10">
@@ -22412,10 +22368,10 @@
         <v>2914</v>
       </c>
       <c r="I230" s="14" t="s">
-        <v>3724</v>
+        <v>3722</v>
       </c>
       <c r="J230" s="14" t="s">
-        <v>3887</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="231" spans="1:10">
@@ -22444,10 +22400,10 @@
         <v>2916</v>
       </c>
       <c r="I231" s="14" t="s">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="J231" s="14" t="s">
-        <v>3888</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="232" spans="1:10">
@@ -22476,10 +22432,10 @@
         <v>2915</v>
       </c>
       <c r="I232" s="14" t="s">
-        <v>3467</v>
+        <v>3465</v>
       </c>
       <c r="J232" s="14" t="s">
-        <v>3889</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="233" spans="1:10">
@@ -22508,10 +22464,10 @@
         <v>2917</v>
       </c>
       <c r="I233" s="14" t="s">
-        <v>3468</v>
+        <v>3466</v>
       </c>
       <c r="J233" s="14" t="s">
-        <v>3890</v>
+        <v>3888</v>
       </c>
     </row>
     <row r="234" spans="1:10">
@@ -22540,10 +22496,10 @@
         <v>3238</v>
       </c>
       <c r="I234" s="14" t="s">
-        <v>3725</v>
+        <v>3723</v>
       </c>
       <c r="J234" s="14" t="s">
-        <v>4083</v>
+        <v>4081</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -22572,10 +22528,10 @@
         <v>3237</v>
       </c>
       <c r="I235" s="14" t="s">
-        <v>3729</v>
+        <v>3727</v>
       </c>
       <c r="J235" s="14" t="s">
-        <v>4084</v>
+        <v>4082</v>
       </c>
     </row>
     <row r="236" spans="1:10">
@@ -22604,10 +22560,10 @@
         <v>3236</v>
       </c>
       <c r="I236" s="14" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
       <c r="J236" s="14" t="s">
-        <v>4085</v>
+        <v>4083</v>
       </c>
     </row>
     <row r="237" spans="1:10">
@@ -22636,10 +22592,10 @@
         <v>3235</v>
       </c>
       <c r="I237" s="14" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
       <c r="J237" s="14" t="s">
-        <v>4086</v>
+        <v>4084</v>
       </c>
     </row>
     <row r="238" spans="1:10">
@@ -22668,10 +22624,10 @@
         <v>3234</v>
       </c>
       <c r="I238" s="14" t="s">
-        <v>3726</v>
+        <v>3724</v>
       </c>
       <c r="J238" s="14" t="s">
-        <v>4087</v>
+        <v>4085</v>
       </c>
     </row>
     <row r="239" spans="1:10">
@@ -22700,10 +22656,10 @@
         <v>3273</v>
       </c>
       <c r="I239" s="14" t="s">
-        <v>3730</v>
+        <v>3728</v>
       </c>
       <c r="J239" s="14" t="s">
-        <v>4160</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="240" spans="1:10">
@@ -22732,10 +22688,10 @@
         <v>3274</v>
       </c>
       <c r="I240" s="14" t="s">
-        <v>3731</v>
+        <v>3729</v>
       </c>
       <c r="J240" s="14" t="s">
-        <v>3936</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="241" spans="1:10">
@@ -22764,10 +22720,10 @@
         <v>3275</v>
       </c>
       <c r="I241" s="14" t="s">
-        <v>3732</v>
+        <v>3730</v>
       </c>
       <c r="J241" s="14" t="s">
-        <v>4161</v>
+        <v>4159</v>
       </c>
     </row>
     <row r="242" spans="1:10">
@@ -22796,10 +22752,10 @@
         <v>3276</v>
       </c>
       <c r="I242" s="14" t="s">
-        <v>3733</v>
+        <v>3731</v>
       </c>
       <c r="J242" s="14" t="s">
-        <v>4162</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="243" spans="1:10">
@@ -22828,10 +22784,10 @@
         <v>3277</v>
       </c>
       <c r="I243" s="14" t="s">
-        <v>3788</v>
+        <v>3786</v>
       </c>
       <c r="J243" s="14" t="s">
-        <v>4164</v>
+        <v>4162</v>
       </c>
     </row>
     <row r="244" spans="1:10">
@@ -22860,10 +22816,10 @@
         <v>3278</v>
       </c>
       <c r="I244" s="14" t="s">
-        <v>3787</v>
+        <v>3785</v>
       </c>
       <c r="J244" s="14" t="s">
-        <v>4163</v>
+        <v>4161</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -22892,10 +22848,10 @@
         <v>3239</v>
       </c>
       <c r="I245" s="14" t="s">
-        <v>3769</v>
+        <v>3767</v>
       </c>
       <c r="J245" s="14" t="s">
-        <v>4165</v>
+        <v>4163</v>
       </c>
     </row>
     <row r="246" spans="1:10">
@@ -22924,10 +22880,10 @@
         <v>3240</v>
       </c>
       <c r="I246" s="14" t="s">
-        <v>3770</v>
+        <v>3768</v>
       </c>
       <c r="J246" s="14" t="s">
-        <v>4166</v>
+        <v>4164</v>
       </c>
     </row>
     <row r="247" spans="1:10">
@@ -22956,10 +22912,10 @@
         <v>3241</v>
       </c>
       <c r="I247" s="14" t="s">
-        <v>3771</v>
+        <v>3769</v>
       </c>
       <c r="J247" s="14" t="s">
-        <v>4167</v>
+        <v>4165</v>
       </c>
     </row>
     <row r="248" spans="1:10">
@@ -22988,10 +22944,10 @@
         <v>3242</v>
       </c>
       <c r="I248" s="14" t="s">
-        <v>3772</v>
+        <v>3770</v>
       </c>
       <c r="J248" s="14" t="s">
-        <v>4168</v>
+        <v>4166</v>
       </c>
     </row>
     <row r="249" spans="1:10">
@@ -23020,10 +22976,10 @@
         <v>3243</v>
       </c>
       <c r="I249" s="14" t="s">
-        <v>3773</v>
+        <v>3771</v>
       </c>
       <c r="J249" s="14" t="s">
-        <v>4211</v>
+        <v>4209</v>
       </c>
     </row>
     <row r="250" spans="1:10">
@@ -23052,10 +23008,10 @@
         <v>3244</v>
       </c>
       <c r="I250" s="14" t="s">
-        <v>3774</v>
+        <v>3772</v>
       </c>
       <c r="J250" s="14" t="s">
-        <v>4210</v>
+        <v>4208</v>
       </c>
     </row>
     <row r="251" spans="1:10">
@@ -23084,10 +23040,10 @@
         <v>3221</v>
       </c>
       <c r="I251" s="14" t="s">
-        <v>3775</v>
+        <v>3773</v>
       </c>
       <c r="J251" s="14" t="s">
-        <v>4209</v>
+        <v>4207</v>
       </c>
     </row>
     <row r="252" spans="1:10">
@@ -23116,10 +23072,10 @@
         <v>3222</v>
       </c>
       <c r="I252" s="14" t="s">
-        <v>3776</v>
+        <v>3774</v>
       </c>
       <c r="J252" s="14" t="s">
-        <v>4208</v>
+        <v>4206</v>
       </c>
     </row>
     <row r="253" spans="1:10">
@@ -23148,10 +23104,10 @@
         <v>3223</v>
       </c>
       <c r="I253" s="14" t="s">
-        <v>3643</v>
+        <v>3641</v>
       </c>
       <c r="J253" s="14" t="s">
-        <v>4204</v>
+        <v>4202</v>
       </c>
     </row>
     <row r="254" spans="1:10">
@@ -23180,10 +23136,10 @@
         <v>3224</v>
       </c>
       <c r="I254" s="14" t="s">
-        <v>3777</v>
+        <v>3775</v>
       </c>
       <c r="J254" s="14" t="s">
-        <v>4205</v>
+        <v>4203</v>
       </c>
     </row>
     <row r="255" spans="1:10">
@@ -23212,10 +23168,10 @@
         <v>3225</v>
       </c>
       <c r="I255" s="14" t="s">
-        <v>3778</v>
+        <v>3776</v>
       </c>
       <c r="J255" s="14" t="s">
-        <v>4206</v>
+        <v>4204</v>
       </c>
     </row>
     <row r="256" spans="1:10">
@@ -23244,10 +23200,10 @@
         <v>3226</v>
       </c>
       <c r="I256" s="14" t="s">
-        <v>3779</v>
+        <v>3777</v>
       </c>
       <c r="J256" s="14" t="s">
-        <v>4207</v>
+        <v>4205</v>
       </c>
     </row>
     <row r="257" spans="1:10">
@@ -23276,10 +23232,10 @@
         <v>3227</v>
       </c>
       <c r="I257" s="14" t="s">
-        <v>3780</v>
+        <v>3778</v>
       </c>
       <c r="J257" s="14" t="s">
-        <v>4216</v>
+        <v>4214</v>
       </c>
     </row>
     <row r="258" spans="1:10">
@@ -23308,10 +23264,10 @@
         <v>3228</v>
       </c>
       <c r="I258" s="14" t="s">
-        <v>3781</v>
+        <v>3779</v>
       </c>
       <c r="J258" s="14" t="s">
-        <v>4217</v>
+        <v>4215</v>
       </c>
     </row>
     <row r="259" spans="1:10">
@@ -23340,10 +23296,10 @@
         <v>3229</v>
       </c>
       <c r="I259" s="14" t="s">
-        <v>3782</v>
+        <v>3780</v>
       </c>
       <c r="J259" s="14" t="s">
-        <v>4218</v>
+        <v>4216</v>
       </c>
     </row>
     <row r="260" spans="1:10">
@@ -23372,10 +23328,10 @@
         <v>3229</v>
       </c>
       <c r="I260" s="14" t="s">
-        <v>3782</v>
+        <v>3780</v>
       </c>
       <c r="J260" s="14" t="s">
-        <v>4218</v>
+        <v>4216</v>
       </c>
     </row>
     <row r="261" spans="1:10">
@@ -23404,10 +23360,10 @@
         <v>3230</v>
       </c>
       <c r="I261" s="14" t="s">
-        <v>3783</v>
+        <v>3781</v>
       </c>
       <c r="J261" s="14" t="s">
-        <v>4219</v>
+        <v>4217</v>
       </c>
     </row>
     <row r="262" spans="1:10">
@@ -23439,7 +23395,7 @@
         <v>1534</v>
       </c>
       <c r="J262" s="14" t="s">
-        <v>4212</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="263" spans="1:10">
@@ -23468,10 +23424,10 @@
         <v>1536</v>
       </c>
       <c r="I263" s="14" t="s">
-        <v>3784</v>
+        <v>3782</v>
       </c>
       <c r="J263" s="14" t="s">
-        <v>4213</v>
+        <v>4211</v>
       </c>
     </row>
     <row r="264" spans="1:10">
@@ -23500,10 +23456,10 @@
         <v>1541</v>
       </c>
       <c r="I264" s="14" t="s">
-        <v>3785</v>
+        <v>3783</v>
       </c>
       <c r="J264" s="14" t="s">
-        <v>4214</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="265" spans="1:10">
@@ -23532,10 +23488,10 @@
         <v>3134</v>
       </c>
       <c r="I265" s="14" t="s">
-        <v>3786</v>
+        <v>3784</v>
       </c>
       <c r="J265" s="14" t="s">
-        <v>4215</v>
+        <v>4213</v>
       </c>
     </row>
     <row r="266" spans="1:10">
@@ -23564,10 +23520,10 @@
         <v>3135</v>
       </c>
       <c r="I266" s="14" t="s">
-        <v>3791</v>
+        <v>3789</v>
       </c>
       <c r="J266" s="14" t="s">
-        <v>4088</v>
+        <v>4086</v>
       </c>
     </row>
     <row r="267" spans="1:10">
@@ -23596,10 +23552,10 @@
         <v>3136</v>
       </c>
       <c r="I267" s="14" t="s">
-        <v>3789</v>
+        <v>3787</v>
       </c>
       <c r="J267" s="14" t="s">
-        <v>4089</v>
+        <v>4087</v>
       </c>
     </row>
     <row r="268" spans="1:10">
@@ -23628,10 +23584,10 @@
         <v>3137</v>
       </c>
       <c r="I268" s="14" t="s">
-        <v>3790</v>
+        <v>3788</v>
       </c>
       <c r="J268" s="14" t="s">
-        <v>4090</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="269" spans="1:10">
@@ -23660,10 +23616,10 @@
         <v>3138</v>
       </c>
       <c r="I269" s="14" t="s">
-        <v>3792</v>
+        <v>3790</v>
       </c>
       <c r="J269" s="14" t="s">
-        <v>4091</v>
+        <v>4089</v>
       </c>
     </row>
     <row r="270" spans="1:10">
@@ -23692,10 +23648,10 @@
         <v>3139</v>
       </c>
       <c r="I270" s="14" t="s">
-        <v>3793</v>
+        <v>3791</v>
       </c>
       <c r="J270" s="14" t="s">
-        <v>4092</v>
+        <v>4090</v>
       </c>
     </row>
     <row r="271" spans="1:10">
@@ -23724,10 +23680,10 @@
         <v>3140</v>
       </c>
       <c r="I271" s="14" t="s">
-        <v>3794</v>
+        <v>3792</v>
       </c>
       <c r="J271" s="14" t="s">
-        <v>4093</v>
+        <v>4091</v>
       </c>
     </row>
     <row r="272" spans="1:10">
@@ -23756,10 +23712,10 @@
         <v>3141</v>
       </c>
       <c r="I272" s="14" t="s">
-        <v>3870</v>
+        <v>3868</v>
       </c>
       <c r="J272" s="14" t="s">
-        <v>4094</v>
+        <v>4092</v>
       </c>
     </row>
     <row r="273" spans="1:10">
@@ -23788,10 +23744,10 @@
         <v>3142</v>
       </c>
       <c r="I273" s="14" t="s">
-        <v>3871</v>
+        <v>3869</v>
       </c>
       <c r="J273" s="14" t="s">
-        <v>4095</v>
+        <v>4093</v>
       </c>
     </row>
     <row r="274" spans="1:10">
@@ -23820,10 +23776,10 @@
         <v>3202</v>
       </c>
       <c r="I274" s="14" t="s">
-        <v>3869</v>
+        <v>3867</v>
       </c>
       <c r="J274" s="14" t="s">
-        <v>4096</v>
+        <v>4094</v>
       </c>
     </row>
     <row r="275" spans="1:10">
@@ -23852,10 +23808,10 @@
         <v>3203</v>
       </c>
       <c r="I275" s="14" t="s">
-        <v>3872</v>
+        <v>3870</v>
       </c>
       <c r="J275" s="14" t="s">
-        <v>4097</v>
+        <v>4095</v>
       </c>
     </row>
     <row r="276" spans="1:10">
@@ -23884,10 +23840,10 @@
         <v>3204</v>
       </c>
       <c r="I276" s="14" t="s">
-        <v>3873</v>
+        <v>3871</v>
       </c>
       <c r="J276" s="14" t="s">
-        <v>4098</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="277" spans="1:10">
@@ -23916,10 +23872,10 @@
         <v>3039</v>
       </c>
       <c r="I277" s="14" t="s">
-        <v>3874</v>
+        <v>3872</v>
       </c>
       <c r="J277" s="14" t="s">
-        <v>4099</v>
+        <v>4097</v>
       </c>
     </row>
     <row r="278" spans="1:10">
@@ -23948,10 +23904,10 @@
         <v>3205</v>
       </c>
       <c r="I278" s="14" t="s">
-        <v>3866</v>
+        <v>3864</v>
       </c>
       <c r="J278" s="14" t="s">
-        <v>4100</v>
+        <v>4098</v>
       </c>
     </row>
     <row r="279" spans="1:10">
@@ -23980,10 +23936,10 @@
         <v>3206</v>
       </c>
       <c r="I279" s="14" t="s">
-        <v>3867</v>
+        <v>3865</v>
       </c>
       <c r="J279" s="14" t="s">
-        <v>4101</v>
+        <v>4099</v>
       </c>
     </row>
     <row r="280" spans="1:10">
@@ -24012,10 +23968,10 @@
         <v>3207</v>
       </c>
       <c r="I280" s="14" t="s">
-        <v>3868</v>
+        <v>3866</v>
       </c>
       <c r="J280" s="14" t="s">
-        <v>4102</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="281" spans="1:10">
@@ -24044,10 +24000,10 @@
         <v>1642</v>
       </c>
       <c r="I281" s="14" t="s">
-        <v>3858</v>
+        <v>3856</v>
       </c>
       <c r="J281" s="14" t="s">
-        <v>4103</v>
+        <v>4101</v>
       </c>
     </row>
     <row r="282" spans="1:10">
@@ -24076,10 +24032,10 @@
         <v>3208</v>
       </c>
       <c r="I282" s="14" t="s">
-        <v>3859</v>
+        <v>3857</v>
       </c>
       <c r="J282" s="14" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="283" spans="1:10">
@@ -24108,10 +24064,10 @@
         <v>3209</v>
       </c>
       <c r="I283" s="14" t="s">
-        <v>3860</v>
+        <v>3858</v>
       </c>
       <c r="J283" s="14" t="s">
-        <v>4105</v>
+        <v>4103</v>
       </c>
     </row>
     <row r="284" spans="1:10">
@@ -24140,10 +24096,10 @@
         <v>3210</v>
       </c>
       <c r="I284" s="14" t="s">
-        <v>3861</v>
+        <v>3859</v>
       </c>
       <c r="J284" s="14" t="s">
-        <v>4106</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="285" spans="1:10">
@@ -24172,10 +24128,10 @@
         <v>3211</v>
       </c>
       <c r="I285" s="14" t="s">
-        <v>3862</v>
+        <v>3860</v>
       </c>
       <c r="J285" s="14" t="s">
-        <v>4111</v>
+        <v>4109</v>
       </c>
     </row>
     <row r="286" spans="1:10">
@@ -24204,10 +24160,10 @@
         <v>3212</v>
       </c>
       <c r="I286" s="14" t="s">
-        <v>3863</v>
+        <v>3861</v>
       </c>
       <c r="J286" s="14" t="s">
-        <v>4112</v>
+        <v>4110</v>
       </c>
     </row>
     <row r="287" spans="1:10">
@@ -24236,10 +24192,10 @@
         <v>3213</v>
       </c>
       <c r="I287" s="14" t="s">
-        <v>3865</v>
+        <v>3863</v>
       </c>
       <c r="J287" s="14" t="s">
-        <v>4113</v>
+        <v>4111</v>
       </c>
     </row>
     <row r="288" spans="1:10">
@@ -24268,10 +24224,10 @@
         <v>3214</v>
       </c>
       <c r="I288" s="14" t="s">
-        <v>3864</v>
+        <v>3862</v>
       </c>
       <c r="J288" s="14" t="s">
-        <v>4116</v>
+        <v>4114</v>
       </c>
     </row>
     <row r="289" spans="1:10">
@@ -24300,10 +24256,10 @@
         <v>3215</v>
       </c>
       <c r="I289" s="14" t="s">
-        <v>3795</v>
+        <v>3793</v>
       </c>
       <c r="J289" s="14" t="s">
-        <v>4114</v>
+        <v>4112</v>
       </c>
     </row>
     <row r="290" spans="1:10">
@@ -24332,10 +24288,10 @@
         <v>3216</v>
       </c>
       <c r="I290" s="14" t="s">
-        <v>3796</v>
+        <v>3794</v>
       </c>
       <c r="J290" s="14" t="s">
-        <v>4115</v>
+        <v>4113</v>
       </c>
     </row>
     <row r="291" spans="1:10">
@@ -24364,10 +24320,10 @@
         <v>3186</v>
       </c>
       <c r="I291" s="14" t="s">
-        <v>3797</v>
+        <v>3795</v>
       </c>
       <c r="J291" s="14" t="s">
-        <v>4110</v>
+        <v>4108</v>
       </c>
     </row>
     <row r="292" spans="1:10">
@@ -24396,10 +24352,10 @@
         <v>3187</v>
       </c>
       <c r="I292" s="14" t="s">
-        <v>3798</v>
+        <v>3796</v>
       </c>
       <c r="J292" s="14" t="s">
-        <v>4109</v>
+        <v>4107</v>
       </c>
     </row>
     <row r="293" spans="1:10">
@@ -24428,10 +24384,10 @@
         <v>3189</v>
       </c>
       <c r="I293" s="14" t="s">
-        <v>3799</v>
+        <v>3797</v>
       </c>
       <c r="J293" s="14" t="s">
-        <v>4108</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="294" spans="1:10">
@@ -24460,10 +24416,10 @@
         <v>3188</v>
       </c>
       <c r="I294" s="14" t="s">
-        <v>3801</v>
+        <v>3799</v>
       </c>
       <c r="J294" s="14" t="s">
-        <v>4107</v>
+        <v>4105</v>
       </c>
     </row>
     <row r="295" spans="1:10">
@@ -24492,10 +24448,10 @@
         <v>3014</v>
       </c>
       <c r="I295" s="14" t="s">
-        <v>3800</v>
+        <v>3798</v>
       </c>
       <c r="J295" s="14" t="s">
-        <v>4154</v>
+        <v>4152</v>
       </c>
     </row>
     <row r="296" spans="1:10">
@@ -24524,10 +24480,10 @@
         <v>3190</v>
       </c>
       <c r="I296" s="14" t="s">
-        <v>3802</v>
+        <v>3800</v>
       </c>
       <c r="J296" s="14" t="s">
-        <v>4155</v>
+        <v>4153</v>
       </c>
     </row>
     <row r="297" spans="1:10">
@@ -24556,10 +24512,10 @@
         <v>3191</v>
       </c>
       <c r="I297" s="14" t="s">
-        <v>3803</v>
+        <v>3801</v>
       </c>
       <c r="J297" s="14" t="s">
-        <v>4156</v>
+        <v>4154</v>
       </c>
     </row>
     <row r="298" spans="1:10">
@@ -24588,10 +24544,10 @@
         <v>3183</v>
       </c>
       <c r="I298" s="14" t="s">
-        <v>3804</v>
+        <v>3802</v>
       </c>
       <c r="J298" s="14" t="s">
-        <v>4157</v>
+        <v>4155</v>
       </c>
     </row>
     <row r="299" spans="1:10">
@@ -24620,10 +24576,10 @@
         <v>3184</v>
       </c>
       <c r="I299" s="14" t="s">
-        <v>3805</v>
+        <v>3803</v>
       </c>
       <c r="J299" s="14" t="s">
-        <v>4158</v>
+        <v>4156</v>
       </c>
     </row>
     <row r="300" spans="1:10">
@@ -24652,10 +24608,10 @@
         <v>3185</v>
       </c>
       <c r="I300" s="14" t="s">
-        <v>3806</v>
+        <v>3804</v>
       </c>
       <c r="J300" s="14" t="s">
-        <v>4159</v>
+        <v>4157</v>
       </c>
     </row>
     <row r="301" spans="1:10">
@@ -24684,10 +24640,10 @@
         <v>3245</v>
       </c>
       <c r="I301" s="14" t="s">
-        <v>3807</v>
+        <v>3805</v>
       </c>
       <c r="J301" s="14" t="s">
-        <v>4236</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="302" spans="1:10">
@@ -24716,10 +24672,10 @@
         <v>3246</v>
       </c>
       <c r="I302" s="14" t="s">
-        <v>3808</v>
+        <v>3806</v>
       </c>
       <c r="J302" s="14" t="s">
-        <v>4237</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="303" spans="1:10">
@@ -24748,10 +24704,10 @@
         <v>3247</v>
       </c>
       <c r="I303" s="14" t="s">
-        <v>3809</v>
+        <v>3807</v>
       </c>
       <c r="J303" s="14" t="s">
-        <v>4238</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="304" spans="1:10">
@@ -24780,10 +24736,10 @@
         <v>3248</v>
       </c>
       <c r="I304" s="14" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
       <c r="J304" s="14" t="s">
-        <v>4239</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="305" spans="1:10">
@@ -24812,10 +24768,10 @@
         <v>3249</v>
       </c>
       <c r="I305" s="14" t="s">
-        <v>3823</v>
+        <v>3821</v>
       </c>
       <c r="J305" s="14" t="s">
-        <v>4240</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="306" spans="1:10">
@@ -24844,10 +24800,10 @@
         <v>3250</v>
       </c>
       <c r="I306" s="14" t="s">
-        <v>3824</v>
+        <v>3822</v>
       </c>
       <c r="J306" s="14" t="s">
-        <v>4241</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="307" spans="1:10">
@@ -24876,10 +24832,10 @@
         <v>3266</v>
       </c>
       <c r="I307" s="14" t="s">
-        <v>3825</v>
+        <v>3823</v>
       </c>
       <c r="J307" s="14" t="s">
-        <v>4262</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="308" spans="1:10">
@@ -24908,10 +24864,10 @@
         <v>3267</v>
       </c>
       <c r="I308" s="14" t="s">
-        <v>3826</v>
+        <v>3824</v>
       </c>
       <c r="J308" s="14" t="s">
-        <v>4263</v>
+        <v>4261</v>
       </c>
     </row>
     <row r="309" spans="1:10">
@@ -24940,10 +24896,10 @@
         <v>3268</v>
       </c>
       <c r="I309" s="14" t="s">
-        <v>3827</v>
+        <v>3825</v>
       </c>
       <c r="J309" s="14" t="s">
-        <v>4260</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="310" spans="1:10">
@@ -24972,10 +24928,10 @@
         <v>3269</v>
       </c>
       <c r="I310" s="14" t="s">
-        <v>3828</v>
+        <v>3826</v>
       </c>
       <c r="J310" s="14" t="s">
-        <v>4261</v>
+        <v>4259</v>
       </c>
     </row>
     <row r="311" spans="1:10">
@@ -25004,10 +24960,10 @@
         <v>3270</v>
       </c>
       <c r="I311" s="14" t="s">
-        <v>3829</v>
+        <v>3827</v>
       </c>
       <c r="J311" s="14" t="s">
-        <v>4266</v>
+        <v>4264</v>
       </c>
     </row>
     <row r="312" spans="1:10">
@@ -25036,10 +24992,10 @@
         <v>3271</v>
       </c>
       <c r="I312" s="14" t="s">
-        <v>3830</v>
+        <v>3828</v>
       </c>
       <c r="J312" s="14" t="s">
-        <v>4265</v>
+        <v>4263</v>
       </c>
     </row>
     <row r="313" spans="1:10">
@@ -25068,10 +25024,10 @@
         <v>3272</v>
       </c>
       <c r="I313" s="14" t="s">
-        <v>3831</v>
+        <v>3829</v>
       </c>
       <c r="J313" s="14" t="s">
-        <v>4264</v>
+        <v>4262</v>
       </c>
     </row>
     <row r="314" spans="1:10">
@@ -25100,10 +25056,10 @@
         <v>3251</v>
       </c>
       <c r="I314" s="14" t="s">
-        <v>3832</v>
+        <v>3830</v>
       </c>
       <c r="J314" s="14" t="s">
-        <v>4267</v>
+        <v>4265</v>
       </c>
     </row>
     <row r="315" spans="1:10">
@@ -25132,10 +25088,10 @@
         <v>3252</v>
       </c>
       <c r="I315" s="14" t="s">
-        <v>3833</v>
+        <v>3831</v>
       </c>
       <c r="J315" s="14" t="s">
-        <v>4268</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="316" spans="1:10">
@@ -25164,10 +25120,10 @@
         <v>3253</v>
       </c>
       <c r="I316" s="14" t="s">
-        <v>3834</v>
+        <v>3832</v>
       </c>
       <c r="J316" s="14" t="s">
-        <v>4243</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="317" spans="1:10">
@@ -25196,10 +25152,10 @@
         <v>3254</v>
       </c>
       <c r="I317" s="14" t="s">
-        <v>3835</v>
+        <v>3833</v>
       </c>
       <c r="J317" s="14" t="s">
-        <v>4244</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="318" spans="1:10">
@@ -25228,10 +25184,10 @@
         <v>3256</v>
       </c>
       <c r="I318" s="14" t="s">
-        <v>3836</v>
+        <v>3834</v>
       </c>
       <c r="J318" s="14" t="s">
-        <v>3836</v>
+        <v>3834</v>
       </c>
     </row>
     <row r="319" spans="1:10">
@@ -25260,10 +25216,10 @@
         <v>3255</v>
       </c>
       <c r="I319" s="14" t="s">
-        <v>3837</v>
+        <v>3835</v>
       </c>
       <c r="J319" s="14" t="s">
-        <v>4242</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="320" spans="1:10">
@@ -25292,10 +25248,10 @@
         <v>3258</v>
       </c>
       <c r="I320" s="14" t="s">
-        <v>3838</v>
+        <v>3836</v>
       </c>
       <c r="J320" s="14" t="s">
-        <v>4277</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="321" spans="1:10">
@@ -25324,10 +25280,10 @@
         <v>3257</v>
       </c>
       <c r="I321" s="14" t="s">
-        <v>3839</v>
+        <v>3837</v>
       </c>
       <c r="J321" s="14" t="s">
-        <v>4278</v>
+        <v>4276</v>
       </c>
     </row>
     <row r="322" spans="1:10">
@@ -25356,10 +25312,10 @@
         <v>3259</v>
       </c>
       <c r="I322" s="14" t="s">
-        <v>3840</v>
+        <v>3838</v>
       </c>
       <c r="J322" s="14" t="s">
-        <v>4279</v>
+        <v>4277</v>
       </c>
     </row>
     <row r="323" spans="1:10">
@@ -25388,10 +25344,10 @@
         <v>3260</v>
       </c>
       <c r="I323" s="14" t="s">
-        <v>3841</v>
+        <v>3839</v>
       </c>
       <c r="J323" s="14" t="s">
-        <v>4281</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="324" spans="1:10">
@@ -25420,10 +25376,10 @@
         <v>3261</v>
       </c>
       <c r="I324" s="14" t="s">
-        <v>3842</v>
+        <v>3840</v>
       </c>
       <c r="J324" s="14" t="s">
-        <v>4280</v>
+        <v>4278</v>
       </c>
     </row>
     <row r="325" spans="1:10">
@@ -25452,10 +25408,10 @@
         <v>3262</v>
       </c>
       <c r="I325" s="14" t="s">
-        <v>3843</v>
+        <v>3841</v>
       </c>
       <c r="J325" s="14" t="s">
-        <v>4282</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="326" spans="1:10">
@@ -25484,10 +25440,10 @@
         <v>3263</v>
       </c>
       <c r="I326" s="14" t="s">
-        <v>3844</v>
+        <v>3842</v>
       </c>
       <c r="J326" s="14" t="s">
-        <v>4283</v>
+        <v>4281</v>
       </c>
     </row>
     <row r="327" spans="1:10">
@@ -25516,10 +25472,10 @@
         <v>3264</v>
       </c>
       <c r="I327" s="14" t="s">
-        <v>3845</v>
+        <v>3843</v>
       </c>
       <c r="J327" s="14" t="s">
-        <v>4284</v>
+        <v>4282</v>
       </c>
     </row>
     <row r="328" spans="1:10">
@@ -25548,10 +25504,10 @@
         <v>3265</v>
       </c>
       <c r="I328" s="14" t="s">
-        <v>3846</v>
+        <v>3844</v>
       </c>
       <c r="J328" s="14" t="s">
-        <v>4285</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="329" spans="1:10">
@@ -25580,10 +25536,10 @@
         <v>3192</v>
       </c>
       <c r="I329" s="14" t="s">
-        <v>3847</v>
+        <v>3845</v>
       </c>
       <c r="J329" s="14" t="s">
-        <v>4286</v>
+        <v>4284</v>
       </c>
     </row>
     <row r="330" spans="1:10">
@@ -25612,10 +25568,10 @@
         <v>1950</v>
       </c>
       <c r="I330" s="14" t="s">
-        <v>3848</v>
+        <v>3846</v>
       </c>
       <c r="J330" s="14" t="s">
-        <v>4287</v>
+        <v>4285</v>
       </c>
     </row>
     <row r="331" spans="1:10">
@@ -25644,10 +25600,10 @@
         <v>3193</v>
       </c>
       <c r="I331" s="14" t="s">
-        <v>3849</v>
+        <v>3847</v>
       </c>
       <c r="J331" s="14" t="s">
-        <v>4301</v>
+        <v>4299</v>
       </c>
     </row>
     <row r="332" spans="1:10">
@@ -25676,10 +25632,10 @@
         <v>3194</v>
       </c>
       <c r="I332" s="14" t="s">
-        <v>3850</v>
+        <v>3848</v>
       </c>
       <c r="J332" s="14" t="s">
-        <v>4300</v>
+        <v>4298</v>
       </c>
     </row>
     <row r="333" spans="1:10">
@@ -25708,10 +25664,10 @@
         <v>3195</v>
       </c>
       <c r="I333" s="14" t="s">
-        <v>3851</v>
+        <v>3849</v>
       </c>
       <c r="J333" s="14" t="s">
-        <v>4299</v>
+        <v>4297</v>
       </c>
     </row>
     <row r="334" spans="1:10">
@@ -25740,10 +25696,10 @@
         <v>3196</v>
       </c>
       <c r="I334" s="14" t="s">
-        <v>3852</v>
+        <v>3850</v>
       </c>
       <c r="J334" s="14" t="s">
-        <v>4295</v>
+        <v>4293</v>
       </c>
     </row>
     <row r="335" spans="1:10">
@@ -25772,10 +25728,10 @@
         <v>3197</v>
       </c>
       <c r="I335" s="14" t="s">
-        <v>3853</v>
+        <v>3851</v>
       </c>
       <c r="J335" s="14" t="s">
-        <v>4296</v>
+        <v>4294</v>
       </c>
     </row>
     <row r="336" spans="1:10">
@@ -25804,10 +25760,10 @@
         <v>3198</v>
       </c>
       <c r="I336" s="14" t="s">
-        <v>3857</v>
+        <v>3855</v>
       </c>
       <c r="J336" s="14" t="s">
-        <v>4297</v>
+        <v>4295</v>
       </c>
     </row>
     <row r="337" spans="1:10">
@@ -25836,10 +25792,10 @@
         <v>3201</v>
       </c>
       <c r="I337" s="14" t="s">
-        <v>3856</v>
+        <v>3854</v>
       </c>
       <c r="J337" s="14" t="s">
-        <v>4298</v>
+        <v>4296</v>
       </c>
     </row>
     <row r="338" spans="1:10">
@@ -25868,10 +25824,10 @@
         <v>3199</v>
       </c>
       <c r="I338" s="14" t="s">
-        <v>3855</v>
+        <v>3853</v>
       </c>
       <c r="J338" s="14" t="s">
-        <v>4291</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="339" spans="1:10">
@@ -25900,10 +25856,10 @@
         <v>2007</v>
       </c>
       <c r="I339" s="14" t="s">
-        <v>3854</v>
+        <v>3852</v>
       </c>
       <c r="J339" s="14" t="s">
-        <v>4292</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="340" spans="1:10">
@@ -25932,10 +25888,10 @@
         <v>3200</v>
       </c>
       <c r="I340" s="14" t="s">
-        <v>3818</v>
+        <v>3816</v>
       </c>
       <c r="J340" s="14" t="s">
-        <v>4293</v>
+        <v>4291</v>
       </c>
     </row>
     <row r="341" spans="1:10">
@@ -25964,10 +25920,10 @@
         <v>3143</v>
       </c>
       <c r="I341" s="14" t="s">
-        <v>3817</v>
+        <v>3815</v>
       </c>
       <c r="J341" s="14" t="s">
-        <v>4294</v>
+        <v>4292</v>
       </c>
     </row>
     <row r="342" spans="1:10">
@@ -25996,10 +25952,10 @@
         <v>3144</v>
       </c>
       <c r="I342" s="14" t="s">
-        <v>3816</v>
+        <v>3814</v>
       </c>
       <c r="J342" s="14" t="s">
-        <v>4290</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="343" spans="1:10">
@@ -26028,10 +25984,10 @@
         <v>3146</v>
       </c>
       <c r="I343" s="14" t="s">
-        <v>3815</v>
+        <v>3813</v>
       </c>
       <c r="J343" s="14" t="s">
-        <v>4289</v>
+        <v>4287</v>
       </c>
     </row>
     <row r="344" spans="1:10">
@@ -26060,10 +26016,10 @@
         <v>3145</v>
       </c>
       <c r="I344" s="14" t="s">
-        <v>3814</v>
+        <v>3812</v>
       </c>
       <c r="J344" s="14" t="s">
-        <v>4288</v>
+        <v>4286</v>
       </c>
     </row>
     <row r="345" spans="1:10">
@@ -26092,10 +26048,10 @@
         <v>3148</v>
       </c>
       <c r="I345" s="14" t="s">
-        <v>3822</v>
+        <v>3820</v>
       </c>
       <c r="J345" s="14" t="s">
-        <v>4271</v>
+        <v>4269</v>
       </c>
     </row>
     <row r="346" spans="1:10">
@@ -26124,10 +26080,10 @@
         <v>3147</v>
       </c>
       <c r="I346" s="14" t="s">
-        <v>3821</v>
+        <v>3819</v>
       </c>
       <c r="J346" s="14" t="s">
-        <v>4272</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="347" spans="1:10">
@@ -26156,10 +26112,10 @@
         <v>3153</v>
       </c>
       <c r="I347" s="14" t="s">
-        <v>3820</v>
+        <v>3818</v>
       </c>
       <c r="J347" s="14" t="s">
-        <v>4273</v>
+        <v>4271</v>
       </c>
     </row>
     <row r="348" spans="1:10">
@@ -26188,10 +26144,10 @@
         <v>3152</v>
       </c>
       <c r="I348" s="14" t="s">
-        <v>3819</v>
+        <v>3817</v>
       </c>
       <c r="J348" s="14" t="s">
-        <v>4274</v>
+        <v>4272</v>
       </c>
     </row>
     <row r="349" spans="1:10">
@@ -26220,10 +26176,10 @@
         <v>3150</v>
       </c>
       <c r="I349" s="14" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
       <c r="J349" s="14" t="s">
-        <v>4275</v>
+        <v>4273</v>
       </c>
     </row>
     <row r="350" spans="1:10">
@@ -26252,10 +26208,10 @@
         <v>3151</v>
       </c>
       <c r="I350" s="14" t="s">
-        <v>3812</v>
+        <v>3810</v>
       </c>
       <c r="J350" s="14" t="s">
-        <v>4276</v>
+        <v>4274</v>
       </c>
     </row>
     <row r="351" spans="1:10">
@@ -26284,10 +26240,10 @@
         <v>3149</v>
       </c>
       <c r="I351" s="14" t="s">
-        <v>3813</v>
+        <v>3811</v>
       </c>
       <c r="J351" s="14" t="s">
-        <v>4270</v>
+        <v>4268</v>
       </c>
     </row>
     <row r="352" spans="1:10">
@@ -26316,10 +26272,10 @@
         <v>3173</v>
       </c>
       <c r="I352" s="14" t="s">
-        <v>3756</v>
+        <v>3754</v>
       </c>
       <c r="J352" s="14" t="s">
-        <v>4269</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="353" spans="1:10">
@@ -26348,10 +26304,10 @@
         <v>3174</v>
       </c>
       <c r="I353" s="14" t="s">
-        <v>3757</v>
+        <v>3755</v>
       </c>
       <c r="J353" s="14" t="s">
-        <v>4245</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="354" spans="1:10">
@@ -26380,10 +26336,10 @@
         <v>3177</v>
       </c>
       <c r="I354" s="14" t="s">
-        <v>3758</v>
+        <v>3756</v>
       </c>
       <c r="J354" s="14" t="s">
-        <v>4246</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="355" spans="1:10">
@@ -26412,10 +26368,10 @@
         <v>3176</v>
       </c>
       <c r="I355" s="14" t="s">
-        <v>3759</v>
+        <v>3757</v>
       </c>
       <c r="J355" s="14" t="s">
-        <v>4247</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="356" spans="1:10">
@@ -26444,10 +26400,10 @@
         <v>3175</v>
       </c>
       <c r="I356" s="14" t="s">
-        <v>3760</v>
+        <v>3758</v>
       </c>
       <c r="J356" s="14" t="s">
-        <v>4248</v>
+        <v>4246</v>
       </c>
     </row>
     <row r="357" spans="1:10">
@@ -26476,10 +26432,10 @@
         <v>3178</v>
       </c>
       <c r="I357" s="14" t="s">
-        <v>3761</v>
+        <v>3759</v>
       </c>
       <c r="J357" s="14" t="s">
-        <v>4249</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="358" spans="1:10">
@@ -26508,10 +26464,10 @@
         <v>3179</v>
       </c>
       <c r="I358" s="14" t="s">
-        <v>3762</v>
+        <v>3760</v>
       </c>
       <c r="J358" s="14" t="s">
-        <v>4252</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="359" spans="1:10">
@@ -26540,10 +26496,10 @@
         <v>3180</v>
       </c>
       <c r="I359" s="14" t="s">
-        <v>3763</v>
+        <v>3761</v>
       </c>
       <c r="J359" s="14" t="s">
-        <v>4251</v>
+        <v>4249</v>
       </c>
     </row>
     <row r="360" spans="1:10">
@@ -26572,10 +26528,10 @@
         <v>3181</v>
       </c>
       <c r="I360" s="14" t="s">
-        <v>3764</v>
+        <v>3762</v>
       </c>
       <c r="J360" s="14" t="s">
-        <v>4250</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="361" spans="1:10">
@@ -26604,10 +26560,10 @@
         <v>3182</v>
       </c>
       <c r="I361" s="14" t="s">
-        <v>3765</v>
+        <v>3763</v>
       </c>
       <c r="J361" s="14" t="s">
-        <v>4255</v>
+        <v>4253</v>
       </c>
     </row>
     <row r="362" spans="1:10">
@@ -26636,10 +26592,10 @@
         <v>3154</v>
       </c>
       <c r="I362" s="14" t="s">
-        <v>3766</v>
+        <v>3764</v>
       </c>
       <c r="J362" s="14" t="s">
-        <v>4253</v>
+        <v>4251</v>
       </c>
     </row>
     <row r="363" spans="1:10">
@@ -26668,10 +26624,10 @@
         <v>2148</v>
       </c>
       <c r="I363" s="14" t="s">
-        <v>3767</v>
+        <v>3765</v>
       </c>
       <c r="J363" s="14" t="s">
-        <v>4254</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="364" spans="1:10">
@@ -26700,10 +26656,10 @@
         <v>3155</v>
       </c>
       <c r="I364" s="14" t="s">
-        <v>3768</v>
+        <v>3766</v>
       </c>
       <c r="J364" s="14" t="s">
-        <v>4256</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="365" spans="1:10">
@@ -26732,10 +26688,10 @@
         <v>3162</v>
       </c>
       <c r="I365" s="14" t="s">
-        <v>3753</v>
+        <v>3751</v>
       </c>
       <c r="J365" s="14" t="s">
-        <v>4257</v>
+        <v>4255</v>
       </c>
     </row>
     <row r="366" spans="1:10">
@@ -26764,10 +26720,10 @@
         <v>3161</v>
       </c>
       <c r="I366" s="14" t="s">
-        <v>3754</v>
+        <v>3752</v>
       </c>
       <c r="J366" s="14" t="s">
-        <v>4259</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="367" spans="1:10">
@@ -26796,10 +26752,10 @@
         <v>3160</v>
       </c>
       <c r="I367" s="14" t="s">
-        <v>3755</v>
+        <v>3753</v>
       </c>
       <c r="J367" s="14" t="s">
-        <v>4259</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="368" spans="1:10">
@@ -26828,10 +26784,10 @@
         <v>3159</v>
       </c>
       <c r="I368" s="14" t="s">
-        <v>3752</v>
+        <v>3750</v>
       </c>
       <c r="J368" s="14" t="s">
-        <v>4258</v>
+        <v>4256</v>
       </c>
     </row>
     <row r="369" spans="1:10">
@@ -26860,10 +26816,10 @@
         <v>2190</v>
       </c>
       <c r="I369" s="14" t="s">
-        <v>3742</v>
+        <v>3740</v>
       </c>
       <c r="J369" s="14" t="s">
-        <v>4228</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="370" spans="1:10">
@@ -26892,10 +26848,10 @@
         <v>3156</v>
       </c>
       <c r="I370" s="14" t="s">
-        <v>3743</v>
+        <v>3741</v>
       </c>
       <c r="J370" s="14" t="s">
-        <v>4229</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="371" spans="1:10">
@@ -26924,10 +26880,10 @@
         <v>3158</v>
       </c>
       <c r="I371" s="14" t="s">
-        <v>3744</v>
+        <v>3742</v>
       </c>
       <c r="J371" s="14" t="s">
-        <v>4230</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="372" spans="1:10">
@@ -26956,10 +26912,10 @@
         <v>3157</v>
       </c>
       <c r="I372" s="14" t="s">
-        <v>3745</v>
+        <v>3743</v>
       </c>
       <c r="J372" s="14" t="s">
-        <v>4231</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="373" spans="1:10">
@@ -26988,10 +26944,10 @@
         <v>3163</v>
       </c>
       <c r="I373" s="14" t="s">
-        <v>3746</v>
+        <v>3744</v>
       </c>
       <c r="J373" s="14" t="s">
-        <v>3746</v>
+        <v>3744</v>
       </c>
     </row>
     <row r="374" spans="1:10">
@@ -27020,10 +26976,10 @@
         <v>2222</v>
       </c>
       <c r="I374" s="14" t="s">
-        <v>3747</v>
+        <v>3745</v>
       </c>
       <c r="J374" s="14" t="s">
-        <v>4232</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="375" spans="1:10">
@@ -27052,10 +27008,10 @@
         <v>3166</v>
       </c>
       <c r="I375" s="14" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
       <c r="J375" s="14" t="s">
-        <v>4233</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="376" spans="1:10">
@@ -27084,10 +27040,10 @@
         <v>3165</v>
       </c>
       <c r="I376" s="14" t="s">
-        <v>3749</v>
+        <v>3747</v>
       </c>
       <c r="J376" s="14" t="s">
-        <v>4234</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="377" spans="1:10">
@@ -27116,10 +27072,10 @@
         <v>3165</v>
       </c>
       <c r="I377" s="14" t="s">
-        <v>3750</v>
+        <v>3748</v>
       </c>
       <c r="J377" s="14" t="s">
-        <v>4235</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="378" spans="1:10">
@@ -27148,10 +27104,10 @@
         <v>3164</v>
       </c>
       <c r="I378" s="14" t="s">
-        <v>3751</v>
+        <v>3749</v>
       </c>
       <c r="J378" s="14" t="s">
-        <v>4224</v>
+        <v>4222</v>
       </c>
     </row>
     <row r="379" spans="1:10">
@@ -27180,10 +27136,10 @@
         <v>3167</v>
       </c>
       <c r="I379" s="14" t="s">
-        <v>3734</v>
+        <v>3732</v>
       </c>
       <c r="J379" s="14" t="s">
-        <v>4225</v>
+        <v>4223</v>
       </c>
     </row>
     <row r="380" spans="1:10">
@@ -27212,10 +27168,10 @@
         <v>3168</v>
       </c>
       <c r="I380" s="14" t="s">
-        <v>3735</v>
+        <v>3733</v>
       </c>
       <c r="J380" s="14" t="s">
-        <v>4226</v>
+        <v>4224</v>
       </c>
     </row>
     <row r="381" spans="1:10">
@@ -27244,10 +27200,10 @@
         <v>3169</v>
       </c>
       <c r="I381" s="14" t="s">
-        <v>3736</v>
+        <v>3734</v>
       </c>
       <c r="J381" s="14" t="s">
-        <v>4227</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="382" spans="1:10">
@@ -27276,10 +27232,10 @@
         <v>3170</v>
       </c>
       <c r="I382" s="14" t="s">
-        <v>3737</v>
+        <v>3735</v>
       </c>
       <c r="J382" s="14" t="s">
-        <v>4223</v>
+        <v>4221</v>
       </c>
     </row>
     <row r="383" spans="1:10">
@@ -27308,10 +27264,10 @@
         <v>3171</v>
       </c>
       <c r="I383" s="14" t="s">
-        <v>3738</v>
+        <v>3736</v>
       </c>
       <c r="J383" s="14" t="s">
-        <v>4222</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="384" spans="1:10">
@@ -27340,10 +27296,10 @@
         <v>3172</v>
       </c>
       <c r="I384" s="14" t="s">
-        <v>3739</v>
+        <v>3737</v>
       </c>
       <c r="J384" s="14" t="s">
-        <v>4220</v>
+        <v>4218</v>
       </c>
     </row>
     <row r="385" spans="1:10">
@@ -27372,10 +27328,10 @@
         <v>3097</v>
       </c>
       <c r="I385" s="14" t="s">
-        <v>3740</v>
+        <v>3738</v>
       </c>
       <c r="J385" s="14" t="s">
-        <v>4221</v>
+        <v>4219</v>
       </c>
     </row>
     <row r="386" spans="1:10">
@@ -27404,10 +27360,10 @@
         <v>3098</v>
       </c>
       <c r="I386" s="14" t="s">
-        <v>3741</v>
+        <v>3739</v>
       </c>
       <c r="J386" s="14" t="s">
-        <v>4002</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="387" spans="1:10">
@@ -27436,10 +27392,10 @@
         <v>3099</v>
       </c>
       <c r="I387" s="14" t="s">
-        <v>3677</v>
+        <v>3675</v>
       </c>
       <c r="J387" s="14" t="s">
-        <v>4003</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="388" spans="1:10">
@@ -27468,10 +27424,10 @@
         <v>3100</v>
       </c>
       <c r="I388" s="14" t="s">
-        <v>3678</v>
+        <v>3676</v>
       </c>
       <c r="J388" s="14" t="s">
-        <v>4004</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -27500,10 +27456,10 @@
         <v>3101</v>
       </c>
       <c r="I389" s="14" t="s">
-        <v>3679</v>
+        <v>3677</v>
       </c>
       <c r="J389" s="14" t="s">
-        <v>4005</v>
+        <v>4003</v>
       </c>
     </row>
     <row r="390" spans="1:10">
@@ -27532,10 +27488,10 @@
         <v>3102</v>
       </c>
       <c r="I390" s="14" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
       <c r="J390" s="14" t="s">
-        <v>4006</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="391" spans="1:10">
@@ -27564,10 +27520,10 @@
         <v>3103</v>
       </c>
       <c r="I391" s="14" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
       <c r="J391" s="14" t="s">
-        <v>4007</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="392" spans="1:10">
@@ -27596,10 +27552,10 @@
         <v>3104</v>
       </c>
       <c r="I392" s="14" t="s">
-        <v>3682</v>
+        <v>3680</v>
       </c>
       <c r="J392" s="14" t="s">
-        <v>4008</v>
+        <v>4006</v>
       </c>
     </row>
     <row r="393" spans="1:10">
@@ -27628,10 +27584,10 @@
         <v>3105</v>
       </c>
       <c r="I393" s="14" t="s">
-        <v>3683</v>
+        <v>3681</v>
       </c>
       <c r="J393" s="14" t="s">
-        <v>4009</v>
+        <v>4007</v>
       </c>
     </row>
     <row r="394" spans="1:10">
@@ -27660,10 +27616,10 @@
         <v>3106</v>
       </c>
       <c r="I394" s="14" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
       <c r="J394" s="14" t="s">
-        <v>4010</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="395" spans="1:10">
@@ -27692,10 +27648,10 @@
         <v>3108</v>
       </c>
       <c r="I395" s="14" t="s">
-        <v>3685</v>
+        <v>3683</v>
       </c>
       <c r="J395" s="14" t="s">
-        <v>4013</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="396" spans="1:10">
@@ -27724,10 +27680,10 @@
         <v>3107</v>
       </c>
       <c r="I396" s="14" t="s">
-        <v>3686</v>
+        <v>3684</v>
       </c>
       <c r="J396" s="14" t="s">
-        <v>4012</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="397" spans="1:10">
@@ -27756,10 +27712,10 @@
         <v>3109</v>
       </c>
       <c r="I397" s="14" t="s">
-        <v>3687</v>
+        <v>3685</v>
       </c>
       <c r="J397" s="14" t="s">
-        <v>4011</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="398" spans="1:10">
@@ -27788,10 +27744,10 @@
         <v>3111</v>
       </c>
       <c r="I398" s="14" t="s">
-        <v>3671</v>
+        <v>3669</v>
       </c>
       <c r="J398" s="14" t="s">
-        <v>3996</v>
+        <v>3994</v>
       </c>
     </row>
     <row r="399" spans="1:10">
@@ -27820,10 +27776,10 @@
         <v>3110</v>
       </c>
       <c r="I399" s="30" t="s">
-        <v>3672</v>
+        <v>3670</v>
       </c>
       <c r="J399" s="14" t="s">
-        <v>3997</v>
+        <v>3995</v>
       </c>
     </row>
     <row r="400" spans="1:10">
@@ -27852,10 +27808,10 @@
         <v>3112</v>
       </c>
       <c r="I400" s="30" t="s">
-        <v>3673</v>
+        <v>3671</v>
       </c>
       <c r="J400" s="14" t="s">
-        <v>3998</v>
+        <v>3996</v>
       </c>
     </row>
     <row r="401" spans="1:10">
@@ -27884,10 +27840,10 @@
         <v>3113</v>
       </c>
       <c r="I401" s="14" t="s">
-        <v>3674</v>
+        <v>3672</v>
       </c>
       <c r="J401" s="14" t="s">
-        <v>4001</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="402" spans="1:10">
@@ -27916,10 +27872,10 @@
         <v>3114</v>
       </c>
       <c r="I402" s="14" t="s">
-        <v>3675</v>
+        <v>3673</v>
       </c>
       <c r="J402" s="14" t="s">
-        <v>4000</v>
+        <v>3998</v>
       </c>
     </row>
     <row r="403" spans="1:10">
@@ -27948,10 +27904,10 @@
         <v>3115</v>
       </c>
       <c r="I403" s="14" t="s">
-        <v>3676</v>
+        <v>3674</v>
       </c>
       <c r="J403" s="14" t="s">
-        <v>3999</v>
+        <v>3997</v>
       </c>
     </row>
     <row r="404" spans="1:10">
@@ -27980,10 +27936,10 @@
         <v>3116</v>
       </c>
       <c r="I404" s="14" t="s">
-        <v>3649</v>
+        <v>3647</v>
       </c>
       <c r="J404" s="14" t="s">
-        <v>4014</v>
+        <v>4012</v>
       </c>
     </row>
     <row r="405" spans="1:10">
@@ -28012,10 +27968,10 @@
         <v>3117</v>
       </c>
       <c r="I405" s="14" t="s">
-        <v>3650</v>
+        <v>3648</v>
       </c>
       <c r="J405" s="14" t="s">
-        <v>4015</v>
+        <v>4013</v>
       </c>
     </row>
     <row r="406" spans="1:10">
@@ -28044,10 +28000,10 @@
         <v>3118</v>
       </c>
       <c r="I406" s="14" t="s">
-        <v>3651</v>
+        <v>3649</v>
       </c>
       <c r="J406" s="14" t="s">
-        <v>4016</v>
+        <v>4014</v>
       </c>
     </row>
     <row r="407" spans="1:10">
@@ -28076,10 +28032,10 @@
         <v>3119</v>
       </c>
       <c r="I407" s="14" t="s">
-        <v>3652</v>
+        <v>3650</v>
       </c>
       <c r="J407" s="14" t="s">
-        <v>4017</v>
+        <v>4015</v>
       </c>
     </row>
     <row r="408" spans="1:10">
@@ -28108,10 +28064,10 @@
         <v>3120</v>
       </c>
       <c r="I408" s="14" t="s">
-        <v>3653</v>
+        <v>3651</v>
       </c>
       <c r="J408" s="14" t="s">
-        <v>4018</v>
+        <v>4016</v>
       </c>
     </row>
     <row r="409" spans="1:10">
@@ -28140,10 +28096,10 @@
         <v>3121</v>
       </c>
       <c r="I409" s="14" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="J409" s="14" t="s">
-        <v>4021</v>
+        <v>4019</v>
       </c>
     </row>
     <row r="410" spans="1:10">
@@ -28172,10 +28128,10 @@
         <v>3122</v>
       </c>
       <c r="I410" s="14" t="s">
-        <v>3655</v>
+        <v>3653</v>
       </c>
       <c r="J410" s="14" t="s">
-        <v>4020</v>
+        <v>4018</v>
       </c>
     </row>
     <row r="411" spans="1:10">
@@ -28204,10 +28160,10 @@
         <v>3123</v>
       </c>
       <c r="I411" s="14" t="s">
-        <v>3656</v>
+        <v>3654</v>
       </c>
       <c r="J411" s="14" t="s">
-        <v>4019</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="412" spans="1:10">
@@ -28236,10 +28192,10 @@
         <v>3124</v>
       </c>
       <c r="I412" s="14" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
       <c r="J412" s="14" t="s">
-        <v>4030</v>
+        <v>4028</v>
       </c>
     </row>
     <row r="413" spans="1:10">
@@ -28268,10 +28224,10 @@
         <v>3125</v>
       </c>
       <c r="I413" s="14" t="s">
-        <v>3658</v>
+        <v>3656</v>
       </c>
       <c r="J413" s="14" t="s">
-        <v>4025</v>
+        <v>4023</v>
       </c>
     </row>
     <row r="414" spans="1:10">
@@ -28300,10 +28256,10 @@
         <v>3126</v>
       </c>
       <c r="I414" s="14" t="s">
-        <v>3659</v>
+        <v>3657</v>
       </c>
       <c r="J414" s="14" t="s">
-        <v>4026</v>
+        <v>4024</v>
       </c>
     </row>
     <row r="415" spans="1:10">
@@ -28332,10 +28288,10 @@
         <v>3127</v>
       </c>
       <c r="I415" s="14" t="s">
-        <v>3660</v>
+        <v>3658</v>
       </c>
       <c r="J415" s="14" t="s">
-        <v>4027</v>
+        <v>4025</v>
       </c>
     </row>
     <row r="416" spans="1:10">
@@ -28364,10 +28320,10 @@
         <v>3128</v>
       </c>
       <c r="I416" s="14" t="s">
-        <v>3661</v>
+        <v>3659</v>
       </c>
       <c r="J416" s="14" t="s">
-        <v>4028</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="417" spans="1:10">
@@ -28396,10 +28352,10 @@
         <v>3129</v>
       </c>
       <c r="I417" s="14" t="s">
-        <v>3662</v>
+        <v>3660</v>
       </c>
       <c r="J417" s="14" t="s">
-        <v>4029</v>
+        <v>4027</v>
       </c>
     </row>
     <row r="418" spans="1:10">
@@ -28428,10 +28384,10 @@
         <v>3130</v>
       </c>
       <c r="I418" s="14" t="s">
-        <v>3663</v>
+        <v>3661</v>
       </c>
       <c r="J418" s="14" t="s">
-        <v>4022</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="419" spans="1:10">
@@ -28460,10 +28416,10 @@
         <v>3131</v>
       </c>
       <c r="I419" s="14" t="s">
-        <v>3664</v>
+        <v>3662</v>
       </c>
       <c r="J419" s="14" t="s">
-        <v>4023</v>
+        <v>4021</v>
       </c>
     </row>
     <row r="420" spans="1:10">
@@ -28492,10 +28448,10 @@
         <v>3132</v>
       </c>
       <c r="I420" s="14" t="s">
-        <v>3665</v>
+        <v>3663</v>
       </c>
       <c r="J420" s="14" t="s">
-        <v>4024</v>
+        <v>4022</v>
       </c>
     </row>
     <row r="421" spans="1:10">
@@ -28524,10 +28480,10 @@
         <v>3133</v>
       </c>
       <c r="I421" s="14" t="s">
-        <v>3666</v>
+        <v>3664</v>
       </c>
       <c r="J421" s="14" t="s">
-        <v>3965</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="422" spans="1:10">
@@ -28556,10 +28512,10 @@
         <v>3086</v>
       </c>
       <c r="I422" s="14" t="s">
-        <v>3667</v>
+        <v>3665</v>
       </c>
       <c r="J422" s="14" t="s">
-        <v>3966</v>
+        <v>3964</v>
       </c>
     </row>
     <row r="423" spans="1:10">
@@ -28588,10 +28544,10 @@
         <v>3091</v>
       </c>
       <c r="I423" s="14" t="s">
-        <v>3668</v>
+        <v>3666</v>
       </c>
       <c r="J423" s="14" t="s">
-        <v>3967</v>
+        <v>3965</v>
       </c>
     </row>
     <row r="424" spans="1:10">
@@ -28620,10 +28576,10 @@
         <v>3092</v>
       </c>
       <c r="I424" s="14" t="s">
-        <v>3669</v>
+        <v>3667</v>
       </c>
       <c r="J424" s="14" t="s">
-        <v>3964</v>
+        <v>3962</v>
       </c>
     </row>
     <row r="425" spans="1:10">
@@ -28652,10 +28608,10 @@
         <v>3093</v>
       </c>
       <c r="I425" s="14" t="s">
-        <v>3670</v>
+        <v>3668</v>
       </c>
       <c r="J425" s="14" t="s">
-        <v>3963</v>
+        <v>3961</v>
       </c>
     </row>
     <row r="426" spans="1:10">
@@ -28684,10 +28640,10 @@
         <v>3094</v>
       </c>
       <c r="I426" s="14" t="s">
-        <v>3646</v>
+        <v>3644</v>
       </c>
       <c r="J426" s="14" t="s">
-        <v>3960</v>
+        <v>3958</v>
       </c>
     </row>
     <row r="427" spans="1:10">
@@ -28716,10 +28672,10 @@
         <v>3095</v>
       </c>
       <c r="I427" s="14" t="s">
-        <v>3647</v>
+        <v>3645</v>
       </c>
       <c r="J427" s="14" t="s">
-        <v>3961</v>
+        <v>3959</v>
       </c>
     </row>
     <row r="428" spans="1:10">
@@ -28748,10 +28704,10 @@
         <v>3096</v>
       </c>
       <c r="I428" s="14" t="s">
-        <v>3648</v>
+        <v>3646</v>
       </c>
       <c r="J428" s="14" t="s">
-        <v>3962</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="429" spans="1:10">
@@ -28780,10 +28736,10 @@
         <v>3090</v>
       </c>
       <c r="I429" s="14" t="s">
-        <v>3632</v>
+        <v>3630</v>
       </c>
       <c r="J429" s="14" t="s">
-        <v>3948</v>
+        <v>3946</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -28812,10 +28768,10 @@
         <v>3089</v>
       </c>
       <c r="I430" s="14" t="s">
-        <v>3633</v>
+        <v>3631</v>
       </c>
       <c r="J430" s="14" t="s">
-        <v>3949</v>
+        <v>3947</v>
       </c>
     </row>
     <row r="431" spans="1:10">
@@ -28844,10 +28800,10 @@
         <v>3079</v>
       </c>
       <c r="I431" s="14" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
       <c r="J431" s="14" t="s">
-        <v>3950</v>
+        <v>3948</v>
       </c>
     </row>
     <row r="432" spans="1:10">
@@ -28876,10 +28832,10 @@
         <v>3080</v>
       </c>
       <c r="I432" s="14" t="s">
-        <v>3635</v>
+        <v>3633</v>
       </c>
       <c r="J432" s="14" t="s">
-        <v>3951</v>
+        <v>3949</v>
       </c>
     </row>
     <row r="433" spans="1:10">
@@ -28908,10 +28864,10 @@
         <v>3081</v>
       </c>
       <c r="I433" s="14" t="s">
-        <v>3615</v>
+        <v>3613</v>
       </c>
       <c r="J433" s="14" t="s">
-        <v>3952</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="434" spans="1:10">
@@ -28940,10 +28896,10 @@
         <v>3082</v>
       </c>
       <c r="I434" s="14" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="J434" s="14" t="s">
-        <v>3953</v>
+        <v>3951</v>
       </c>
     </row>
     <row r="435" spans="1:10">
@@ -28972,10 +28928,10 @@
         <v>3083</v>
       </c>
       <c r="I435" s="14" t="s">
-        <v>3617</v>
+        <v>3615</v>
       </c>
       <c r="J435" s="14" t="s">
-        <v>3954</v>
+        <v>3952</v>
       </c>
     </row>
     <row r="436" spans="1:10">
@@ -29004,10 +28960,10 @@
         <v>2836</v>
       </c>
       <c r="I436" s="14" t="s">
-        <v>3618</v>
+        <v>3616</v>
       </c>
       <c r="J436" s="14" t="s">
-        <v>3955</v>
+        <v>3953</v>
       </c>
     </row>
     <row r="437" spans="1:10">
@@ -29036,10 +28992,10 @@
         <v>3084</v>
       </c>
       <c r="I437" s="14" t="s">
-        <v>3619</v>
+        <v>3617</v>
       </c>
       <c r="J437" s="14" t="s">
-        <v>3956</v>
+        <v>3954</v>
       </c>
     </row>
     <row r="438" spans="1:10">
@@ -29068,10 +29024,10 @@
         <v>3085</v>
       </c>
       <c r="I438" s="14" t="s">
-        <v>3620</v>
+        <v>3618</v>
       </c>
       <c r="J438" s="14" t="s">
-        <v>3957</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="439" spans="1:10">
@@ -29100,10 +29056,10 @@
         <v>3078</v>
       </c>
       <c r="I439" s="14" t="s">
-        <v>3621</v>
+        <v>3619</v>
       </c>
       <c r="J439" s="14" t="s">
-        <v>3958</v>
+        <v>3956</v>
       </c>
     </row>
     <row r="440" spans="1:10">
@@ -29132,10 +29088,10 @@
         <v>3077</v>
       </c>
       <c r="I440" s="14" t="s">
-        <v>3622</v>
+        <v>3620</v>
       </c>
       <c r="J440" s="14" t="s">
-        <v>3959</v>
+        <v>3957</v>
       </c>
     </row>
     <row r="441" spans="1:10">
@@ -29164,10 +29120,10 @@
         <v>3076</v>
       </c>
       <c r="I441" s="14" t="s">
-        <v>3623</v>
+        <v>3621</v>
       </c>
       <c r="J441" s="14" t="s">
-        <v>3941</v>
+        <v>3939</v>
       </c>
     </row>
     <row r="442" spans="1:10">
@@ -29196,10 +29152,10 @@
         <v>3075</v>
       </c>
       <c r="I442" s="14" t="s">
-        <v>3624</v>
+        <v>3622</v>
       </c>
       <c r="J442" s="14" t="s">
-        <v>3942</v>
+        <v>3940</v>
       </c>
     </row>
     <row r="443" spans="1:10">
@@ -29228,10 +29184,10 @@
         <v>3365</v>
       </c>
       <c r="I443" s="14" t="s">
-        <v>3625</v>
+        <v>3623</v>
       </c>
       <c r="J443" s="14" t="s">
-        <v>3943</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="444" spans="1:10">
@@ -29260,10 +29216,10 @@
         <v>3366</v>
       </c>
       <c r="I444" s="14" t="s">
-        <v>3626</v>
+        <v>3624</v>
       </c>
       <c r="J444" s="14" t="s">
-        <v>3944</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="445" spans="1:10">
@@ -29292,10 +29248,10 @@
         <v>3367</v>
       </c>
       <c r="I445" s="14" t="s">
-        <v>3627</v>
+        <v>3625</v>
       </c>
       <c r="J445" s="14" t="s">
-        <v>3945</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="446" spans="1:10">
@@ -29324,10 +29280,10 @@
         <v>3368</v>
       </c>
       <c r="I446" s="14" t="s">
-        <v>3628</v>
+        <v>3626</v>
       </c>
       <c r="J446" s="14" t="s">
-        <v>3946</v>
+        <v>3944</v>
       </c>
     </row>
     <row r="447" spans="1:10">
@@ -29356,10 +29312,10 @@
         <v>3369</v>
       </c>
       <c r="I447" s="14" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
       <c r="J447" s="14" t="s">
-        <v>3947</v>
+        <v>3945</v>
       </c>
     </row>
     <row r="448" spans="1:10">
@@ -29388,10 +29344,10 @@
         <v>3370</v>
       </c>
       <c r="I448" s="14" t="s">
-        <v>3630</v>
+        <v>3628</v>
       </c>
       <c r="J448" s="14" t="s">
-        <v>3939</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="449" spans="1:10">
@@ -29420,10 +29376,10 @@
         <v>3371</v>
       </c>
       <c r="I449" s="14" t="s">
-        <v>3631</v>
+        <v>3629</v>
       </c>
       <c r="J449" s="14" t="s">
-        <v>3940</v>
+        <v>3938</v>
       </c>
     </row>
     <row r="450" spans="1:10">
@@ -29452,10 +29408,10 @@
         <v>3082</v>
       </c>
       <c r="I450" s="14" t="s">
-        <v>3605</v>
+        <v>3603</v>
       </c>
       <c r="J450" s="14" t="s">
-        <v>3938</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="451" spans="1:10">
@@ -29484,10 +29440,10 @@
         <v>3293</v>
       </c>
       <c r="I451" s="14" t="s">
-        <v>3606</v>
+        <v>3604</v>
       </c>
       <c r="J451" s="14" t="s">
-        <v>3932</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="452" spans="1:10">
@@ -29516,10 +29472,10 @@
         <v>3105</v>
       </c>
       <c r="I452" s="14" t="s">
-        <v>3607</v>
+        <v>3605</v>
       </c>
       <c r="J452" s="14" t="s">
-        <v>3933</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="453" spans="1:10">
@@ -29548,10 +29504,10 @@
         <v>3372</v>
       </c>
       <c r="I453" s="14" t="s">
-        <v>3608</v>
+        <v>3606</v>
       </c>
       <c r="J453" s="14" t="s">
-        <v>3934</v>
+        <v>3932</v>
       </c>
     </row>
     <row r="454" spans="1:10">
@@ -29580,10 +29536,10 @@
         <v>3373</v>
       </c>
       <c r="I454" s="14" t="s">
-        <v>3609</v>
+        <v>3607</v>
       </c>
       <c r="J454" s="14" t="s">
-        <v>3935</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="455" spans="1:10">
@@ -29612,10 +29568,10 @@
         <v>3274</v>
       </c>
       <c r="I455" s="14" t="s">
-        <v>3610</v>
+        <v>3608</v>
       </c>
       <c r="J455" s="14" t="s">
-        <v>3936</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="456" spans="1:10">
@@ -29644,10 +29600,10 @@
         <v>3374</v>
       </c>
       <c r="I456" s="14" t="s">
-        <v>3611</v>
+        <v>3609</v>
       </c>
       <c r="J456" s="14" t="s">
-        <v>3937</v>
+        <v>3935</v>
       </c>
     </row>
     <row r="457" spans="1:10">
@@ -29676,10 +29632,10 @@
         <v>3375</v>
       </c>
       <c r="I457" s="14" t="s">
-        <v>3612</v>
+        <v>3610</v>
       </c>
       <c r="J457" s="14" t="s">
-        <v>3929</v>
+        <v>3927</v>
       </c>
     </row>
     <row r="458" spans="1:10">
@@ -29708,10 +29664,10 @@
         <v>3376</v>
       </c>
       <c r="I458" s="14" t="s">
-        <v>3613</v>
+        <v>3611</v>
       </c>
       <c r="J458" s="14" t="s">
-        <v>3930</v>
+        <v>3928</v>
       </c>
     </row>
     <row r="459" spans="1:10">
@@ -29740,13 +29696,13 @@
         <v>3377</v>
       </c>
       <c r="I459" s="14" t="s">
-        <v>3614</v>
+        <v>3612</v>
       </c>
       <c r="J459" s="14" t="s">
-        <v>3931</v>
-      </c>
-    </row>
-    <row r="460" spans="1:10" ht="181">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="460" spans="1:10" ht="193">
       <c r="A460" s="33" t="s">
         <v>3378</v>
       </c>
@@ -29754,10 +29710,10 @@
         <v>3383</v>
       </c>
       <c r="C460" s="34" t="s">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="D460" s="34" t="s">
-        <v>4398</v>
+        <v>4390</v>
       </c>
       <c r="E460" s="34" t="s">
         <v>3390</v>
@@ -29766,17 +29722,13 @@
         <v>3389</v>
       </c>
       <c r="G460" s="34" t="s">
-        <v>3408</v>
+        <v>3406</v>
       </c>
       <c r="H460" s="34" t="s">
-        <v>3401</v>
-      </c>
-      <c r="I460" s="35" t="s">
-        <v>4310</v>
-      </c>
-      <c r="J460" s="35" t="s">
-        <v>4305</v>
-      </c>
+        <v>3400</v>
+      </c>
+      <c r="I460" s="35"/>
+      <c r="J460" s="35"/>
     </row>
     <row r="461" spans="1:10" ht="25">
       <c r="A461" s="33" t="s">
@@ -29786,10 +29738,10 @@
         <v>3385</v>
       </c>
       <c r="C461" s="34" t="s">
-        <v>3399</v>
-      </c>
-      <c r="D461" s="34" t="s">
-        <v>3396</v>
+        <v>3398</v>
+      </c>
+      <c r="D461" s="30" t="s">
+        <v>4715</v>
       </c>
       <c r="E461" s="34" t="s">
         <v>3391</v>
@@ -29797,18 +29749,14 @@
       <c r="F461" s="34" t="s">
         <v>3386</v>
       </c>
-      <c r="G461" s="34" t="s">
-        <v>3407</v>
+      <c r="G461" s="30" t="s">
+        <v>4716</v>
       </c>
       <c r="H461" s="34" t="s">
-        <v>3402</v>
-      </c>
-      <c r="I461" s="14" t="s">
-        <v>4309</v>
-      </c>
-      <c r="J461" s="14" t="s">
-        <v>4302</v>
-      </c>
+        <v>3401</v>
+      </c>
+      <c r="I461" s="14"/>
+      <c r="J461" s="14"/>
     </row>
     <row r="462" spans="1:10">
       <c r="A462" s="33" t="s">
@@ -29818,7 +29766,7 @@
         <v>3384</v>
       </c>
       <c r="C462" s="30" t="s">
-        <v>3398</v>
+        <v>3397</v>
       </c>
       <c r="D462" s="30" t="s">
         <v>3394</v>
@@ -29830,16 +29778,16 @@
         <v>3387</v>
       </c>
       <c r="G462" s="30" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
       <c r="H462" s="30" t="s">
-        <v>3403</v>
+        <v>3402</v>
       </c>
       <c r="I462" s="14" t="s">
-        <v>4308</v>
+        <v>4302</v>
       </c>
       <c r="J462" s="14" t="s">
-        <v>4304</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="463" spans="1:10">
@@ -29850,7 +29798,7 @@
         <v>3382</v>
       </c>
       <c r="C463" s="30" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="D463" s="30" t="s">
         <v>3395</v>
@@ -29862,1432 +29810,1424 @@
         <v>3388</v>
       </c>
       <c r="G463" s="30" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
       <c r="H463" s="30" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
       <c r="I463" s="14" t="s">
-        <v>4307</v>
+        <v>4301</v>
       </c>
       <c r="J463" s="14" t="s">
-        <v>3928</v>
+        <v>3926</v>
       </c>
     </row>
     <row r="464" spans="1:10">
       <c r="A464" s="33" t="s">
+        <v>3407</v>
+      </c>
+      <c r="B464" s="30" t="s">
+        <v>3408</v>
+      </c>
+      <c r="C464" s="30" t="s">
+        <v>3408</v>
+      </c>
+      <c r="D464" s="3" t="s">
+        <v>3415</v>
+      </c>
+      <c r="E464" s="30" t="s">
+        <v>3418</v>
+      </c>
+      <c r="F464" s="30" t="s">
+        <v>3421</v>
+      </c>
+      <c r="G464" s="4" t="s">
+        <v>3424</v>
+      </c>
+      <c r="H464" s="4" t="s">
+        <v>3428</v>
+      </c>
+      <c r="I464" s="14" t="s">
+        <v>3642</v>
+      </c>
+      <c r="J464" s="14" t="s">
+        <v>3925</v>
+      </c>
+    </row>
+    <row r="465" spans="1:10" ht="25">
+      <c r="A465" s="33" t="s">
         <v>3409</v>
       </c>
-      <c r="B464" s="30" t="s">
+      <c r="B465" s="34" t="s">
         <v>3410</v>
       </c>
-      <c r="C464" s="30" t="s">
-        <v>3410</v>
-      </c>
-      <c r="D464" s="3" t="s">
+      <c r="C465" s="30" t="s">
+        <v>3413</v>
+      </c>
+      <c r="D465" s="30" t="s">
         <v>3417</v>
       </c>
-      <c r="E464" s="30" t="s">
+      <c r="E465" s="30" t="s">
         <v>3420</v>
       </c>
-      <c r="F464" s="30" t="s">
+      <c r="F465" s="30" t="s">
         <v>3423</v>
       </c>
-      <c r="G464" s="4" t="s">
+      <c r="G465" s="30" t="s">
         <v>3426</v>
       </c>
-      <c r="H464" s="4" t="s">
-        <v>3430</v>
-      </c>
-      <c r="I464" s="14" t="s">
-        <v>3644</v>
-      </c>
-      <c r="J464" s="14" t="s">
-        <v>3927</v>
-      </c>
-    </row>
-    <row r="465" spans="1:10" ht="49">
-      <c r="A465" s="33" t="s">
-        <v>3411</v>
-      </c>
-      <c r="B465" s="34" t="s">
-        <v>3412</v>
-      </c>
-      <c r="C465" s="30" t="s">
-        <v>3415</v>
-      </c>
-      <c r="D465" s="30" t="s">
-        <v>3419</v>
-      </c>
-      <c r="E465" s="30" t="s">
-        <v>3422</v>
-      </c>
-      <c r="F465" s="30" t="s">
-        <v>3425</v>
-      </c>
-      <c r="G465" s="30" t="s">
-        <v>3428</v>
-      </c>
       <c r="H465" s="30" t="s">
-        <v>3431</v>
-      </c>
-      <c r="I465" s="35" t="s">
-        <v>4306</v>
-      </c>
-      <c r="J465" s="35" t="s">
-        <v>4303</v>
-      </c>
+        <v>3429</v>
+      </c>
+      <c r="I465" s="35"/>
+      <c r="J465" s="35"/>
     </row>
     <row r="466" spans="1:10">
       <c r="A466" s="33" t="s">
-        <v>3413</v>
+        <v>3411</v>
       </c>
       <c r="B466" s="30" t="s">
+        <v>3412</v>
+      </c>
+      <c r="C466" s="30" t="s">
         <v>3414</v>
       </c>
-      <c r="C466" s="30" t="s">
+      <c r="D466" s="30" t="s">
         <v>3416</v>
       </c>
-      <c r="D466" s="30" t="s">
-        <v>3418</v>
-      </c>
       <c r="E466" s="30" t="s">
-        <v>3421</v>
+        <v>3419</v>
       </c>
       <c r="F466" s="30" t="s">
-        <v>3424</v>
+        <v>3422</v>
       </c>
       <c r="G466" s="4" t="s">
+        <v>3425</v>
+      </c>
+      <c r="H466" s="4" t="s">
         <v>3427</v>
       </c>
-      <c r="H466" s="4" t="s">
-        <v>3429</v>
-      </c>
       <c r="I466" s="14" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="J466" s="14" t="s">
-        <v>3926</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="467" spans="1:10">
       <c r="A467" s="33" t="s">
-        <v>4311</v>
+        <v>4303</v>
       </c>
       <c r="B467" s="30" t="s">
-        <v>4312</v>
+        <v>4304</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>4323</v>
+        <v>4315</v>
       </c>
       <c r="D467" s="3" t="s">
-        <v>4329</v>
+        <v>4321</v>
       </c>
       <c r="E467" s="3" t="s">
-        <v>4323</v>
+        <v>4315</v>
       </c>
       <c r="F467" s="3" t="s">
-        <v>4340</v>
+        <v>4332</v>
       </c>
       <c r="G467" s="4" t="s">
         <v>1254</v>
       </c>
       <c r="H467" s="4" t="s">
-        <v>4366</v>
+        <v>4358</v>
       </c>
       <c r="I467" s="14" t="s">
-        <v>4346</v>
+        <v>4338</v>
       </c>
       <c r="J467" s="14" t="s">
-        <v>4352</v>
+        <v>4344</v>
       </c>
     </row>
     <row r="468" spans="1:10">
       <c r="A468" s="33" t="s">
-        <v>4313</v>
+        <v>4305</v>
       </c>
       <c r="B468" s="30" t="s">
-        <v>4314</v>
+        <v>4306</v>
       </c>
       <c r="C468" s="3" t="s">
+        <v>4316</v>
+      </c>
+      <c r="D468" s="3" t="s">
         <v>4324</v>
       </c>
-      <c r="D468" s="3" t="s">
-        <v>4332</v>
-      </c>
       <c r="E468" s="3" t="s">
-        <v>4335</v>
+        <v>4327</v>
       </c>
       <c r="F468" s="3" t="s">
-        <v>4341</v>
+        <v>4333</v>
       </c>
       <c r="G468" s="4" t="s">
-        <v>4358</v>
+        <v>4350</v>
       </c>
       <c r="H468" s="4" t="s">
-        <v>4367</v>
+        <v>4359</v>
       </c>
       <c r="I468" s="14" t="s">
-        <v>4347</v>
+        <v>4339</v>
       </c>
       <c r="J468" s="14" t="s">
-        <v>4353</v>
+        <v>4345</v>
       </c>
     </row>
     <row r="469" spans="1:10">
       <c r="A469" s="33" t="s">
-        <v>4315</v>
+        <v>4307</v>
       </c>
       <c r="B469" s="30" t="s">
-        <v>4316</v>
+        <v>4308</v>
       </c>
       <c r="C469" s="3" t="s">
+        <v>4317</v>
+      </c>
+      <c r="D469" s="3" t="s">
         <v>4325</v>
       </c>
-      <c r="D469" s="3" t="s">
-        <v>4333</v>
-      </c>
       <c r="E469" s="3" t="s">
-        <v>4336</v>
+        <v>4328</v>
       </c>
       <c r="F469" s="3" t="s">
-        <v>4342</v>
+        <v>4334</v>
       </c>
       <c r="G469" s="4" t="s">
-        <v>4359</v>
+        <v>4351</v>
       </c>
       <c r="H469" s="4" t="s">
-        <v>4368</v>
+        <v>4360</v>
       </c>
       <c r="I469" s="14" t="s">
-        <v>4348</v>
+        <v>4340</v>
       </c>
       <c r="J469" s="14" t="s">
-        <v>4354</v>
+        <v>4346</v>
       </c>
     </row>
     <row r="470" spans="1:10">
       <c r="A470" s="33" t="s">
-        <v>4317</v>
+        <v>4309</v>
       </c>
       <c r="B470" s="30" t="s">
+        <v>4310</v>
+      </c>
+      <c r="C470" s="3" t="s">
         <v>4318</v>
       </c>
-      <c r="C470" s="3" t="s">
-        <v>4326</v>
-      </c>
       <c r="D470" s="3" t="s">
-        <v>4330</v>
+        <v>4322</v>
       </c>
       <c r="E470" s="3" t="s">
-        <v>4337</v>
+        <v>4329</v>
       </c>
       <c r="F470" s="3" t="s">
-        <v>4343</v>
+        <v>4335</v>
       </c>
       <c r="G470" s="4" t="s">
-        <v>4362</v>
+        <v>4354</v>
       </c>
       <c r="H470" s="4" t="s">
-        <v>4369</v>
+        <v>4361</v>
       </c>
       <c r="I470" s="14" t="s">
-        <v>4349</v>
+        <v>4341</v>
       </c>
       <c r="J470" s="14" t="s">
-        <v>4355</v>
+        <v>4347</v>
       </c>
     </row>
     <row r="471" spans="1:10">
       <c r="A471" s="33" t="s">
+        <v>4311</v>
+      </c>
+      <c r="B471" s="30" t="s">
+        <v>4312</v>
+      </c>
+      <c r="C471" s="3" t="s">
         <v>4319</v>
       </c>
-      <c r="B471" s="30" t="s">
-        <v>4320</v>
-      </c>
-      <c r="C471" s="3" t="s">
-        <v>4327</v>
-      </c>
       <c r="D471" s="3" t="s">
-        <v>4331</v>
+        <v>4323</v>
       </c>
       <c r="E471" s="3" t="s">
-        <v>4338</v>
+        <v>4330</v>
       </c>
       <c r="F471" s="3" t="s">
-        <v>4344</v>
+        <v>4336</v>
       </c>
       <c r="G471" s="4" t="s">
-        <v>4360</v>
+        <v>4352</v>
       </c>
       <c r="H471" s="4" t="s">
-        <v>4370</v>
+        <v>4362</v>
       </c>
       <c r="I471" s="14" t="s">
-        <v>4350</v>
+        <v>4342</v>
       </c>
       <c r="J471" s="14" t="s">
-        <v>4356</v>
+        <v>4348</v>
       </c>
     </row>
     <row r="472" spans="1:10">
       <c r="A472" s="33" t="s">
-        <v>4321</v>
+        <v>4313</v>
       </c>
       <c r="B472" s="30" t="s">
-        <v>4322</v>
+        <v>4314</v>
       </c>
       <c r="C472" s="3" t="s">
-        <v>4328</v>
+        <v>4320</v>
       </c>
       <c r="D472" s="3" t="s">
-        <v>4334</v>
+        <v>4326</v>
       </c>
       <c r="E472" s="3" t="s">
-        <v>4339</v>
+        <v>4331</v>
       </c>
       <c r="F472" s="3" t="s">
-        <v>4345</v>
+        <v>4337</v>
       </c>
       <c r="G472" s="4" t="s">
-        <v>4361</v>
+        <v>4353</v>
       </c>
       <c r="H472" s="4" t="s">
-        <v>4371</v>
+        <v>4363</v>
       </c>
       <c r="I472" s="14" t="s">
-        <v>4351</v>
+        <v>4343</v>
       </c>
       <c r="J472" s="14" t="s">
-        <v>4357</v>
+        <v>4349</v>
       </c>
     </row>
     <row r="473" spans="1:10">
       <c r="A473" s="33" t="s">
-        <v>4363</v>
+        <v>4355</v>
       </c>
       <c r="B473" s="30" t="s">
+        <v>4356</v>
+      </c>
+      <c r="C473" s="3" t="s">
+        <v>4370</v>
+      </c>
+      <c r="D473" s="3" t="s">
+        <v>4369</v>
+      </c>
+      <c r="E473" s="3" t="s">
+        <v>4368</v>
+      </c>
+      <c r="F473" s="3" t="s">
+        <v>4367</v>
+      </c>
+      <c r="G473" s="4" t="s">
+        <v>4357</v>
+      </c>
+      <c r="H473" s="4" t="s">
         <v>4364</v>
       </c>
-      <c r="C473" s="3" t="s">
-        <v>4378</v>
-      </c>
-      <c r="D473" s="3" t="s">
-        <v>4377</v>
-      </c>
-      <c r="E473" s="3" t="s">
-        <v>4376</v>
-      </c>
-      <c r="F473" s="3" t="s">
-        <v>4375</v>
-      </c>
-      <c r="G473" s="4" t="s">
+      <c r="I473" s="14" t="s">
+        <v>4366</v>
+      </c>
+      <c r="J473" s="14" t="s">
         <v>4365</v>
-      </c>
-      <c r="H473" s="4" t="s">
-        <v>4372</v>
-      </c>
-      <c r="I473" s="14" t="s">
-        <v>4374</v>
-      </c>
-      <c r="J473" s="14" t="s">
-        <v>4373</v>
       </c>
     </row>
     <row r="474" spans="1:10">
       <c r="A474" s="33" t="s">
+        <v>4371</v>
+      </c>
+      <c r="B474" s="30" t="s">
+        <v>4372</v>
+      </c>
+      <c r="C474" s="3" t="s">
+        <v>4373</v>
+      </c>
+      <c r="D474" s="3" t="s">
+        <v>4374</v>
+      </c>
+      <c r="E474" s="3" t="s">
+        <v>4375</v>
+      </c>
+      <c r="F474" s="3" t="s">
+        <v>4376</v>
+      </c>
+      <c r="G474" s="4" t="s">
+        <v>4378</v>
+      </c>
+      <c r="H474" s="4" t="s">
+        <v>4377</v>
+      </c>
+      <c r="I474" s="14" t="s">
+        <v>4380</v>
+      </c>
+      <c r="J474" s="14" t="s">
         <v>4379</v>
-      </c>
-      <c r="B474" s="30" t="s">
-        <v>4380</v>
-      </c>
-      <c r="C474" s="3" t="s">
-        <v>4381</v>
-      </c>
-      <c r="D474" s="3" t="s">
-        <v>4382</v>
-      </c>
-      <c r="E474" s="3" t="s">
-        <v>4383</v>
-      </c>
-      <c r="F474" s="3" t="s">
-        <v>4384</v>
-      </c>
-      <c r="G474" s="4" t="s">
-        <v>4386</v>
-      </c>
-      <c r="H474" s="4" t="s">
-        <v>4385</v>
-      </c>
-      <c r="I474" s="14" t="s">
-        <v>4388</v>
-      </c>
-      <c r="J474" s="14" t="s">
-        <v>4387</v>
       </c>
     </row>
     <row r="475" spans="1:10">
       <c r="A475" s="33" t="s">
-        <v>4390</v>
+        <v>4382</v>
       </c>
       <c r="B475" s="30" t="s">
-        <v>4389</v>
+        <v>4381</v>
       </c>
       <c r="C475" s="3" t="s">
-        <v>4394</v>
+        <v>4386</v>
       </c>
       <c r="D475" s="3" t="s">
-        <v>4389</v>
+        <v>4381</v>
       </c>
       <c r="E475" s="3" t="s">
-        <v>4394</v>
+        <v>4386</v>
       </c>
       <c r="F475" s="3" t="s">
-        <v>4391</v>
+        <v>4383</v>
       </c>
       <c r="G475" s="4" t="s">
-        <v>4395</v>
+        <v>4387</v>
       </c>
       <c r="H475" s="3" t="s">
-        <v>4389</v>
+        <v>4381</v>
       </c>
       <c r="I475" s="14" t="s">
-        <v>4392</v>
+        <v>4384</v>
       </c>
       <c r="J475" s="14" t="s">
-        <v>4393</v>
+        <v>4385</v>
       </c>
     </row>
     <row r="476" spans="1:10">
       <c r="A476" s="33" t="s">
-        <v>4399</v>
+        <v>4391</v>
       </c>
       <c r="B476" s="30" t="s">
-        <v>4400</v>
+        <v>4392</v>
       </c>
       <c r="C476" s="10" t="s">
-        <v>4433</v>
+        <v>4425</v>
       </c>
       <c r="D476" s="3" t="s">
-        <v>4443</v>
+        <v>4435</v>
       </c>
       <c r="E476" s="3" t="s">
-        <v>4438</v>
+        <v>4430</v>
       </c>
       <c r="F476" s="10" t="s">
-        <v>4447</v>
+        <v>4439</v>
       </c>
       <c r="G476" s="7" t="s">
-        <v>4462</v>
+        <v>4454</v>
       </c>
       <c r="H476" s="11" t="s">
-        <v>4467</v>
+        <v>4459</v>
       </c>
       <c r="I476" s="14" t="s">
-        <v>4457</v>
+        <v>4449</v>
       </c>
       <c r="J476" s="14" t="s">
-        <v>4452</v>
+        <v>4444</v>
       </c>
     </row>
     <row r="477" spans="1:10" ht="49">
       <c r="A477" s="33" t="s">
-        <v>4401</v>
+        <v>4393</v>
       </c>
       <c r="B477" s="34" t="s">
-        <v>4402</v>
+        <v>4394</v>
       </c>
       <c r="C477" s="10" t="s">
-        <v>4434</v>
+        <v>4426</v>
       </c>
       <c r="D477" s="10" t="s">
-        <v>4444</v>
+        <v>4436</v>
       </c>
       <c r="E477" s="10" t="s">
-        <v>4439</v>
+        <v>4431</v>
       </c>
       <c r="F477" s="10" t="s">
-        <v>4448</v>
+        <v>4440</v>
       </c>
       <c r="G477" s="7" t="s">
-        <v>4463</v>
+        <v>4455</v>
       </c>
       <c r="H477" s="10" t="s">
-        <v>4468</v>
+        <v>4460</v>
       </c>
       <c r="I477" s="35" t="s">
-        <v>4458</v>
+        <v>4450</v>
       </c>
       <c r="J477" s="35" t="s">
-        <v>4453</v>
+        <v>4445</v>
       </c>
     </row>
     <row r="478" spans="1:10" ht="97">
       <c r="A478" s="33" t="s">
-        <v>4403</v>
+        <v>4395</v>
       </c>
       <c r="B478" s="34" t="s">
-        <v>4404</v>
+        <v>4396</v>
       </c>
       <c r="C478" s="10" t="s">
-        <v>4435</v>
+        <v>4427</v>
       </c>
       <c r="D478" s="10" t="s">
-        <v>4709</v>
+        <v>4699</v>
       </c>
       <c r="E478" s="10" t="s">
-        <v>4440</v>
+        <v>4432</v>
       </c>
       <c r="F478" s="10" t="s">
-        <v>4449</v>
+        <v>4441</v>
       </c>
       <c r="G478" s="7" t="s">
-        <v>4464</v>
+        <v>4456</v>
       </c>
       <c r="H478" s="10" t="s">
-        <v>4469</v>
+        <v>4461</v>
       </c>
       <c r="I478" s="35" t="s">
-        <v>4459</v>
+        <v>4451</v>
       </c>
       <c r="J478" s="35" t="s">
-        <v>4454</v>
+        <v>4446</v>
       </c>
     </row>
     <row r="479" spans="1:10" ht="97">
       <c r="A479" s="33" t="s">
-        <v>4425</v>
+        <v>4417</v>
       </c>
       <c r="B479" s="34" t="s">
-        <v>4426</v>
+        <v>4418</v>
       </c>
       <c r="C479" s="10" t="s">
-        <v>4436</v>
+        <v>4428</v>
       </c>
       <c r="D479" s="10" t="s">
-        <v>4445</v>
+        <v>4437</v>
       </c>
       <c r="E479" s="10" t="s">
-        <v>4441</v>
+        <v>4433</v>
       </c>
       <c r="F479" s="10" t="s">
-        <v>4450</v>
+        <v>4442</v>
       </c>
       <c r="G479" s="8" t="s">
-        <v>4465</v>
+        <v>4457</v>
       </c>
       <c r="H479" s="10" t="s">
-        <v>4470</v>
+        <v>4462</v>
       </c>
       <c r="I479" s="35" t="s">
-        <v>4460</v>
+        <v>4452</v>
       </c>
       <c r="J479" s="35" t="s">
-        <v>4455</v>
+        <v>4447</v>
       </c>
     </row>
     <row r="480" spans="1:10" ht="61">
       <c r="A480" s="33" t="s">
-        <v>4427</v>
+        <v>4419</v>
       </c>
       <c r="B480" s="34" t="s">
-        <v>4428</v>
+        <v>4420</v>
       </c>
       <c r="C480" s="10" t="s">
-        <v>4437</v>
+        <v>4429</v>
       </c>
       <c r="D480" s="10" t="s">
-        <v>4446</v>
+        <v>4438</v>
       </c>
       <c r="E480" s="10" t="s">
-        <v>4442</v>
+        <v>4434</v>
       </c>
       <c r="F480" s="10" t="s">
-        <v>4451</v>
+        <v>4443</v>
       </c>
       <c r="G480" s="8" t="s">
-        <v>4466</v>
+        <v>4458</v>
       </c>
       <c r="H480" s="10" t="s">
-        <v>4471</v>
+        <v>4463</v>
       </c>
       <c r="I480" s="35" t="s">
-        <v>4461</v>
+        <v>4453</v>
       </c>
       <c r="J480" s="35" t="s">
-        <v>4456</v>
+        <v>4448</v>
       </c>
     </row>
     <row r="481" spans="1:10" ht="61">
       <c r="A481" s="33" t="s">
-        <v>4429</v>
+        <v>4421</v>
       </c>
       <c r="B481" s="34" t="s">
-        <v>4430</v>
+        <v>4422</v>
       </c>
       <c r="C481" s="10" t="s">
-        <v>4472</v>
+        <v>4464</v>
       </c>
       <c r="D481" s="10" t="s">
-        <v>4479</v>
+        <v>4471</v>
       </c>
       <c r="E481" s="10" t="s">
-        <v>4481</v>
+        <v>4473</v>
       </c>
       <c r="F481" s="10" t="s">
-        <v>4488</v>
+        <v>4480</v>
       </c>
       <c r="G481" s="8" t="s">
-        <v>4516</v>
+        <v>4506</v>
       </c>
       <c r="H481" s="11" t="s">
-        <v>4509</v>
+        <v>4499</v>
       </c>
       <c r="I481" s="35" t="s">
-        <v>4502</v>
+        <v>4493</v>
       </c>
       <c r="J481" s="35" t="s">
-        <v>4495</v>
+        <v>4487</v>
       </c>
     </row>
     <row r="482" spans="1:10" ht="85">
       <c r="A482" s="33" t="s">
-        <v>4405</v>
+        <v>4397</v>
       </c>
       <c r="B482" s="34" t="s">
-        <v>4406</v>
+        <v>4398</v>
       </c>
       <c r="C482" s="10" t="s">
-        <v>4473</v>
+        <v>4465</v>
       </c>
       <c r="D482" s="10" t="s">
-        <v>4720</v>
+        <v>4710</v>
       </c>
       <c r="E482" s="10" t="s">
-        <v>4482</v>
+        <v>4474</v>
       </c>
       <c r="F482" s="10" t="s">
-        <v>4489</v>
+        <v>4481</v>
       </c>
       <c r="G482" s="7" t="s">
-        <v>4517</v>
+        <v>4507</v>
       </c>
       <c r="H482" s="11" t="s">
-        <v>4510</v>
+        <v>4500</v>
       </c>
       <c r="I482" s="35" t="s">
-        <v>4503</v>
+        <v>4494</v>
       </c>
       <c r="J482" s="35" t="s">
-        <v>4496</v>
+        <v>4488</v>
       </c>
     </row>
     <row r="483" spans="1:10" ht="49">
       <c r="A483" s="33" t="s">
-        <v>4407</v>
+        <v>4399</v>
       </c>
       <c r="B483" s="34" t="s">
-        <v>4408</v>
+        <v>4400</v>
       </c>
       <c r="C483" s="10" t="s">
-        <v>4474</v>
+        <v>4466</v>
       </c>
       <c r="D483" s="10" t="s">
-        <v>4710</v>
+        <v>4700</v>
       </c>
       <c r="E483" s="10" t="s">
-        <v>4483</v>
+        <v>4475</v>
       </c>
       <c r="F483" s="10" t="s">
-        <v>4490</v>
+        <v>4482</v>
       </c>
       <c r="G483" s="7" t="s">
-        <v>4518</v>
+        <v>4508</v>
       </c>
       <c r="H483" s="11" t="s">
-        <v>4511</v>
+        <v>4501</v>
       </c>
       <c r="I483" s="35" t="s">
-        <v>4504</v>
+        <v>4495</v>
       </c>
       <c r="J483" s="35" t="s">
-        <v>4497</v>
+        <v>4489</v>
       </c>
     </row>
     <row r="484" spans="1:10" ht="85">
       <c r="A484" s="33" t="s">
-        <v>4409</v>
+        <v>4401</v>
       </c>
       <c r="B484" s="34" t="s">
-        <v>4410</v>
+        <v>4402</v>
       </c>
       <c r="C484" s="10" t="s">
-        <v>4475</v>
+        <v>4467</v>
       </c>
       <c r="D484" s="10" t="s">
-        <v>4721</v>
+        <v>4711</v>
       </c>
       <c r="E484" s="10" t="s">
-        <v>4484</v>
+        <v>4476</v>
       </c>
       <c r="F484" s="10" t="s">
-        <v>4491</v>
+        <v>4483</v>
       </c>
       <c r="G484" s="7" t="s">
-        <v>4519</v>
+        <v>4509</v>
       </c>
       <c r="H484" s="10" t="s">
-        <v>4512</v>
-      </c>
-      <c r="I484" s="35" t="s">
-        <v>4505</v>
-      </c>
-      <c r="J484" s="35" t="s">
-        <v>4498</v>
-      </c>
+        <v>4502</v>
+      </c>
+      <c r="I484" s="35"/>
+      <c r="J484" s="35"/>
     </row>
     <row r="485" spans="1:10" ht="85">
       <c r="A485" s="33" t="s">
-        <v>4413</v>
+        <v>4405</v>
       </c>
       <c r="B485" s="34" t="s">
-        <v>4414</v>
+        <v>4406</v>
       </c>
       <c r="C485" s="10" t="s">
-        <v>4476</v>
+        <v>4468</v>
       </c>
       <c r="D485" s="10" t="s">
-        <v>4722</v>
+        <v>4712</v>
       </c>
       <c r="E485" s="10" t="s">
-        <v>4485</v>
+        <v>4477</v>
       </c>
       <c r="F485" s="10" t="s">
-        <v>4492</v>
+        <v>4484</v>
       </c>
       <c r="G485" s="8" t="s">
-        <v>4520</v>
+        <v>4510</v>
       </c>
       <c r="H485" s="10" t="s">
-        <v>4513</v>
+        <v>4503</v>
       </c>
       <c r="I485" s="35" t="s">
-        <v>4506</v>
+        <v>4496</v>
       </c>
       <c r="J485" s="35" t="s">
-        <v>4499</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="486" spans="1:10" ht="61">
       <c r="A486" s="33" t="s">
-        <v>4411</v>
+        <v>4403</v>
       </c>
       <c r="B486" s="34" t="s">
-        <v>4412</v>
+        <v>4404</v>
       </c>
       <c r="C486" s="10" t="s">
-        <v>4477</v>
+        <v>4469</v>
       </c>
       <c r="D486" s="10" t="s">
-        <v>4711</v>
+        <v>4701</v>
       </c>
       <c r="E486" s="10" t="s">
-        <v>4486</v>
+        <v>4478</v>
       </c>
       <c r="F486" s="10" t="s">
-        <v>4493</v>
+        <v>4485</v>
       </c>
       <c r="G486" s="7" t="s">
-        <v>4521</v>
+        <v>4511</v>
       </c>
       <c r="H486" s="10" t="s">
-        <v>4514</v>
+        <v>4504</v>
       </c>
       <c r="I486" s="35" t="s">
-        <v>4507</v>
+        <v>4497</v>
       </c>
       <c r="J486" s="35" t="s">
-        <v>4500</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="487" spans="1:10" ht="37">
       <c r="A487" s="33" t="s">
-        <v>4415</v>
+        <v>4407</v>
       </c>
       <c r="B487" s="34" t="s">
-        <v>4416</v>
+        <v>4408</v>
       </c>
       <c r="C487" s="10" t="s">
-        <v>4478</v>
+        <v>4470</v>
       </c>
       <c r="D487" s="10" t="s">
-        <v>4480</v>
+        <v>4472</v>
       </c>
       <c r="E487" s="10" t="s">
-        <v>4487</v>
+        <v>4479</v>
       </c>
       <c r="F487" s="10" t="s">
-        <v>4494</v>
+        <v>4486</v>
       </c>
       <c r="G487" s="7" t="s">
-        <v>4522</v>
+        <v>4512</v>
       </c>
       <c r="H487" s="10" t="s">
-        <v>4515</v>
+        <v>4505</v>
       </c>
       <c r="I487" s="35" t="s">
-        <v>4508</v>
+        <v>4498</v>
       </c>
       <c r="J487" s="35" t="s">
-        <v>4501</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="488" spans="1:10" ht="73">
       <c r="A488" s="33" t="s">
-        <v>4417</v>
+        <v>4409</v>
       </c>
       <c r="B488" s="34" t="s">
-        <v>4418</v>
+        <v>4410</v>
       </c>
       <c r="C488" s="3" t="s">
-        <v>4531</v>
+        <v>4521</v>
       </c>
       <c r="D488" s="3" t="s">
-        <v>4535</v>
+        <v>4525</v>
       </c>
       <c r="E488" s="3" t="s">
-        <v>4539</v>
+        <v>4529</v>
       </c>
       <c r="F488" s="10" t="s">
-        <v>4543</v>
+        <v>4533</v>
       </c>
       <c r="G488" s="7" t="s">
-        <v>4547</v>
+        <v>4537</v>
       </c>
       <c r="H488" s="9" t="s">
-        <v>4551</v>
+        <v>4541</v>
       </c>
       <c r="I488" s="35" t="s">
-        <v>4526</v>
+        <v>4516</v>
       </c>
       <c r="J488" s="35" t="s">
-        <v>4527</v>
+        <v>4517</v>
       </c>
     </row>
     <row r="489" spans="1:10">
       <c r="A489" s="33" t="s">
-        <v>4419</v>
+        <v>4411</v>
       </c>
       <c r="B489" s="30" t="s">
-        <v>4420</v>
+        <v>4412</v>
       </c>
       <c r="C489" s="3" t="s">
-        <v>4532</v>
+        <v>4522</v>
       </c>
       <c r="D489" s="3" t="s">
-        <v>4536</v>
+        <v>4526</v>
       </c>
       <c r="E489" s="3" t="s">
-        <v>4540</v>
+        <v>4530</v>
       </c>
       <c r="F489" s="10" t="s">
-        <v>4544</v>
+        <v>4534</v>
       </c>
       <c r="G489" s="7" t="s">
-        <v>4548</v>
+        <v>4538</v>
       </c>
       <c r="H489" s="9" t="s">
-        <v>4552</v>
+        <v>4542</v>
       </c>
       <c r="I489" s="35" t="s">
-        <v>4525</v>
+        <v>4515</v>
       </c>
       <c r="J489" s="35" t="s">
-        <v>4528</v>
+        <v>4518</v>
       </c>
     </row>
     <row r="490" spans="1:10" ht="49">
       <c r="A490" s="33" t="s">
-        <v>4421</v>
+        <v>4413</v>
       </c>
       <c r="B490" s="34" t="s">
-        <v>4422</v>
+        <v>4414</v>
       </c>
       <c r="C490" s="3" t="s">
-        <v>4533</v>
+        <v>4523</v>
       </c>
       <c r="D490" s="3" t="s">
-        <v>4537</v>
+        <v>4527</v>
       </c>
       <c r="E490" s="3" t="s">
-        <v>4541</v>
+        <v>4531</v>
       </c>
       <c r="F490" s="10" t="s">
-        <v>4545</v>
+        <v>4535</v>
       </c>
       <c r="G490" s="9" t="s">
-        <v>4549</v>
+        <v>4539</v>
       </c>
       <c r="H490" s="9" t="s">
-        <v>4553</v>
+        <v>4543</v>
       </c>
       <c r="I490" s="35" t="s">
-        <v>4524</v>
+        <v>4514</v>
       </c>
       <c r="J490" s="35" t="s">
-        <v>4529</v>
+        <v>4519</v>
       </c>
     </row>
     <row r="491" spans="1:10" ht="25">
       <c r="A491" s="33" t="s">
-        <v>4423</v>
+        <v>4415</v>
       </c>
       <c r="B491" s="30" t="s">
-        <v>4424</v>
+        <v>4416</v>
       </c>
       <c r="C491" s="3" t="s">
-        <v>4534</v>
+        <v>4524</v>
       </c>
       <c r="D491" s="3" t="s">
-        <v>4538</v>
+        <v>4528</v>
       </c>
       <c r="E491" s="3" t="s">
-        <v>4542</v>
+        <v>4532</v>
       </c>
       <c r="F491" s="10" t="s">
-        <v>4546</v>
+        <v>4536</v>
       </c>
       <c r="G491" s="9" t="s">
-        <v>4550</v>
+        <v>4540</v>
       </c>
       <c r="H491" s="10" t="s">
-        <v>4554</v>
+        <v>4544</v>
       </c>
       <c r="I491" s="35" t="s">
-        <v>4523</v>
+        <v>4513</v>
       </c>
       <c r="J491" s="35" t="s">
-        <v>4530</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="492" spans="1:10" ht="25">
       <c r="A492" s="33" t="s">
+        <v>4546</v>
+      </c>
+      <c r="B492" s="30" t="s">
+        <v>4551</v>
+      </c>
+      <c r="C492" s="3" t="s">
+        <v>4552</v>
+      </c>
+      <c r="D492" s="3" t="s">
+        <v>4555</v>
+      </c>
+      <c r="E492" s="3" t="s">
+        <v>4558</v>
+      </c>
+      <c r="F492" s="3" t="s">
+        <v>4561</v>
+      </c>
+      <c r="G492" s="11" t="s">
+        <v>4570</v>
+      </c>
+      <c r="H492" s="11" t="s">
+        <v>4573</v>
+      </c>
+      <c r="I492" s="14" t="s">
+        <v>4564</v>
+      </c>
+      <c r="J492" s="14" t="s">
+        <v>4567</v>
+      </c>
+    </row>
+    <row r="493" spans="1:10">
+      <c r="A493" s="33" t="s">
+        <v>4547</v>
+      </c>
+      <c r="B493" s="30" t="s">
+        <v>4548</v>
+      </c>
+      <c r="C493" s="3" t="s">
+        <v>4553</v>
+      </c>
+      <c r="D493" s="3" t="s">
         <v>4556</v>
       </c>
-      <c r="B492" s="30" t="s">
-        <v>4561</v>
-      </c>
-      <c r="C492" s="3" t="s">
+      <c r="E493" s="3" t="s">
+        <v>4559</v>
+      </c>
+      <c r="F493" s="3" t="s">
         <v>4562</v>
       </c>
-      <c r="D492" s="3" t="s">
+      <c r="G493" s="11" t="s">
+        <v>4571</v>
+      </c>
+      <c r="H493" s="11" t="s">
+        <v>4574</v>
+      </c>
+      <c r="I493" s="14" t="s">
         <v>4565</v>
       </c>
-      <c r="E492" s="3" t="s">
+      <c r="J493" s="14" t="s">
         <v>4568</v>
-      </c>
-      <c r="F492" s="3" t="s">
-        <v>4571</v>
-      </c>
-      <c r="G492" s="11" t="s">
-        <v>4580</v>
-      </c>
-      <c r="H492" s="11" t="s">
-        <v>4583</v>
-      </c>
-      <c r="I492" s="14" t="s">
-        <v>4574</v>
-      </c>
-      <c r="J492" s="14" t="s">
-        <v>4577</v>
-      </c>
-    </row>
-    <row r="493" spans="1:10" ht="25">
-      <c r="A493" s="33" t="s">
-        <v>4557</v>
-      </c>
-      <c r="B493" s="30" t="s">
-        <v>4558</v>
-      </c>
-      <c r="C493" s="3" t="s">
-        <v>4563</v>
-      </c>
-      <c r="D493" s="3" t="s">
-        <v>4566</v>
-      </c>
-      <c r="E493" s="3" t="s">
-        <v>4569</v>
-      </c>
-      <c r="F493" s="3" t="s">
-        <v>4572</v>
-      </c>
-      <c r="G493" s="11" t="s">
-        <v>4581</v>
-      </c>
-      <c r="H493" s="11" t="s">
-        <v>4584</v>
-      </c>
-      <c r="I493" s="14" t="s">
-        <v>4575</v>
-      </c>
-      <c r="J493" s="14" t="s">
-        <v>4578</v>
       </c>
     </row>
     <row r="494" spans="1:10">
       <c r="A494" s="33" t="s">
-        <v>4559</v>
+        <v>4549</v>
       </c>
       <c r="B494" s="30" t="s">
+        <v>4550</v>
+      </c>
+      <c r="C494" s="3" t="s">
+        <v>4554</v>
+      </c>
+      <c r="D494" s="3" t="s">
+        <v>4557</v>
+      </c>
+      <c r="E494" s="3" t="s">
         <v>4560</v>
       </c>
-      <c r="C494" s="3" t="s">
-        <v>4564</v>
-      </c>
-      <c r="D494" s="3" t="s">
-        <v>4567</v>
-      </c>
-      <c r="E494" s="3" t="s">
-        <v>4570</v>
-      </c>
       <c r="F494" s="3" t="s">
-        <v>4573</v>
+        <v>4563</v>
       </c>
       <c r="G494" s="11" t="s">
-        <v>4582</v>
+        <v>4572</v>
       </c>
       <c r="H494" s="11" t="s">
-        <v>4585</v>
+        <v>4575</v>
       </c>
       <c r="I494" s="14" t="s">
-        <v>4576</v>
+        <v>4566</v>
       </c>
       <c r="J494" s="14" t="s">
-        <v>4579</v>
+        <v>4569</v>
       </c>
     </row>
     <row r="495" spans="1:10">
       <c r="A495" s="33" t="s">
-        <v>4586</v>
+        <v>4576</v>
       </c>
       <c r="B495" s="36" t="s">
-        <v>4599</v>
+        <v>4589</v>
       </c>
       <c r="C495" s="3" t="s">
-        <v>4612</v>
+        <v>4602</v>
       </c>
       <c r="D495" s="3" t="s">
-        <v>4624</v>
+        <v>4614</v>
       </c>
       <c r="E495" s="3" t="s">
-        <v>4635</v>
+        <v>4625</v>
       </c>
       <c r="F495" s="3" t="s">
         <v>2852</v>
       </c>
       <c r="G495" s="5" t="s">
-        <v>4689</v>
+        <v>4679</v>
       </c>
       <c r="H495" s="3" t="s">
-        <v>4677</v>
+        <v>4667</v>
       </c>
       <c r="I495" s="14" t="s">
-        <v>4656</v>
+        <v>4646</v>
       </c>
       <c r="J495" s="14" t="s">
-        <v>3959</v>
+        <v>3957</v>
       </c>
     </row>
     <row r="496" spans="1:10">
       <c r="A496" s="33" t="s">
-        <v>4587</v>
+        <v>4577</v>
       </c>
       <c r="B496" s="36" t="s">
-        <v>4600</v>
+        <v>4590</v>
       </c>
       <c r="C496" s="3" t="s">
-        <v>4613</v>
+        <v>4603</v>
       </c>
       <c r="D496" s="3" t="s">
-        <v>4625</v>
+        <v>4615</v>
       </c>
       <c r="E496" s="3" t="s">
+        <v>4626</v>
+      </c>
+      <c r="F496" s="3" t="s">
         <v>4636</v>
       </c>
-      <c r="F496" s="3" t="s">
-        <v>4646</v>
-      </c>
       <c r="G496" s="5" t="s">
-        <v>4690</v>
+        <v>4680</v>
       </c>
       <c r="H496" s="3" t="s">
-        <v>4678</v>
+        <v>4668</v>
       </c>
       <c r="I496" s="14" t="s">
+        <v>4647</v>
+      </c>
+      <c r="J496" s="14" t="s">
         <v>4657</v>
-      </c>
-      <c r="J496" s="14" t="s">
-        <v>4667</v>
       </c>
     </row>
     <row r="497" spans="1:10">
       <c r="A497" s="33" t="s">
-        <v>4588</v>
+        <v>4578</v>
       </c>
       <c r="B497" s="30" t="s">
-        <v>4601</v>
+        <v>4591</v>
       </c>
       <c r="C497" s="3" t="s">
-        <v>4614</v>
+        <v>4604</v>
       </c>
       <c r="D497" s="3" t="s">
-        <v>4626</v>
+        <v>4616</v>
       </c>
       <c r="E497" s="3" t="s">
-        <v>4614</v>
+        <v>4604</v>
       </c>
       <c r="F497" s="3" t="s">
-        <v>4647</v>
+        <v>4637</v>
       </c>
       <c r="G497" s="5" t="s">
-        <v>4691</v>
+        <v>4681</v>
       </c>
       <c r="H497" s="3" t="s">
-        <v>4679</v>
+        <v>4669</v>
       </c>
       <c r="I497" s="14" t="s">
+        <v>4648</v>
+      </c>
+      <c r="J497" s="14" t="s">
         <v>4658</v>
-      </c>
-      <c r="J497" s="14" t="s">
-        <v>4668</v>
       </c>
     </row>
     <row r="498" spans="1:10">
       <c r="A498" s="33" t="s">
-        <v>4589</v>
+        <v>4579</v>
       </c>
       <c r="B498" s="36" t="s">
-        <v>4602</v>
+        <v>4592</v>
       </c>
       <c r="C498" s="3" t="s">
-        <v>4615</v>
+        <v>4605</v>
       </c>
       <c r="D498" s="3" t="s">
+        <v>4617</v>
+      </c>
+      <c r="E498" s="3" t="s">
         <v>4627</v>
       </c>
-      <c r="E498" s="3" t="s">
-        <v>4637</v>
-      </c>
       <c r="F498" s="3" t="s">
-        <v>4648</v>
+        <v>4638</v>
       </c>
       <c r="G498" s="5" t="s">
-        <v>4692</v>
+        <v>4682</v>
       </c>
       <c r="H498" s="3" t="s">
-        <v>4680</v>
+        <v>4670</v>
       </c>
       <c r="I498" s="14" t="s">
+        <v>4649</v>
+      </c>
+      <c r="J498" s="14" t="s">
         <v>4659</v>
-      </c>
-      <c r="J498" s="14" t="s">
-        <v>4669</v>
       </c>
     </row>
     <row r="499" spans="1:10">
       <c r="A499" s="33" t="s">
-        <v>4590</v>
+        <v>4580</v>
       </c>
       <c r="B499" s="36" t="s">
-        <v>4603</v>
+        <v>4593</v>
       </c>
       <c r="C499" s="3" t="s">
-        <v>4616</v>
+        <v>4606</v>
       </c>
       <c r="D499" s="3" t="s">
-        <v>4625</v>
+        <v>4615</v>
       </c>
       <c r="E499" s="3" t="s">
-        <v>4638</v>
+        <v>4628</v>
       </c>
       <c r="F499" s="3" t="s">
-        <v>4646</v>
+        <v>4636</v>
       </c>
       <c r="G499" s="5" t="s">
-        <v>4693</v>
+        <v>4683</v>
       </c>
       <c r="H499" s="3" t="s">
-        <v>4681</v>
+        <v>4671</v>
       </c>
       <c r="I499" s="14" t="s">
+        <v>4647</v>
+      </c>
+      <c r="J499" s="14" t="s">
         <v>4657</v>
-      </c>
-      <c r="J499" s="14" t="s">
-        <v>4667</v>
       </c>
     </row>
     <row r="500" spans="1:10">
       <c r="A500" s="33" t="s">
-        <v>4591</v>
+        <v>4581</v>
       </c>
       <c r="B500" s="36" t="s">
-        <v>4604</v>
+        <v>4594</v>
       </c>
       <c r="C500" s="3" t="s">
-        <v>4617</v>
+        <v>4607</v>
       </c>
       <c r="D500" s="3" t="s">
-        <v>4628</v>
+        <v>4618</v>
       </c>
       <c r="E500" s="3" t="s">
+        <v>4629</v>
+      </c>
+      <c r="F500" s="3" t="s">
         <v>4639</v>
       </c>
-      <c r="F500" s="3" t="s">
-        <v>4649</v>
-      </c>
       <c r="G500" s="5" t="s">
-        <v>4694</v>
+        <v>4684</v>
       </c>
       <c r="H500" s="3" t="s">
-        <v>4682</v>
+        <v>4672</v>
       </c>
       <c r="I500" s="14" t="s">
+        <v>4650</v>
+      </c>
+      <c r="J500" s="14" t="s">
         <v>4660</v>
-      </c>
-      <c r="J500" s="14" t="s">
-        <v>4670</v>
       </c>
     </row>
     <row r="501" spans="1:10">
       <c r="A501" s="33" t="s">
-        <v>4592</v>
+        <v>4582</v>
       </c>
       <c r="B501" s="36" t="s">
-        <v>4605</v>
+        <v>4595</v>
       </c>
       <c r="C501" s="3" t="s">
-        <v>4618</v>
+        <v>4608</v>
       </c>
       <c r="D501" s="3" t="s">
-        <v>4629</v>
+        <v>4619</v>
       </c>
       <c r="E501" s="3" t="s">
+        <v>4630</v>
+      </c>
+      <c r="F501" s="3" t="s">
         <v>4640</v>
       </c>
-      <c r="F501" s="3" t="s">
-        <v>4650</v>
-      </c>
       <c r="G501" s="5" t="s">
-        <v>4695</v>
+        <v>4685</v>
       </c>
       <c r="H501" s="3" t="s">
-        <v>4683</v>
+        <v>4673</v>
       </c>
       <c r="I501" s="14" t="s">
+        <v>4651</v>
+      </c>
+      <c r="J501" s="14" t="s">
         <v>4661</v>
-      </c>
-      <c r="J501" s="14" t="s">
-        <v>4671</v>
       </c>
     </row>
     <row r="502" spans="1:10">
       <c r="A502" s="33" t="s">
-        <v>4593</v>
+        <v>4583</v>
       </c>
       <c r="B502" s="36" t="s">
-        <v>4606</v>
+        <v>4596</v>
       </c>
       <c r="C502" s="3" t="s">
-        <v>4619</v>
+        <v>4609</v>
       </c>
       <c r="D502" s="3" t="s">
-        <v>4630</v>
+        <v>4620</v>
       </c>
       <c r="E502" s="3" t="s">
+        <v>4631</v>
+      </c>
+      <c r="F502" s="3" t="s">
         <v>4641</v>
       </c>
-      <c r="F502" s="3" t="s">
-        <v>4651</v>
-      </c>
       <c r="G502" s="5" t="s">
-        <v>4696</v>
+        <v>4686</v>
       </c>
       <c r="H502" s="3" t="s">
-        <v>4684</v>
+        <v>4674</v>
       </c>
       <c r="I502" s="14" t="s">
+        <v>4652</v>
+      </c>
+      <c r="J502" s="14" t="s">
         <v>4662</v>
-      </c>
-      <c r="J502" s="14" t="s">
-        <v>4672</v>
       </c>
     </row>
     <row r="503" spans="1:10">
       <c r="A503" s="33" t="s">
-        <v>4594</v>
+        <v>4584</v>
       </c>
       <c r="B503" s="36" t="s">
-        <v>4607</v>
+        <v>4597</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>4620</v>
+        <v>4610</v>
       </c>
       <c r="D503" s="3" t="s">
-        <v>4631</v>
+        <v>4621</v>
       </c>
       <c r="E503" s="3" t="s">
+        <v>4632</v>
+      </c>
+      <c r="F503" s="3" t="s">
         <v>4642</v>
       </c>
-      <c r="F503" s="3" t="s">
-        <v>4652</v>
-      </c>
       <c r="G503" s="5" t="s">
-        <v>4697</v>
+        <v>4687</v>
       </c>
       <c r="H503" s="3" t="s">
-        <v>4685</v>
+        <v>4675</v>
       </c>
       <c r="I503" s="14" t="s">
+        <v>4653</v>
+      </c>
+      <c r="J503" s="14" t="s">
         <v>4663</v>
-      </c>
-      <c r="J503" s="14" t="s">
-        <v>4673</v>
       </c>
     </row>
     <row r="504" spans="1:10">
       <c r="A504" s="33" t="s">
-        <v>4595</v>
+        <v>4585</v>
       </c>
       <c r="B504" s="36" t="s">
-        <v>4608</v>
+        <v>4598</v>
       </c>
       <c r="C504" s="3" t="s">
-        <v>4621</v>
+        <v>4611</v>
       </c>
       <c r="D504" s="3" t="s">
-        <v>4632</v>
+        <v>4622</v>
       </c>
       <c r="E504" s="3" t="s">
+        <v>4633</v>
+      </c>
+      <c r="F504" s="3" t="s">
         <v>4643</v>
       </c>
-      <c r="F504" s="3" t="s">
-        <v>4653</v>
-      </c>
       <c r="G504" s="5" t="s">
-        <v>4698</v>
+        <v>4688</v>
       </c>
       <c r="H504" s="3" t="s">
-        <v>4686</v>
+        <v>4676</v>
       </c>
       <c r="I504" s="14" t="s">
+        <v>4654</v>
+      </c>
+      <c r="J504" s="14" t="s">
         <v>4664</v>
-      </c>
-      <c r="J504" s="14" t="s">
-        <v>4674</v>
       </c>
     </row>
     <row r="505" spans="1:10">
       <c r="A505" s="33" t="s">
-        <v>4596</v>
+        <v>4586</v>
       </c>
       <c r="B505" s="30" t="s">
-        <v>4609</v>
+        <v>4599</v>
       </c>
       <c r="C505" s="3" t="s">
-        <v>4622</v>
+        <v>4612</v>
       </c>
       <c r="D505" s="3" t="s">
-        <v>4633</v>
+        <v>4623</v>
       </c>
       <c r="E505" s="3" t="s">
+        <v>4634</v>
+      </c>
+      <c r="F505" s="3" t="s">
         <v>4644</v>
       </c>
-      <c r="F505" s="3" t="s">
-        <v>4654</v>
-      </c>
       <c r="G505" s="5" t="s">
-        <v>4699</v>
+        <v>4689</v>
       </c>
       <c r="H505" s="3" t="s">
-        <v>4687</v>
+        <v>4677</v>
       </c>
       <c r="I505" s="14" t="s">
+        <v>4655</v>
+      </c>
+      <c r="J505" s="14" t="s">
         <v>4665</v>
-      </c>
-      <c r="J505" s="14" t="s">
-        <v>4675</v>
       </c>
     </row>
     <row r="506" spans="1:10">
       <c r="A506" s="33" t="s">
-        <v>4597</v>
+        <v>4587</v>
       </c>
       <c r="B506" s="30" t="s">
-        <v>4610</v>
+        <v>4600</v>
       </c>
       <c r="C506" s="3" t="s">
-        <v>4701</v>
+        <v>4691</v>
       </c>
       <c r="D506" s="3" t="s">
-        <v>4702</v>
+        <v>4692</v>
       </c>
       <c r="E506" s="3" t="s">
-        <v>4703</v>
+        <v>4693</v>
       </c>
       <c r="F506" s="3" t="s">
-        <v>4704</v>
+        <v>4694</v>
       </c>
       <c r="G506" s="9" t="s">
-        <v>4707</v>
+        <v>4697</v>
       </c>
       <c r="H506" s="9" t="s">
-        <v>4708</v>
+        <v>4698</v>
       </c>
       <c r="I506" s="14" t="s">
-        <v>4705</v>
+        <v>4695</v>
       </c>
       <c r="J506" s="14" t="s">
-        <v>4706</v>
+        <v>4696</v>
       </c>
     </row>
     <row r="507" spans="1:10">
       <c r="A507" s="33" t="s">
-        <v>4598</v>
+        <v>4588</v>
       </c>
       <c r="B507" s="36" t="s">
-        <v>4611</v>
+        <v>4601</v>
       </c>
       <c r="C507" s="3" t="s">
-        <v>4623</v>
+        <v>4613</v>
       </c>
       <c r="D507" s="3" t="s">
-        <v>4634</v>
+        <v>4624</v>
       </c>
       <c r="E507" s="3" t="s">
+        <v>4635</v>
+      </c>
+      <c r="F507" s="3" t="s">
         <v>4645</v>
       </c>
-      <c r="F507" s="3" t="s">
-        <v>4655</v>
-      </c>
       <c r="G507" s="5" t="s">
-        <v>4700</v>
+        <v>4690</v>
       </c>
       <c r="H507" s="3" t="s">
-        <v>4688</v>
+        <v>4678</v>
       </c>
       <c r="I507" s="14" t="s">
+        <v>4656</v>
+      </c>
+      <c r="J507" s="14" t="s">
         <v>4666</v>
-      </c>
-      <c r="J507" s="14" t="s">
-        <v>4676</v>
       </c>
     </row>
     <row r="508" spans="1:10">
       <c r="A508" s="33" t="s">
-        <v>4712</v>
+        <v>4702</v>
       </c>
       <c r="B508" s="30" t="s">
-        <v>4716</v>
+        <v>4706</v>
       </c>
       <c r="C508" s="3"/>
       <c r="D508" s="3"/>
@@ -31300,10 +31240,10 @@
     </row>
     <row r="509" spans="1:10">
       <c r="A509" s="33" t="s">
-        <v>4713</v>
+        <v>4703</v>
       </c>
       <c r="B509" s="30" t="s">
-        <v>4717</v>
+        <v>4707</v>
       </c>
       <c r="C509" s="3"/>
       <c r="D509" s="3"/>
@@ -31316,10 +31256,10 @@
     </row>
     <row r="510" spans="1:10">
       <c r="A510" s="33" t="s">
-        <v>4714</v>
+        <v>4704</v>
       </c>
       <c r="B510" s="30" t="s">
-        <v>4718</v>
+        <v>4708</v>
       </c>
       <c r="C510" s="3"/>
       <c r="D510" s="3"/>
@@ -31332,10 +31272,10 @@
     </row>
     <row r="511" spans="1:10">
       <c r="A511" s="33" t="s">
-        <v>4715</v>
+        <v>4705</v>
       </c>
       <c r="B511" s="30" t="s">
-        <v>4723</v>
+        <v>4713</v>
       </c>
       <c r="C511" s="3"/>
       <c r="D511" s="3"/>
@@ -31348,10 +31288,10 @@
     </row>
     <row r="512" spans="1:10">
       <c r="A512" s="33" t="s">
-        <v>4432</v>
+        <v>4424</v>
       </c>
       <c r="B512" s="30" t="s">
-        <v>4719</v>
+        <v>4709</v>
       </c>
       <c r="C512" s="3"/>
       <c r="D512" s="3"/>
@@ -31362,23 +31302,21 @@
       <c r="I512" s="14"/>
       <c r="J512" s="14"/>
     </row>
-    <row r="513" spans="1:10" ht="37">
+    <row r="513" spans="1:10">
       <c r="A513" s="33" t="s">
-        <v>4431</v>
-      </c>
-      <c r="B513" s="34" t="s">
-        <v>4724</v>
-      </c>
-      <c r="C513" s="10" t="s">
-        <v>4725</v>
-      </c>
-      <c r="D513" s="10"/>
-      <c r="E513" s="10"/>
-      <c r="F513" s="10"/>
-      <c r="G513" s="8"/>
-      <c r="H513" s="10"/>
-      <c r="I513" s="35"/>
-      <c r="J513" s="35"/>
+        <v>4423</v>
+      </c>
+      <c r="B513" s="30" t="s">
+        <v>4714</v>
+      </c>
+      <c r="C513" s="3"/>
+      <c r="D513" s="3"/>
+      <c r="E513" s="3"/>
+      <c r="F513" s="3"/>
+      <c r="G513" s="5"/>
+      <c r="H513" s="3"/>
+      <c r="I513" s="14"/>
+      <c r="J513" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -31403,6 +31341,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F12BE0DB4A3DF641BF113FBF1C7EA261" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c6b4b409d6b6c81c2874e5a51d11715e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="43e153a8-5ef1-4f65-aac7-dc4685f18eaa" xmlns:ns3="6e0cf07b-8188-4b76-8f54-3cda03d37414" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0521fade2ab7bf037697e8e8677cb864" ns2:_="" ns3:_="">
     <xsd:import namespace="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
@@ -31643,15 +31590,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E20926E-9EFB-4B7E-90D4-905B08F8E59C}">
   <ds:schemaRefs>
@@ -31670,6 +31608,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6201EF1-2938-4925-833A-11BB4654F7B4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31686,12 +31632,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/translations/translations.xlsx
+++ b/translations/translations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/russell/Projects/GPS-Sample/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE9ECBF-98C1-2940-B27E-36707EB3B85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C65A7A-04B4-BE42-AD7B-51EFD0191B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5074" uniqueCount="4717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5076" uniqueCount="4719">
   <si>
     <t>app_name</t>
   </si>
@@ -10218,66 +10218,18 @@
     <t>Background Location Permission</t>
   </si>
   <si>
-    <t>GPSSample records your route (breadcrumb trail) while you travel between households and map households.\n\nRecording starts only when you tap the RECORD button in the app and stops recording when you tap the STOP button.\n\nLocation is collected continuously while recording, even if the app is in the background or your device is locked.\n\nYour location data is stored securely on your device and is only exported if you choose to do so.\n\nYou can revoke background location access at any time in Android Settings.</t>
-  </si>
-  <si>
-    <t>Not Now:\ntracking feature won't work</t>
-  </si>
-  <si>
-    <t>Enable Background Location:\nALLOW ALL THE TIME</t>
-  </si>
-  <si>
-    <t>Включить фоновое местоположение:\nВСЕГДА РАЗРЕШАТЬ</t>
-  </si>
-  <si>
-    <t>Не сейчас:\nфункция отслеживания не будет работать</t>
-  </si>
-  <si>
     <t>Разрешение на фоновое местоположение</t>
   </si>
   <si>
-    <t>GPSSample записывает ваш маршрут (хлебные крошки) во время поездок между домохозяйствами и нанесения их на карту.\n\nЗапись начинается только после нажатия кнопки RECORD в приложении и останавливается после нажатия кнопки STOP.\n\nМестоположение собирается непрерывно во время записи, даже если приложение находится в фоновом режиме или ваше устройство заблокировано.\n\nДанные о вашем местоположении надежно хранятся на вашем устройстве и экспортируются только по вашему желанию.\n\nВы можете в любой момент отменить доступ к фоновому местоположению в настройках Android.</t>
-  </si>
-  <si>
-    <t>O GPSSample grava a sua rota (trilha de navegação) enquanto você se desloca entre residências e mapeia residências.\n\nA gravação só começa quando você toca no botão GRAVAR no aplicativo e para quando você toca no botão PARAR.\n\nA localização é coletada continuamente durante a gravação, mesmo que o aplicativo esteja em segundo plano ou o seu dispositivo esteja bloqueado.\n\nOs seus dados de localização são armazenados com segurança no seu dispositivo e só são exportados se você optar por fazê-lo.\n\nVocê pode revogar o acesso à localização em segundo plano a qualquer momento nas Definições do Android.</t>
-  </si>
-  <si>
-    <t>Ativar localização em segundo plano:\nPERMITIR SEMPRE</t>
-  </si>
-  <si>
-    <t>Agora não:\nA funcionalidade de rastreamento não funcionará</t>
-  </si>
-  <si>
     <t>Permissão de localização em segundo plano</t>
   </si>
   <si>
-    <t>Pas maintenant : \nla fonction de suivi ne fonctionnera pas</t>
-  </si>
-  <si>
     <t>Autorisation de localisation en arrière-plan</t>
   </si>
   <si>
     <t>Permiso de ubicación en segundo plano</t>
   </si>
   <si>
-    <t>Ahora no:\nla función de seguimiento no funcionará</t>
-  </si>
-  <si>
-    <t>Habilitar ubicación en segundo plano:\nPERMITIR SIEMPRE</t>
-  </si>
-  <si>
-    <t>GPSSample registra tu ruta (rastro de navegación) mientras te desplazas entre hogares y los mapeas.\n\nLa grabación solo comienza cuando pulsas el botón GRABAR en la aplicación y se detiene cuando pulsas el botón DETENER.\n\nLa ubicación se recopila de forma continua durante la grabación, incluso si la aplicación está en segundo plano o tu dispositivo está bloqueado.\n\nSus datos de ubicación se almacenan de forma segura en su dispositivo y solo se exportan si usted decide hacerlo.\n\nPuede revocar el acceso a la ubicación en segundo plano en cualquier momento en los ajustes de Android.</t>
-  </si>
-  <si>
-    <t>Itinatala ng GPSSample ang iyong ruta (breadcrumb trail) habang naglalakbay ka sa pagitan ng mga sambahayan at mga sambahayan sa mapa.\n\nNagsisimula lamang ang pagre-record kapag pinindot mo ang RECORD button sa app at humihinto sa pagre-record kapag pinindot mo ang STOP button.\n\nPatuloy na kinokolekta ang lokasyon habang nagre-record, kahit na nasa background ang app o naka-lock ang iyong device.\n\nLigtas na nakaimbak ang data ng iyong lokasyon sa iyong device at ine-export lamang kung pipiliin mong gawin ito.\n\nMaaari mong bawiin ang access sa lokasyon sa background anumang oras sa Mga Setting ng Android.</t>
-  </si>
-  <si>
-    <t>Paganahin ang Lokasyon sa Background:\nPAHINTUlutan SA LAHAT NG ORAS</t>
-  </si>
-  <si>
-    <t>Hindi Ngayon:\nhindi gagana ang feature na pagsubaybay</t>
-  </si>
-  <si>
     <t>Pahintulot sa Lokasyon sa Background</t>
   </si>
   <si>
@@ -10287,9 +10239,6 @@
     <t>Nanti: fitur pelacakan tidak akan berfungsi</t>
   </si>
   <si>
-    <t>GPSSample merekam rute Anda (jejak perjalanan) saat Anda bepergian antar rumah tangga dan memetakan rumah tangga.\n\nPerekaman hanya dimulai saat Anda mengetuk tombol REKAM di aplikasi dan berhenti merekam saat Anda mengetuk tombol BERHENTI.\n\nLokasi dikumpulkan terus menerus selama perekaman, bahkan jika aplikasi berada di latar belakang atau perangkat Anda terkunci.\n\nData lokasi Anda disimpan dengan aman di perangkat Anda dan hanya diekspor jika Anda memilih untuk melakukannya.\n\nAnda dapat mencabut akses lokasi latar belakang kapan saja di Pengaturan Android.</t>
-  </si>
-  <si>
     <t>enable_background_activity_title</t>
   </si>
   <si>
@@ -10299,18 +10248,12 @@
     <t>enable_background_activity_body</t>
   </si>
   <si>
-    <t>1. Tap the OPEN SETTINGS button\n2. Find GPSSample in the list.\n3. Enable ALLOW BACKGROUND ACTIVITY.\n4. Return to this app.</t>
-  </si>
-  <si>
     <t>open_settings</t>
   </si>
   <si>
     <t>Open Settings</t>
   </si>
   <si>
-    <t>1. Pulse el botón ABRIR CONFIGURACIÓN\n2. Busque GPSSample en la lista.\n3.Habilite PERMITIR ACTIVIDAD EN SEGUNDO PLANO.\n4. Vuelva a esta aplicación.</t>
-  </si>
-  <si>
     <t>Abrir configuración</t>
   </si>
   <si>
@@ -10320,45 +10263,30 @@
     <t>Ouvrir les paramètres</t>
   </si>
   <si>
-    <t>1. Appuyez sur le bouton OUVRIR LES PARAMÈTRES\n2. Recherchez GPSSample dans la liste.\n3. Activez AUTORISER L'ACTIVITÉ EN ARRIÈRE-PLAN.\n4. Revenez à cette application.</t>
-  </si>
-  <si>
     <t>Ativar atividade em segundo plano</t>
   </si>
   <si>
     <t>Abrir configurações</t>
   </si>
   <si>
-    <t>1. Toque no botão ABRIR CONFIGURAÇÕES \n2. Encontre GPSSample na lista.\n3. Ative PERMITIR ATIVIDADE EM SEGUNDO PLANO.\n4. Volte para este aplicativo.</t>
-  </si>
-  <si>
     <t>Включение фоновой активности</t>
   </si>
   <si>
     <t>Откройте настройки</t>
   </si>
   <si>
-    <t>1. Нажмите кнопку ОТКРЫТЬ НАСТРОЙКИ \n2. Найдите GPSSample в списке.\n3.Включите РАЗРЕШИТЬ ФОНОВУЮ АКТИВНОСТЬ.\n4. Вернитесь в это приложение.</t>
-  </si>
-  <si>
     <t>Aktifkan Aktivitas Latar Belakang</t>
   </si>
   <si>
     <t>Buka Pengaturan</t>
   </si>
   <si>
-    <t>1. Ketuk tombol BUKA PENGATURAN\n2. Temukan GPSSample dalam daftar.\n3. Aktifkan IZINKAN AKTIVITAS LATAR BELAKANG.\n4. Kembali ke aplikasi ini.</t>
-  </si>
-  <si>
     <t>Buksan ang Mga Setting</t>
   </si>
   <si>
     <t>Paganahin ang Aktibidad sa Background</t>
   </si>
   <si>
-    <t>1. Pindutin ang buton na BUKASIN ANG MGA SETTING\n2. Hanapin ang GPSSample sa listahan.\n3. Paganahin ang PAHINTULOT SA AKTIBIDAD SA BACKGROUND.\n4. Bumalik sa app na ito.</t>
-  </si>
-  <si>
     <t>تنظیمات</t>
   </si>
   <si>
@@ -12969,15 +12897,9 @@
     <t>ایا تاسو ډاډه یاست چې غواړئ نقشه پاکه کړئ؟</t>
   </si>
   <si>
-    <t>اوس نه:\nتعقیب به کار ونه کړي</t>
-  </si>
-  <si>
     <t>مجوز موقعیت مکانی پس‌زمینه</t>
   </si>
   <si>
-    <t>فعلاً نه:\nویژگی ردیابی کار نخواهد کرد</t>
-  </si>
-  <si>
     <t>note</t>
   </si>
   <si>
@@ -13237,9 +13159,6 @@
   </si>
   <si>
     <t>GPSSample::ps</t>
-  </si>
-  <si>
-    <t>GPSSample enregistre votre itinéraire (fil d\'Ariane) lorsque vous vous déplacez entre les foyers et cartographiez les foyers.\n\nL\'enregistrement ne commence que lorsque vous appuyez sur le bouton ENREGISTRER dans l\'application et s\'arrête lorsque vous appuyez sur le bouton ARRÊTER.\n\nLa localisation est collectée en continu pendant l\'enregistrement, même si l\'application est en arrière-plan ou si votre appareil est verrouillé.\n\nVos données de localisation sont stockées en toute sécurité sur votre appareil et ne sont exportées que si vous le souhaitez.\n\nVous pouvez révoquer l\'accès à la localisation en arrière-plan à tout moment dans les paramètres Android.</t>
   </si>
   <si>
     <t>password_error</t>
@@ -14229,20 +14148,107 @@
     <t>Data Collector: Navigates to sampled households and launches the survey.</t>
   </si>
   <si>
-    <t>Method descriptions:\n\nSimple Random Sample:\nEach household has an equal chance of being selected.\n\nCluster Sample (# of households):\nSelect a fixed number of households from each cluster.\n\nCluster Sample (% of households):\nSelect a percentage of households from each cluster.</t>
-  </si>
-  <si>
-    <t>Activer la localisation en arrière-plan :\nTOUJOURS AUTORISER</t>
-  </si>
-  <si>
     <t>Aktifkan Lokasi Latar Belakang:&amp;#10;IZINKAN SEPANJANG WAKTU</t>
+  </si>
+  <si>
+    <t>GPSSample records your route (breadcrumb trail) while you travel between households and map households._N__N_Recording starts only when you tap the RECORD button in the app and stops recording when you tap the STOP button._N__N_Location is collected continuously while recording, even if the app is in the background or your device is locked._N__N_Your location data is stored securely on your device and is only exported if you choose to do so._N__N_You can revoke background location access at any time in Android Settings.</t>
+  </si>
+  <si>
+    <t>GPSSample registra tu ruta (rastro de navegación) mientras te desplazas entre hogares y los mapeas._N__N_La grabación solo comienza cuando pulsas el botón GRABAR en la aplicación y se detiene cuando pulsas el botón DETENER._N__N_La ubicación se recopila de forma continua durante la grabación, incluso si la aplicación está en segundo plano o tu dispositivo está bloqueado._N__N_Sus datos de ubicación se almacenan de forma segura en su dispositivo y solo se exportan si usted decide hacerlo._N__N_Puede revocar el acceso a la ubicación en segundo plano en cualquier momento en los ajustes de Android.</t>
+  </si>
+  <si>
+    <t>GPSSample enregistre votre itinéraire (fil d\'Ariane) lorsque vous vous déplacez entre les foyers et cartographiez les foyers._N__N_L\'enregistrement ne commence que lorsque vous appuyez sur le bouton ENREGISTRER dans l\'application et s\'arrête lorsque vous appuyez sur le bouton ARRÊTER._N__N_La localisation est collectée en continu pendant l\'enregistrement, même si l\'application est en arrière-plan ou si votre appareil est verrouillé._N__N_Vos données de localisation sont stockées en toute sécurité sur votre appareil et ne sont exportées que si vous le souhaitez._N__N_Vous pouvez révoquer l\'accès à la localisation en arrière-plan à tout moment dans les paramètres Android.</t>
+  </si>
+  <si>
+    <t>O GPSSample grava a sua rota (trilha de navegação) enquanto você se desloca entre residências e mapeia residências._N__N_A gravação só começa quando você toca no botão GRAVAR no aplicativo e para quando você toca no botão PARAR._N__N_A localização é coletada continuamente durante a gravação, mesmo que o aplicativo esteja em segundo plano ou o seu dispositivo esteja bloqueado._N__N_Os seus dados de localização são armazenados com segurança no seu dispositivo e só são exportados se você optar por fazê-lo._N__N_Você pode revogar o acesso à localização em segundo plano a qualquer momento nas Definições do Android.</t>
+  </si>
+  <si>
+    <t>GPSSample записывает ваш маршрут (хлебные крошки) во время поездок между домохозяйствами и нанесения их на карту._N__N_Запись начинается только после нажатия кнопки RECORD в приложении и останавливается после нажатия кнопки STOP._N__N_Местоположение собирается непрерывно во время записи, даже если приложение находится в фоновом режиме или ваше устройство заблокировано._N__N_Данные о вашем местоположении надежно хранятся на вашем устройстве и экспортируются только по вашему желанию._N__N_Вы можете в любой момент отменить доступ к фоновому местоположению в настройках Android.</t>
+  </si>
+  <si>
+    <t>GPSSample merekam rute Anda (jejak perjalanan) saat Anda bepergian antar rumah tangga dan memetakan rumah tangga._N__N_Perekaman hanya dimulai saat Anda mengetuk tombol REKAM di aplikasi dan berhenti merekam saat Anda mengetuk tombol BERHENTI._N__N_Lokasi dikumpulkan terus menerus selama perekaman, bahkan jika aplikasi berada di latar belakang atau perangkat Anda terkunci._N__N_Data lokasi Anda disimpan dengan aman di perangkat Anda dan hanya diekspor jika Anda memilih untuk melakukannya._N__N_Anda dapat mencabut akses lokasi latar belakang kapan saja di Pengaturan Android.</t>
+  </si>
+  <si>
+    <t>Itinatala ng GPSSample ang iyong ruta (breadcrumb trail) habang naglalakbay ka sa pagitan ng mga sambahayan at mga sambahayan sa mapa._N__N_Nagsisimula lamang ang pagre-record kapag pinindot mo ang RECORD button sa app at humihinto sa pagre-record kapag pinindot mo ang STOP button._N__N_Patuloy na kinokolekta ang lokasyon habang nagre-record, kahit na nasa background ang app o naka-lock ang iyong device._N__N_Ligtas na nakaimbak ang data ng iyong lokasyon sa iyong device at ine-export lamang kung pipiliin mong gawin ito._N__N_Maaari mong bawiin ang access sa lokasyon sa background anumang oras sa Mga Setting ng Android.</t>
+  </si>
+  <si>
+    <t>Enable Background Location:_N_ALLOW ALL THE TIME</t>
+  </si>
+  <si>
+    <t>Habilitar ubicación en segundo plano:_N_PERMITIR SIEMPRE</t>
+  </si>
+  <si>
+    <t>Activer la localisation en arrière-plan :_N_TOUJOURS AUTORISER</t>
+  </si>
+  <si>
+    <t>Ativar localização em segundo plano:_N_PERMITIR SEMPRE</t>
+  </si>
+  <si>
+    <t>Включить фоновое местоположение:_N_ВСЕГДА РАЗРЕШАТЬ</t>
+  </si>
+  <si>
+    <t>Paganahin ang Lokasyon sa Background:_N_PAHINTUlutan SA LAHAT NG ORAS</t>
+  </si>
+  <si>
+    <t>Not Now:_N_tracking feature won't work</t>
+  </si>
+  <si>
+    <t>Ahora no:_N_la función de seguimiento no funcionará</t>
+  </si>
+  <si>
+    <t>Pas maintenant : _N_la fonction de suivi ne fonctionnera pas</t>
+  </si>
+  <si>
+    <t>Agora não:_N_A funcionalidade de rastreamento não funcionará</t>
+  </si>
+  <si>
+    <t>Не сейчас:_N_функция отслеживания не будет работать</t>
+  </si>
+  <si>
+    <t>Hindi Ngayon:_N_hindi gagana ang feature na pagsubaybay</t>
+  </si>
+  <si>
+    <t>فعلاً نه:_N_ویژگی ردیابی کار نخواهد کرد</t>
+  </si>
+  <si>
+    <t>اوس نه:_N_تعقیب به کار ونه کړي</t>
+  </si>
+  <si>
+    <t>1. Tap the OPEN SETTINGS button_N_2. Find GPSSample in the list._N_3. Enable ALLOW BACKGROUND ACTIVITY._N_4. Return to this app.</t>
+  </si>
+  <si>
+    <t>1. Pulse el botón ABRIR CONFIGURACIÓN_N_2. Busque GPSSample en la lista._N_3.Habilite PERMITIR ACTIVIDAD EN SEGUNDO PLANO._N_4. Vuelva a esta aplicación.</t>
+  </si>
+  <si>
+    <t>1. Appuyez sur le bouton OUVRIR LES PARAMÈTRES_N_2. Recherchez GPSSample dans la liste._N_3. Activez AUTORISER L'ACTIVITÉ EN ARRIÈRE-PLAN._N_4. Revenez à cette application.</t>
+  </si>
+  <si>
+    <t>1. Toque no botão ABRIR CONFIGURAÇÕES _N_2. Encontre GPSSample na lista._N_3. Ative PERMITIR ATIVIDADE EM SEGUNDO PLANO._N_4. Volte para este aplicativo.</t>
+  </si>
+  <si>
+    <t>1. Нажмите кнопку ОТКРЫТЬ НАСТРОЙКИ _N_2. Найдите GPSSample в списке._N_3.Включите РАЗРЕШИТЬ ФОНОВУЮ АКТИВНОСТЬ._N_4. Вернитесь в это приложение.</t>
+  </si>
+  <si>
+    <t>1. Ketuk tombol BUKA PENGATURAN_N_2. Temukan GPSSample dalam daftar._N_3. Aktifkan IZINKAN AKTIVITAS LATAR BELAKANG._N_4. Kembali ke aplikasi ini.</t>
+  </si>
+  <si>
+    <t>1. Pindutin ang buton na BUKASIN ANG MGA SETTING_N_2. Hanapin ang GPSSample sa listahan._N_3. Paganahin ang PAHINTULOT SA AKTIBIDAD SA BACKGROUND._N_4. Bumalik sa app na ito.</t>
+  </si>
+  <si>
+    <t>Method descriptions:_N__N_Simple Random Sample:_N_Each household has an equal chance of being selected._N__N_Cluster Sample (# of households):_N_Select a fixed number of households from each cluster._N__N_Cluster Sample (% of households):_N_Select a percentage of households from each cluster.</t>
+  </si>
+  <si>
+    <t>enter_forgot_pin_question</t>
+  </si>
+  <si>
+    <t>Enter the forgot PIN question</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -14342,6 +14348,12 @@
       <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF067D17"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -14423,7 +14435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -14483,6 +14495,7 @@
       <alignment horizontal="right" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14999,7 +15012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD3E6CC-854C-5841-9577-D3ADD2982DB6}">
-  <dimension ref="A1:J513"/>
+  <dimension ref="A1:J514"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="28.33203125" customWidth="1"/>
@@ -15040,10 +15053,10 @@
         <v>2884</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>4388</v>
+        <v>4362</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>4389</v>
+        <v>4363</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -15072,10 +15085,10 @@
         <v>2885</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>3430</v>
+        <v>3406</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>3430</v>
+        <v>3406</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -15104,10 +15117,10 @@
         <v>2886</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>3431</v>
+        <v>3407</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>3873</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -15136,10 +15149,10 @@
         <v>2887</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>3432</v>
+        <v>3408</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>3874</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -15168,10 +15181,10 @@
         <v>2888</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>3433</v>
+        <v>3409</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>3875</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -15200,10 +15213,10 @@
         <v>33</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>3434</v>
+        <v>3410</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>3434</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -15232,10 +15245,10 @@
         <v>2889</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>3435</v>
+        <v>3411</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>3876</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -15264,10 +15277,10 @@
         <v>2890</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>3436</v>
+        <v>3412</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>3877</v>
+        <v>3853</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -15296,10 +15309,10 @@
         <v>2891</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>3437</v>
+        <v>3413</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>3881</v>
+        <v>3857</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -15328,10 +15341,10 @@
         <v>2892</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>3438</v>
+        <v>3414</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>3880</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -15360,10 +15373,10 @@
         <v>2893</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>3439</v>
+        <v>3415</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>3878</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -15392,10 +15405,10 @@
         <v>2894</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>3440</v>
+        <v>3416</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>3879</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -15424,10 +15437,10 @@
         <v>2895</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>3441</v>
+        <v>3417</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>3910</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -15456,10 +15469,10 @@
         <v>2896</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>3442</v>
+        <v>3418</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>3911</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -15488,10 +15501,10 @@
         <v>2897</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>3443</v>
+        <v>3419</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>3912</v>
+        <v>3888</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -15520,10 +15533,10 @@
         <v>2898</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>3444</v>
+        <v>3420</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>3913</v>
+        <v>3889</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -15552,10 +15565,10 @@
         <v>2899</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>3445</v>
+        <v>3421</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>3914</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -15584,10 +15597,10 @@
         <v>2900</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>3446</v>
+        <v>3422</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>3915</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -15616,10 +15629,10 @@
         <v>2901</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>3447</v>
+        <v>3423</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>3916</v>
+        <v>3892</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -15648,10 +15661,10 @@
         <v>2902</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>3448</v>
+        <v>3424</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>3917</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -15680,10 +15693,10 @@
         <v>2903</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>3449</v>
+        <v>3425</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>3918</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -15712,10 +15725,10 @@
         <v>2904</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>3450</v>
+        <v>3426</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>3923</v>
+        <v>3899</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -15744,10 +15757,10 @@
         <v>2905</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>3451</v>
+        <v>3427</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>3922</v>
+        <v>3898</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -15776,10 +15789,10 @@
         <v>2906</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>3452</v>
+        <v>3428</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>3921</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -15808,10 +15821,10 @@
         <v>2907</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>3453</v>
+        <v>3429</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>3920</v>
+        <v>3896</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -15840,10 +15853,10 @@
         <v>2908</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>3454</v>
+        <v>3430</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>3919</v>
+        <v>3895</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -15872,10 +15885,10 @@
         <v>2909</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>3455</v>
+        <v>3431</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>3906</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -15904,10 +15917,10 @@
         <v>2910</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>3456</v>
+        <v>3432</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>3907</v>
+        <v>3883</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -15936,10 +15949,10 @@
         <v>175</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>3457</v>
+        <v>3433</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>3908</v>
+        <v>3884</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -15968,10 +15981,10 @@
         <v>2911</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>3458</v>
+        <v>3434</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>3458</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -16000,10 +16013,10 @@
         <v>2912</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>3459</v>
+        <v>3435</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>3909</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -16032,10 +16045,10 @@
         <v>190</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>3460</v>
+        <v>3436</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>3882</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -16064,10 +16077,10 @@
         <v>196</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>3461</v>
+        <v>3437</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>3883</v>
+        <v>3859</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -16096,10 +16109,10 @@
         <v>2913</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>3462</v>
+        <v>3438</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>3884</v>
+        <v>3860</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -16128,10 +16141,10 @@
         <v>2914</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>3463</v>
+        <v>3439</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>3885</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -16160,10 +16173,10 @@
         <v>2916</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>3464</v>
+        <v>3440</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>3886</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -16192,10 +16205,10 @@
         <v>2915</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>3465</v>
+        <v>3441</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>3887</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -16224,10 +16237,10 @@
         <v>2917</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>3466</v>
+        <v>3442</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>3888</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -16256,10 +16269,10 @@
         <v>2918</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>3467</v>
+        <v>3443</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>3889</v>
+        <v>3865</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -16288,10 +16301,10 @@
         <v>238</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>3468</v>
+        <v>3444</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>3468</v>
+        <v>3444</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -16320,10 +16333,10 @@
         <v>2919</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>3469</v>
+        <v>3445</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>3469</v>
+        <v>3445</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -16352,10 +16365,10 @@
         <v>249</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>3470</v>
+        <v>3446</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>3890</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -16384,10 +16397,10 @@
         <v>255</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>3471</v>
+        <v>3447</v>
       </c>
       <c r="J43" s="14" t="s">
-        <v>3891</v>
+        <v>3867</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -16416,10 +16429,10 @@
         <v>2920</v>
       </c>
       <c r="I44" s="14" t="s">
-        <v>3472</v>
+        <v>3448</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>3892</v>
+        <v>3868</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -16448,10 +16461,10 @@
         <v>267</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>3473</v>
+        <v>3449</v>
       </c>
       <c r="J45" s="14" t="s">
-        <v>3893</v>
+        <v>3869</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -16480,10 +16493,10 @@
         <v>2921</v>
       </c>
       <c r="I46" s="14" t="s">
-        <v>3434</v>
+        <v>3410</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>3434</v>
+        <v>3410</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -16512,10 +16525,10 @@
         <v>2922</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>3474</v>
+        <v>3450</v>
       </c>
       <c r="J47" s="14" t="s">
-        <v>3894</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -16544,10 +16557,10 @@
         <v>284</v>
       </c>
       <c r="I48" s="14" t="s">
-        <v>3475</v>
+        <v>3451</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>3895</v>
+        <v>3871</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -16576,10 +16589,10 @@
         <v>289</v>
       </c>
       <c r="I49" s="14" t="s">
-        <v>3476</v>
+        <v>3452</v>
       </c>
       <c r="J49" s="14" t="s">
-        <v>3896</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -16608,10 +16621,10 @@
         <v>2923</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>3477</v>
+        <v>3453</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>3430</v>
+        <v>3406</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -16640,10 +16653,10 @@
         <v>2924</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>3478</v>
+        <v>3454</v>
       </c>
       <c r="J51" s="14" t="s">
-        <v>3897</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -16672,10 +16685,10 @@
         <v>2925</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>3479</v>
+        <v>3455</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>3898</v>
+        <v>3874</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -16704,10 +16717,10 @@
         <v>314</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>3480</v>
+        <v>3456</v>
       </c>
       <c r="J53" s="14" t="s">
-        <v>3899</v>
+        <v>3875</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -16736,10 +16749,10 @@
         <v>2926</v>
       </c>
       <c r="I54" s="14" t="s">
-        <v>3481</v>
+        <v>3457</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>3900</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -16768,10 +16781,10 @@
         <v>2927</v>
       </c>
       <c r="I55" s="14" t="s">
-        <v>3482</v>
+        <v>3458</v>
       </c>
       <c r="J55" s="14" t="s">
-        <v>3901</v>
+        <v>3877</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -16800,10 +16813,10 @@
         <v>2928</v>
       </c>
       <c r="I56" s="14" t="s">
-        <v>3483</v>
+        <v>3459</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>3902</v>
+        <v>3878</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -16832,10 +16845,10 @@
         <v>2929</v>
       </c>
       <c r="I57" s="14" t="s">
-        <v>3484</v>
+        <v>3460</v>
       </c>
       <c r="J57" s="14" t="s">
-        <v>3903</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -16864,10 +16877,10 @@
         <v>2930</v>
       </c>
       <c r="I58" s="14" t="s">
-        <v>3485</v>
+        <v>3461</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>3904</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -16896,10 +16909,10 @@
         <v>2931</v>
       </c>
       <c r="I59" s="14" t="s">
-        <v>3486</v>
+        <v>3462</v>
       </c>
       <c r="J59" s="14" t="s">
-        <v>3905</v>
+        <v>3881</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -16928,10 +16941,10 @@
         <v>2932</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>3487</v>
+        <v>3463</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>3982</v>
+        <v>3958</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -16960,10 +16973,10 @@
         <v>2933</v>
       </c>
       <c r="I61" s="14" t="s">
-        <v>3488</v>
+        <v>3464</v>
       </c>
       <c r="J61" s="14" t="s">
-        <v>3983</v>
+        <v>3959</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -16992,10 +17005,10 @@
         <v>2934</v>
       </c>
       <c r="I62" s="14" t="s">
-        <v>3489</v>
+        <v>3465</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>3984</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -17024,10 +17037,10 @@
         <v>2935</v>
       </c>
       <c r="I63" s="14" t="s">
-        <v>3490</v>
+        <v>3466</v>
       </c>
       <c r="J63" s="14" t="s">
-        <v>3985</v>
+        <v>3961</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -17041,7 +17054,7 @@
         <v>372</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>4545</v>
+        <v>4518</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>373</v>
@@ -17056,10 +17069,10 @@
         <v>2936</v>
       </c>
       <c r="I64" s="14" t="s">
-        <v>3491</v>
+        <v>3467</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>3986</v>
+        <v>3962</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -17088,10 +17101,10 @@
         <v>2937</v>
       </c>
       <c r="I65" s="14" t="s">
-        <v>3492</v>
+        <v>3468</v>
       </c>
       <c r="J65" s="14" t="s">
-        <v>3987</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -17120,10 +17133,10 @@
         <v>2939</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>3493</v>
+        <v>3469</v>
       </c>
       <c r="J66" s="14" t="s">
-        <v>3988</v>
+        <v>3964</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -17152,10 +17165,10 @@
         <v>2938</v>
       </c>
       <c r="I67" s="14" t="s">
-        <v>3494</v>
+        <v>3470</v>
       </c>
       <c r="J67" s="14" t="s">
-        <v>3989</v>
+        <v>3965</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -17184,10 +17197,10 @@
         <v>2940</v>
       </c>
       <c r="I68" s="14" t="s">
-        <v>3495</v>
+        <v>3471</v>
       </c>
       <c r="J68" s="14" t="s">
-        <v>3990</v>
+        <v>3966</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -17216,10 +17229,10 @@
         <v>2941</v>
       </c>
       <c r="I69" s="14" t="s">
-        <v>3496</v>
+        <v>3472</v>
       </c>
       <c r="J69" s="14" t="s">
-        <v>3991</v>
+        <v>3967</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -17248,10 +17261,10 @@
         <v>2942</v>
       </c>
       <c r="I70" s="14" t="s">
-        <v>3497</v>
+        <v>3473</v>
       </c>
       <c r="J70" s="14" t="s">
-        <v>3992</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -17280,10 +17293,10 @@
         <v>2943</v>
       </c>
       <c r="I71" s="14" t="s">
-        <v>3498</v>
+        <v>3474</v>
       </c>
       <c r="J71" s="14" t="s">
-        <v>3993</v>
+        <v>3969</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -17312,10 +17325,10 @@
         <v>2944</v>
       </c>
       <c r="I72" s="14" t="s">
-        <v>3499</v>
+        <v>3475</v>
       </c>
       <c r="J72" s="14" t="s">
-        <v>3966</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -17344,10 +17357,10 @@
         <v>2946</v>
       </c>
       <c r="I73" s="14" t="s">
-        <v>3500</v>
+        <v>3476</v>
       </c>
       <c r="J73" s="14" t="s">
-        <v>3967</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -17376,10 +17389,10 @@
         <v>2945</v>
       </c>
       <c r="I74" s="14" t="s">
-        <v>3431</v>
+        <v>3407</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>3873</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -17408,10 +17421,10 @@
         <v>2947</v>
       </c>
       <c r="I75" s="14" t="s">
-        <v>3501</v>
+        <v>3477</v>
       </c>
       <c r="J75" s="14" t="s">
-        <v>3968</v>
+        <v>3944</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -17440,10 +17453,10 @@
         <v>2948</v>
       </c>
       <c r="I76" s="14" t="s">
-        <v>3502</v>
+        <v>3478</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>3969</v>
+        <v>3945</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -17472,10 +17485,10 @@
         <v>2949</v>
       </c>
       <c r="I77" s="14" t="s">
-        <v>3503</v>
+        <v>3479</v>
       </c>
       <c r="J77" s="14" t="s">
-        <v>3970</v>
+        <v>3946</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -17504,10 +17517,10 @@
         <v>450</v>
       </c>
       <c r="I78" s="14" t="s">
-        <v>3504</v>
+        <v>3480</v>
       </c>
       <c r="J78" s="14" t="s">
-        <v>3971</v>
+        <v>3947</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -17536,10 +17549,10 @@
         <v>2950</v>
       </c>
       <c r="I79" s="14" t="s">
-        <v>3505</v>
+        <v>3481</v>
       </c>
       <c r="J79" s="14" t="s">
-        <v>3972</v>
+        <v>3948</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -17568,10 +17581,10 @@
         <v>2951</v>
       </c>
       <c r="I80" s="14" t="s">
-        <v>3506</v>
+        <v>3482</v>
       </c>
       <c r="J80" s="14" t="s">
-        <v>3973</v>
+        <v>3949</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -17600,10 +17613,10 @@
         <v>2952</v>
       </c>
       <c r="I81" s="14" t="s">
-        <v>3507</v>
+        <v>3483</v>
       </c>
       <c r="J81" s="14" t="s">
-        <v>3974</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -17632,10 +17645,10 @@
         <v>2953</v>
       </c>
       <c r="I82" s="14" t="s">
-        <v>3508</v>
+        <v>3484</v>
       </c>
       <c r="J82" s="14" t="s">
-        <v>3975</v>
+        <v>3951</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -17664,10 +17677,10 @@
         <v>2954</v>
       </c>
       <c r="I83" s="14" t="s">
-        <v>3509</v>
+        <v>3485</v>
       </c>
       <c r="J83" s="14" t="s">
-        <v>3976</v>
+        <v>3952</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -17696,10 +17709,10 @@
         <v>2955</v>
       </c>
       <c r="I84" s="14" t="s">
-        <v>3510</v>
+        <v>3486</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>3977</v>
+        <v>3953</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -17728,10 +17741,10 @@
         <v>2956</v>
       </c>
       <c r="I85" s="14" t="s">
-        <v>3511</v>
+        <v>3487</v>
       </c>
       <c r="J85" s="14" t="s">
-        <v>3978</v>
+        <v>3954</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -17760,10 +17773,10 @@
         <v>2957</v>
       </c>
       <c r="I86" s="14" t="s">
-        <v>3512</v>
+        <v>3488</v>
       </c>
       <c r="J86" s="14" t="s">
-        <v>3979</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -17792,10 +17805,10 @@
         <v>2958</v>
       </c>
       <c r="I87" s="14" t="s">
-        <v>3513</v>
+        <v>3489</v>
       </c>
       <c r="J87" s="14" t="s">
-        <v>3980</v>
+        <v>3956</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -17824,10 +17837,10 @@
         <v>2959</v>
       </c>
       <c r="I88" s="14" t="s">
-        <v>3514</v>
+        <v>3490</v>
       </c>
       <c r="J88" s="14" t="s">
-        <v>3981</v>
+        <v>3957</v>
       </c>
     </row>
     <row r="89" spans="1:10">
@@ -17856,10 +17869,10 @@
         <v>2960</v>
       </c>
       <c r="I89" s="14" t="s">
-        <v>3515</v>
+        <v>3491</v>
       </c>
       <c r="J89" s="14" t="s">
-        <v>4039</v>
+        <v>4015</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -17888,10 +17901,10 @@
         <v>2961</v>
       </c>
       <c r="I90" s="14" t="s">
-        <v>3516</v>
+        <v>3492</v>
       </c>
       <c r="J90" s="14" t="s">
-        <v>4040</v>
+        <v>4016</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -17920,10 +17933,10 @@
         <v>2962</v>
       </c>
       <c r="I91" s="14" t="s">
-        <v>3517</v>
+        <v>3493</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>4041</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -17952,10 +17965,10 @@
         <v>2963</v>
       </c>
       <c r="I92" s="14" t="s">
-        <v>3518</v>
+        <v>3494</v>
       </c>
       <c r="J92" s="14" t="s">
-        <v>4042</v>
+        <v>4018</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -17984,10 +17997,10 @@
         <v>2964</v>
       </c>
       <c r="I93" s="14" t="s">
-        <v>3519</v>
+        <v>3495</v>
       </c>
       <c r="J93" s="14" t="s">
-        <v>4036</v>
+        <v>4012</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -18016,10 +18029,10 @@
         <v>2965</v>
       </c>
       <c r="I94" s="14" t="s">
-        <v>3520</v>
+        <v>3496</v>
       </c>
       <c r="J94" s="14" t="s">
-        <v>4037</v>
+        <v>4013</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -18048,10 +18061,10 @@
         <v>2966</v>
       </c>
       <c r="I95" s="14" t="s">
-        <v>3521</v>
+        <v>3497</v>
       </c>
       <c r="J95" s="14" t="s">
-        <v>4038</v>
+        <v>4014</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -18080,10 +18093,10 @@
         <v>2967</v>
       </c>
       <c r="I96" s="14" t="s">
-        <v>3522</v>
+        <v>3498</v>
       </c>
       <c r="J96" s="14" t="s">
-        <v>4035</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -18112,10 +18125,10 @@
         <v>2968</v>
       </c>
       <c r="I97" s="14" t="s">
-        <v>3523</v>
+        <v>3499</v>
       </c>
       <c r="J97" s="14" t="s">
-        <v>4033</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -18144,10 +18157,10 @@
         <v>2969</v>
       </c>
       <c r="I98" s="14" t="s">
-        <v>3524</v>
+        <v>3500</v>
       </c>
       <c r="J98" s="14" t="s">
-        <v>4034</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -18176,10 +18189,10 @@
         <v>2970</v>
       </c>
       <c r="I99" s="14" t="s">
-        <v>3525</v>
+        <v>3501</v>
       </c>
       <c r="J99" s="14" t="s">
-        <v>4032</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -18208,10 +18221,10 @@
         <v>2971</v>
       </c>
       <c r="I100" s="14" t="s">
-        <v>3526</v>
+        <v>3502</v>
       </c>
       <c r="J100" s="14" t="s">
-        <v>4031</v>
+        <v>4007</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -18240,10 +18253,10 @@
         <v>2972</v>
       </c>
       <c r="I101" s="14" t="s">
-        <v>3527</v>
+        <v>3503</v>
       </c>
       <c r="J101" s="14" t="s">
-        <v>4029</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="102" spans="1:10">
@@ -18272,10 +18285,10 @@
         <v>2973</v>
       </c>
       <c r="I102" s="14" t="s">
-        <v>3528</v>
+        <v>3504</v>
       </c>
       <c r="J102" s="14" t="s">
-        <v>4030</v>
+        <v>4006</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -18304,10 +18317,10 @@
         <v>2974</v>
       </c>
       <c r="I103" s="14" t="s">
-        <v>3529</v>
+        <v>3505</v>
       </c>
       <c r="J103" s="14" t="s">
-        <v>4043</v>
+        <v>4019</v>
       </c>
     </row>
     <row r="104" spans="1:10">
@@ -18336,10 +18349,10 @@
         <v>2975</v>
       </c>
       <c r="I104" s="14" t="s">
-        <v>3530</v>
+        <v>3506</v>
       </c>
       <c r="J104" s="14" t="s">
-        <v>4044</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="105" spans="1:10">
@@ -18368,10 +18381,10 @@
         <v>2976</v>
       </c>
       <c r="I105" s="14" t="s">
-        <v>3531</v>
+        <v>3507</v>
       </c>
       <c r="J105" s="14" t="s">
-        <v>4045</v>
+        <v>4021</v>
       </c>
     </row>
     <row r="106" spans="1:10">
@@ -18400,10 +18413,10 @@
         <v>2977</v>
       </c>
       <c r="I106" s="14" t="s">
-        <v>3532</v>
+        <v>3508</v>
       </c>
       <c r="J106" s="14" t="s">
-        <v>4046</v>
+        <v>4022</v>
       </c>
     </row>
     <row r="107" spans="1:10">
@@ -18432,10 +18445,10 @@
         <v>2978</v>
       </c>
       <c r="I107" s="14" t="s">
-        <v>3533</v>
+        <v>3509</v>
       </c>
       <c r="J107" s="14" t="s">
-        <v>4047</v>
+        <v>4023</v>
       </c>
     </row>
     <row r="108" spans="1:10">
@@ -18464,10 +18477,10 @@
         <v>2979</v>
       </c>
       <c r="I108" s="14" t="s">
-        <v>3534</v>
+        <v>3510</v>
       </c>
       <c r="J108" s="14" t="s">
-        <v>3534</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="109" spans="1:10">
@@ -18496,10 +18509,10 @@
         <v>2980</v>
       </c>
       <c r="I109" s="14" t="s">
-        <v>3535</v>
+        <v>3511</v>
       </c>
       <c r="J109" s="14" t="s">
-        <v>4115</v>
+        <v>4091</v>
       </c>
     </row>
     <row r="110" spans="1:10">
@@ -18528,10 +18541,10 @@
         <v>2981</v>
       </c>
       <c r="I110" s="14" t="s">
-        <v>3536</v>
+        <v>3512</v>
       </c>
       <c r="J110" s="14" t="s">
-        <v>4116</v>
+        <v>4092</v>
       </c>
     </row>
     <row r="111" spans="1:10">
@@ -18560,10 +18573,10 @@
         <v>2982</v>
       </c>
       <c r="I111" s="14" t="s">
-        <v>3537</v>
+        <v>3513</v>
       </c>
       <c r="J111" s="14" t="s">
-        <v>4117</v>
+        <v>4093</v>
       </c>
     </row>
     <row r="112" spans="1:10">
@@ -18592,10 +18605,10 @@
         <v>2983</v>
       </c>
       <c r="I112" s="14" t="s">
-        <v>3538</v>
+        <v>3514</v>
       </c>
       <c r="J112" s="14" t="s">
-        <v>4118</v>
+        <v>4094</v>
       </c>
     </row>
     <row r="113" spans="1:10">
@@ -18624,10 +18637,10 @@
         <v>2984</v>
       </c>
       <c r="I113" s="14" t="s">
-        <v>3539</v>
+        <v>3515</v>
       </c>
       <c r="J113" s="14" t="s">
-        <v>4119</v>
+        <v>4095</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -18656,10 +18669,10 @@
         <v>2985</v>
       </c>
       <c r="I114" s="14" t="s">
-        <v>3430</v>
+        <v>3406</v>
       </c>
       <c r="J114" s="14" t="s">
-        <v>3430</v>
+        <v>3406</v>
       </c>
     </row>
     <row r="115" spans="1:10">
@@ -18688,10 +18701,10 @@
         <v>2986</v>
       </c>
       <c r="I115" s="14" t="s">
-        <v>3540</v>
+        <v>3516</v>
       </c>
       <c r="J115" s="14" t="s">
-        <v>4167</v>
+        <v>4143</v>
       </c>
     </row>
     <row r="116" spans="1:10">
@@ -18720,10 +18733,10 @@
         <v>2987</v>
       </c>
       <c r="I116" s="14" t="s">
-        <v>3541</v>
+        <v>3517</v>
       </c>
       <c r="J116" s="14" t="s">
-        <v>4168</v>
+        <v>4144</v>
       </c>
     </row>
     <row r="117" spans="1:10">
@@ -18752,10 +18765,10 @@
         <v>2988</v>
       </c>
       <c r="I117" s="14" t="s">
-        <v>3542</v>
+        <v>3518</v>
       </c>
       <c r="J117" s="14" t="s">
-        <v>4169</v>
+        <v>4145</v>
       </c>
     </row>
     <row r="118" spans="1:10">
@@ -18784,10 +18797,10 @@
         <v>2989</v>
       </c>
       <c r="I118" s="14" t="s">
-        <v>3543</v>
+        <v>3519</v>
       </c>
       <c r="J118" s="14" t="s">
-        <v>4170</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="119" spans="1:10">
@@ -18816,10 +18829,10 @@
         <v>2990</v>
       </c>
       <c r="I119" s="14" t="s">
-        <v>3544</v>
+        <v>3520</v>
       </c>
       <c r="J119" s="14" t="s">
-        <v>4171</v>
+        <v>4147</v>
       </c>
     </row>
     <row r="120" spans="1:10">
@@ -18848,10 +18861,10 @@
         <v>2991</v>
       </c>
       <c r="I120" s="14" t="s">
-        <v>3545</v>
+        <v>3521</v>
       </c>
       <c r="J120" s="14" t="s">
-        <v>4172</v>
+        <v>4148</v>
       </c>
     </row>
     <row r="121" spans="1:10">
@@ -18880,10 +18893,10 @@
         <v>2992</v>
       </c>
       <c r="I121" s="14" t="s">
-        <v>3546</v>
+        <v>3522</v>
       </c>
       <c r="J121" s="14" t="s">
-        <v>4173</v>
+        <v>4149</v>
       </c>
     </row>
     <row r="122" spans="1:10">
@@ -18912,10 +18925,10 @@
         <v>2993</v>
       </c>
       <c r="I122" s="14" t="s">
-        <v>3547</v>
+        <v>3523</v>
       </c>
       <c r="J122" s="14" t="s">
-        <v>4174</v>
+        <v>4150</v>
       </c>
     </row>
     <row r="123" spans="1:10">
@@ -18944,10 +18957,10 @@
         <v>3004</v>
       </c>
       <c r="I123" s="14" t="s">
-        <v>3548</v>
+        <v>3524</v>
       </c>
       <c r="J123" s="14" t="s">
-        <v>4175</v>
+        <v>4151</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -18976,10 +18989,10 @@
         <v>3005</v>
       </c>
       <c r="I124" s="14" t="s">
-        <v>3549</v>
+        <v>3525</v>
       </c>
       <c r="J124" s="14" t="s">
-        <v>4176</v>
+        <v>4152</v>
       </c>
     </row>
     <row r="125" spans="1:10">
@@ -19008,10 +19021,10 @@
         <v>3006</v>
       </c>
       <c r="I125" s="14" t="s">
-        <v>3550</v>
+        <v>3526</v>
       </c>
       <c r="J125" s="14" t="s">
-        <v>4176</v>
+        <v>4152</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -19040,10 +19053,10 @@
         <v>3007</v>
       </c>
       <c r="I126" s="14" t="s">
-        <v>3551</v>
+        <v>3527</v>
       </c>
       <c r="J126" s="14" t="s">
-        <v>3878</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="127" spans="1:10">
@@ -19072,10 +19085,10 @@
         <v>3000</v>
       </c>
       <c r="I127" s="14" t="s">
-        <v>3552</v>
+        <v>3528</v>
       </c>
       <c r="J127" s="14" t="s">
-        <v>4177</v>
+        <v>4153</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -19104,10 +19117,10 @@
         <v>3001</v>
       </c>
       <c r="I128" s="14" t="s">
-        <v>3553</v>
+        <v>3529</v>
       </c>
       <c r="J128" s="14" t="s">
-        <v>4178</v>
+        <v>4154</v>
       </c>
     </row>
     <row r="129" spans="1:10">
@@ -19136,10 +19149,10 @@
         <v>3002</v>
       </c>
       <c r="I129" s="14" t="s">
-        <v>3554</v>
+        <v>3530</v>
       </c>
       <c r="J129" s="14" t="s">
-        <v>4179</v>
+        <v>4155</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -19168,10 +19181,10 @@
         <v>3003</v>
       </c>
       <c r="I130" s="14" t="s">
-        <v>3555</v>
+        <v>3531</v>
       </c>
       <c r="J130" s="14" t="s">
-        <v>4180</v>
+        <v>4156</v>
       </c>
     </row>
     <row r="131" spans="1:10">
@@ -19200,10 +19213,10 @@
         <v>785</v>
       </c>
       <c r="I131" s="14" t="s">
-        <v>3556</v>
+        <v>3532</v>
       </c>
       <c r="J131" s="14" t="s">
-        <v>4197</v>
+        <v>4173</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -19232,10 +19245,10 @@
         <v>2994</v>
       </c>
       <c r="I132" s="14" t="s">
-        <v>3557</v>
+        <v>3533</v>
       </c>
       <c r="J132" s="14" t="s">
-        <v>4198</v>
+        <v>4174</v>
       </c>
     </row>
     <row r="133" spans="1:10">
@@ -19264,10 +19277,10 @@
         <v>2995</v>
       </c>
       <c r="I133" s="14" t="s">
-        <v>3558</v>
+        <v>3534</v>
       </c>
       <c r="J133" s="14" t="s">
-        <v>4199</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -19296,10 +19309,10 @@
         <v>2996</v>
       </c>
       <c r="I134" s="14" t="s">
-        <v>3559</v>
+        <v>3535</v>
       </c>
       <c r="J134" s="14" t="s">
-        <v>4200</v>
+        <v>4176</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -19328,10 +19341,10 @@
         <v>2997</v>
       </c>
       <c r="I135" s="14" t="s">
-        <v>3560</v>
+        <v>3536</v>
       </c>
       <c r="J135" s="14" t="s">
-        <v>4201</v>
+        <v>4177</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -19360,10 +19373,10 @@
         <v>2998</v>
       </c>
       <c r="I136" s="14" t="s">
-        <v>3561</v>
+        <v>3537</v>
       </c>
       <c r="J136" s="14" t="s">
-        <v>4185</v>
+        <v>4161</v>
       </c>
     </row>
     <row r="137" spans="1:10">
@@ -19392,10 +19405,10 @@
         <v>2999</v>
       </c>
       <c r="I137" s="14" t="s">
-        <v>3562</v>
+        <v>3538</v>
       </c>
       <c r="J137" s="14" t="s">
-        <v>4186</v>
+        <v>4162</v>
       </c>
     </row>
     <row r="138" spans="1:10">
@@ -19424,10 +19437,10 @@
         <v>3010</v>
       </c>
       <c r="I138" s="14" t="s">
-        <v>3563</v>
+        <v>3539</v>
       </c>
       <c r="J138" s="14" t="s">
-        <v>4187</v>
+        <v>4163</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -19456,10 +19469,10 @@
         <v>3009</v>
       </c>
       <c r="I139" s="14" t="s">
-        <v>3564</v>
+        <v>3540</v>
       </c>
       <c r="J139" s="14" t="s">
-        <v>4188</v>
+        <v>4164</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -19488,10 +19501,10 @@
         <v>3008</v>
       </c>
       <c r="I140" s="14" t="s">
-        <v>3565</v>
+        <v>3541</v>
       </c>
       <c r="J140" s="14" t="s">
-        <v>4189</v>
+        <v>4165</v>
       </c>
     </row>
     <row r="141" spans="1:10">
@@ -19520,10 +19533,10 @@
         <v>3014</v>
       </c>
       <c r="I141" s="14" t="s">
-        <v>3566</v>
+        <v>3542</v>
       </c>
       <c r="J141" s="14" t="s">
-        <v>4190</v>
+        <v>4166</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -19552,10 +19565,10 @@
         <v>3004</v>
       </c>
       <c r="I142" s="14" t="s">
-        <v>3567</v>
+        <v>3543</v>
       </c>
       <c r="J142" s="14" t="s">
-        <v>4191</v>
+        <v>4167</v>
       </c>
     </row>
     <row r="143" spans="1:10">
@@ -19584,10 +19597,10 @@
         <v>3013</v>
       </c>
       <c r="I143" s="14" t="s">
-        <v>3568</v>
+        <v>3544</v>
       </c>
       <c r="J143" s="14" t="s">
-        <v>4192</v>
+        <v>4168</v>
       </c>
     </row>
     <row r="144" spans="1:10">
@@ -19616,10 +19629,10 @@
         <v>3012</v>
       </c>
       <c r="I144" s="14" t="s">
-        <v>3569</v>
+        <v>3545</v>
       </c>
       <c r="J144" s="14" t="s">
-        <v>4193</v>
+        <v>4169</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -19648,10 +19661,10 @@
         <v>3011</v>
       </c>
       <c r="I145" s="14" t="s">
-        <v>3570</v>
+        <v>3546</v>
       </c>
       <c r="J145" s="14" t="s">
-        <v>4194</v>
+        <v>4170</v>
       </c>
     </row>
     <row r="146" spans="1:10">
@@ -19680,10 +19693,10 @@
         <v>3015</v>
       </c>
       <c r="I146" s="14" t="s">
-        <v>3571</v>
+        <v>3547</v>
       </c>
       <c r="J146" s="14" t="s">
-        <v>4195</v>
+        <v>4171</v>
       </c>
     </row>
     <row r="147" spans="1:10">
@@ -19712,10 +19725,10 @@
         <v>3017</v>
       </c>
       <c r="I147" s="14" t="s">
-        <v>3572</v>
+        <v>3548</v>
       </c>
       <c r="J147" s="14" t="s">
-        <v>4196</v>
+        <v>4172</v>
       </c>
     </row>
     <row r="148" spans="1:10">
@@ -19744,10 +19757,10 @@
         <v>3016</v>
       </c>
       <c r="I148" s="14" t="s">
-        <v>3573</v>
+        <v>3549</v>
       </c>
       <c r="J148" s="14" t="s">
-        <v>4181</v>
+        <v>4157</v>
       </c>
     </row>
     <row r="149" spans="1:10">
@@ -19776,10 +19789,10 @@
         <v>3018</v>
       </c>
       <c r="I149" s="14" t="s">
-        <v>3574</v>
+        <v>3550</v>
       </c>
       <c r="J149" s="14" t="s">
-        <v>4182</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="150" spans="1:10">
@@ -19808,10 +19821,10 @@
         <v>3019</v>
       </c>
       <c r="I150" s="14" t="s">
-        <v>3575</v>
+        <v>3551</v>
       </c>
       <c r="J150" s="14" t="s">
-        <v>4183</v>
+        <v>4159</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -19840,10 +19853,10 @@
         <v>3020</v>
       </c>
       <c r="I151" s="14" t="s">
-        <v>3576</v>
+        <v>3552</v>
       </c>
       <c r="J151" s="14" t="s">
-        <v>4184</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -19872,10 +19885,10 @@
         <v>3027</v>
       </c>
       <c r="I152" s="14" t="s">
-        <v>3577</v>
+        <v>3553</v>
       </c>
       <c r="J152" s="14" t="s">
-        <v>4120</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -19904,10 +19917,10 @@
         <v>3028</v>
       </c>
       <c r="I153" s="14" t="s">
-        <v>3578</v>
+        <v>3554</v>
       </c>
       <c r="J153" s="14" t="s">
-        <v>4121</v>
+        <v>4097</v>
       </c>
     </row>
     <row r="154" spans="1:10">
@@ -19936,10 +19949,10 @@
         <v>3029</v>
       </c>
       <c r="I154" s="14" t="s">
-        <v>3579</v>
+        <v>3555</v>
       </c>
       <c r="J154" s="14" t="s">
-        <v>4122</v>
+        <v>4098</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -19968,10 +19981,10 @@
         <v>3030</v>
       </c>
       <c r="I155" s="14" t="s">
-        <v>3580</v>
+        <v>3556</v>
       </c>
       <c r="J155" s="14" t="s">
-        <v>4123</v>
+        <v>4099</v>
       </c>
     </row>
     <row r="156" spans="1:10">
@@ -20000,10 +20013,10 @@
         <v>3031</v>
       </c>
       <c r="I156" s="14" t="s">
-        <v>3581</v>
+        <v>3557</v>
       </c>
       <c r="J156" s="14" t="s">
-        <v>4124</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -20032,10 +20045,10 @@
         <v>3032</v>
       </c>
       <c r="I157" s="14" t="s">
-        <v>3582</v>
+        <v>3558</v>
       </c>
       <c r="J157" s="14" t="s">
-        <v>4125</v>
+        <v>4101</v>
       </c>
     </row>
     <row r="158" spans="1:10">
@@ -20064,10 +20077,10 @@
         <v>3033</v>
       </c>
       <c r="I158" s="14" t="s">
-        <v>3583</v>
+        <v>3559</v>
       </c>
       <c r="J158" s="14" t="s">
-        <v>4126</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="159" spans="1:10">
@@ -20096,10 +20109,10 @@
         <v>3034</v>
       </c>
       <c r="I159" s="14" t="s">
-        <v>3584</v>
+        <v>3560</v>
       </c>
       <c r="J159" s="14" t="s">
-        <v>4127</v>
+        <v>4103</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -20128,10 +20141,10 @@
         <v>3035</v>
       </c>
       <c r="I160" s="14" t="s">
-        <v>3585</v>
+        <v>3561</v>
       </c>
       <c r="J160" s="14" t="s">
-        <v>4128</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -20160,10 +20173,10 @@
         <v>3036</v>
       </c>
       <c r="I161" s="14" t="s">
-        <v>3586</v>
+        <v>3562</v>
       </c>
       <c r="J161" s="14" t="s">
-        <v>4129</v>
+        <v>4105</v>
       </c>
     </row>
     <row r="162" spans="1:10">
@@ -20192,10 +20205,10 @@
         <v>3037</v>
       </c>
       <c r="I162" s="14" t="s">
-        <v>3587</v>
+        <v>3563</v>
       </c>
       <c r="J162" s="14" t="s">
-        <v>4130</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -20224,10 +20237,10 @@
         <v>3038</v>
       </c>
       <c r="I163" s="14" t="s">
-        <v>3588</v>
+        <v>3564</v>
       </c>
       <c r="J163" s="14" t="s">
-        <v>4131</v>
+        <v>4107</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -20256,10 +20269,10 @@
         <v>3039</v>
       </c>
       <c r="I164" s="14" t="s">
-        <v>3589</v>
+        <v>3565</v>
       </c>
       <c r="J164" s="14" t="s">
-        <v>4097</v>
+        <v>4073</v>
       </c>
     </row>
     <row r="165" spans="1:10">
@@ -20288,10 +20301,10 @@
         <v>3040</v>
       </c>
       <c r="I165" s="14" t="s">
-        <v>3590</v>
+        <v>3566</v>
       </c>
       <c r="J165" s="14" t="s">
-        <v>4132</v>
+        <v>4108</v>
       </c>
     </row>
     <row r="166" spans="1:10">
@@ -20320,10 +20333,10 @@
         <v>3041</v>
       </c>
       <c r="I166" s="14" t="s">
-        <v>3591</v>
+        <v>3567</v>
       </c>
       <c r="J166" s="14" t="s">
-        <v>4133</v>
+        <v>4109</v>
       </c>
     </row>
     <row r="167" spans="1:10">
@@ -20352,10 +20365,10 @@
         <v>3026</v>
       </c>
       <c r="I167" s="14" t="s">
-        <v>3592</v>
+        <v>3568</v>
       </c>
       <c r="J167" s="14" t="s">
-        <v>4134</v>
+        <v>4110</v>
       </c>
     </row>
     <row r="168" spans="1:10">
@@ -20384,10 +20397,10 @@
         <v>3025</v>
       </c>
       <c r="I168" s="14" t="s">
-        <v>3593</v>
+        <v>3569</v>
       </c>
       <c r="J168" s="14" t="s">
-        <v>4135</v>
+        <v>4111</v>
       </c>
     </row>
     <row r="169" spans="1:10">
@@ -20416,10 +20429,10 @@
         <v>3024</v>
       </c>
       <c r="I169" s="14" t="s">
-        <v>3594</v>
+        <v>3570</v>
       </c>
       <c r="J169" s="14" t="s">
-        <v>4048</v>
+        <v>4024</v>
       </c>
     </row>
     <row r="170" spans="1:10">
@@ -20448,10 +20461,10 @@
         <v>3023</v>
       </c>
       <c r="I170" s="14" t="s">
-        <v>3595</v>
+        <v>3571</v>
       </c>
       <c r="J170" s="14" t="s">
-        <v>3469</v>
+        <v>3445</v>
       </c>
     </row>
     <row r="171" spans="1:10">
@@ -20480,10 +20493,10 @@
         <v>1045</v>
       </c>
       <c r="I171" s="14" t="s">
-        <v>3596</v>
+        <v>3572</v>
       </c>
       <c r="J171" s="14" t="s">
-        <v>4049</v>
+        <v>4025</v>
       </c>
     </row>
     <row r="172" spans="1:10">
@@ -20512,10 +20525,10 @@
         <v>1051</v>
       </c>
       <c r="I172" s="14" t="s">
-        <v>3597</v>
+        <v>3573</v>
       </c>
       <c r="J172" s="14" t="s">
-        <v>4050</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="173" spans="1:10">
@@ -20544,10 +20557,10 @@
         <v>1057</v>
       </c>
       <c r="I173" s="14" t="s">
-        <v>3598</v>
+        <v>3574</v>
       </c>
       <c r="J173" s="14" t="s">
-        <v>4051</v>
+        <v>4027</v>
       </c>
     </row>
     <row r="174" spans="1:10">
@@ -20576,10 +20589,10 @@
         <v>3022</v>
       </c>
       <c r="I174" s="14" t="s">
-        <v>3599</v>
+        <v>3575</v>
       </c>
       <c r="J174" s="14" t="s">
-        <v>4052</v>
+        <v>4028</v>
       </c>
     </row>
     <row r="175" spans="1:10">
@@ -20608,10 +20621,10 @@
         <v>3021</v>
       </c>
       <c r="I175" s="14" t="s">
-        <v>3600</v>
+        <v>3576</v>
       </c>
       <c r="J175" s="14" t="s">
-        <v>4136</v>
+        <v>4112</v>
       </c>
     </row>
     <row r="176" spans="1:10">
@@ -20640,10 +20653,10 @@
         <v>3042</v>
       </c>
       <c r="I176" s="14" t="s">
-        <v>3601</v>
+        <v>3577</v>
       </c>
       <c r="J176" s="14" t="s">
-        <v>4137</v>
+        <v>4113</v>
       </c>
     </row>
     <row r="177" spans="1:10">
@@ -20672,10 +20685,10 @@
         <v>3043</v>
       </c>
       <c r="I177" s="14" t="s">
-        <v>3602</v>
+        <v>3578</v>
       </c>
       <c r="J177" s="14" t="s">
-        <v>4138</v>
+        <v>4114</v>
       </c>
     </row>
     <row r="178" spans="1:10">
@@ -20704,10 +20717,10 @@
         <v>3035</v>
       </c>
       <c r="I178" s="14" t="s">
-        <v>3585</v>
+        <v>3561</v>
       </c>
       <c r="J178" s="14" t="s">
-        <v>4128</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="179" spans="1:10">
@@ -20736,10 +20749,10 @@
         <v>3044</v>
       </c>
       <c r="I179" s="14" t="s">
-        <v>3634</v>
+        <v>3610</v>
       </c>
       <c r="J179" s="14" t="s">
-        <v>4139</v>
+        <v>4115</v>
       </c>
     </row>
     <row r="180" spans="1:10">
@@ -20768,10 +20781,10 @@
         <v>3045</v>
       </c>
       <c r="I180" s="14" t="s">
-        <v>3635</v>
+        <v>3611</v>
       </c>
       <c r="J180" s="14" t="s">
-        <v>4140</v>
+        <v>4116</v>
       </c>
     </row>
     <row r="181" spans="1:10">
@@ -20800,10 +20813,10 @@
         <v>3046</v>
       </c>
       <c r="I181" s="14" t="s">
-        <v>3636</v>
+        <v>3612</v>
       </c>
       <c r="J181" s="14" t="s">
-        <v>4141</v>
+        <v>4117</v>
       </c>
     </row>
     <row r="182" spans="1:10">
@@ -20832,10 +20845,10 @@
         <v>3047</v>
       </c>
       <c r="I182" s="14" t="s">
-        <v>3637</v>
+        <v>3613</v>
       </c>
       <c r="J182" s="14" t="s">
-        <v>4142</v>
+        <v>4118</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -20864,10 +20877,10 @@
         <v>3048</v>
       </c>
       <c r="I183" s="14" t="s">
-        <v>3638</v>
+        <v>3614</v>
       </c>
       <c r="J183" s="14" t="s">
-        <v>4143</v>
+        <v>4119</v>
       </c>
     </row>
     <row r="184" spans="1:10">
@@ -20896,10 +20909,10 @@
         <v>3049</v>
       </c>
       <c r="I184" s="14" t="s">
-        <v>3640</v>
+        <v>3616</v>
       </c>
       <c r="J184" s="14" t="s">
-        <v>4053</v>
+        <v>4029</v>
       </c>
     </row>
     <row r="185" spans="1:10">
@@ -20928,10 +20941,10 @@
         <v>3050</v>
       </c>
       <c r="I185" s="14" t="s">
-        <v>3641</v>
+        <v>3617</v>
       </c>
       <c r="J185" s="14" t="s">
-        <v>4054</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="186" spans="1:10">
@@ -20960,10 +20973,10 @@
         <v>3051</v>
       </c>
       <c r="I186" s="14" t="s">
-        <v>3639</v>
+        <v>3615</v>
       </c>
       <c r="J186" s="14" t="s">
-        <v>4055</v>
+        <v>4031</v>
       </c>
     </row>
     <row r="187" spans="1:10">
@@ -20992,10 +21005,10 @@
         <v>3052</v>
       </c>
       <c r="I187" s="14" t="s">
-        <v>3686</v>
+        <v>3662</v>
       </c>
       <c r="J187" s="14" t="s">
-        <v>4057</v>
+        <v>4033</v>
       </c>
     </row>
     <row r="188" spans="1:10">
@@ -21024,10 +21037,10 @@
         <v>3069</v>
       </c>
       <c r="I188" s="14" t="s">
-        <v>3687</v>
+        <v>3663</v>
       </c>
       <c r="J188" s="14" t="s">
-        <v>4056</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="189" spans="1:10">
@@ -21056,10 +21069,10 @@
         <v>3068</v>
       </c>
       <c r="I189" s="14" t="s">
-        <v>3688</v>
+        <v>3664</v>
       </c>
       <c r="J189" s="14" t="s">
-        <v>4058</v>
+        <v>4034</v>
       </c>
     </row>
     <row r="190" spans="1:10">
@@ -21088,10 +21101,10 @@
         <v>3070</v>
       </c>
       <c r="I190" s="14" t="s">
-        <v>3689</v>
+        <v>3665</v>
       </c>
       <c r="J190" s="14" t="s">
-        <v>4059</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="191" spans="1:10">
@@ -21120,10 +21133,10 @@
         <v>2906</v>
       </c>
       <c r="I191" s="14" t="s">
-        <v>3690</v>
+        <v>3666</v>
       </c>
       <c r="J191" s="14" t="s">
-        <v>4060</v>
+        <v>4036</v>
       </c>
     </row>
     <row r="192" spans="1:10">
@@ -21152,10 +21165,10 @@
         <v>3071</v>
       </c>
       <c r="I192" s="14" t="s">
-        <v>3691</v>
+        <v>3667</v>
       </c>
       <c r="J192" s="14" t="s">
-        <v>4061</v>
+        <v>4037</v>
       </c>
     </row>
     <row r="193" spans="1:10">
@@ -21184,10 +21197,10 @@
         <v>3072</v>
       </c>
       <c r="I193" s="14" t="s">
-        <v>3692</v>
+        <v>3668</v>
       </c>
       <c r="J193" s="14" t="s">
-        <v>4062</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="194" spans="1:10">
@@ -21216,10 +21229,10 @@
         <v>3073</v>
       </c>
       <c r="I194" s="14" t="s">
-        <v>3693</v>
+        <v>3669</v>
       </c>
       <c r="J194" s="14" t="s">
-        <v>4063</v>
+        <v>4039</v>
       </c>
     </row>
     <row r="195" spans="1:10">
@@ -21248,10 +21261,10 @@
         <v>3074</v>
       </c>
       <c r="I195" s="14" t="s">
-        <v>3694</v>
+        <v>3670</v>
       </c>
       <c r="J195" s="14" t="s">
-        <v>4064</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="196" spans="1:10">
@@ -21280,10 +21293,10 @@
         <v>3053</v>
       </c>
       <c r="I196" s="14" t="s">
-        <v>3695</v>
+        <v>3671</v>
       </c>
       <c r="J196" s="14" t="s">
-        <v>4065</v>
+        <v>4041</v>
       </c>
     </row>
     <row r="197" spans="1:10">
@@ -21312,10 +21325,10 @@
         <v>3054</v>
       </c>
       <c r="I197" s="14" t="s">
-        <v>3696</v>
+        <v>3672</v>
       </c>
       <c r="J197" s="14" t="s">
-        <v>4066</v>
+        <v>4042</v>
       </c>
     </row>
     <row r="198" spans="1:10">
@@ -21344,10 +21357,10 @@
         <v>1206</v>
       </c>
       <c r="I198" s="14" t="s">
-        <v>3697</v>
+        <v>3673</v>
       </c>
       <c r="J198" s="14" t="s">
-        <v>4067</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="199" spans="1:10">
@@ -21376,10 +21389,10 @@
         <v>3055</v>
       </c>
       <c r="I199" s="14" t="s">
-        <v>3698</v>
+        <v>3674</v>
       </c>
       <c r="J199" s="14" t="s">
-        <v>4068</v>
+        <v>4044</v>
       </c>
     </row>
     <row r="200" spans="1:10">
@@ -21408,10 +21421,10 @@
         <v>3056</v>
       </c>
       <c r="I200" s="14" t="s">
-        <v>3699</v>
+        <v>3675</v>
       </c>
       <c r="J200" s="14" t="s">
-        <v>4069</v>
+        <v>4045</v>
       </c>
     </row>
     <row r="201" spans="1:10">
@@ -21440,10 +21453,10 @@
         <v>3057</v>
       </c>
       <c r="I201" s="14" t="s">
-        <v>3700</v>
+        <v>3676</v>
       </c>
       <c r="J201" s="14" t="s">
-        <v>4070</v>
+        <v>4046</v>
       </c>
     </row>
     <row r="202" spans="1:10">
@@ -21472,10 +21485,10 @@
         <v>3058</v>
       </c>
       <c r="I202" s="14" t="s">
-        <v>3607</v>
+        <v>3583</v>
       </c>
       <c r="J202" s="14" t="s">
-        <v>3933</v>
+        <v>3909</v>
       </c>
     </row>
     <row r="203" spans="1:10">
@@ -21504,10 +21517,10 @@
         <v>3059</v>
       </c>
       <c r="I203" s="14" t="s">
-        <v>3701</v>
+        <v>3677</v>
       </c>
       <c r="J203" s="14" t="s">
-        <v>4071</v>
+        <v>4047</v>
       </c>
     </row>
     <row r="204" spans="1:10">
@@ -21536,10 +21549,10 @@
         <v>3060</v>
       </c>
       <c r="I204" s="14" t="s">
-        <v>3702</v>
+        <v>3678</v>
       </c>
       <c r="J204" s="14" t="s">
-        <v>4072</v>
+        <v>4048</v>
       </c>
     </row>
     <row r="205" spans="1:10">
@@ -21568,10 +21581,10 @@
         <v>3061</v>
       </c>
       <c r="I205" s="14" t="s">
-        <v>3703</v>
+        <v>3679</v>
       </c>
       <c r="J205" s="14" t="s">
-        <v>4073</v>
+        <v>4049</v>
       </c>
     </row>
     <row r="206" spans="1:10">
@@ -21600,10 +21613,10 @@
         <v>1256</v>
       </c>
       <c r="I206" s="14" t="s">
-        <v>3704</v>
+        <v>3680</v>
       </c>
       <c r="J206" s="14" t="s">
-        <v>3704</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="207" spans="1:10">
@@ -21632,10 +21645,10 @@
         <v>3067</v>
       </c>
       <c r="I207" s="14" t="s">
-        <v>3705</v>
+        <v>3681</v>
       </c>
       <c r="J207" s="14" t="s">
-        <v>4074</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="208" spans="1:10">
@@ -21664,10 +21677,10 @@
         <v>2911</v>
       </c>
       <c r="I208" s="14" t="s">
-        <v>3458</v>
+        <v>3434</v>
       </c>
       <c r="J208" s="14" t="s">
-        <v>3458</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="209" spans="1:10">
@@ -21696,10 +21709,10 @@
         <v>175</v>
       </c>
       <c r="I209" s="14" t="s">
-        <v>3706</v>
+        <v>3682</v>
       </c>
       <c r="J209" s="14" t="s">
-        <v>3457</v>
+        <v>3433</v>
       </c>
     </row>
     <row r="210" spans="1:10">
@@ -21728,10 +21741,10 @@
         <v>190</v>
       </c>
       <c r="I210" s="14" t="s">
-        <v>3707</v>
+        <v>3683</v>
       </c>
       <c r="J210" s="14" t="s">
-        <v>3882</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="211" spans="1:10">
@@ -21760,10 +21773,10 @@
         <v>3066</v>
       </c>
       <c r="I211" s="14" t="s">
-        <v>3709</v>
+        <v>3685</v>
       </c>
       <c r="J211" s="14" t="s">
-        <v>4075</v>
+        <v>4051</v>
       </c>
     </row>
     <row r="212" spans="1:10">
@@ -21792,10 +21805,10 @@
         <v>3065</v>
       </c>
       <c r="I212" s="14" t="s">
-        <v>3710</v>
+        <v>3686</v>
       </c>
       <c r="J212" s="14" t="s">
-        <v>4076</v>
+        <v>4052</v>
       </c>
     </row>
     <row r="213" spans="1:10">
@@ -21824,10 +21837,10 @@
         <v>3064</v>
       </c>
       <c r="I213" s="14" t="s">
-        <v>3711</v>
+        <v>3687</v>
       </c>
       <c r="J213" s="14" t="s">
-        <v>4077</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="214" spans="1:10">
@@ -21856,10 +21869,10 @@
         <v>3063</v>
       </c>
       <c r="I214" s="14" t="s">
-        <v>3708</v>
+        <v>3684</v>
       </c>
       <c r="J214" s="14" t="s">
-        <v>4146</v>
+        <v>4122</v>
       </c>
     </row>
     <row r="215" spans="1:10">
@@ -21888,10 +21901,10 @@
         <v>3062</v>
       </c>
       <c r="I215" s="14" t="s">
-        <v>3712</v>
+        <v>3688</v>
       </c>
       <c r="J215" s="14" t="s">
-        <v>4147</v>
+        <v>4123</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -21920,10 +21933,10 @@
         <v>3217</v>
       </c>
       <c r="I216" s="14" t="s">
-        <v>3713</v>
+        <v>3689</v>
       </c>
       <c r="J216" s="14" t="s">
-        <v>4148</v>
+        <v>4124</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -21952,10 +21965,10 @@
         <v>3218</v>
       </c>
       <c r="I217" s="14" t="s">
-        <v>3714</v>
+        <v>3690</v>
       </c>
       <c r="J217" s="14" t="s">
-        <v>4149</v>
+        <v>4125</v>
       </c>
     </row>
     <row r="218" spans="1:10">
@@ -21984,10 +21997,10 @@
         <v>2912</v>
       </c>
       <c r="I218" s="14" t="s">
-        <v>3459</v>
+        <v>3435</v>
       </c>
       <c r="J218" s="14" t="s">
-        <v>3909</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="219" spans="1:10">
@@ -22016,10 +22029,10 @@
         <v>196</v>
       </c>
       <c r="I219" s="14" t="s">
-        <v>3715</v>
+        <v>3691</v>
       </c>
       <c r="J219" s="14" t="s">
-        <v>4150</v>
+        <v>4126</v>
       </c>
     </row>
     <row r="220" spans="1:10">
@@ -22048,10 +22061,10 @@
         <v>3219</v>
       </c>
       <c r="I220" s="14" t="s">
-        <v>3716</v>
+        <v>3692</v>
       </c>
       <c r="J220" s="14" t="s">
-        <v>4151</v>
+        <v>4127</v>
       </c>
     </row>
     <row r="221" spans="1:10">
@@ -22080,10 +22093,10 @@
         <v>3220</v>
       </c>
       <c r="I221" s="14" t="s">
-        <v>3717</v>
+        <v>3693</v>
       </c>
       <c r="J221" s="14" t="s">
-        <v>3717</v>
+        <v>3693</v>
       </c>
     </row>
     <row r="222" spans="1:10">
@@ -22112,10 +22125,10 @@
         <v>249</v>
       </c>
       <c r="I222" s="14" t="s">
-        <v>3470</v>
+        <v>3446</v>
       </c>
       <c r="J222" s="14" t="s">
-        <v>3890</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="223" spans="1:10">
@@ -22144,10 +22157,10 @@
         <v>255</v>
       </c>
       <c r="I223" s="14" t="s">
-        <v>3471</v>
+        <v>3447</v>
       </c>
       <c r="J223" s="14" t="s">
-        <v>3891</v>
+        <v>3867</v>
       </c>
     </row>
     <row r="224" spans="1:10">
@@ -22176,10 +22189,10 @@
         <v>2920</v>
       </c>
       <c r="I224" s="14" t="s">
-        <v>3472</v>
+        <v>3448</v>
       </c>
       <c r="J224" s="14" t="s">
-        <v>4144</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="225" spans="1:10">
@@ -22208,10 +22221,10 @@
         <v>267</v>
       </c>
       <c r="I225" s="14" t="s">
-        <v>3473</v>
+        <v>3449</v>
       </c>
       <c r="J225" s="14" t="s">
-        <v>4145</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="226" spans="1:10">
@@ -22240,10 +22253,10 @@
         <v>3231</v>
       </c>
       <c r="I226" s="14" t="s">
-        <v>3718</v>
+        <v>3694</v>
       </c>
       <c r="J226" s="14" t="s">
-        <v>4078</v>
+        <v>4054</v>
       </c>
     </row>
     <row r="227" spans="1:10">
@@ -22272,10 +22285,10 @@
         <v>3232</v>
       </c>
       <c r="I227" s="14" t="s">
-        <v>3719</v>
+        <v>3695</v>
       </c>
       <c r="J227" s="14" t="s">
-        <v>4079</v>
+        <v>4055</v>
       </c>
     </row>
     <row r="228" spans="1:10">
@@ -22304,10 +22317,10 @@
         <v>3233</v>
       </c>
       <c r="I228" s="14" t="s">
-        <v>3720</v>
+        <v>3696</v>
       </c>
       <c r="J228" s="14" t="s">
-        <v>4080</v>
+        <v>4056</v>
       </c>
     </row>
     <row r="229" spans="1:10">
@@ -22336,10 +22349,10 @@
         <v>2913</v>
       </c>
       <c r="I229" s="14" t="s">
-        <v>3721</v>
+        <v>3697</v>
       </c>
       <c r="J229" s="14" t="s">
-        <v>3884</v>
+        <v>3860</v>
       </c>
     </row>
     <row r="230" spans="1:10">
@@ -22368,10 +22381,10 @@
         <v>2914</v>
       </c>
       <c r="I230" s="14" t="s">
-        <v>3722</v>
+        <v>3698</v>
       </c>
       <c r="J230" s="14" t="s">
-        <v>3885</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="231" spans="1:10">
@@ -22400,10 +22413,10 @@
         <v>2916</v>
       </c>
       <c r="I231" s="14" t="s">
-        <v>3464</v>
+        <v>3440</v>
       </c>
       <c r="J231" s="14" t="s">
-        <v>3886</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="232" spans="1:10">
@@ -22432,10 +22445,10 @@
         <v>2915</v>
       </c>
       <c r="I232" s="14" t="s">
-        <v>3465</v>
+        <v>3441</v>
       </c>
       <c r="J232" s="14" t="s">
-        <v>3887</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="233" spans="1:10">
@@ -22464,10 +22477,10 @@
         <v>2917</v>
       </c>
       <c r="I233" s="14" t="s">
-        <v>3466</v>
+        <v>3442</v>
       </c>
       <c r="J233" s="14" t="s">
-        <v>3888</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="234" spans="1:10">
@@ -22496,10 +22509,10 @@
         <v>3238</v>
       </c>
       <c r="I234" s="14" t="s">
-        <v>3723</v>
+        <v>3699</v>
       </c>
       <c r="J234" s="14" t="s">
-        <v>4081</v>
+        <v>4057</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -22528,10 +22541,10 @@
         <v>3237</v>
       </c>
       <c r="I235" s="14" t="s">
-        <v>3727</v>
+        <v>3703</v>
       </c>
       <c r="J235" s="14" t="s">
-        <v>4082</v>
+        <v>4058</v>
       </c>
     </row>
     <row r="236" spans="1:10">
@@ -22560,10 +22573,10 @@
         <v>3236</v>
       </c>
       <c r="I236" s="14" t="s">
-        <v>3726</v>
+        <v>3702</v>
       </c>
       <c r="J236" s="14" t="s">
-        <v>4083</v>
+        <v>4059</v>
       </c>
     </row>
     <row r="237" spans="1:10">
@@ -22592,10 +22605,10 @@
         <v>3235</v>
       </c>
       <c r="I237" s="14" t="s">
-        <v>3725</v>
+        <v>3701</v>
       </c>
       <c r="J237" s="14" t="s">
-        <v>4084</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="238" spans="1:10">
@@ -22624,10 +22637,10 @@
         <v>3234</v>
       </c>
       <c r="I238" s="14" t="s">
-        <v>3724</v>
+        <v>3700</v>
       </c>
       <c r="J238" s="14" t="s">
-        <v>4085</v>
+        <v>4061</v>
       </c>
     </row>
     <row r="239" spans="1:10">
@@ -22656,10 +22669,10 @@
         <v>3273</v>
       </c>
       <c r="I239" s="14" t="s">
-        <v>3728</v>
+        <v>3704</v>
       </c>
       <c r="J239" s="14" t="s">
-        <v>4158</v>
+        <v>4134</v>
       </c>
     </row>
     <row r="240" spans="1:10">
@@ -22688,10 +22701,10 @@
         <v>3274</v>
       </c>
       <c r="I240" s="14" t="s">
-        <v>3729</v>
+        <v>3705</v>
       </c>
       <c r="J240" s="14" t="s">
-        <v>3934</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="241" spans="1:10">
@@ -22720,10 +22733,10 @@
         <v>3275</v>
       </c>
       <c r="I241" s="14" t="s">
-        <v>3730</v>
+        <v>3706</v>
       </c>
       <c r="J241" s="14" t="s">
-        <v>4159</v>
+        <v>4135</v>
       </c>
     </row>
     <row r="242" spans="1:10">
@@ -22752,10 +22765,10 @@
         <v>3276</v>
       </c>
       <c r="I242" s="14" t="s">
-        <v>3731</v>
+        <v>3707</v>
       </c>
       <c r="J242" s="14" t="s">
-        <v>4160</v>
+        <v>4136</v>
       </c>
     </row>
     <row r="243" spans="1:10">
@@ -22784,10 +22797,10 @@
         <v>3277</v>
       </c>
       <c r="I243" s="14" t="s">
-        <v>3786</v>
+        <v>3762</v>
       </c>
       <c r="J243" s="14" t="s">
-        <v>4162</v>
+        <v>4138</v>
       </c>
     </row>
     <row r="244" spans="1:10">
@@ -22816,10 +22829,10 @@
         <v>3278</v>
       </c>
       <c r="I244" s="14" t="s">
-        <v>3785</v>
+        <v>3761</v>
       </c>
       <c r="J244" s="14" t="s">
-        <v>4161</v>
+        <v>4137</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -22848,10 +22861,10 @@
         <v>3239</v>
       </c>
       <c r="I245" s="14" t="s">
-        <v>3767</v>
+        <v>3743</v>
       </c>
       <c r="J245" s="14" t="s">
-        <v>4163</v>
+        <v>4139</v>
       </c>
     </row>
     <row r="246" spans="1:10">
@@ -22880,10 +22893,10 @@
         <v>3240</v>
       </c>
       <c r="I246" s="14" t="s">
-        <v>3768</v>
+        <v>3744</v>
       </c>
       <c r="J246" s="14" t="s">
-        <v>4164</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="247" spans="1:10">
@@ -22912,10 +22925,10 @@
         <v>3241</v>
       </c>
       <c r="I247" s="14" t="s">
-        <v>3769</v>
+        <v>3745</v>
       </c>
       <c r="J247" s="14" t="s">
-        <v>4165</v>
+        <v>4141</v>
       </c>
     </row>
     <row r="248" spans="1:10">
@@ -22944,10 +22957,10 @@
         <v>3242</v>
       </c>
       <c r="I248" s="14" t="s">
-        <v>3770</v>
+        <v>3746</v>
       </c>
       <c r="J248" s="14" t="s">
-        <v>4166</v>
+        <v>4142</v>
       </c>
     </row>
     <row r="249" spans="1:10">
@@ -22976,10 +22989,10 @@
         <v>3243</v>
       </c>
       <c r="I249" s="14" t="s">
-        <v>3771</v>
+        <v>3747</v>
       </c>
       <c r="J249" s="14" t="s">
-        <v>4209</v>
+        <v>4185</v>
       </c>
     </row>
     <row r="250" spans="1:10">
@@ -23008,10 +23021,10 @@
         <v>3244</v>
       </c>
       <c r="I250" s="14" t="s">
-        <v>3772</v>
+        <v>3748</v>
       </c>
       <c r="J250" s="14" t="s">
-        <v>4208</v>
+        <v>4184</v>
       </c>
     </row>
     <row r="251" spans="1:10">
@@ -23040,10 +23053,10 @@
         <v>3221</v>
       </c>
       <c r="I251" s="14" t="s">
-        <v>3773</v>
+        <v>3749</v>
       </c>
       <c r="J251" s="14" t="s">
-        <v>4207</v>
+        <v>4183</v>
       </c>
     </row>
     <row r="252" spans="1:10">
@@ -23072,10 +23085,10 @@
         <v>3222</v>
       </c>
       <c r="I252" s="14" t="s">
-        <v>3774</v>
+        <v>3750</v>
       </c>
       <c r="J252" s="14" t="s">
-        <v>4206</v>
+        <v>4182</v>
       </c>
     </row>
     <row r="253" spans="1:10">
@@ -23104,10 +23117,10 @@
         <v>3223</v>
       </c>
       <c r="I253" s="14" t="s">
-        <v>3641</v>
+        <v>3617</v>
       </c>
       <c r="J253" s="14" t="s">
-        <v>4202</v>
+        <v>4178</v>
       </c>
     </row>
     <row r="254" spans="1:10">
@@ -23136,10 +23149,10 @@
         <v>3224</v>
       </c>
       <c r="I254" s="14" t="s">
-        <v>3775</v>
+        <v>3751</v>
       </c>
       <c r="J254" s="14" t="s">
-        <v>4203</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="255" spans="1:10">
@@ -23168,10 +23181,10 @@
         <v>3225</v>
       </c>
       <c r="I255" s="14" t="s">
-        <v>3776</v>
+        <v>3752</v>
       </c>
       <c r="J255" s="14" t="s">
-        <v>4204</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="256" spans="1:10">
@@ -23200,10 +23213,10 @@
         <v>3226</v>
       </c>
       <c r="I256" s="14" t="s">
-        <v>3777</v>
+        <v>3753</v>
       </c>
       <c r="J256" s="14" t="s">
-        <v>4205</v>
+        <v>4181</v>
       </c>
     </row>
     <row r="257" spans="1:10">
@@ -23232,10 +23245,10 @@
         <v>3227</v>
       </c>
       <c r="I257" s="14" t="s">
-        <v>3778</v>
+        <v>3754</v>
       </c>
       <c r="J257" s="14" t="s">
-        <v>4214</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="258" spans="1:10">
@@ -23264,10 +23277,10 @@
         <v>3228</v>
       </c>
       <c r="I258" s="14" t="s">
-        <v>3779</v>
+        <v>3755</v>
       </c>
       <c r="J258" s="14" t="s">
-        <v>4215</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="259" spans="1:10">
@@ -23296,10 +23309,10 @@
         <v>3229</v>
       </c>
       <c r="I259" s="14" t="s">
-        <v>3780</v>
+        <v>3756</v>
       </c>
       <c r="J259" s="14" t="s">
-        <v>4216</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="260" spans="1:10">
@@ -23328,10 +23341,10 @@
         <v>3229</v>
       </c>
       <c r="I260" s="14" t="s">
-        <v>3780</v>
+        <v>3756</v>
       </c>
       <c r="J260" s="14" t="s">
-        <v>4216</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="261" spans="1:10">
@@ -23360,10 +23373,10 @@
         <v>3230</v>
       </c>
       <c r="I261" s="14" t="s">
-        <v>3781</v>
+        <v>3757</v>
       </c>
       <c r="J261" s="14" t="s">
-        <v>4217</v>
+        <v>4193</v>
       </c>
     </row>
     <row r="262" spans="1:10">
@@ -23395,7 +23408,7 @@
         <v>1534</v>
       </c>
       <c r="J262" s="14" t="s">
-        <v>4210</v>
+        <v>4186</v>
       </c>
     </row>
     <row r="263" spans="1:10">
@@ -23424,10 +23437,10 @@
         <v>1536</v>
       </c>
       <c r="I263" s="14" t="s">
-        <v>3782</v>
+        <v>3758</v>
       </c>
       <c r="J263" s="14" t="s">
-        <v>4211</v>
+        <v>4187</v>
       </c>
     </row>
     <row r="264" spans="1:10">
@@ -23456,10 +23469,10 @@
         <v>1541</v>
       </c>
       <c r="I264" s="14" t="s">
-        <v>3783</v>
+        <v>3759</v>
       </c>
       <c r="J264" s="14" t="s">
-        <v>4212</v>
+        <v>4188</v>
       </c>
     </row>
     <row r="265" spans="1:10">
@@ -23488,10 +23501,10 @@
         <v>3134</v>
       </c>
       <c r="I265" s="14" t="s">
-        <v>3784</v>
+        <v>3760</v>
       </c>
       <c r="J265" s="14" t="s">
-        <v>4213</v>
+        <v>4189</v>
       </c>
     </row>
     <row r="266" spans="1:10">
@@ -23520,10 +23533,10 @@
         <v>3135</v>
       </c>
       <c r="I266" s="14" t="s">
-        <v>3789</v>
+        <v>3765</v>
       </c>
       <c r="J266" s="14" t="s">
-        <v>4086</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="267" spans="1:10">
@@ -23552,10 +23565,10 @@
         <v>3136</v>
       </c>
       <c r="I267" s="14" t="s">
-        <v>3787</v>
+        <v>3763</v>
       </c>
       <c r="J267" s="14" t="s">
-        <v>4087</v>
+        <v>4063</v>
       </c>
     </row>
     <row r="268" spans="1:10">
@@ -23584,10 +23597,10 @@
         <v>3137</v>
       </c>
       <c r="I268" s="14" t="s">
-        <v>3788</v>
+        <v>3764</v>
       </c>
       <c r="J268" s="14" t="s">
-        <v>4088</v>
+        <v>4064</v>
       </c>
     </row>
     <row r="269" spans="1:10">
@@ -23616,10 +23629,10 @@
         <v>3138</v>
       </c>
       <c r="I269" s="14" t="s">
-        <v>3790</v>
+        <v>3766</v>
       </c>
       <c r="J269" s="14" t="s">
-        <v>4089</v>
+        <v>4065</v>
       </c>
     </row>
     <row r="270" spans="1:10">
@@ -23648,10 +23661,10 @@
         <v>3139</v>
       </c>
       <c r="I270" s="14" t="s">
-        <v>3791</v>
+        <v>3767</v>
       </c>
       <c r="J270" s="14" t="s">
-        <v>4090</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="271" spans="1:10">
@@ -23680,10 +23693,10 @@
         <v>3140</v>
       </c>
       <c r="I271" s="14" t="s">
-        <v>3792</v>
+        <v>3768</v>
       </c>
       <c r="J271" s="14" t="s">
-        <v>4091</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="272" spans="1:10">
@@ -23712,10 +23725,10 @@
         <v>3141</v>
       </c>
       <c r="I272" s="14" t="s">
-        <v>3868</v>
+        <v>3844</v>
       </c>
       <c r="J272" s="14" t="s">
-        <v>4092</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="273" spans="1:10">
@@ -23744,10 +23757,10 @@
         <v>3142</v>
       </c>
       <c r="I273" s="14" t="s">
-        <v>3869</v>
+        <v>3845</v>
       </c>
       <c r="J273" s="14" t="s">
-        <v>4093</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="274" spans="1:10">
@@ -23776,10 +23789,10 @@
         <v>3202</v>
       </c>
       <c r="I274" s="14" t="s">
-        <v>3867</v>
+        <v>3843</v>
       </c>
       <c r="J274" s="14" t="s">
-        <v>4094</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="275" spans="1:10">
@@ -23808,10 +23821,10 @@
         <v>3203</v>
       </c>
       <c r="I275" s="14" t="s">
-        <v>3870</v>
+        <v>3846</v>
       </c>
       <c r="J275" s="14" t="s">
-        <v>4095</v>
+        <v>4071</v>
       </c>
     </row>
     <row r="276" spans="1:10">
@@ -23840,10 +23853,10 @@
         <v>3204</v>
       </c>
       <c r="I276" s="14" t="s">
-        <v>3871</v>
+        <v>3847</v>
       </c>
       <c r="J276" s="14" t="s">
-        <v>4096</v>
+        <v>4072</v>
       </c>
     </row>
     <row r="277" spans="1:10">
@@ -23872,10 +23885,10 @@
         <v>3039</v>
       </c>
       <c r="I277" s="14" t="s">
-        <v>3872</v>
+        <v>3848</v>
       </c>
       <c r="J277" s="14" t="s">
-        <v>4097</v>
+        <v>4073</v>
       </c>
     </row>
     <row r="278" spans="1:10">
@@ -23904,10 +23917,10 @@
         <v>3205</v>
       </c>
       <c r="I278" s="14" t="s">
-        <v>3864</v>
+        <v>3840</v>
       </c>
       <c r="J278" s="14" t="s">
-        <v>4098</v>
+        <v>4074</v>
       </c>
     </row>
     <row r="279" spans="1:10">
@@ -23936,10 +23949,10 @@
         <v>3206</v>
       </c>
       <c r="I279" s="14" t="s">
-        <v>3865</v>
+        <v>3841</v>
       </c>
       <c r="J279" s="14" t="s">
-        <v>4099</v>
+        <v>4075</v>
       </c>
     </row>
     <row r="280" spans="1:10">
@@ -23968,10 +23981,10 @@
         <v>3207</v>
       </c>
       <c r="I280" s="14" t="s">
-        <v>3866</v>
+        <v>3842</v>
       </c>
       <c r="J280" s="14" t="s">
-        <v>4100</v>
+        <v>4076</v>
       </c>
     </row>
     <row r="281" spans="1:10">
@@ -24000,10 +24013,10 @@
         <v>1642</v>
       </c>
       <c r="I281" s="14" t="s">
-        <v>3856</v>
+        <v>3832</v>
       </c>
       <c r="J281" s="14" t="s">
-        <v>4101</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="282" spans="1:10">
@@ -24032,10 +24045,10 @@
         <v>3208</v>
       </c>
       <c r="I282" s="14" t="s">
-        <v>3857</v>
+        <v>3833</v>
       </c>
       <c r="J282" s="14" t="s">
-        <v>4102</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="283" spans="1:10">
@@ -24064,10 +24077,10 @@
         <v>3209</v>
       </c>
       <c r="I283" s="14" t="s">
-        <v>3858</v>
+        <v>3834</v>
       </c>
       <c r="J283" s="14" t="s">
-        <v>4103</v>
+        <v>4079</v>
       </c>
     </row>
     <row r="284" spans="1:10">
@@ -24096,10 +24109,10 @@
         <v>3210</v>
       </c>
       <c r="I284" s="14" t="s">
-        <v>3859</v>
+        <v>3835</v>
       </c>
       <c r="J284" s="14" t="s">
-        <v>4104</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="285" spans="1:10">
@@ -24128,10 +24141,10 @@
         <v>3211</v>
       </c>
       <c r="I285" s="14" t="s">
-        <v>3860</v>
+        <v>3836</v>
       </c>
       <c r="J285" s="14" t="s">
-        <v>4109</v>
+        <v>4085</v>
       </c>
     </row>
     <row r="286" spans="1:10">
@@ -24160,10 +24173,10 @@
         <v>3212</v>
       </c>
       <c r="I286" s="14" t="s">
-        <v>3861</v>
+        <v>3837</v>
       </c>
       <c r="J286" s="14" t="s">
-        <v>4110</v>
+        <v>4086</v>
       </c>
     </row>
     <row r="287" spans="1:10">
@@ -24192,10 +24205,10 @@
         <v>3213</v>
       </c>
       <c r="I287" s="14" t="s">
-        <v>3863</v>
+        <v>3839</v>
       </c>
       <c r="J287" s="14" t="s">
-        <v>4111</v>
+        <v>4087</v>
       </c>
     </row>
     <row r="288" spans="1:10">
@@ -24224,10 +24237,10 @@
         <v>3214</v>
       </c>
       <c r="I288" s="14" t="s">
-        <v>3862</v>
+        <v>3838</v>
       </c>
       <c r="J288" s="14" t="s">
-        <v>4114</v>
+        <v>4090</v>
       </c>
     </row>
     <row r="289" spans="1:10">
@@ -24256,10 +24269,10 @@
         <v>3215</v>
       </c>
       <c r="I289" s="14" t="s">
-        <v>3793</v>
+        <v>3769</v>
       </c>
       <c r="J289" s="14" t="s">
-        <v>4112</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="290" spans="1:10">
@@ -24288,10 +24301,10 @@
         <v>3216</v>
       </c>
       <c r="I290" s="14" t="s">
-        <v>3794</v>
+        <v>3770</v>
       </c>
       <c r="J290" s="14" t="s">
-        <v>4113</v>
+        <v>4089</v>
       </c>
     </row>
     <row r="291" spans="1:10">
@@ -24320,10 +24333,10 @@
         <v>3186</v>
       </c>
       <c r="I291" s="14" t="s">
-        <v>3795</v>
+        <v>3771</v>
       </c>
       <c r="J291" s="14" t="s">
-        <v>4108</v>
+        <v>4084</v>
       </c>
     </row>
     <row r="292" spans="1:10">
@@ -24352,10 +24365,10 @@
         <v>3187</v>
       </c>
       <c r="I292" s="14" t="s">
-        <v>3796</v>
+        <v>3772</v>
       </c>
       <c r="J292" s="14" t="s">
-        <v>4107</v>
+        <v>4083</v>
       </c>
     </row>
     <row r="293" spans="1:10">
@@ -24384,10 +24397,10 @@
         <v>3189</v>
       </c>
       <c r="I293" s="14" t="s">
-        <v>3797</v>
+        <v>3773</v>
       </c>
       <c r="J293" s="14" t="s">
-        <v>4106</v>
+        <v>4082</v>
       </c>
     </row>
     <row r="294" spans="1:10">
@@ -24416,10 +24429,10 @@
         <v>3188</v>
       </c>
       <c r="I294" s="14" t="s">
-        <v>3799</v>
+        <v>3775</v>
       </c>
       <c r="J294" s="14" t="s">
-        <v>4105</v>
+        <v>4081</v>
       </c>
     </row>
     <row r="295" spans="1:10">
@@ -24448,10 +24461,10 @@
         <v>3014</v>
       </c>
       <c r="I295" s="14" t="s">
-        <v>3798</v>
+        <v>3774</v>
       </c>
       <c r="J295" s="14" t="s">
-        <v>4152</v>
+        <v>4128</v>
       </c>
     </row>
     <row r="296" spans="1:10">
@@ -24480,10 +24493,10 @@
         <v>3190</v>
       </c>
       <c r="I296" s="14" t="s">
-        <v>3800</v>
+        <v>3776</v>
       </c>
       <c r="J296" s="14" t="s">
-        <v>4153</v>
+        <v>4129</v>
       </c>
     </row>
     <row r="297" spans="1:10">
@@ -24512,10 +24525,10 @@
         <v>3191</v>
       </c>
       <c r="I297" s="14" t="s">
-        <v>3801</v>
+        <v>3777</v>
       </c>
       <c r="J297" s="14" t="s">
-        <v>4154</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="298" spans="1:10">
@@ -24544,10 +24557,10 @@
         <v>3183</v>
       </c>
       <c r="I298" s="14" t="s">
-        <v>3802</v>
+        <v>3778</v>
       </c>
       <c r="J298" s="14" t="s">
-        <v>4155</v>
+        <v>4131</v>
       </c>
     </row>
     <row r="299" spans="1:10">
@@ -24576,10 +24589,10 @@
         <v>3184</v>
       </c>
       <c r="I299" s="14" t="s">
-        <v>3803</v>
+        <v>3779</v>
       </c>
       <c r="J299" s="14" t="s">
-        <v>4156</v>
+        <v>4132</v>
       </c>
     </row>
     <row r="300" spans="1:10">
@@ -24608,10 +24621,10 @@
         <v>3185</v>
       </c>
       <c r="I300" s="14" t="s">
-        <v>3804</v>
+        <v>3780</v>
       </c>
       <c r="J300" s="14" t="s">
-        <v>4157</v>
+        <v>4133</v>
       </c>
     </row>
     <row r="301" spans="1:10">
@@ -24640,10 +24653,10 @@
         <v>3245</v>
       </c>
       <c r="I301" s="14" t="s">
-        <v>3805</v>
+        <v>3781</v>
       </c>
       <c r="J301" s="14" t="s">
-        <v>4234</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="302" spans="1:10">
@@ -24672,10 +24685,10 @@
         <v>3246</v>
       </c>
       <c r="I302" s="14" t="s">
-        <v>3806</v>
+        <v>3782</v>
       </c>
       <c r="J302" s="14" t="s">
-        <v>4235</v>
+        <v>4211</v>
       </c>
     </row>
     <row r="303" spans="1:10">
@@ -24704,10 +24717,10 @@
         <v>3247</v>
       </c>
       <c r="I303" s="14" t="s">
-        <v>3807</v>
+        <v>3783</v>
       </c>
       <c r="J303" s="14" t="s">
-        <v>4236</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="304" spans="1:10">
@@ -24736,10 +24749,10 @@
         <v>3248</v>
       </c>
       <c r="I304" s="14" t="s">
-        <v>3808</v>
+        <v>3784</v>
       </c>
       <c r="J304" s="14" t="s">
-        <v>4237</v>
+        <v>4213</v>
       </c>
     </row>
     <row r="305" spans="1:10">
@@ -24768,10 +24781,10 @@
         <v>3249</v>
       </c>
       <c r="I305" s="14" t="s">
-        <v>3821</v>
+        <v>3797</v>
       </c>
       <c r="J305" s="14" t="s">
-        <v>4238</v>
+        <v>4214</v>
       </c>
     </row>
     <row r="306" spans="1:10">
@@ -24800,10 +24813,10 @@
         <v>3250</v>
       </c>
       <c r="I306" s="14" t="s">
-        <v>3822</v>
+        <v>3798</v>
       </c>
       <c r="J306" s="14" t="s">
-        <v>4239</v>
+        <v>4215</v>
       </c>
     </row>
     <row r="307" spans="1:10">
@@ -24832,10 +24845,10 @@
         <v>3266</v>
       </c>
       <c r="I307" s="14" t="s">
-        <v>3823</v>
+        <v>3799</v>
       </c>
       <c r="J307" s="14" t="s">
-        <v>4260</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="308" spans="1:10">
@@ -24864,10 +24877,10 @@
         <v>3267</v>
       </c>
       <c r="I308" s="14" t="s">
-        <v>3824</v>
+        <v>3800</v>
       </c>
       <c r="J308" s="14" t="s">
-        <v>4261</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="309" spans="1:10">
@@ -24896,10 +24909,10 @@
         <v>3268</v>
       </c>
       <c r="I309" s="14" t="s">
-        <v>3825</v>
+        <v>3801</v>
       </c>
       <c r="J309" s="14" t="s">
-        <v>4258</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="310" spans="1:10">
@@ -24928,10 +24941,10 @@
         <v>3269</v>
       </c>
       <c r="I310" s="14" t="s">
-        <v>3826</v>
+        <v>3802</v>
       </c>
       <c r="J310" s="14" t="s">
-        <v>4259</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="311" spans="1:10">
@@ -24960,10 +24973,10 @@
         <v>3270</v>
       </c>
       <c r="I311" s="14" t="s">
-        <v>3827</v>
+        <v>3803</v>
       </c>
       <c r="J311" s="14" t="s">
-        <v>4264</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="312" spans="1:10">
@@ -24992,10 +25005,10 @@
         <v>3271</v>
       </c>
       <c r="I312" s="14" t="s">
-        <v>3828</v>
+        <v>3804</v>
       </c>
       <c r="J312" s="14" t="s">
-        <v>4263</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="313" spans="1:10">
@@ -25024,10 +25037,10 @@
         <v>3272</v>
       </c>
       <c r="I313" s="14" t="s">
-        <v>3829</v>
+        <v>3805</v>
       </c>
       <c r="J313" s="14" t="s">
-        <v>4262</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="314" spans="1:10">
@@ -25056,10 +25069,10 @@
         <v>3251</v>
       </c>
       <c r="I314" s="14" t="s">
-        <v>3830</v>
+        <v>3806</v>
       </c>
       <c r="J314" s="14" t="s">
-        <v>4265</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="315" spans="1:10">
@@ -25088,10 +25101,10 @@
         <v>3252</v>
       </c>
       <c r="I315" s="14" t="s">
-        <v>3831</v>
+        <v>3807</v>
       </c>
       <c r="J315" s="14" t="s">
-        <v>4266</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="316" spans="1:10">
@@ -25120,10 +25133,10 @@
         <v>3253</v>
       </c>
       <c r="I316" s="14" t="s">
-        <v>3832</v>
+        <v>3808</v>
       </c>
       <c r="J316" s="14" t="s">
-        <v>4241</v>
+        <v>4217</v>
       </c>
     </row>
     <row r="317" spans="1:10">
@@ -25152,10 +25165,10 @@
         <v>3254</v>
       </c>
       <c r="I317" s="14" t="s">
-        <v>3833</v>
+        <v>3809</v>
       </c>
       <c r="J317" s="14" t="s">
-        <v>4242</v>
+        <v>4218</v>
       </c>
     </row>
     <row r="318" spans="1:10">
@@ -25184,10 +25197,10 @@
         <v>3256</v>
       </c>
       <c r="I318" s="14" t="s">
-        <v>3834</v>
+        <v>3810</v>
       </c>
       <c r="J318" s="14" t="s">
-        <v>3834</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="319" spans="1:10">
@@ -25216,10 +25229,10 @@
         <v>3255</v>
       </c>
       <c r="I319" s="14" t="s">
-        <v>3835</v>
+        <v>3811</v>
       </c>
       <c r="J319" s="14" t="s">
-        <v>4240</v>
+        <v>4216</v>
       </c>
     </row>
     <row r="320" spans="1:10">
@@ -25248,10 +25261,10 @@
         <v>3258</v>
       </c>
       <c r="I320" s="14" t="s">
-        <v>3836</v>
+        <v>3812</v>
       </c>
       <c r="J320" s="14" t="s">
-        <v>4275</v>
+        <v>4251</v>
       </c>
     </row>
     <row r="321" spans="1:10">
@@ -25280,10 +25293,10 @@
         <v>3257</v>
       </c>
       <c r="I321" s="14" t="s">
-        <v>3837</v>
+        <v>3813</v>
       </c>
       <c r="J321" s="14" t="s">
-        <v>4276</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="322" spans="1:10">
@@ -25312,10 +25325,10 @@
         <v>3259</v>
       </c>
       <c r="I322" s="14" t="s">
-        <v>3838</v>
+        <v>3814</v>
       </c>
       <c r="J322" s="14" t="s">
-        <v>4277</v>
+        <v>4253</v>
       </c>
     </row>
     <row r="323" spans="1:10">
@@ -25344,10 +25357,10 @@
         <v>3260</v>
       </c>
       <c r="I323" s="14" t="s">
-        <v>3839</v>
+        <v>3815</v>
       </c>
       <c r="J323" s="14" t="s">
-        <v>4279</v>
+        <v>4255</v>
       </c>
     </row>
     <row r="324" spans="1:10">
@@ -25376,10 +25389,10 @@
         <v>3261</v>
       </c>
       <c r="I324" s="14" t="s">
-        <v>3840</v>
+        <v>3816</v>
       </c>
       <c r="J324" s="14" t="s">
-        <v>4278</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="325" spans="1:10">
@@ -25408,10 +25421,10 @@
         <v>3262</v>
       </c>
       <c r="I325" s="14" t="s">
-        <v>3841</v>
+        <v>3817</v>
       </c>
       <c r="J325" s="14" t="s">
-        <v>4280</v>
+        <v>4256</v>
       </c>
     </row>
     <row r="326" spans="1:10">
@@ -25440,10 +25453,10 @@
         <v>3263</v>
       </c>
       <c r="I326" s="14" t="s">
-        <v>3842</v>
+        <v>3818</v>
       </c>
       <c r="J326" s="14" t="s">
-        <v>4281</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="327" spans="1:10">
@@ -25472,10 +25485,10 @@
         <v>3264</v>
       </c>
       <c r="I327" s="14" t="s">
-        <v>3843</v>
+        <v>3819</v>
       </c>
       <c r="J327" s="14" t="s">
-        <v>4282</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="328" spans="1:10">
@@ -25504,10 +25517,10 @@
         <v>3265</v>
       </c>
       <c r="I328" s="14" t="s">
-        <v>3844</v>
+        <v>3820</v>
       </c>
       <c r="J328" s="14" t="s">
-        <v>4283</v>
+        <v>4259</v>
       </c>
     </row>
     <row r="329" spans="1:10">
@@ -25536,10 +25549,10 @@
         <v>3192</v>
       </c>
       <c r="I329" s="14" t="s">
-        <v>3845</v>
+        <v>3821</v>
       </c>
       <c r="J329" s="14" t="s">
-        <v>4284</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="330" spans="1:10">
@@ -25568,10 +25581,10 @@
         <v>1950</v>
       </c>
       <c r="I330" s="14" t="s">
-        <v>3846</v>
+        <v>3822</v>
       </c>
       <c r="J330" s="14" t="s">
-        <v>4285</v>
+        <v>4261</v>
       </c>
     </row>
     <row r="331" spans="1:10">
@@ -25600,10 +25613,10 @@
         <v>3193</v>
       </c>
       <c r="I331" s="14" t="s">
-        <v>3847</v>
+        <v>3823</v>
       </c>
       <c r="J331" s="14" t="s">
-        <v>4299</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="332" spans="1:10">
@@ -25632,10 +25645,10 @@
         <v>3194</v>
       </c>
       <c r="I332" s="14" t="s">
-        <v>3848</v>
+        <v>3824</v>
       </c>
       <c r="J332" s="14" t="s">
-        <v>4298</v>
+        <v>4274</v>
       </c>
     </row>
     <row r="333" spans="1:10">
@@ -25664,10 +25677,10 @@
         <v>3195</v>
       </c>
       <c r="I333" s="14" t="s">
-        <v>3849</v>
+        <v>3825</v>
       </c>
       <c r="J333" s="14" t="s">
-        <v>4297</v>
+        <v>4273</v>
       </c>
     </row>
     <row r="334" spans="1:10">
@@ -25696,10 +25709,10 @@
         <v>3196</v>
       </c>
       <c r="I334" s="14" t="s">
-        <v>3850</v>
+        <v>3826</v>
       </c>
       <c r="J334" s="14" t="s">
-        <v>4293</v>
+        <v>4269</v>
       </c>
     </row>
     <row r="335" spans="1:10">
@@ -25728,10 +25741,10 @@
         <v>3197</v>
       </c>
       <c r="I335" s="14" t="s">
-        <v>3851</v>
+        <v>3827</v>
       </c>
       <c r="J335" s="14" t="s">
-        <v>4294</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="336" spans="1:10">
@@ -25760,10 +25773,10 @@
         <v>3198</v>
       </c>
       <c r="I336" s="14" t="s">
-        <v>3855</v>
+        <v>3831</v>
       </c>
       <c r="J336" s="14" t="s">
-        <v>4295</v>
+        <v>4271</v>
       </c>
     </row>
     <row r="337" spans="1:10">
@@ -25792,10 +25805,10 @@
         <v>3201</v>
       </c>
       <c r="I337" s="14" t="s">
-        <v>3854</v>
+        <v>3830</v>
       </c>
       <c r="J337" s="14" t="s">
-        <v>4296</v>
+        <v>4272</v>
       </c>
     </row>
     <row r="338" spans="1:10">
@@ -25824,10 +25837,10 @@
         <v>3199</v>
       </c>
       <c r="I338" s="14" t="s">
-        <v>3853</v>
+        <v>3829</v>
       </c>
       <c r="J338" s="14" t="s">
-        <v>4289</v>
+        <v>4265</v>
       </c>
     </row>
     <row r="339" spans="1:10">
@@ -25856,10 +25869,10 @@
         <v>2007</v>
       </c>
       <c r="I339" s="14" t="s">
-        <v>3852</v>
+        <v>3828</v>
       </c>
       <c r="J339" s="14" t="s">
-        <v>4290</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="340" spans="1:10">
@@ -25888,10 +25901,10 @@
         <v>3200</v>
       </c>
       <c r="I340" s="14" t="s">
-        <v>3816</v>
+        <v>3792</v>
       </c>
       <c r="J340" s="14" t="s">
-        <v>4291</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="341" spans="1:10">
@@ -25920,10 +25933,10 @@
         <v>3143</v>
       </c>
       <c r="I341" s="14" t="s">
-        <v>3815</v>
+        <v>3791</v>
       </c>
       <c r="J341" s="14" t="s">
-        <v>4292</v>
+        <v>4268</v>
       </c>
     </row>
     <row r="342" spans="1:10">
@@ -25952,10 +25965,10 @@
         <v>3144</v>
       </c>
       <c r="I342" s="14" t="s">
-        <v>3814</v>
+        <v>3790</v>
       </c>
       <c r="J342" s="14" t="s">
-        <v>4288</v>
+        <v>4264</v>
       </c>
     </row>
     <row r="343" spans="1:10">
@@ -25984,10 +25997,10 @@
         <v>3146</v>
       </c>
       <c r="I343" s="14" t="s">
-        <v>3813</v>
+        <v>3789</v>
       </c>
       <c r="J343" s="14" t="s">
-        <v>4287</v>
+        <v>4263</v>
       </c>
     </row>
     <row r="344" spans="1:10">
@@ -26016,10 +26029,10 @@
         <v>3145</v>
       </c>
       <c r="I344" s="14" t="s">
-        <v>3812</v>
+        <v>3788</v>
       </c>
       <c r="J344" s="14" t="s">
-        <v>4286</v>
+        <v>4262</v>
       </c>
     </row>
     <row r="345" spans="1:10">
@@ -26048,10 +26061,10 @@
         <v>3148</v>
       </c>
       <c r="I345" s="14" t="s">
-        <v>3820</v>
+        <v>3796</v>
       </c>
       <c r="J345" s="14" t="s">
-        <v>4269</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="346" spans="1:10">
@@ -26080,10 +26093,10 @@
         <v>3147</v>
       </c>
       <c r="I346" s="14" t="s">
-        <v>3819</v>
+        <v>3795</v>
       </c>
       <c r="J346" s="14" t="s">
-        <v>4270</v>
+        <v>4246</v>
       </c>
     </row>
     <row r="347" spans="1:10">
@@ -26112,10 +26125,10 @@
         <v>3153</v>
       </c>
       <c r="I347" s="14" t="s">
-        <v>3818</v>
+        <v>3794</v>
       </c>
       <c r="J347" s="14" t="s">
-        <v>4271</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="348" spans="1:10">
@@ -26144,10 +26157,10 @@
         <v>3152</v>
       </c>
       <c r="I348" s="14" t="s">
-        <v>3817</v>
+        <v>3793</v>
       </c>
       <c r="J348" s="14" t="s">
-        <v>4272</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="349" spans="1:10">
@@ -26176,10 +26189,10 @@
         <v>3150</v>
       </c>
       <c r="I349" s="14" t="s">
-        <v>3809</v>
+        <v>3785</v>
       </c>
       <c r="J349" s="14" t="s">
-        <v>4273</v>
+        <v>4249</v>
       </c>
     </row>
     <row r="350" spans="1:10">
@@ -26208,10 +26221,10 @@
         <v>3151</v>
       </c>
       <c r="I350" s="14" t="s">
-        <v>3810</v>
+        <v>3786</v>
       </c>
       <c r="J350" s="14" t="s">
-        <v>4274</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="351" spans="1:10">
@@ -26240,10 +26253,10 @@
         <v>3149</v>
       </c>
       <c r="I351" s="14" t="s">
-        <v>3811</v>
+        <v>3787</v>
       </c>
       <c r="J351" s="14" t="s">
-        <v>4268</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="352" spans="1:10">
@@ -26272,10 +26285,10 @@
         <v>3173</v>
       </c>
       <c r="I352" s="14" t="s">
-        <v>3754</v>
+        <v>3730</v>
       </c>
       <c r="J352" s="14" t="s">
-        <v>4267</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="353" spans="1:10">
@@ -26304,10 +26317,10 @@
         <v>3174</v>
       </c>
       <c r="I353" s="14" t="s">
-        <v>3755</v>
+        <v>3731</v>
       </c>
       <c r="J353" s="14" t="s">
-        <v>4243</v>
+        <v>4219</v>
       </c>
     </row>
     <row r="354" spans="1:10">
@@ -26336,10 +26349,10 @@
         <v>3177</v>
       </c>
       <c r="I354" s="14" t="s">
-        <v>3756</v>
+        <v>3732</v>
       </c>
       <c r="J354" s="14" t="s">
-        <v>4244</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="355" spans="1:10">
@@ -26368,10 +26381,10 @@
         <v>3176</v>
       </c>
       <c r="I355" s="14" t="s">
-        <v>3757</v>
+        <v>3733</v>
       </c>
       <c r="J355" s="14" t="s">
-        <v>4245</v>
+        <v>4221</v>
       </c>
     </row>
     <row r="356" spans="1:10">
@@ -26400,10 +26413,10 @@
         <v>3175</v>
       </c>
       <c r="I356" s="14" t="s">
-        <v>3758</v>
+        <v>3734</v>
       </c>
       <c r="J356" s="14" t="s">
-        <v>4246</v>
+        <v>4222</v>
       </c>
     </row>
     <row r="357" spans="1:10">
@@ -26432,10 +26445,10 @@
         <v>3178</v>
       </c>
       <c r="I357" s="14" t="s">
-        <v>3759</v>
+        <v>3735</v>
       </c>
       <c r="J357" s="14" t="s">
-        <v>4247</v>
+        <v>4223</v>
       </c>
     </row>
     <row r="358" spans="1:10">
@@ -26464,10 +26477,10 @@
         <v>3179</v>
       </c>
       <c r="I358" s="14" t="s">
-        <v>3760</v>
+        <v>3736</v>
       </c>
       <c r="J358" s="14" t="s">
-        <v>4250</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="359" spans="1:10">
@@ -26496,10 +26509,10 @@
         <v>3180</v>
       </c>
       <c r="I359" s="14" t="s">
-        <v>3761</v>
+        <v>3737</v>
       </c>
       <c r="J359" s="14" t="s">
-        <v>4249</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="360" spans="1:10">
@@ -26528,10 +26541,10 @@
         <v>3181</v>
       </c>
       <c r="I360" s="14" t="s">
-        <v>3762</v>
+        <v>3738</v>
       </c>
       <c r="J360" s="14" t="s">
-        <v>4248</v>
+        <v>4224</v>
       </c>
     </row>
     <row r="361" spans="1:10">
@@ -26560,10 +26573,10 @@
         <v>3182</v>
       </c>
       <c r="I361" s="14" t="s">
-        <v>3763</v>
+        <v>3739</v>
       </c>
       <c r="J361" s="14" t="s">
-        <v>4253</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="362" spans="1:10">
@@ -26592,10 +26605,10 @@
         <v>3154</v>
       </c>
       <c r="I362" s="14" t="s">
-        <v>3764</v>
+        <v>3740</v>
       </c>
       <c r="J362" s="14" t="s">
-        <v>4251</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="363" spans="1:10">
@@ -26624,10 +26637,10 @@
         <v>2148</v>
       </c>
       <c r="I363" s="14" t="s">
-        <v>3765</v>
+        <v>3741</v>
       </c>
       <c r="J363" s="14" t="s">
-        <v>4252</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="364" spans="1:10">
@@ -26656,10 +26669,10 @@
         <v>3155</v>
       </c>
       <c r="I364" s="14" t="s">
-        <v>3766</v>
+        <v>3742</v>
       </c>
       <c r="J364" s="14" t="s">
-        <v>4254</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="365" spans="1:10">
@@ -26688,10 +26701,10 @@
         <v>3162</v>
       </c>
       <c r="I365" s="14" t="s">
-        <v>3751</v>
+        <v>3727</v>
       </c>
       <c r="J365" s="14" t="s">
-        <v>4255</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="366" spans="1:10">
@@ -26720,10 +26733,10 @@
         <v>3161</v>
       </c>
       <c r="I366" s="14" t="s">
-        <v>3752</v>
+        <v>3728</v>
       </c>
       <c r="J366" s="14" t="s">
-        <v>4257</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="367" spans="1:10">
@@ -26752,10 +26765,10 @@
         <v>3160</v>
       </c>
       <c r="I367" s="14" t="s">
-        <v>3753</v>
+        <v>3729</v>
       </c>
       <c r="J367" s="14" t="s">
-        <v>4257</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="368" spans="1:10">
@@ -26784,10 +26797,10 @@
         <v>3159</v>
       </c>
       <c r="I368" s="14" t="s">
-        <v>3750</v>
+        <v>3726</v>
       </c>
       <c r="J368" s="14" t="s">
-        <v>4256</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="369" spans="1:10">
@@ -26816,10 +26829,10 @@
         <v>2190</v>
       </c>
       <c r="I369" s="14" t="s">
-        <v>3740</v>
+        <v>3716</v>
       </c>
       <c r="J369" s="14" t="s">
-        <v>4226</v>
+        <v>4202</v>
       </c>
     </row>
     <row r="370" spans="1:10">
@@ -26848,10 +26861,10 @@
         <v>3156</v>
       </c>
       <c r="I370" s="14" t="s">
-        <v>3741</v>
+        <v>3717</v>
       </c>
       <c r="J370" s="14" t="s">
-        <v>4227</v>
+        <v>4203</v>
       </c>
     </row>
     <row r="371" spans="1:10">
@@ -26880,10 +26893,10 @@
         <v>3158</v>
       </c>
       <c r="I371" s="14" t="s">
-        <v>3742</v>
+        <v>3718</v>
       </c>
       <c r="J371" s="14" t="s">
-        <v>4228</v>
+        <v>4204</v>
       </c>
     </row>
     <row r="372" spans="1:10">
@@ -26912,10 +26925,10 @@
         <v>3157</v>
       </c>
       <c r="I372" s="14" t="s">
-        <v>3743</v>
+        <v>3719</v>
       </c>
       <c r="J372" s="14" t="s">
-        <v>4229</v>
+        <v>4205</v>
       </c>
     </row>
     <row r="373" spans="1:10">
@@ -26944,10 +26957,10 @@
         <v>3163</v>
       </c>
       <c r="I373" s="14" t="s">
-        <v>3744</v>
+        <v>3720</v>
       </c>
       <c r="J373" s="14" t="s">
-        <v>3744</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="374" spans="1:10">
@@ -26976,10 +26989,10 @@
         <v>2222</v>
       </c>
       <c r="I374" s="14" t="s">
-        <v>3745</v>
+        <v>3721</v>
       </c>
       <c r="J374" s="14" t="s">
-        <v>4230</v>
+        <v>4206</v>
       </c>
     </row>
     <row r="375" spans="1:10">
@@ -27008,10 +27021,10 @@
         <v>3166</v>
       </c>
       <c r="I375" s="14" t="s">
-        <v>3746</v>
+        <v>3722</v>
       </c>
       <c r="J375" s="14" t="s">
-        <v>4231</v>
+        <v>4207</v>
       </c>
     </row>
     <row r="376" spans="1:10">
@@ -27040,10 +27053,10 @@
         <v>3165</v>
       </c>
       <c r="I376" s="14" t="s">
-        <v>3747</v>
+        <v>3723</v>
       </c>
       <c r="J376" s="14" t="s">
-        <v>4232</v>
+        <v>4208</v>
       </c>
     </row>
     <row r="377" spans="1:10">
@@ -27072,10 +27085,10 @@
         <v>3165</v>
       </c>
       <c r="I377" s="14" t="s">
-        <v>3748</v>
+        <v>3724</v>
       </c>
       <c r="J377" s="14" t="s">
-        <v>4233</v>
+        <v>4209</v>
       </c>
     </row>
     <row r="378" spans="1:10">
@@ -27104,10 +27117,10 @@
         <v>3164</v>
       </c>
       <c r="I378" s="14" t="s">
-        <v>3749</v>
+        <v>3725</v>
       </c>
       <c r="J378" s="14" t="s">
-        <v>4222</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="379" spans="1:10">
@@ -27136,10 +27149,10 @@
         <v>3167</v>
       </c>
       <c r="I379" s="14" t="s">
-        <v>3732</v>
+        <v>3708</v>
       </c>
       <c r="J379" s="14" t="s">
-        <v>4223</v>
+        <v>4199</v>
       </c>
     </row>
     <row r="380" spans="1:10">
@@ -27168,10 +27181,10 @@
         <v>3168</v>
       </c>
       <c r="I380" s="14" t="s">
-        <v>3733</v>
+        <v>3709</v>
       </c>
       <c r="J380" s="14" t="s">
-        <v>4224</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="381" spans="1:10">
@@ -27200,10 +27213,10 @@
         <v>3169</v>
       </c>
       <c r="I381" s="14" t="s">
-        <v>3734</v>
+        <v>3710</v>
       </c>
       <c r="J381" s="14" t="s">
-        <v>4225</v>
+        <v>4201</v>
       </c>
     </row>
     <row r="382" spans="1:10">
@@ -27232,10 +27245,10 @@
         <v>3170</v>
       </c>
       <c r="I382" s="14" t="s">
-        <v>3735</v>
+        <v>3711</v>
       </c>
       <c r="J382" s="14" t="s">
-        <v>4221</v>
+        <v>4197</v>
       </c>
     </row>
     <row r="383" spans="1:10">
@@ -27264,10 +27277,10 @@
         <v>3171</v>
       </c>
       <c r="I383" s="14" t="s">
-        <v>3736</v>
+        <v>3712</v>
       </c>
       <c r="J383" s="14" t="s">
-        <v>4220</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="384" spans="1:10">
@@ -27296,10 +27309,10 @@
         <v>3172</v>
       </c>
       <c r="I384" s="14" t="s">
-        <v>3737</v>
+        <v>3713</v>
       </c>
       <c r="J384" s="14" t="s">
-        <v>4218</v>
+        <v>4194</v>
       </c>
     </row>
     <row r="385" spans="1:10">
@@ -27328,10 +27341,10 @@
         <v>3097</v>
       </c>
       <c r="I385" s="14" t="s">
-        <v>3738</v>
+        <v>3714</v>
       </c>
       <c r="J385" s="14" t="s">
-        <v>4219</v>
+        <v>4195</v>
       </c>
     </row>
     <row r="386" spans="1:10">
@@ -27360,10 +27373,10 @@
         <v>3098</v>
       </c>
       <c r="I386" s="14" t="s">
-        <v>3739</v>
+        <v>3715</v>
       </c>
       <c r="J386" s="14" t="s">
-        <v>4000</v>
+        <v>3976</v>
       </c>
     </row>
     <row r="387" spans="1:10">
@@ -27392,10 +27405,10 @@
         <v>3099</v>
       </c>
       <c r="I387" s="14" t="s">
-        <v>3675</v>
+        <v>3651</v>
       </c>
       <c r="J387" s="14" t="s">
-        <v>4001</v>
+        <v>3977</v>
       </c>
     </row>
     <row r="388" spans="1:10">
@@ -27424,10 +27437,10 @@
         <v>3100</v>
       </c>
       <c r="I388" s="14" t="s">
-        <v>3676</v>
+        <v>3652</v>
       </c>
       <c r="J388" s="14" t="s">
-        <v>4002</v>
+        <v>3978</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -27456,10 +27469,10 @@
         <v>3101</v>
       </c>
       <c r="I389" s="14" t="s">
-        <v>3677</v>
+        <v>3653</v>
       </c>
       <c r="J389" s="14" t="s">
-        <v>4003</v>
+        <v>3979</v>
       </c>
     </row>
     <row r="390" spans="1:10">
@@ -27488,10 +27501,10 @@
         <v>3102</v>
       </c>
       <c r="I390" s="14" t="s">
-        <v>3678</v>
+        <v>3654</v>
       </c>
       <c r="J390" s="14" t="s">
-        <v>4004</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="391" spans="1:10">
@@ -27520,10 +27533,10 @@
         <v>3103</v>
       </c>
       <c r="I391" s="14" t="s">
-        <v>3679</v>
+        <v>3655</v>
       </c>
       <c r="J391" s="14" t="s">
-        <v>4005</v>
+        <v>3981</v>
       </c>
     </row>
     <row r="392" spans="1:10">
@@ -27552,10 +27565,10 @@
         <v>3104</v>
       </c>
       <c r="I392" s="14" t="s">
-        <v>3680</v>
+        <v>3656</v>
       </c>
       <c r="J392" s="14" t="s">
-        <v>4006</v>
+        <v>3982</v>
       </c>
     </row>
     <row r="393" spans="1:10">
@@ -27584,10 +27597,10 @@
         <v>3105</v>
       </c>
       <c r="I393" s="14" t="s">
-        <v>3681</v>
+        <v>3657</v>
       </c>
       <c r="J393" s="14" t="s">
-        <v>4007</v>
+        <v>3983</v>
       </c>
     </row>
     <row r="394" spans="1:10">
@@ -27616,10 +27629,10 @@
         <v>3106</v>
       </c>
       <c r="I394" s="14" t="s">
-        <v>3682</v>
+        <v>3658</v>
       </c>
       <c r="J394" s="14" t="s">
-        <v>4008</v>
+        <v>3984</v>
       </c>
     </row>
     <row r="395" spans="1:10">
@@ -27648,10 +27661,10 @@
         <v>3108</v>
       </c>
       <c r="I395" s="14" t="s">
-        <v>3683</v>
+        <v>3659</v>
       </c>
       <c r="J395" s="14" t="s">
-        <v>4011</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="396" spans="1:10">
@@ -27680,10 +27693,10 @@
         <v>3107</v>
       </c>
       <c r="I396" s="14" t="s">
-        <v>3684</v>
+        <v>3660</v>
       </c>
       <c r="J396" s="14" t="s">
-        <v>4010</v>
+        <v>3986</v>
       </c>
     </row>
     <row r="397" spans="1:10">
@@ -27712,10 +27725,10 @@
         <v>3109</v>
       </c>
       <c r="I397" s="14" t="s">
-        <v>3685</v>
+        <v>3661</v>
       </c>
       <c r="J397" s="14" t="s">
-        <v>4009</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="398" spans="1:10">
@@ -27744,10 +27757,10 @@
         <v>3111</v>
       </c>
       <c r="I398" s="14" t="s">
-        <v>3669</v>
+        <v>3645</v>
       </c>
       <c r="J398" s="14" t="s">
-        <v>3994</v>
+        <v>3970</v>
       </c>
     </row>
     <row r="399" spans="1:10">
@@ -27776,10 +27789,10 @@
         <v>3110</v>
       </c>
       <c r="I399" s="30" t="s">
-        <v>3670</v>
+        <v>3646</v>
       </c>
       <c r="J399" s="14" t="s">
-        <v>3995</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="400" spans="1:10">
@@ -27808,10 +27821,10 @@
         <v>3112</v>
       </c>
       <c r="I400" s="30" t="s">
-        <v>3671</v>
+        <v>3647</v>
       </c>
       <c r="J400" s="14" t="s">
-        <v>3996</v>
+        <v>3972</v>
       </c>
     </row>
     <row r="401" spans="1:10">
@@ -27840,10 +27853,10 @@
         <v>3113</v>
       </c>
       <c r="I401" s="14" t="s">
-        <v>3672</v>
+        <v>3648</v>
       </c>
       <c r="J401" s="14" t="s">
-        <v>3999</v>
+        <v>3975</v>
       </c>
     </row>
     <row r="402" spans="1:10">
@@ -27872,10 +27885,10 @@
         <v>3114</v>
       </c>
       <c r="I402" s="14" t="s">
-        <v>3673</v>
+        <v>3649</v>
       </c>
       <c r="J402" s="14" t="s">
-        <v>3998</v>
+        <v>3974</v>
       </c>
     </row>
     <row r="403" spans="1:10">
@@ -27904,10 +27917,10 @@
         <v>3115</v>
       </c>
       <c r="I403" s="14" t="s">
-        <v>3674</v>
+        <v>3650</v>
       </c>
       <c r="J403" s="14" t="s">
-        <v>3997</v>
+        <v>3973</v>
       </c>
     </row>
     <row r="404" spans="1:10">
@@ -27936,10 +27949,10 @@
         <v>3116</v>
       </c>
       <c r="I404" s="14" t="s">
-        <v>3647</v>
+        <v>3623</v>
       </c>
       <c r="J404" s="14" t="s">
-        <v>4012</v>
+        <v>3988</v>
       </c>
     </row>
     <row r="405" spans="1:10">
@@ -27968,10 +27981,10 @@
         <v>3117</v>
       </c>
       <c r="I405" s="14" t="s">
-        <v>3648</v>
+        <v>3624</v>
       </c>
       <c r="J405" s="14" t="s">
-        <v>4013</v>
+        <v>3989</v>
       </c>
     </row>
     <row r="406" spans="1:10">
@@ -28000,10 +28013,10 @@
         <v>3118</v>
       </c>
       <c r="I406" s="14" t="s">
-        <v>3649</v>
+        <v>3625</v>
       </c>
       <c r="J406" s="14" t="s">
-        <v>4014</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="407" spans="1:10">
@@ -28032,10 +28045,10 @@
         <v>3119</v>
       </c>
       <c r="I407" s="14" t="s">
-        <v>3650</v>
+        <v>3626</v>
       </c>
       <c r="J407" s="14" t="s">
-        <v>4015</v>
+        <v>3991</v>
       </c>
     </row>
     <row r="408" spans="1:10">
@@ -28064,10 +28077,10 @@
         <v>3120</v>
       </c>
       <c r="I408" s="14" t="s">
-        <v>3651</v>
+        <v>3627</v>
       </c>
       <c r="J408" s="14" t="s">
-        <v>4016</v>
+        <v>3992</v>
       </c>
     </row>
     <row r="409" spans="1:10">
@@ -28096,10 +28109,10 @@
         <v>3121</v>
       </c>
       <c r="I409" s="14" t="s">
-        <v>3652</v>
+        <v>3628</v>
       </c>
       <c r="J409" s="14" t="s">
-        <v>4019</v>
+        <v>3995</v>
       </c>
     </row>
     <row r="410" spans="1:10">
@@ -28128,10 +28141,10 @@
         <v>3122</v>
       </c>
       <c r="I410" s="14" t="s">
-        <v>3653</v>
+        <v>3629</v>
       </c>
       <c r="J410" s="14" t="s">
-        <v>4018</v>
+        <v>3994</v>
       </c>
     </row>
     <row r="411" spans="1:10">
@@ -28160,10 +28173,10 @@
         <v>3123</v>
       </c>
       <c r="I411" s="14" t="s">
-        <v>3654</v>
+        <v>3630</v>
       </c>
       <c r="J411" s="14" t="s">
-        <v>4017</v>
+        <v>3993</v>
       </c>
     </row>
     <row r="412" spans="1:10">
@@ -28192,10 +28205,10 @@
         <v>3124</v>
       </c>
       <c r="I412" s="14" t="s">
-        <v>3655</v>
+        <v>3631</v>
       </c>
       <c r="J412" s="14" t="s">
-        <v>4028</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="413" spans="1:10">
@@ -28224,10 +28237,10 @@
         <v>3125</v>
       </c>
       <c r="I413" s="14" t="s">
-        <v>3656</v>
+        <v>3632</v>
       </c>
       <c r="J413" s="14" t="s">
-        <v>4023</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="414" spans="1:10">
@@ -28256,10 +28269,10 @@
         <v>3126</v>
       </c>
       <c r="I414" s="14" t="s">
-        <v>3657</v>
+        <v>3633</v>
       </c>
       <c r="J414" s="14" t="s">
-        <v>4024</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="415" spans="1:10">
@@ -28288,10 +28301,10 @@
         <v>3127</v>
       </c>
       <c r="I415" s="14" t="s">
-        <v>3658</v>
+        <v>3634</v>
       </c>
       <c r="J415" s="14" t="s">
-        <v>4025</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="416" spans="1:10">
@@ -28320,10 +28333,10 @@
         <v>3128</v>
       </c>
       <c r="I416" s="14" t="s">
-        <v>3659</v>
+        <v>3635</v>
       </c>
       <c r="J416" s="14" t="s">
-        <v>4026</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="417" spans="1:10">
@@ -28352,10 +28365,10 @@
         <v>3129</v>
       </c>
       <c r="I417" s="14" t="s">
-        <v>3660</v>
+        <v>3636</v>
       </c>
       <c r="J417" s="14" t="s">
-        <v>4027</v>
+        <v>4003</v>
       </c>
     </row>
     <row r="418" spans="1:10">
@@ -28384,10 +28397,10 @@
         <v>3130</v>
       </c>
       <c r="I418" s="14" t="s">
-        <v>3661</v>
+        <v>3637</v>
       </c>
       <c r="J418" s="14" t="s">
-        <v>4020</v>
+        <v>3996</v>
       </c>
     </row>
     <row r="419" spans="1:10">
@@ -28416,10 +28429,10 @@
         <v>3131</v>
       </c>
       <c r="I419" s="14" t="s">
-        <v>3662</v>
+        <v>3638</v>
       </c>
       <c r="J419" s="14" t="s">
-        <v>4021</v>
+        <v>3997</v>
       </c>
     </row>
     <row r="420" spans="1:10">
@@ -28448,10 +28461,10 @@
         <v>3132</v>
       </c>
       <c r="I420" s="14" t="s">
-        <v>3663</v>
+        <v>3639</v>
       </c>
       <c r="J420" s="14" t="s">
-        <v>4022</v>
+        <v>3998</v>
       </c>
     </row>
     <row r="421" spans="1:10">
@@ -28480,10 +28493,10 @@
         <v>3133</v>
       </c>
       <c r="I421" s="14" t="s">
-        <v>3664</v>
+        <v>3640</v>
       </c>
       <c r="J421" s="14" t="s">
-        <v>3963</v>
+        <v>3939</v>
       </c>
     </row>
     <row r="422" spans="1:10">
@@ -28512,10 +28525,10 @@
         <v>3086</v>
       </c>
       <c r="I422" s="14" t="s">
-        <v>3665</v>
+        <v>3641</v>
       </c>
       <c r="J422" s="14" t="s">
-        <v>3964</v>
+        <v>3940</v>
       </c>
     </row>
     <row r="423" spans="1:10">
@@ -28544,10 +28557,10 @@
         <v>3091</v>
       </c>
       <c r="I423" s="14" t="s">
-        <v>3666</v>
+        <v>3642</v>
       </c>
       <c r="J423" s="14" t="s">
-        <v>3965</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="424" spans="1:10">
@@ -28576,10 +28589,10 @@
         <v>3092</v>
       </c>
       <c r="I424" s="14" t="s">
-        <v>3667</v>
+        <v>3643</v>
       </c>
       <c r="J424" s="14" t="s">
-        <v>3962</v>
+        <v>3938</v>
       </c>
     </row>
     <row r="425" spans="1:10">
@@ -28608,10 +28621,10 @@
         <v>3093</v>
       </c>
       <c r="I425" s="14" t="s">
-        <v>3668</v>
+        <v>3644</v>
       </c>
       <c r="J425" s="14" t="s">
-        <v>3961</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="426" spans="1:10">
@@ -28640,10 +28653,10 @@
         <v>3094</v>
       </c>
       <c r="I426" s="14" t="s">
-        <v>3644</v>
+        <v>3620</v>
       </c>
       <c r="J426" s="14" t="s">
-        <v>3958</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="427" spans="1:10">
@@ -28672,10 +28685,10 @@
         <v>3095</v>
       </c>
       <c r="I427" s="14" t="s">
-        <v>3645</v>
+        <v>3621</v>
       </c>
       <c r="J427" s="14" t="s">
-        <v>3959</v>
+        <v>3935</v>
       </c>
     </row>
     <row r="428" spans="1:10">
@@ -28704,10 +28717,10 @@
         <v>3096</v>
       </c>
       <c r="I428" s="14" t="s">
-        <v>3646</v>
+        <v>3622</v>
       </c>
       <c r="J428" s="14" t="s">
-        <v>3960</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="429" spans="1:10">
@@ -28736,10 +28749,10 @@
         <v>3090</v>
       </c>
       <c r="I429" s="14" t="s">
-        <v>3630</v>
+        <v>3606</v>
       </c>
       <c r="J429" s="14" t="s">
-        <v>3946</v>
+        <v>3922</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -28768,10 +28781,10 @@
         <v>3089</v>
       </c>
       <c r="I430" s="14" t="s">
-        <v>3631</v>
+        <v>3607</v>
       </c>
       <c r="J430" s="14" t="s">
-        <v>3947</v>
+        <v>3923</v>
       </c>
     </row>
     <row r="431" spans="1:10">
@@ -28800,10 +28813,10 @@
         <v>3079</v>
       </c>
       <c r="I431" s="14" t="s">
-        <v>3632</v>
+        <v>3608</v>
       </c>
       <c r="J431" s="14" t="s">
-        <v>3948</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="432" spans="1:10">
@@ -28832,10 +28845,10 @@
         <v>3080</v>
       </c>
       <c r="I432" s="14" t="s">
-        <v>3633</v>
+        <v>3609</v>
       </c>
       <c r="J432" s="14" t="s">
-        <v>3949</v>
+        <v>3925</v>
       </c>
     </row>
     <row r="433" spans="1:10">
@@ -28864,10 +28877,10 @@
         <v>3081</v>
       </c>
       <c r="I433" s="14" t="s">
-        <v>3613</v>
+        <v>3589</v>
       </c>
       <c r="J433" s="14" t="s">
-        <v>3950</v>
+        <v>3926</v>
       </c>
     </row>
     <row r="434" spans="1:10">
@@ -28896,10 +28909,10 @@
         <v>3082</v>
       </c>
       <c r="I434" s="14" t="s">
-        <v>3614</v>
+        <v>3590</v>
       </c>
       <c r="J434" s="14" t="s">
-        <v>3951</v>
+        <v>3927</v>
       </c>
     </row>
     <row r="435" spans="1:10">
@@ -28928,10 +28941,10 @@
         <v>3083</v>
       </c>
       <c r="I435" s="14" t="s">
-        <v>3615</v>
+        <v>3591</v>
       </c>
       <c r="J435" s="14" t="s">
-        <v>3952</v>
+        <v>3928</v>
       </c>
     </row>
     <row r="436" spans="1:10">
@@ -28960,10 +28973,10 @@
         <v>2836</v>
       </c>
       <c r="I436" s="14" t="s">
-        <v>3616</v>
+        <v>3592</v>
       </c>
       <c r="J436" s="14" t="s">
-        <v>3953</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="437" spans="1:10">
@@ -28992,10 +29005,10 @@
         <v>3084</v>
       </c>
       <c r="I437" s="14" t="s">
-        <v>3617</v>
+        <v>3593</v>
       </c>
       <c r="J437" s="14" t="s">
-        <v>3954</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="438" spans="1:10">
@@ -29024,10 +29037,10 @@
         <v>3085</v>
       </c>
       <c r="I438" s="14" t="s">
-        <v>3618</v>
+        <v>3594</v>
       </c>
       <c r="J438" s="14" t="s">
-        <v>3955</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="439" spans="1:10">
@@ -29056,10 +29069,10 @@
         <v>3078</v>
       </c>
       <c r="I439" s="14" t="s">
-        <v>3619</v>
+        <v>3595</v>
       </c>
       <c r="J439" s="14" t="s">
-        <v>3956</v>
+        <v>3932</v>
       </c>
     </row>
     <row r="440" spans="1:10">
@@ -29088,10 +29101,10 @@
         <v>3077</v>
       </c>
       <c r="I440" s="14" t="s">
-        <v>3620</v>
+        <v>3596</v>
       </c>
       <c r="J440" s="14" t="s">
-        <v>3957</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="441" spans="1:10">
@@ -29120,10 +29133,10 @@
         <v>3076</v>
       </c>
       <c r="I441" s="14" t="s">
-        <v>3621</v>
+        <v>3597</v>
       </c>
       <c r="J441" s="14" t="s">
-        <v>3939</v>
+        <v>3915</v>
       </c>
     </row>
     <row r="442" spans="1:10">
@@ -29152,10 +29165,10 @@
         <v>3075</v>
       </c>
       <c r="I442" s="14" t="s">
-        <v>3622</v>
+        <v>3598</v>
       </c>
       <c r="J442" s="14" t="s">
-        <v>3940</v>
+        <v>3916</v>
       </c>
     </row>
     <row r="443" spans="1:10">
@@ -29184,10 +29197,10 @@
         <v>3365</v>
       </c>
       <c r="I443" s="14" t="s">
-        <v>3623</v>
+        <v>3599</v>
       </c>
       <c r="J443" s="14" t="s">
-        <v>3941</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="444" spans="1:10">
@@ -29216,10 +29229,10 @@
         <v>3366</v>
       </c>
       <c r="I444" s="14" t="s">
-        <v>3624</v>
+        <v>3600</v>
       </c>
       <c r="J444" s="14" t="s">
-        <v>3942</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="445" spans="1:10">
@@ -29248,10 +29261,10 @@
         <v>3367</v>
       </c>
       <c r="I445" s="14" t="s">
-        <v>3625</v>
+        <v>3601</v>
       </c>
       <c r="J445" s="14" t="s">
-        <v>3943</v>
+        <v>3919</v>
       </c>
     </row>
     <row r="446" spans="1:10">
@@ -29280,10 +29293,10 @@
         <v>3368</v>
       </c>
       <c r="I446" s="14" t="s">
-        <v>3626</v>
+        <v>3602</v>
       </c>
       <c r="J446" s="14" t="s">
-        <v>3944</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="447" spans="1:10">
@@ -29312,10 +29325,10 @@
         <v>3369</v>
       </c>
       <c r="I447" s="14" t="s">
-        <v>3627</v>
+        <v>3603</v>
       </c>
       <c r="J447" s="14" t="s">
-        <v>3945</v>
+        <v>3921</v>
       </c>
     </row>
     <row r="448" spans="1:10">
@@ -29344,10 +29357,10 @@
         <v>3370</v>
       </c>
       <c r="I448" s="14" t="s">
-        <v>3628</v>
+        <v>3604</v>
       </c>
       <c r="J448" s="14" t="s">
-        <v>3937</v>
+        <v>3913</v>
       </c>
     </row>
     <row r="449" spans="1:10">
@@ -29376,10 +29389,10 @@
         <v>3371</v>
       </c>
       <c r="I449" s="14" t="s">
-        <v>3629</v>
+        <v>3605</v>
       </c>
       <c r="J449" s="14" t="s">
-        <v>3938</v>
+        <v>3914</v>
       </c>
     </row>
     <row r="450" spans="1:10">
@@ -29408,10 +29421,10 @@
         <v>3082</v>
       </c>
       <c r="I450" s="14" t="s">
-        <v>3603</v>
+        <v>3579</v>
       </c>
       <c r="J450" s="14" t="s">
-        <v>3936</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="451" spans="1:10">
@@ -29440,10 +29453,10 @@
         <v>3293</v>
       </c>
       <c r="I451" s="14" t="s">
-        <v>3604</v>
+        <v>3580</v>
       </c>
       <c r="J451" s="14" t="s">
-        <v>3930</v>
+        <v>3906</v>
       </c>
     </row>
     <row r="452" spans="1:10">
@@ -29472,10 +29485,10 @@
         <v>3105</v>
       </c>
       <c r="I452" s="14" t="s">
-        <v>3605</v>
+        <v>3581</v>
       </c>
       <c r="J452" s="14" t="s">
-        <v>3931</v>
+        <v>3907</v>
       </c>
     </row>
     <row r="453" spans="1:10">
@@ -29504,10 +29517,10 @@
         <v>3372</v>
       </c>
       <c r="I453" s="14" t="s">
-        <v>3606</v>
+        <v>3582</v>
       </c>
       <c r="J453" s="14" t="s">
-        <v>3932</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="454" spans="1:10">
@@ -29536,10 +29549,10 @@
         <v>3373</v>
       </c>
       <c r="I454" s="14" t="s">
-        <v>3607</v>
+        <v>3583</v>
       </c>
       <c r="J454" s="14" t="s">
-        <v>3933</v>
+        <v>3909</v>
       </c>
     </row>
     <row r="455" spans="1:10">
@@ -29568,10 +29581,10 @@
         <v>3274</v>
       </c>
       <c r="I455" s="14" t="s">
-        <v>3608</v>
+        <v>3584</v>
       </c>
       <c r="J455" s="14" t="s">
-        <v>3934</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="456" spans="1:10">
@@ -29600,10 +29613,10 @@
         <v>3374</v>
       </c>
       <c r="I456" s="14" t="s">
-        <v>3609</v>
+        <v>3585</v>
       </c>
       <c r="J456" s="14" t="s">
-        <v>3935</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="457" spans="1:10">
@@ -29632,10 +29645,10 @@
         <v>3375</v>
       </c>
       <c r="I457" s="14" t="s">
-        <v>3610</v>
+        <v>3586</v>
       </c>
       <c r="J457" s="14" t="s">
-        <v>3927</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="458" spans="1:10">
@@ -29664,10 +29677,10 @@
         <v>3376</v>
       </c>
       <c r="I458" s="14" t="s">
-        <v>3611</v>
+        <v>3587</v>
       </c>
       <c r="J458" s="14" t="s">
-        <v>3928</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="459" spans="1:10">
@@ -29696,36 +29709,36 @@
         <v>3377</v>
       </c>
       <c r="I459" s="14" t="s">
-        <v>3612</v>
+        <v>3588</v>
       </c>
       <c r="J459" s="14" t="s">
-        <v>3929</v>
-      </c>
-    </row>
-    <row r="460" spans="1:10" ht="193">
+        <v>3905</v>
+      </c>
+    </row>
+    <row r="460" spans="1:10" ht="205">
       <c r="A460" s="33" t="s">
         <v>3378</v>
       </c>
       <c r="B460" s="34" t="s">
-        <v>3383</v>
+        <v>4688</v>
       </c>
       <c r="C460" s="34" t="s">
-        <v>3399</v>
+        <v>4689</v>
       </c>
       <c r="D460" s="34" t="s">
-        <v>4390</v>
+        <v>4690</v>
       </c>
       <c r="E460" s="34" t="s">
-        <v>3390</v>
+        <v>4691</v>
       </c>
       <c r="F460" s="34" t="s">
-        <v>3389</v>
+        <v>4692</v>
       </c>
       <c r="G460" s="34" t="s">
-        <v>3406</v>
+        <v>4693</v>
       </c>
       <c r="H460" s="34" t="s">
-        <v>3400</v>
+        <v>4694</v>
       </c>
       <c r="I460" s="35"/>
       <c r="J460" s="35"/>
@@ -29735,25 +29748,25 @@
         <v>3379</v>
       </c>
       <c r="B461" s="34" t="s">
-        <v>3385</v>
+        <v>4695</v>
       </c>
       <c r="C461" s="34" t="s">
-        <v>3398</v>
+        <v>4696</v>
       </c>
       <c r="D461" s="30" t="s">
-        <v>4715</v>
+        <v>4697</v>
       </c>
       <c r="E461" s="34" t="s">
-        <v>3391</v>
+        <v>4698</v>
       </c>
       <c r="F461" s="34" t="s">
-        <v>3386</v>
+        <v>4699</v>
       </c>
       <c r="G461" s="30" t="s">
-        <v>4716</v>
+        <v>4687</v>
       </c>
       <c r="H461" s="34" t="s">
-        <v>3401</v>
+        <v>4700</v>
       </c>
       <c r="I461" s="14"/>
       <c r="J461" s="14"/>
@@ -29763,31 +29776,31 @@
         <v>3380</v>
       </c>
       <c r="B462" s="30" t="s">
-        <v>3384</v>
+        <v>4701</v>
       </c>
       <c r="C462" s="30" t="s">
-        <v>3397</v>
+        <v>4702</v>
       </c>
       <c r="D462" s="30" t="s">
-        <v>3394</v>
+        <v>4703</v>
       </c>
       <c r="E462" s="30" t="s">
-        <v>3392</v>
+        <v>4704</v>
       </c>
       <c r="F462" s="30" t="s">
-        <v>3387</v>
+        <v>4705</v>
       </c>
       <c r="G462" s="30" t="s">
-        <v>3405</v>
+        <v>3389</v>
       </c>
       <c r="H462" s="30" t="s">
-        <v>3402</v>
+        <v>4706</v>
       </c>
       <c r="I462" s="14" t="s">
-        <v>4302</v>
+        <v>4707</v>
       </c>
       <c r="J462" s="14" t="s">
-        <v>4300</v>
+        <v>4708</v>
       </c>
     </row>
     <row r="463" spans="1:10">
@@ -29798,1436 +29811,1436 @@
         <v>3382</v>
       </c>
       <c r="C463" s="30" t="s">
-        <v>3396</v>
+        <v>3386</v>
       </c>
       <c r="D463" s="30" t="s">
-        <v>3395</v>
+        <v>3385</v>
       </c>
       <c r="E463" s="30" t="s">
-        <v>3393</v>
+        <v>3384</v>
       </c>
       <c r="F463" s="30" t="s">
+        <v>3383</v>
+      </c>
+      <c r="G463" s="30" t="s">
         <v>3388</v>
       </c>
-      <c r="G463" s="30" t="s">
-        <v>3404</v>
-      </c>
       <c r="H463" s="30" t="s">
-        <v>3403</v>
+        <v>3387</v>
       </c>
       <c r="I463" s="14" t="s">
-        <v>4301</v>
+        <v>4276</v>
       </c>
       <c r="J463" s="14" t="s">
-        <v>3926</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="464" spans="1:10">
       <c r="A464" s="33" t="s">
-        <v>3407</v>
+        <v>3390</v>
       </c>
       <c r="B464" s="30" t="s">
-        <v>3408</v>
+        <v>3391</v>
       </c>
       <c r="C464" s="30" t="s">
-        <v>3408</v>
+        <v>3391</v>
       </c>
       <c r="D464" s="3" t="s">
-        <v>3415</v>
+        <v>3396</v>
       </c>
       <c r="E464" s="30" t="s">
-        <v>3418</v>
+        <v>3398</v>
       </c>
       <c r="F464" s="30" t="s">
-        <v>3421</v>
+        <v>3400</v>
       </c>
       <c r="G464" s="4" t="s">
-        <v>3424</v>
+        <v>3402</v>
       </c>
       <c r="H464" s="4" t="s">
-        <v>3428</v>
+        <v>3405</v>
       </c>
       <c r="I464" s="14" t="s">
-        <v>3642</v>
+        <v>3618</v>
       </c>
       <c r="J464" s="14" t="s">
-        <v>3925</v>
+        <v>3901</v>
       </c>
     </row>
     <row r="465" spans="1:10" ht="25">
       <c r="A465" s="33" t="s">
-        <v>3409</v>
+        <v>3392</v>
       </c>
       <c r="B465" s="34" t="s">
-        <v>3410</v>
+        <v>4709</v>
       </c>
       <c r="C465" s="30" t="s">
-        <v>3413</v>
+        <v>4710</v>
       </c>
       <c r="D465" s="30" t="s">
-        <v>3417</v>
+        <v>4711</v>
       </c>
       <c r="E465" s="30" t="s">
-        <v>3420</v>
+        <v>4712</v>
       </c>
       <c r="F465" s="30" t="s">
-        <v>3423</v>
+        <v>4713</v>
       </c>
       <c r="G465" s="30" t="s">
-        <v>3426</v>
+        <v>4714</v>
       </c>
       <c r="H465" s="30" t="s">
-        <v>3429</v>
+        <v>4715</v>
       </c>
       <c r="I465" s="35"/>
       <c r="J465" s="35"/>
     </row>
     <row r="466" spans="1:10">
       <c r="A466" s="33" t="s">
-        <v>3411</v>
+        <v>3393</v>
       </c>
       <c r="B466" s="30" t="s">
-        <v>3412</v>
+        <v>3394</v>
       </c>
       <c r="C466" s="30" t="s">
-        <v>3414</v>
+        <v>3395</v>
       </c>
       <c r="D466" s="30" t="s">
-        <v>3416</v>
+        <v>3397</v>
       </c>
       <c r="E466" s="30" t="s">
-        <v>3419</v>
+        <v>3399</v>
       </c>
       <c r="F466" s="30" t="s">
-        <v>3422</v>
+        <v>3401</v>
       </c>
       <c r="G466" s="4" t="s">
-        <v>3425</v>
+        <v>3403</v>
       </c>
       <c r="H466" s="4" t="s">
-        <v>3427</v>
+        <v>3404</v>
       </c>
       <c r="I466" s="14" t="s">
-        <v>3643</v>
+        <v>3619</v>
       </c>
       <c r="J466" s="14" t="s">
-        <v>3924</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="467" spans="1:10">
       <c r="A467" s="33" t="s">
-        <v>4303</v>
+        <v>4277</v>
       </c>
       <c r="B467" s="30" t="s">
-        <v>4304</v>
+        <v>4278</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>4315</v>
+        <v>4289</v>
       </c>
       <c r="D467" s="3" t="s">
-        <v>4321</v>
+        <v>4295</v>
       </c>
       <c r="E467" s="3" t="s">
-        <v>4315</v>
+        <v>4289</v>
       </c>
       <c r="F467" s="3" t="s">
-        <v>4332</v>
+        <v>4306</v>
       </c>
       <c r="G467" s="4" t="s">
         <v>1254</v>
       </c>
       <c r="H467" s="4" t="s">
-        <v>4358</v>
+        <v>4332</v>
       </c>
       <c r="I467" s="14" t="s">
-        <v>4338</v>
+        <v>4312</v>
       </c>
       <c r="J467" s="14" t="s">
-        <v>4344</v>
+        <v>4318</v>
       </c>
     </row>
     <row r="468" spans="1:10">
       <c r="A468" s="33" t="s">
-        <v>4305</v>
+        <v>4279</v>
       </c>
       <c r="B468" s="30" t="s">
-        <v>4306</v>
+        <v>4280</v>
       </c>
       <c r="C468" s="3" t="s">
-        <v>4316</v>
+        <v>4290</v>
       </c>
       <c r="D468" s="3" t="s">
+        <v>4298</v>
+      </c>
+      <c r="E468" s="3" t="s">
+        <v>4301</v>
+      </c>
+      <c r="F468" s="3" t="s">
+        <v>4307</v>
+      </c>
+      <c r="G468" s="4" t="s">
         <v>4324</v>
       </c>
-      <c r="E468" s="3" t="s">
-        <v>4327</v>
-      </c>
-      <c r="F468" s="3" t="s">
+      <c r="H468" s="4" t="s">
         <v>4333</v>
       </c>
-      <c r="G468" s="4" t="s">
-        <v>4350</v>
-      </c>
-      <c r="H468" s="4" t="s">
-        <v>4359</v>
-      </c>
       <c r="I468" s="14" t="s">
-        <v>4339</v>
+        <v>4313</v>
       </c>
       <c r="J468" s="14" t="s">
-        <v>4345</v>
+        <v>4319</v>
       </c>
     </row>
     <row r="469" spans="1:10">
       <c r="A469" s="33" t="s">
-        <v>4307</v>
+        <v>4281</v>
       </c>
       <c r="B469" s="30" t="s">
+        <v>4282</v>
+      </c>
+      <c r="C469" s="3" t="s">
+        <v>4291</v>
+      </c>
+      <c r="D469" s="3" t="s">
+        <v>4299</v>
+      </c>
+      <c r="E469" s="3" t="s">
+        <v>4302</v>
+      </c>
+      <c r="F469" s="3" t="s">
         <v>4308</v>
       </c>
-      <c r="C469" s="3" t="s">
-        <v>4317</v>
-      </c>
-      <c r="D469" s="3" t="s">
+      <c r="G469" s="4" t="s">
         <v>4325</v>
       </c>
-      <c r="E469" s="3" t="s">
-        <v>4328</v>
-      </c>
-      <c r="F469" s="3" t="s">
+      <c r="H469" s="4" t="s">
         <v>4334</v>
       </c>
-      <c r="G469" s="4" t="s">
-        <v>4351</v>
-      </c>
-      <c r="H469" s="4" t="s">
-        <v>4360</v>
-      </c>
       <c r="I469" s="14" t="s">
-        <v>4340</v>
+        <v>4314</v>
       </c>
       <c r="J469" s="14" t="s">
-        <v>4346</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="470" spans="1:10">
       <c r="A470" s="33" t="s">
+        <v>4283</v>
+      </c>
+      <c r="B470" s="30" t="s">
+        <v>4284</v>
+      </c>
+      <c r="C470" s="3" t="s">
+        <v>4292</v>
+      </c>
+      <c r="D470" s="3" t="s">
+        <v>4296</v>
+      </c>
+      <c r="E470" s="3" t="s">
+        <v>4303</v>
+      </c>
+      <c r="F470" s="3" t="s">
         <v>4309</v>
       </c>
-      <c r="B470" s="30" t="s">
-        <v>4310</v>
-      </c>
-      <c r="C470" s="3" t="s">
-        <v>4318</v>
-      </c>
-      <c r="D470" s="3" t="s">
-        <v>4322</v>
-      </c>
-      <c r="E470" s="3" t="s">
-        <v>4329</v>
-      </c>
-      <c r="F470" s="3" t="s">
+      <c r="G470" s="4" t="s">
+        <v>4328</v>
+      </c>
+      <c r="H470" s="4" t="s">
         <v>4335</v>
       </c>
-      <c r="G470" s="4" t="s">
-        <v>4354</v>
-      </c>
-      <c r="H470" s="4" t="s">
-        <v>4361</v>
-      </c>
       <c r="I470" s="14" t="s">
-        <v>4341</v>
+        <v>4315</v>
       </c>
       <c r="J470" s="14" t="s">
-        <v>4347</v>
+        <v>4321</v>
       </c>
     </row>
     <row r="471" spans="1:10">
       <c r="A471" s="33" t="s">
-        <v>4311</v>
+        <v>4285</v>
       </c>
       <c r="B471" s="30" t="s">
-        <v>4312</v>
+        <v>4286</v>
       </c>
       <c r="C471" s="3" t="s">
-        <v>4319</v>
+        <v>4293</v>
       </c>
       <c r="D471" s="3" t="s">
-        <v>4323</v>
+        <v>4297</v>
       </c>
       <c r="E471" s="3" t="s">
-        <v>4330</v>
+        <v>4304</v>
       </c>
       <c r="F471" s="3" t="s">
+        <v>4310</v>
+      </c>
+      <c r="G471" s="4" t="s">
+        <v>4326</v>
+      </c>
+      <c r="H471" s="4" t="s">
         <v>4336</v>
       </c>
-      <c r="G471" s="4" t="s">
-        <v>4352</v>
-      </c>
-      <c r="H471" s="4" t="s">
-        <v>4362</v>
-      </c>
       <c r="I471" s="14" t="s">
-        <v>4342</v>
+        <v>4316</v>
       </c>
       <c r="J471" s="14" t="s">
-        <v>4348</v>
+        <v>4322</v>
       </c>
     </row>
     <row r="472" spans="1:10">
       <c r="A472" s="33" t="s">
-        <v>4313</v>
+        <v>4287</v>
       </c>
       <c r="B472" s="30" t="s">
-        <v>4314</v>
+        <v>4288</v>
       </c>
       <c r="C472" s="3" t="s">
-        <v>4320</v>
+        <v>4294</v>
       </c>
       <c r="D472" s="3" t="s">
-        <v>4326</v>
+        <v>4300</v>
       </c>
       <c r="E472" s="3" t="s">
-        <v>4331</v>
+        <v>4305</v>
       </c>
       <c r="F472" s="3" t="s">
+        <v>4311</v>
+      </c>
+      <c r="G472" s="4" t="s">
+        <v>4327</v>
+      </c>
+      <c r="H472" s="4" t="s">
         <v>4337</v>
       </c>
-      <c r="G472" s="4" t="s">
-        <v>4353</v>
-      </c>
-      <c r="H472" s="4" t="s">
-        <v>4363</v>
-      </c>
       <c r="I472" s="14" t="s">
-        <v>4343</v>
+        <v>4317</v>
       </c>
       <c r="J472" s="14" t="s">
-        <v>4349</v>
+        <v>4323</v>
       </c>
     </row>
     <row r="473" spans="1:10">
       <c r="A473" s="33" t="s">
-        <v>4355</v>
+        <v>4329</v>
       </c>
       <c r="B473" s="30" t="s">
-        <v>4356</v>
+        <v>4330</v>
       </c>
       <c r="C473" s="3" t="s">
-        <v>4370</v>
+        <v>4344</v>
       </c>
       <c r="D473" s="3" t="s">
-        <v>4369</v>
+        <v>4343</v>
       </c>
       <c r="E473" s="3" t="s">
-        <v>4368</v>
+        <v>4342</v>
       </c>
       <c r="F473" s="3" t="s">
-        <v>4367</v>
+        <v>4341</v>
       </c>
       <c r="G473" s="4" t="s">
-        <v>4357</v>
+        <v>4331</v>
       </c>
       <c r="H473" s="4" t="s">
-        <v>4364</v>
+        <v>4338</v>
       </c>
       <c r="I473" s="14" t="s">
-        <v>4366</v>
+        <v>4340</v>
       </c>
       <c r="J473" s="14" t="s">
-        <v>4365</v>
+        <v>4339</v>
       </c>
     </row>
     <row r="474" spans="1:10">
       <c r="A474" s="33" t="s">
-        <v>4371</v>
+        <v>4345</v>
       </c>
       <c r="B474" s="30" t="s">
-        <v>4372</v>
+        <v>4346</v>
       </c>
       <c r="C474" s="3" t="s">
-        <v>4373</v>
+        <v>4347</v>
       </c>
       <c r="D474" s="3" t="s">
-        <v>4374</v>
+        <v>4348</v>
       </c>
       <c r="E474" s="3" t="s">
-        <v>4375</v>
+        <v>4349</v>
       </c>
       <c r="F474" s="3" t="s">
-        <v>4376</v>
+        <v>4350</v>
       </c>
       <c r="G474" s="4" t="s">
-        <v>4378</v>
+        <v>4352</v>
       </c>
       <c r="H474" s="4" t="s">
-        <v>4377</v>
+        <v>4351</v>
       </c>
       <c r="I474" s="14" t="s">
-        <v>4380</v>
+        <v>4354</v>
       </c>
       <c r="J474" s="14" t="s">
-        <v>4379</v>
+        <v>4353</v>
       </c>
     </row>
     <row r="475" spans="1:10">
       <c r="A475" s="33" t="s">
-        <v>4382</v>
+        <v>4356</v>
       </c>
       <c r="B475" s="30" t="s">
-        <v>4381</v>
+        <v>4355</v>
       </c>
       <c r="C475" s="3" t="s">
-        <v>4386</v>
+        <v>4360</v>
       </c>
       <c r="D475" s="3" t="s">
-        <v>4381</v>
+        <v>4355</v>
       </c>
       <c r="E475" s="3" t="s">
-        <v>4386</v>
+        <v>4360</v>
       </c>
       <c r="F475" s="3" t="s">
-        <v>4383</v>
+        <v>4357</v>
       </c>
       <c r="G475" s="4" t="s">
-        <v>4387</v>
+        <v>4361</v>
       </c>
       <c r="H475" s="3" t="s">
-        <v>4381</v>
+        <v>4355</v>
       </c>
       <c r="I475" s="14" t="s">
-        <v>4384</v>
+        <v>4358</v>
       </c>
       <c r="J475" s="14" t="s">
-        <v>4385</v>
+        <v>4359</v>
       </c>
     </row>
     <row r="476" spans="1:10">
       <c r="A476" s="33" t="s">
-        <v>4391</v>
+        <v>4364</v>
       </c>
       <c r="B476" s="30" t="s">
-        <v>4392</v>
+        <v>4365</v>
       </c>
       <c r="C476" s="10" t="s">
-        <v>4425</v>
+        <v>4398</v>
       </c>
       <c r="D476" s="3" t="s">
-        <v>4435</v>
+        <v>4408</v>
       </c>
       <c r="E476" s="3" t="s">
-        <v>4430</v>
+        <v>4403</v>
       </c>
       <c r="F476" s="10" t="s">
-        <v>4439</v>
+        <v>4412</v>
       </c>
       <c r="G476" s="7" t="s">
-        <v>4454</v>
+        <v>4427</v>
       </c>
       <c r="H476" s="11" t="s">
-        <v>4459</v>
+        <v>4432</v>
       </c>
       <c r="I476" s="14" t="s">
-        <v>4449</v>
+        <v>4422</v>
       </c>
       <c r="J476" s="14" t="s">
-        <v>4444</v>
+        <v>4417</v>
       </c>
     </row>
     <row r="477" spans="1:10" ht="49">
       <c r="A477" s="33" t="s">
-        <v>4393</v>
+        <v>4366</v>
       </c>
       <c r="B477" s="34" t="s">
-        <v>4394</v>
+        <v>4367</v>
       </c>
       <c r="C477" s="10" t="s">
-        <v>4426</v>
+        <v>4399</v>
       </c>
       <c r="D477" s="10" t="s">
-        <v>4436</v>
+        <v>4409</v>
       </c>
       <c r="E477" s="10" t="s">
-        <v>4431</v>
+        <v>4404</v>
       </c>
       <c r="F477" s="10" t="s">
-        <v>4440</v>
+        <v>4413</v>
       </c>
       <c r="G477" s="7" t="s">
-        <v>4455</v>
+        <v>4428</v>
       </c>
       <c r="H477" s="10" t="s">
-        <v>4460</v>
+        <v>4433</v>
       </c>
       <c r="I477" s="35" t="s">
-        <v>4450</v>
+        <v>4423</v>
       </c>
       <c r="J477" s="35" t="s">
-        <v>4445</v>
+        <v>4418</v>
       </c>
     </row>
     <row r="478" spans="1:10" ht="97">
       <c r="A478" s="33" t="s">
-        <v>4395</v>
+        <v>4368</v>
       </c>
       <c r="B478" s="34" t="s">
-        <v>4396</v>
+        <v>4369</v>
       </c>
       <c r="C478" s="10" t="s">
-        <v>4427</v>
+        <v>4400</v>
       </c>
       <c r="D478" s="10" t="s">
-        <v>4699</v>
+        <v>4672</v>
       </c>
       <c r="E478" s="10" t="s">
-        <v>4432</v>
+        <v>4405</v>
       </c>
       <c r="F478" s="10" t="s">
-        <v>4441</v>
+        <v>4414</v>
       </c>
       <c r="G478" s="7" t="s">
-        <v>4456</v>
+        <v>4429</v>
       </c>
       <c r="H478" s="10" t="s">
-        <v>4461</v>
+        <v>4434</v>
       </c>
       <c r="I478" s="35" t="s">
-        <v>4451</v>
+        <v>4424</v>
       </c>
       <c r="J478" s="35" t="s">
-        <v>4446</v>
+        <v>4419</v>
       </c>
     </row>
     <row r="479" spans="1:10" ht="97">
       <c r="A479" s="33" t="s">
-        <v>4417</v>
+        <v>4390</v>
       </c>
       <c r="B479" s="34" t="s">
-        <v>4418</v>
+        <v>4391</v>
       </c>
       <c r="C479" s="10" t="s">
-        <v>4428</v>
+        <v>4401</v>
       </c>
       <c r="D479" s="10" t="s">
-        <v>4437</v>
+        <v>4410</v>
       </c>
       <c r="E479" s="10" t="s">
-        <v>4433</v>
+        <v>4406</v>
       </c>
       <c r="F479" s="10" t="s">
-        <v>4442</v>
+        <v>4415</v>
       </c>
       <c r="G479" s="8" t="s">
-        <v>4457</v>
+        <v>4430</v>
       </c>
       <c r="H479" s="10" t="s">
-        <v>4462</v>
+        <v>4435</v>
       </c>
       <c r="I479" s="35" t="s">
-        <v>4452</v>
+        <v>4425</v>
       </c>
       <c r="J479" s="35" t="s">
-        <v>4447</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="480" spans="1:10" ht="61">
       <c r="A480" s="33" t="s">
-        <v>4419</v>
+        <v>4392</v>
       </c>
       <c r="B480" s="34" t="s">
-        <v>4420</v>
+        <v>4393</v>
       </c>
       <c r="C480" s="10" t="s">
-        <v>4429</v>
+        <v>4402</v>
       </c>
       <c r="D480" s="10" t="s">
-        <v>4438</v>
+        <v>4411</v>
       </c>
       <c r="E480" s="10" t="s">
-        <v>4434</v>
+        <v>4407</v>
       </c>
       <c r="F480" s="10" t="s">
-        <v>4443</v>
+        <v>4416</v>
       </c>
       <c r="G480" s="8" t="s">
-        <v>4458</v>
+        <v>4431</v>
       </c>
       <c r="H480" s="10" t="s">
-        <v>4463</v>
+        <v>4436</v>
       </c>
       <c r="I480" s="35" t="s">
-        <v>4453</v>
+        <v>4426</v>
       </c>
       <c r="J480" s="35" t="s">
-        <v>4448</v>
+        <v>4421</v>
       </c>
     </row>
     <row r="481" spans="1:10" ht="61">
       <c r="A481" s="33" t="s">
-        <v>4421</v>
+        <v>4394</v>
       </c>
       <c r="B481" s="34" t="s">
-        <v>4422</v>
+        <v>4395</v>
       </c>
       <c r="C481" s="10" t="s">
-        <v>4464</v>
+        <v>4437</v>
       </c>
       <c r="D481" s="10" t="s">
-        <v>4471</v>
+        <v>4444</v>
       </c>
       <c r="E481" s="10" t="s">
-        <v>4473</v>
+        <v>4446</v>
       </c>
       <c r="F481" s="10" t="s">
-        <v>4480</v>
+        <v>4453</v>
       </c>
       <c r="G481" s="8" t="s">
-        <v>4506</v>
+        <v>4479</v>
       </c>
       <c r="H481" s="11" t="s">
-        <v>4499</v>
+        <v>4472</v>
       </c>
       <c r="I481" s="35" t="s">
-        <v>4493</v>
+        <v>4466</v>
       </c>
       <c r="J481" s="35" t="s">
-        <v>4487</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="482" spans="1:10" ht="85">
       <c r="A482" s="33" t="s">
-        <v>4397</v>
+        <v>4370</v>
       </c>
       <c r="B482" s="34" t="s">
-        <v>4398</v>
+        <v>4371</v>
       </c>
       <c r="C482" s="10" t="s">
-        <v>4465</v>
+        <v>4438</v>
       </c>
       <c r="D482" s="10" t="s">
-        <v>4710</v>
+        <v>4683</v>
       </c>
       <c r="E482" s="10" t="s">
-        <v>4474</v>
+        <v>4447</v>
       </c>
       <c r="F482" s="10" t="s">
-        <v>4481</v>
+        <v>4454</v>
       </c>
       <c r="G482" s="7" t="s">
-        <v>4507</v>
+        <v>4480</v>
       </c>
       <c r="H482" s="11" t="s">
-        <v>4500</v>
+        <v>4473</v>
       </c>
       <c r="I482" s="35" t="s">
-        <v>4494</v>
+        <v>4467</v>
       </c>
       <c r="J482" s="35" t="s">
-        <v>4488</v>
+        <v>4461</v>
       </c>
     </row>
     <row r="483" spans="1:10" ht="49">
       <c r="A483" s="33" t="s">
-        <v>4399</v>
+        <v>4372</v>
       </c>
       <c r="B483" s="34" t="s">
-        <v>4400</v>
+        <v>4373</v>
       </c>
       <c r="C483" s="10" t="s">
-        <v>4466</v>
+        <v>4439</v>
       </c>
       <c r="D483" s="10" t="s">
-        <v>4700</v>
+        <v>4673</v>
       </c>
       <c r="E483" s="10" t="s">
-        <v>4475</v>
+        <v>4448</v>
       </c>
       <c r="F483" s="10" t="s">
-        <v>4482</v>
+        <v>4455</v>
       </c>
       <c r="G483" s="7" t="s">
-        <v>4508</v>
+        <v>4481</v>
       </c>
       <c r="H483" s="11" t="s">
-        <v>4501</v>
+        <v>4474</v>
       </c>
       <c r="I483" s="35" t="s">
-        <v>4495</v>
+        <v>4468</v>
       </c>
       <c r="J483" s="35" t="s">
-        <v>4489</v>
+        <v>4462</v>
       </c>
     </row>
     <row r="484" spans="1:10" ht="85">
       <c r="A484" s="33" t="s">
-        <v>4401</v>
+        <v>4374</v>
       </c>
       <c r="B484" s="34" t="s">
-        <v>4402</v>
+        <v>4375</v>
       </c>
       <c r="C484" s="10" t="s">
-        <v>4467</v>
+        <v>4440</v>
       </c>
       <c r="D484" s="10" t="s">
-        <v>4711</v>
+        <v>4684</v>
       </c>
       <c r="E484" s="10" t="s">
-        <v>4476</v>
+        <v>4449</v>
       </c>
       <c r="F484" s="10" t="s">
-        <v>4483</v>
+        <v>4456</v>
       </c>
       <c r="G484" s="7" t="s">
-        <v>4509</v>
+        <v>4482</v>
       </c>
       <c r="H484" s="10" t="s">
-        <v>4502</v>
+        <v>4475</v>
       </c>
       <c r="I484" s="35"/>
       <c r="J484" s="35"/>
     </row>
     <row r="485" spans="1:10" ht="85">
       <c r="A485" s="33" t="s">
-        <v>4405</v>
+        <v>4378</v>
       </c>
       <c r="B485" s="34" t="s">
-        <v>4406</v>
+        <v>4379</v>
       </c>
       <c r="C485" s="10" t="s">
-        <v>4468</v>
+        <v>4441</v>
       </c>
       <c r="D485" s="10" t="s">
-        <v>4712</v>
+        <v>4685</v>
       </c>
       <c r="E485" s="10" t="s">
-        <v>4477</v>
+        <v>4450</v>
       </c>
       <c r="F485" s="10" t="s">
-        <v>4484</v>
+        <v>4457</v>
       </c>
       <c r="G485" s="8" t="s">
-        <v>4510</v>
+        <v>4483</v>
       </c>
       <c r="H485" s="10" t="s">
-        <v>4503</v>
+        <v>4476</v>
       </c>
       <c r="I485" s="35" t="s">
-        <v>4496</v>
+        <v>4469</v>
       </c>
       <c r="J485" s="35" t="s">
-        <v>4490</v>
+        <v>4463</v>
       </c>
     </row>
     <row r="486" spans="1:10" ht="61">
       <c r="A486" s="33" t="s">
-        <v>4403</v>
+        <v>4376</v>
       </c>
       <c r="B486" s="34" t="s">
-        <v>4404</v>
+        <v>4377</v>
       </c>
       <c r="C486" s="10" t="s">
-        <v>4469</v>
+        <v>4442</v>
       </c>
       <c r="D486" s="10" t="s">
-        <v>4701</v>
+        <v>4674</v>
       </c>
       <c r="E486" s="10" t="s">
-        <v>4478</v>
+        <v>4451</v>
       </c>
       <c r="F486" s="10" t="s">
-        <v>4485</v>
+        <v>4458</v>
       </c>
       <c r="G486" s="7" t="s">
-        <v>4511</v>
+        <v>4484</v>
       </c>
       <c r="H486" s="10" t="s">
-        <v>4504</v>
+        <v>4477</v>
       </c>
       <c r="I486" s="35" t="s">
-        <v>4497</v>
+        <v>4470</v>
       </c>
       <c r="J486" s="35" t="s">
-        <v>4491</v>
+        <v>4464</v>
       </c>
     </row>
     <row r="487" spans="1:10" ht="37">
       <c r="A487" s="33" t="s">
-        <v>4407</v>
+        <v>4380</v>
       </c>
       <c r="B487" s="34" t="s">
-        <v>4408</v>
+        <v>4381</v>
       </c>
       <c r="C487" s="10" t="s">
-        <v>4470</v>
+        <v>4443</v>
       </c>
       <c r="D487" s="10" t="s">
-        <v>4472</v>
+        <v>4445</v>
       </c>
       <c r="E487" s="10" t="s">
-        <v>4479</v>
+        <v>4452</v>
       </c>
       <c r="F487" s="10" t="s">
-        <v>4486</v>
+        <v>4459</v>
       </c>
       <c r="G487" s="7" t="s">
-        <v>4512</v>
+        <v>4485</v>
       </c>
       <c r="H487" s="10" t="s">
-        <v>4505</v>
+        <v>4478</v>
       </c>
       <c r="I487" s="35" t="s">
-        <v>4498</v>
+        <v>4471</v>
       </c>
       <c r="J487" s="35" t="s">
-        <v>4492</v>
+        <v>4465</v>
       </c>
     </row>
     <row r="488" spans="1:10" ht="73">
       <c r="A488" s="33" t="s">
-        <v>4409</v>
+        <v>4382</v>
       </c>
       <c r="B488" s="34" t="s">
-        <v>4410</v>
+        <v>4383</v>
       </c>
       <c r="C488" s="3" t="s">
-        <v>4521</v>
+        <v>4494</v>
       </c>
       <c r="D488" s="3" t="s">
-        <v>4525</v>
+        <v>4498</v>
       </c>
       <c r="E488" s="3" t="s">
-        <v>4529</v>
+        <v>4502</v>
       </c>
       <c r="F488" s="10" t="s">
-        <v>4533</v>
+        <v>4506</v>
       </c>
       <c r="G488" s="7" t="s">
-        <v>4537</v>
+        <v>4510</v>
       </c>
       <c r="H488" s="9" t="s">
-        <v>4541</v>
+        <v>4514</v>
       </c>
       <c r="I488" s="35" t="s">
-        <v>4516</v>
+        <v>4489</v>
       </c>
       <c r="J488" s="35" t="s">
-        <v>4517</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="489" spans="1:10">
       <c r="A489" s="33" t="s">
-        <v>4411</v>
+        <v>4384</v>
       </c>
       <c r="B489" s="30" t="s">
-        <v>4412</v>
+        <v>4385</v>
       </c>
       <c r="C489" s="3" t="s">
-        <v>4522</v>
+        <v>4495</v>
       </c>
       <c r="D489" s="3" t="s">
-        <v>4526</v>
+        <v>4499</v>
       </c>
       <c r="E489" s="3" t="s">
-        <v>4530</v>
+        <v>4503</v>
       </c>
       <c r="F489" s="10" t="s">
-        <v>4534</v>
+        <v>4507</v>
       </c>
       <c r="G489" s="7" t="s">
-        <v>4538</v>
+        <v>4511</v>
       </c>
       <c r="H489" s="9" t="s">
-        <v>4542</v>
+        <v>4515</v>
       </c>
       <c r="I489" s="35" t="s">
-        <v>4515</v>
+        <v>4488</v>
       </c>
       <c r="J489" s="35" t="s">
-        <v>4518</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="490" spans="1:10" ht="49">
       <c r="A490" s="33" t="s">
-        <v>4413</v>
+        <v>4386</v>
       </c>
       <c r="B490" s="34" t="s">
-        <v>4414</v>
+        <v>4387</v>
       </c>
       <c r="C490" s="3" t="s">
-        <v>4523</v>
+        <v>4496</v>
       </c>
       <c r="D490" s="3" t="s">
-        <v>4527</v>
+        <v>4500</v>
       </c>
       <c r="E490" s="3" t="s">
-        <v>4531</v>
+        <v>4504</v>
       </c>
       <c r="F490" s="10" t="s">
-        <v>4535</v>
+        <v>4508</v>
       </c>
       <c r="G490" s="9" t="s">
-        <v>4539</v>
+        <v>4512</v>
       </c>
       <c r="H490" s="9" t="s">
-        <v>4543</v>
+        <v>4516</v>
       </c>
       <c r="I490" s="35" t="s">
-        <v>4514</v>
+        <v>4487</v>
       </c>
       <c r="J490" s="35" t="s">
-        <v>4519</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="491" spans="1:10" ht="25">
       <c r="A491" s="33" t="s">
-        <v>4415</v>
+        <v>4388</v>
       </c>
       <c r="B491" s="30" t="s">
-        <v>4416</v>
+        <v>4389</v>
       </c>
       <c r="C491" s="3" t="s">
-        <v>4524</v>
+        <v>4497</v>
       </c>
       <c r="D491" s="3" t="s">
-        <v>4528</v>
+        <v>4501</v>
       </c>
       <c r="E491" s="3" t="s">
-        <v>4532</v>
+        <v>4505</v>
       </c>
       <c r="F491" s="10" t="s">
-        <v>4536</v>
+        <v>4509</v>
       </c>
       <c r="G491" s="9" t="s">
-        <v>4540</v>
+        <v>4513</v>
       </c>
       <c r="H491" s="10" t="s">
-        <v>4544</v>
+        <v>4517</v>
       </c>
       <c r="I491" s="35" t="s">
-        <v>4513</v>
+        <v>4486</v>
       </c>
       <c r="J491" s="35" t="s">
-        <v>4520</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="492" spans="1:10" ht="25">
       <c r="A492" s="33" t="s">
+        <v>4519</v>
+      </c>
+      <c r="B492" s="30" t="s">
+        <v>4524</v>
+      </c>
+      <c r="C492" s="3" t="s">
+        <v>4525</v>
+      </c>
+      <c r="D492" s="3" t="s">
+        <v>4528</v>
+      </c>
+      <c r="E492" s="3" t="s">
+        <v>4531</v>
+      </c>
+      <c r="F492" s="3" t="s">
+        <v>4534</v>
+      </c>
+      <c r="G492" s="11" t="s">
+        <v>4543</v>
+      </c>
+      <c r="H492" s="11" t="s">
         <v>4546</v>
       </c>
-      <c r="B492" s="30" t="s">
-        <v>4551</v>
-      </c>
-      <c r="C492" s="3" t="s">
-        <v>4552</v>
-      </c>
-      <c r="D492" s="3" t="s">
-        <v>4555</v>
-      </c>
-      <c r="E492" s="3" t="s">
-        <v>4558</v>
-      </c>
-      <c r="F492" s="3" t="s">
-        <v>4561</v>
-      </c>
-      <c r="G492" s="11" t="s">
-        <v>4570</v>
-      </c>
-      <c r="H492" s="11" t="s">
-        <v>4573</v>
-      </c>
       <c r="I492" s="14" t="s">
-        <v>4564</v>
+        <v>4537</v>
       </c>
       <c r="J492" s="14" t="s">
-        <v>4567</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="493" spans="1:10">
       <c r="A493" s="33" t="s">
+        <v>4520</v>
+      </c>
+      <c r="B493" s="30" t="s">
+        <v>4521</v>
+      </c>
+      <c r="C493" s="3" t="s">
+        <v>4526</v>
+      </c>
+      <c r="D493" s="3" t="s">
+        <v>4529</v>
+      </c>
+      <c r="E493" s="3" t="s">
+        <v>4532</v>
+      </c>
+      <c r="F493" s="3" t="s">
+        <v>4535</v>
+      </c>
+      <c r="G493" s="11" t="s">
+        <v>4544</v>
+      </c>
+      <c r="H493" s="11" t="s">
         <v>4547</v>
       </c>
-      <c r="B493" s="30" t="s">
-        <v>4548</v>
-      </c>
-      <c r="C493" s="3" t="s">
-        <v>4553</v>
-      </c>
-      <c r="D493" s="3" t="s">
-        <v>4556</v>
-      </c>
-      <c r="E493" s="3" t="s">
-        <v>4559</v>
-      </c>
-      <c r="F493" s="3" t="s">
-        <v>4562</v>
-      </c>
-      <c r="G493" s="11" t="s">
-        <v>4571</v>
-      </c>
-      <c r="H493" s="11" t="s">
-        <v>4574</v>
-      </c>
       <c r="I493" s="14" t="s">
-        <v>4565</v>
+        <v>4538</v>
       </c>
       <c r="J493" s="14" t="s">
-        <v>4568</v>
+        <v>4541</v>
       </c>
     </row>
     <row r="494" spans="1:10">
       <c r="A494" s="33" t="s">
-        <v>4549</v>
+        <v>4522</v>
       </c>
       <c r="B494" s="30" t="s">
-        <v>4550</v>
+        <v>4523</v>
       </c>
       <c r="C494" s="3" t="s">
-        <v>4554</v>
+        <v>4527</v>
       </c>
       <c r="D494" s="3" t="s">
-        <v>4557</v>
+        <v>4530</v>
       </c>
       <c r="E494" s="3" t="s">
-        <v>4560</v>
+        <v>4533</v>
       </c>
       <c r="F494" s="3" t="s">
-        <v>4563</v>
+        <v>4536</v>
       </c>
       <c r="G494" s="11" t="s">
-        <v>4572</v>
+        <v>4545</v>
       </c>
       <c r="H494" s="11" t="s">
-        <v>4575</v>
+        <v>4548</v>
       </c>
       <c r="I494" s="14" t="s">
-        <v>4566</v>
+        <v>4539</v>
       </c>
       <c r="J494" s="14" t="s">
-        <v>4569</v>
+        <v>4542</v>
       </c>
     </row>
     <row r="495" spans="1:10">
       <c r="A495" s="33" t="s">
-        <v>4576</v>
+        <v>4549</v>
       </c>
       <c r="B495" s="36" t="s">
-        <v>4589</v>
+        <v>4562</v>
       </c>
       <c r="C495" s="3" t="s">
-        <v>4602</v>
+        <v>4575</v>
       </c>
       <c r="D495" s="3" t="s">
-        <v>4614</v>
+        <v>4587</v>
       </c>
       <c r="E495" s="3" t="s">
-        <v>4625</v>
+        <v>4598</v>
       </c>
       <c r="F495" s="3" t="s">
         <v>2852</v>
       </c>
       <c r="G495" s="5" t="s">
-        <v>4679</v>
+        <v>4652</v>
       </c>
       <c r="H495" s="3" t="s">
-        <v>4667</v>
+        <v>4640</v>
       </c>
       <c r="I495" s="14" t="s">
-        <v>4646</v>
+        <v>4619</v>
       </c>
       <c r="J495" s="14" t="s">
-        <v>3957</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="496" spans="1:10">
       <c r="A496" s="33" t="s">
-        <v>4577</v>
+        <v>4550</v>
       </c>
       <c r="B496" s="36" t="s">
-        <v>4590</v>
+        <v>4563</v>
       </c>
       <c r="C496" s="3" t="s">
-        <v>4603</v>
+        <v>4576</v>
       </c>
       <c r="D496" s="3" t="s">
-        <v>4615</v>
+        <v>4588</v>
       </c>
       <c r="E496" s="3" t="s">
-        <v>4626</v>
+        <v>4599</v>
       </c>
       <c r="F496" s="3" t="s">
-        <v>4636</v>
+        <v>4609</v>
       </c>
       <c r="G496" s="5" t="s">
-        <v>4680</v>
+        <v>4653</v>
       </c>
       <c r="H496" s="3" t="s">
-        <v>4668</v>
+        <v>4641</v>
       </c>
       <c r="I496" s="14" t="s">
-        <v>4647</v>
+        <v>4620</v>
       </c>
       <c r="J496" s="14" t="s">
-        <v>4657</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="497" spans="1:10">
       <c r="A497" s="33" t="s">
-        <v>4578</v>
+        <v>4551</v>
       </c>
       <c r="B497" s="30" t="s">
-        <v>4591</v>
+        <v>4564</v>
       </c>
       <c r="C497" s="3" t="s">
-        <v>4604</v>
+        <v>4577</v>
       </c>
       <c r="D497" s="3" t="s">
-        <v>4616</v>
+        <v>4589</v>
       </c>
       <c r="E497" s="3" t="s">
-        <v>4604</v>
+        <v>4577</v>
       </c>
       <c r="F497" s="3" t="s">
-        <v>4637</v>
+        <v>4610</v>
       </c>
       <c r="G497" s="5" t="s">
-        <v>4681</v>
+        <v>4654</v>
       </c>
       <c r="H497" s="3" t="s">
-        <v>4669</v>
+        <v>4642</v>
       </c>
       <c r="I497" s="14" t="s">
-        <v>4648</v>
+        <v>4621</v>
       </c>
       <c r="J497" s="14" t="s">
-        <v>4658</v>
+        <v>4631</v>
       </c>
     </row>
     <row r="498" spans="1:10">
       <c r="A498" s="33" t="s">
-        <v>4579</v>
+        <v>4552</v>
       </c>
       <c r="B498" s="36" t="s">
-        <v>4592</v>
+        <v>4565</v>
       </c>
       <c r="C498" s="3" t="s">
-        <v>4605</v>
+        <v>4578</v>
       </c>
       <c r="D498" s="3" t="s">
-        <v>4617</v>
+        <v>4590</v>
       </c>
       <c r="E498" s="3" t="s">
-        <v>4627</v>
+        <v>4600</v>
       </c>
       <c r="F498" s="3" t="s">
-        <v>4638</v>
+        <v>4611</v>
       </c>
       <c r="G498" s="5" t="s">
-        <v>4682</v>
+        <v>4655</v>
       </c>
       <c r="H498" s="3" t="s">
-        <v>4670</v>
+        <v>4643</v>
       </c>
       <c r="I498" s="14" t="s">
-        <v>4649</v>
+        <v>4622</v>
       </c>
       <c r="J498" s="14" t="s">
-        <v>4659</v>
+        <v>4632</v>
       </c>
     </row>
     <row r="499" spans="1:10">
       <c r="A499" s="33" t="s">
-        <v>4580</v>
+        <v>4553</v>
       </c>
       <c r="B499" s="36" t="s">
-        <v>4593</v>
+        <v>4566</v>
       </c>
       <c r="C499" s="3" t="s">
-        <v>4606</v>
+        <v>4579</v>
       </c>
       <c r="D499" s="3" t="s">
-        <v>4615</v>
+        <v>4588</v>
       </c>
       <c r="E499" s="3" t="s">
-        <v>4628</v>
+        <v>4601</v>
       </c>
       <c r="F499" s="3" t="s">
-        <v>4636</v>
+        <v>4609</v>
       </c>
       <c r="G499" s="5" t="s">
-        <v>4683</v>
+        <v>4656</v>
       </c>
       <c r="H499" s="3" t="s">
-        <v>4671</v>
+        <v>4644</v>
       </c>
       <c r="I499" s="14" t="s">
-        <v>4647</v>
+        <v>4620</v>
       </c>
       <c r="J499" s="14" t="s">
-        <v>4657</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="500" spans="1:10">
       <c r="A500" s="33" t="s">
-        <v>4581</v>
+        <v>4554</v>
       </c>
       <c r="B500" s="36" t="s">
-        <v>4594</v>
+        <v>4567</v>
       </c>
       <c r="C500" s="3" t="s">
-        <v>4607</v>
+        <v>4580</v>
       </c>
       <c r="D500" s="3" t="s">
-        <v>4618</v>
+        <v>4591</v>
       </c>
       <c r="E500" s="3" t="s">
-        <v>4629</v>
+        <v>4602</v>
       </c>
       <c r="F500" s="3" t="s">
-        <v>4639</v>
+        <v>4612</v>
       </c>
       <c r="G500" s="5" t="s">
-        <v>4684</v>
+        <v>4657</v>
       </c>
       <c r="H500" s="3" t="s">
-        <v>4672</v>
+        <v>4645</v>
       </c>
       <c r="I500" s="14" t="s">
-        <v>4650</v>
+        <v>4623</v>
       </c>
       <c r="J500" s="14" t="s">
-        <v>4660</v>
+        <v>4633</v>
       </c>
     </row>
     <row r="501" spans="1:10">
       <c r="A501" s="33" t="s">
-        <v>4582</v>
+        <v>4555</v>
       </c>
       <c r="B501" s="36" t="s">
-        <v>4595</v>
+        <v>4568</v>
       </c>
       <c r="C501" s="3" t="s">
-        <v>4608</v>
+        <v>4581</v>
       </c>
       <c r="D501" s="3" t="s">
-        <v>4619</v>
+        <v>4592</v>
       </c>
       <c r="E501" s="3" t="s">
-        <v>4630</v>
+        <v>4603</v>
       </c>
       <c r="F501" s="3" t="s">
-        <v>4640</v>
+        <v>4613</v>
       </c>
       <c r="G501" s="5" t="s">
-        <v>4685</v>
+        <v>4658</v>
       </c>
       <c r="H501" s="3" t="s">
-        <v>4673</v>
+        <v>4646</v>
       </c>
       <c r="I501" s="14" t="s">
-        <v>4651</v>
+        <v>4624</v>
       </c>
       <c r="J501" s="14" t="s">
-        <v>4661</v>
+        <v>4634</v>
       </c>
     </row>
     <row r="502" spans="1:10">
       <c r="A502" s="33" t="s">
-        <v>4583</v>
+        <v>4556</v>
       </c>
       <c r="B502" s="36" t="s">
-        <v>4596</v>
+        <v>4569</v>
       </c>
       <c r="C502" s="3" t="s">
-        <v>4609</v>
+        <v>4582</v>
       </c>
       <c r="D502" s="3" t="s">
-        <v>4620</v>
+        <v>4593</v>
       </c>
       <c r="E502" s="3" t="s">
-        <v>4631</v>
+        <v>4604</v>
       </c>
       <c r="F502" s="3" t="s">
-        <v>4641</v>
+        <v>4614</v>
       </c>
       <c r="G502" s="5" t="s">
-        <v>4686</v>
+        <v>4659</v>
       </c>
       <c r="H502" s="3" t="s">
-        <v>4674</v>
+        <v>4647</v>
       </c>
       <c r="I502" s="14" t="s">
-        <v>4652</v>
+        <v>4625</v>
       </c>
       <c r="J502" s="14" t="s">
-        <v>4662</v>
+        <v>4635</v>
       </c>
     </row>
     <row r="503" spans="1:10">
       <c r="A503" s="33" t="s">
-        <v>4584</v>
+        <v>4557</v>
       </c>
       <c r="B503" s="36" t="s">
-        <v>4597</v>
+        <v>4570</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>4610</v>
+        <v>4583</v>
       </c>
       <c r="D503" s="3" t="s">
-        <v>4621</v>
+        <v>4594</v>
       </c>
       <c r="E503" s="3" t="s">
-        <v>4632</v>
+        <v>4605</v>
       </c>
       <c r="F503" s="3" t="s">
-        <v>4642</v>
+        <v>4615</v>
       </c>
       <c r="G503" s="5" t="s">
-        <v>4687</v>
+        <v>4660</v>
       </c>
       <c r="H503" s="3" t="s">
-        <v>4675</v>
+        <v>4648</v>
       </c>
       <c r="I503" s="14" t="s">
-        <v>4653</v>
+        <v>4626</v>
       </c>
       <c r="J503" s="14" t="s">
-        <v>4663</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="504" spans="1:10">
       <c r="A504" s="33" t="s">
-        <v>4585</v>
+        <v>4558</v>
       </c>
       <c r="B504" s="36" t="s">
-        <v>4598</v>
+        <v>4571</v>
       </c>
       <c r="C504" s="3" t="s">
-        <v>4611</v>
+        <v>4584</v>
       </c>
       <c r="D504" s="3" t="s">
-        <v>4622</v>
+        <v>4595</v>
       </c>
       <c r="E504" s="3" t="s">
-        <v>4633</v>
+        <v>4606</v>
       </c>
       <c r="F504" s="3" t="s">
-        <v>4643</v>
+        <v>4616</v>
       </c>
       <c r="G504" s="5" t="s">
-        <v>4688</v>
+        <v>4661</v>
       </c>
       <c r="H504" s="3" t="s">
-        <v>4676</v>
+        <v>4649</v>
       </c>
       <c r="I504" s="14" t="s">
-        <v>4654</v>
+        <v>4627</v>
       </c>
       <c r="J504" s="14" t="s">
-        <v>4664</v>
+        <v>4637</v>
       </c>
     </row>
     <row r="505" spans="1:10">
       <c r="A505" s="33" t="s">
-        <v>4586</v>
+        <v>4559</v>
       </c>
       <c r="B505" s="30" t="s">
-        <v>4599</v>
+        <v>4572</v>
       </c>
       <c r="C505" s="3" t="s">
-        <v>4612</v>
+        <v>4585</v>
       </c>
       <c r="D505" s="3" t="s">
-        <v>4623</v>
+        <v>4596</v>
       </c>
       <c r="E505" s="3" t="s">
-        <v>4634</v>
+        <v>4607</v>
       </c>
       <c r="F505" s="3" t="s">
-        <v>4644</v>
+        <v>4617</v>
       </c>
       <c r="G505" s="5" t="s">
-        <v>4689</v>
+        <v>4662</v>
       </c>
       <c r="H505" s="3" t="s">
-        <v>4677</v>
+        <v>4650</v>
       </c>
       <c r="I505" s="14" t="s">
-        <v>4655</v>
+        <v>4628</v>
       </c>
       <c r="J505" s="14" t="s">
-        <v>4665</v>
+        <v>4638</v>
       </c>
     </row>
     <row r="506" spans="1:10">
       <c r="A506" s="33" t="s">
-        <v>4587</v>
+        <v>4560</v>
       </c>
       <c r="B506" s="30" t="s">
-        <v>4600</v>
+        <v>4573</v>
       </c>
       <c r="C506" s="3" t="s">
-        <v>4691</v>
+        <v>4664</v>
       </c>
       <c r="D506" s="3" t="s">
-        <v>4692</v>
+        <v>4665</v>
       </c>
       <c r="E506" s="3" t="s">
-        <v>4693</v>
+        <v>4666</v>
       </c>
       <c r="F506" s="3" t="s">
-        <v>4694</v>
+        <v>4667</v>
       </c>
       <c r="G506" s="9" t="s">
-        <v>4697</v>
+        <v>4670</v>
       </c>
       <c r="H506" s="9" t="s">
-        <v>4698</v>
+        <v>4671</v>
       </c>
       <c r="I506" s="14" t="s">
-        <v>4695</v>
+        <v>4668</v>
       </c>
       <c r="J506" s="14" t="s">
-        <v>4696</v>
+        <v>4669</v>
       </c>
     </row>
     <row r="507" spans="1:10">
       <c r="A507" s="33" t="s">
-        <v>4588</v>
+        <v>4561</v>
       </c>
       <c r="B507" s="36" t="s">
-        <v>4601</v>
+        <v>4574</v>
       </c>
       <c r="C507" s="3" t="s">
-        <v>4613</v>
+        <v>4586</v>
       </c>
       <c r="D507" s="3" t="s">
-        <v>4624</v>
+        <v>4597</v>
       </c>
       <c r="E507" s="3" t="s">
-        <v>4635</v>
+        <v>4608</v>
       </c>
       <c r="F507" s="3" t="s">
-        <v>4645</v>
+        <v>4618</v>
       </c>
       <c r="G507" s="5" t="s">
-        <v>4690</v>
+        <v>4663</v>
       </c>
       <c r="H507" s="3" t="s">
-        <v>4678</v>
+        <v>4651</v>
       </c>
       <c r="I507" s="14" t="s">
-        <v>4656</v>
+        <v>4629</v>
       </c>
       <c r="J507" s="14" t="s">
-        <v>4666</v>
+        <v>4639</v>
       </c>
     </row>
     <row r="508" spans="1:10">
       <c r="A508" s="33" t="s">
-        <v>4702</v>
+        <v>4675</v>
       </c>
       <c r="B508" s="30" t="s">
-        <v>4706</v>
+        <v>4679</v>
       </c>
       <c r="C508" s="3"/>
       <c r="D508" s="3"/>
@@ -31240,10 +31253,10 @@
     </row>
     <row r="509" spans="1:10">
       <c r="A509" s="33" t="s">
-        <v>4703</v>
+        <v>4676</v>
       </c>
       <c r="B509" s="30" t="s">
-        <v>4707</v>
+        <v>4680</v>
       </c>
       <c r="C509" s="3"/>
       <c r="D509" s="3"/>
@@ -31256,10 +31269,10 @@
     </row>
     <row r="510" spans="1:10">
       <c r="A510" s="33" t="s">
-        <v>4704</v>
+        <v>4677</v>
       </c>
       <c r="B510" s="30" t="s">
-        <v>4708</v>
+        <v>4681</v>
       </c>
       <c r="C510" s="3"/>
       <c r="D510" s="3"/>
@@ -31272,10 +31285,10 @@
     </row>
     <row r="511" spans="1:10">
       <c r="A511" s="33" t="s">
-        <v>4705</v>
+        <v>4678</v>
       </c>
       <c r="B511" s="30" t="s">
-        <v>4713</v>
+        <v>4686</v>
       </c>
       <c r="C511" s="3"/>
       <c r="D511" s="3"/>
@@ -31288,10 +31301,10 @@
     </row>
     <row r="512" spans="1:10">
       <c r="A512" s="33" t="s">
-        <v>4424</v>
+        <v>4397</v>
       </c>
       <c r="B512" s="30" t="s">
-        <v>4709</v>
+        <v>4682</v>
       </c>
       <c r="C512" s="3"/>
       <c r="D512" s="3"/>
@@ -31304,10 +31317,10 @@
     </row>
     <row r="513" spans="1:10">
       <c r="A513" s="33" t="s">
-        <v>4423</v>
+        <v>4396</v>
       </c>
       <c r="B513" s="30" t="s">
-        <v>4714</v>
+        <v>4716</v>
       </c>
       <c r="C513" s="3"/>
       <c r="D513" s="3"/>
@@ -31317,6 +31330,14 @@
       <c r="H513" s="3"/>
       <c r="I513" s="14"/>
       <c r="J513" s="14"/>
+    </row>
+    <row r="514" spans="1:10">
+      <c r="A514" s="37" t="s">
+        <v>4717</v>
+      </c>
+      <c r="B514" t="s">
+        <v>4718</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -31330,26 +31351,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e0cf07b-8188-4b76-8f54-3cda03d37414" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="43e153a8-5ef1-4f65-aac7-dc4685f18eaa">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F12BE0DB4A3DF641BF113FBF1C7EA261" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c6b4b409d6b6c81c2874e5a51d11715e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="43e153a8-5ef1-4f65-aac7-dc4685f18eaa" xmlns:ns3="6e0cf07b-8188-4b76-8f54-3cda03d37414" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0521fade2ab7bf037697e8e8677cb864" ns2:_="" ns3:_="">
     <xsd:import namespace="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
@@ -31590,7 +31591,46 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e0cf07b-8188-4b76-8f54-3cda03d37414" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="43e153a8-5ef1-4f65-aac7-dc4685f18eaa">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6201EF1-2938-4925-833A-11BB4654F7B4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
+    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E20926E-9EFB-4B7E-90D4-905B08F8E59C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -31607,29 +31647,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6201EF1-2938-4925-833A-11BB4654F7B4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
-    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/translations/translations.xlsx
+++ b/translations/translations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/russell/Projects/GPS-Sample/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C65A7A-04B4-BE42-AD7B-51EFD0191B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA50984F-0FEC-C647-98EA-C7F2787C525F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
+    <workbookView xWindow="25140" yWindow="2220" windowWidth="29040" windowHeight="20340" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5076" uniqueCount="4719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5304" uniqueCount="4943">
   <si>
     <t>app_name</t>
   </si>
@@ -10311,42 +10311,21 @@
     <t>ایجاد نقطه داغ</t>
   </si>
   <si>
-    <t>سرور بسازید</t>
-  </si>
-  <si>
-    <t>کد QR ایجاد کنید</t>
-  </si>
-  <si>
     <t>اتصال به هات‌اسپات</t>
   </si>
   <si>
     <t>ثبت دستگاه</t>
   </si>
   <si>
-    <t>فرمان ارسال</t>
-  </si>
-  <si>
-    <t>ارسال داده‌های شمارش</t>
-  </si>
-  <si>
-    <t>دریافت داده‌ها</t>
-  </si>
-  <si>
     <t>پیکربندی دریافت شد</t>
   </si>
   <si>
     <t>نام میانی پدر</t>
   </si>
   <si>
-    <t>نام خانوادگی پیش از ازدواج مادر</t>
-  </si>
-  <si>
     <t>نام حیوان خانگی مورد علاقه</t>
   </si>
   <si>
-    <t>چهار رقم آخر شماره تلفن همراه</t>
-  </si>
-  <si>
     <t>غذای مورد علاقه</t>
   </si>
   <si>
@@ -10365,9 +10344,6 @@
     <t>۱۲ ساعته (صبح/عصر)</t>
   </si>
   <si>
-    <t>بیست و چهار ساعته</t>
-  </si>
-  <si>
     <t>متن</t>
   </si>
   <si>
@@ -10383,12 +10359,6 @@
     <t>منوی کشویی</t>
   </si>
   <si>
-    <t>برابرها</t>
-  </si>
-  <si>
-    <t>برابر نیست</t>
-  </si>
-  <si>
     <t>کمتر از</t>
   </si>
   <si>
@@ -10437,9 +10407,6 @@
     <t>شما هیچ مطالعه‌ای برای این پیکربندی ندارید.</t>
   </si>
   <si>
-    <t>داده‌جمع‌کن</t>
-  </si>
-  <si>
     <t>اسکن کد QR</t>
   </si>
   <si>
@@ -11634,15 +11601,6 @@
     <t>کیو آر کوډ جوړ کړئ</t>
   </si>
   <si>
-    <t>له هاټ سپاټ سره وصل شئ</t>
-  </si>
-  <si>
-    <t>سرور جوړ کړئ</t>
-  </si>
-  <si>
-    <t>هاټ سپاټ جوړ کړئ</t>
-  </si>
-  <si>
     <t>چک باکس</t>
   </si>
   <si>
@@ -11697,9 +11655,6 @@
     <t>د معلوماتو راټولونکی</t>
   </si>
   <si>
-    <t>QR کوډ سکین کړئ</t>
-  </si>
-  <si>
     <t>له موجوده مطالعې سره دوام ورکړئ</t>
   </si>
   <si>
@@ -11733,9 +11688,6 @@
     <t>د امر لیږل</t>
   </si>
   <si>
-    <t>د لیستولو معلوماتو لیږل</t>
-  </si>
-  <si>
     <t>د معلوماتو ترلاسه کول</t>
   </si>
   <si>
@@ -11743,9 +11695,6 @@
   </si>
   <si>
     <t>د پلار منځنی نوم</t>
-  </si>
-  <si>
-    <t>د مور د واده څخه مخکې تخلص</t>
   </si>
   <si>
     <t>د خوښې څاروي نوم</t>
@@ -14243,12 +14192,744 @@
   <si>
     <t>Enter the forgot PIN question</t>
   </si>
+  <si>
+    <t>collection_app</t>
+  </si>
+  <si>
+    <t>clone_configuration</t>
+  </si>
+  <si>
+    <t>confirm_clone_configuration</t>
+  </si>
+  <si>
+    <t>collector_import_error</t>
+  </si>
+  <si>
+    <t>missing_enumeration_area</t>
+  </si>
+  <si>
+    <t>missing_study</t>
+  </si>
+  <si>
+    <t>missing_enumeration_team</t>
+  </si>
+  <si>
+    <t>missing_collection_team</t>
+  </si>
+  <si>
+    <t>edit_enumeration_area</t>
+  </si>
+  <si>
+    <t>delete_all_enumeration_areas</t>
+  </si>
+  <si>
+    <t>delete_all_enumeration_areas_message</t>
+  </si>
+  <si>
+    <t>draw_boundary</t>
+  </si>
+  <si>
+    <t>tap_boundary</t>
+  </si>
+  <si>
+    <t>Tap the team boundary points on the map</t>
+  </si>
+  <si>
+    <t>Draw the team boundary on the map</t>
+  </si>
+  <si>
+    <t>Are you sure you want to permanently delete all Enumeration Areas?</t>
+  </si>
+  <si>
+    <t>Delete all Enumeration Areas</t>
+  </si>
+  <si>
+    <t>Edit Enumeration Area</t>
+  </si>
+  <si>
+    <t>This configuration does not have a Collection Team associated with it.</t>
+  </si>
+  <si>
+    <t>This configuration does not have an Enumeration Team associated with it.</t>
+  </si>
+  <si>
+    <t>This configuration does not have a Study associated with it.</t>
+  </si>
+  <si>
+    <t>This configuration does not have an Enumeration Area associated with it.</t>
+  </si>
+  <si>
+    <t>This configuration does not have an collection team associated with it.</t>
+  </si>
+  <si>
+    <t>Are you sure you want to Clone this Configuration?</t>
+  </si>
+  <si>
+    <t>Clone Configuration</t>
+  </si>
+  <si>
+    <t>Collection App</t>
+  </si>
+  <si>
+    <t>Administrador: se encarga de establecer la configuración completa, el estudio, el método de muestreo, las reglas y los filtros.</t>
+  </si>
+  <si>
+    <t>Administrateur : définit l'ensemble de la configuration, l'étude, la méthode d'échantillonnage, les règles et les filtres.</t>
+  </si>
+  <si>
+    <t>Administrador: Define toda a configuração, o estudo, o método de amostragem, as regras e os filtros.</t>
+  </si>
+  <si>
+    <t>Администратор: настраивает полную конфигурацию, исследование, метод отбора проб, правила и фильтры.</t>
+  </si>
+  <si>
+    <t>Administrator: Mengatur konfigurasi lengkap, studi, metode pengambilan sampel, aturan, dan filter.</t>
+  </si>
+  <si>
+    <t>Tagapangasiwa: Nagtatakda ng buong configuration, pag-aaral, paraan ng sampling, mga panuntunan, at mga filter.</t>
+  </si>
+  <si>
+    <t>مدیر: پیکربندی کامل، مطالعه، روش نمونه‌گیری، قوانین و فیلترها را تنظیم می‌کند.</t>
+  </si>
+  <si>
+    <t>مدیر: بشپړه تشکیلات، مطالعه، د نمونې اخیستنې طریقه، اصول او فلټرونه تنظیموي.</t>
+  </si>
+  <si>
+    <t>Supervisor: gestiona los equipos de campo, toma muestras y transfiere datos.</t>
+  </si>
+  <si>
+    <t>Superviseur : gère les équipes de terrain, prélève des échantillons et transfère les données.</t>
+  </si>
+  <si>
+    <t>Supervisor: Gere as equipas no terreno, recolhe amostras e transfere dados.</t>
+  </si>
+  <si>
+    <t>Супервайзер: управляет полевыми группами, отбирает пробы, передает данные.</t>
+  </si>
+  <si>
+    <t>Supervisor: Mengelola tim lapangan, menentukan sampel, dan mentransfer data.</t>
+  </si>
+  <si>
+    <t>Superbisor: Namamahala sa mga field team, kumukuha ng mga sample, naglilipat ng data.</t>
+  </si>
+  <si>
+    <t>سرپرست: تیم‌های میدانی را مدیریت می‌کند، نمونه‌برداری می‌کند، داده‌ها را منتقل می‌کند.</t>
+  </si>
+  <si>
+    <t>څارونکی: د ساحوي ټیمونو مدیریت کوي، نمونې اخلي، معلومات لېږدوي.</t>
+  </si>
+  <si>
+    <t>Encuestador: localiza y registra los hogares sobre el terreno.</t>
+  </si>
+  <si>
+    <t>Enquêteur : recense et répertorie les ménages sur le terrain.</t>
+  </si>
+  <si>
+    <t>Recenseador: Mapeia e regista os agregados familiares no terreno.</t>
+  </si>
+  <si>
+    <t>Интервьюер: наносит на карту и регистрирует домохозяйства в полевых условиях.</t>
+  </si>
+  <si>
+    <t>Enumerator: Melakukan pemetaan dan pendataan rumah tangga di lapangan.</t>
+  </si>
+  <si>
+    <t>Tagabilang: Nagmamapa at naglilista ng mga kabahayan sa field.</t>
+  </si>
+  <si>
+    <t>موسوم به شمارشگر: نقشه‌ها و فهرست‌های خانوارها را در میدان تهیه می‌کند.</t>
+  </si>
+  <si>
+    <t>شمېرونکی: په ساحه کې د کورنیو نقشې او لیستونه جوړوي.</t>
+  </si>
+  <si>
+    <t>Recopilador de datos: se desplaza hasta los hogares seleccionados y pone en marcha la encuesta.</t>
+  </si>
+  <si>
+    <t>Collecteur de données : se rend dans les ménages sélectionnés et lance l'enquête.</t>
+  </si>
+  <si>
+    <t>Recolhedor de dados: Dirige-se aos agregados familiares selecionados e inicia o inquérito.</t>
+  </si>
+  <si>
+    <t>Сборщик данных: находит домохозяйства, включенные в выборку, и проводит опрос.</t>
+  </si>
+  <si>
+    <t>Pengumpul Data: Menuju lokasi rumah tangga sampel dan memulai survei.</t>
+  </si>
+  <si>
+    <t>Tagakolekta ng Datos: Nagna-navigate sa mga na-sample na kabahayan at naglulunsad ng survey.</t>
+  </si>
+  <si>
+    <t>جمع‌آوری‌کنندهٔ داده‌ها: به خانوارهای نمونه‌گیری‌شده می‌رود و نظرسنجی را آغاز می‌کند.</t>
+  </si>
+  <si>
+    <t>د معلوماتو راټولونکی: نمونې شویو کورنیو ته ځي او سروې پیلوي.</t>
+  </si>
+  <si>
+    <t>GPSSample es una aplicación gratuita para Android destinada al registro de hogares, el muestreo y la navegación sobre el terreno. Selecciona tu función para empezar, o visita gpssample.org para obtener más información. Nota: Una vez que registres una función en este dispositivo, solo estarán disponibles esa función y las funciones subordinadas a ella.</t>
+  </si>
+  <si>
+    <t>GPSSample est une application Android gratuite destinée au recensement des ménages, à l'échantillonnage et à la navigation sur le terrain. Sélectionnez votre rôle pour commencer, ou rendez-vous sur gpssample.org pour en savoir plus. Remarque : une fois que vous avez enregistré un rôle sur cet appareil, seuls ce rôle et les rôles qui lui sont subordonnés seront disponibles.</t>
+  </si>
+  <si>
+    <t>O GPSSample é uma aplicação gratuita para Android destinada ao recenseamento de agregados familiares, amostragem e navegação no terreno. Selecione a sua função para começar ou visite gpssample.org para saber mais. Nota: Depois de registar uma função neste dispositivo, apenas essa função e as funções subordinadas a ela estarão disponíveis.</t>
+  </si>
+  <si>
+    <t>GPSSample — это бесплатное приложение для Android, предназначенное для составления списков домохозяйств, отбора проб и навигации в полевых условиях. Выберите свою роль, чтобы начать работу, или посетите сайт gpssample.org, чтобы узнать больше. Примечание: после регистрации роли на этом устройстве будут доступны только эта роль и роли, находящиеся ниже по иерархии.</t>
+  </si>
+  <si>
+    <t>GPSSample adalah aplikasi Android gratis untuk daftar rumah tangga berbasis lapangan, pengambilan sampel, dan navigasi. Pilih peran Anda untuk memulai, atau kunjungi gpssample.org untuk mempelajari lebih lanjut. Catatan: Setelah Anda mendaftarkan peran pada perangkat ini, hanya peran tersebut dan peran di bawahnya yang akan tersedia.</t>
+  </si>
+  <si>
+    <t>Ang GPSSample ay isang libreng Android app para sa paglilista, pagkuha ng sample, at pag-navigate sa mga sambahayan na nakabatay sa field. Piliin ang iyong tungkulin upang makapagsimula, o bisitahin ang gpssample.org upang matuto nang higit pa. Paalala: Kapag nakapagrehistro ka na ng isang tungkulin sa device na ito, tanging ang tungkulin at mga tungkulin sa ibaba nito ang magiging available.</t>
+  </si>
+  <si>
+    <t>GPSSample یک اپلیکیشن رایگان اندروید برای فهرست‌بندی خانوارها در میدان، نمونه‌گیری و ناوبری است. برای شروع، نقش خود را انتخاب کنید یا برای کسب اطلاعات بیشتر به gpssample.org مراجعه کنید. توجه: پس از ثبت یک نقش روی این دستگاه، تنها آن نقش و نقش‌های زیرمجموعه آن در دسترس خواهند بود.</t>
+  </si>
+  <si>
+    <t>GPSSample د انډرایډ یو وړیا اپلیکیشن دی چې د ساحوي کورونو لیست کولو، نمونې اخیستنې، او لارښوونې لپاره کارول کیږي. د پیل کولو لپاره خپل رول وټاکئ، یا د نورو معلوماتو لپاره gpssample.org ویبپاڼې ته مراجعه وکړئ. یادونه: کله چې تاسو په دې وسیله کې یو رول ثبت کړئ، نو یوازې هماغه رول او تر هغه لاندې رولونه به شتون ولري.</t>
+  </si>
+  <si>
+    <t>Descripciones de los métodos:
+_N__N_Muestra aleatoria simple:_N_Cada hogar tiene las mismas posibilidades de ser seleccionado._N__N_Muestra por conglomerados (n.º de hogares):_N_Se selecciona un número fijo de hogares de cada conglomerado._N__N_Muestra por conglomerados (% de hogares):_N_Se selecciona un porcentaje de hogares de cada conglomerado.</t>
+  </si>
+  <si>
+    <t>Description des méthodes :_N__N_Échantillon aléatoire simple :_N_Chaque ménage a une chance égale d'être sélectionné._N__N_Échantillon par grappes (nombre de ménages) :_N_Sélectionner un nombre fixe de ménages dans chaque grappe._N__N_Échantillon par grappes (pourcentage de ménages) :_N_Sélectionner un pourcentage de ménages dans chaque grappe.</t>
+  </si>
+  <si>
+    <t>Descrições dos métodos:_N__N_Amostra aleatória simples:_N_Cada agregado familiar tem a mesma probabilidade de ser selecionado._N__N_Amostra por conglomerados (n.º de agregados familiares):_N_Selecionar um número fixo de agregados familiares de cada conglomerado._N__N_Amostra por conglomerados (% de agregados familiares):_N_Selecionar uma percentagem de agregados familiares de cada conglomerado.</t>
+  </si>
+  <si>
+    <t>Описание методов:_N__N_Простая случайная выборка:_N_Каждое домохозяйство имеет равные шансы быть отобранным._N__N_Кластерная выборка (количество домохозяйств):_N_Из каждого кластера отбирается фиксированное количество домохозяйств._N__N_Кластерная выборка (процент домохозяйств):_N_Из каждого кластера отбирается определенный процент домохозяйств.</t>
+  </si>
+  <si>
+    <t>Deskripsi metode:_N__N_Sampel Acak Sederhana:_N_Setiap rumah tangga memiliki peluang yang sama untuk terpilih._N__N_Sampel Klaster (jumlah rumah tangga):_N_Memilih sejumlah rumah tangga tertentu dari setiap klaster._N__N_Sampel Klaster (persentase rumah tangga):_N_Memilih persentase tertentu dari rumah tangga di setiap klaster.</t>
+  </si>
+  <si>
+    <t>Mga paglalarawan ng pamamaraan:_N__N_Simpleng Random na Sample:_N_Ang bawat sambahayan ay may pantay na pagkakataong mapili._N__N_Cluster Sample (# ng mga sambahayan):_N_Pumili ng isang takdang bilang ng mga sambahayan mula sa bawat cluster._N__N_Cluster Sample (% ng mga sambahayan):_N_Pumili ng porsyento ng mga sambahayan mula sa bawat cluster.</t>
+  </si>
+  <si>
+    <t>توضیحات روش:
+_N__N_
+نمونهٔ تصادفی ساده:_N_هر خانوار شانس یکسانی برای انتخاب شدن دارد._N__N_
+نمونهٔ خوشه‌ای (تعداد خانوارها):_N_از هر خوشه تعداد ثابتی از خانوارها را انتخاب کنید._N__N_
+نمونهٔ خوشه‌ای (درصد خانوارها):_N_از هر خوشه درصد مشخصی از خانوارها را انتخاب کنید.</t>
+  </si>
+  <si>
+    <t>د میتودونو توضیحات:
+_N__N_ساده تصادفي نمونه:_N_هر کور د ټاکل کېدو مساوي چانس لري.
+_N__N_د خوشې نمونه (د کورونو شمېر):_N_له هرې خوشې څخه یو ټاکلی شمیر کورونه وټاکئ.
+_N__N_د خوشې نمونه (د کورونو سلنه):_N_له هرې خوشې څخه د کورونو یوه سلنه وټاکئ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduce la pregunta de recuperación de PIN
+</t>
+  </si>
+  <si>
+    <t>Entrez la question de sécurité pour le code PIN oublié</t>
+  </si>
+  <si>
+    <t>Introduza a pergunta de recuperação do PIN</t>
+  </si>
+  <si>
+    <t>Введите ответ на секретный вопрос</t>
+  </si>
+  <si>
+    <t>Masukkan pertanyaan untuk pemulihan PIN</t>
+  </si>
+  <si>
+    <t>Ilagay ang tanong tungkol sa nakalimutang PIN</t>
+  </si>
+  <si>
+    <t>سؤال رمز PIN فراموش‌شده را وارد کنید</t>
+  </si>
+  <si>
+    <t>هېر شوی پین پوښتنه ولیکئ</t>
+  </si>
+  <si>
+    <t>هاټ سپاټ جوړول</t>
+  </si>
+  <si>
+    <t>ایجاد سرور</t>
+  </si>
+  <si>
+    <t>سرور جوړول</t>
+  </si>
+  <si>
+    <t>ایجاد کد QR</t>
+  </si>
+  <si>
+    <t>QR کوډ جوړول</t>
+  </si>
+  <si>
+    <t>له هاټ سپاټ سره وصلول</t>
+  </si>
+  <si>
+    <t>درحال ارسال فرمان</t>
+  </si>
+  <si>
+    <t>درحال ارسال داده‌های شمارش</t>
+  </si>
+  <si>
+    <t>د شمېرنې ډیټا لیږل</t>
+  </si>
+  <si>
+    <t>درحال دریافت داده‌ها</t>
+  </si>
+  <si>
+    <t>نام خانوادگی مادر پیش از ازدواج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">د مور تخلص د واده څخه مخکې </t>
+  </si>
+  <si>
+    <t>۴ رقم آخر شماره تلفن همراه</t>
+  </si>
+  <si>
+    <t>مساوي</t>
+  </si>
+  <si>
+    <t>نامساوي</t>
+  </si>
+  <si>
+    <t>لږ له</t>
+  </si>
+  <si>
+    <t>زیات له</t>
+  </si>
+  <si>
+    <t>بزرگ‌تر از یا مساوی</t>
+  </si>
+  <si>
+    <t>زیات له یا مساوي</t>
+  </si>
+  <si>
+    <t>غیر</t>
+  </si>
+  <si>
+    <t>جمع‌آورنده داده</t>
+  </si>
+  <si>
+    <t>QR کوډ اسکنول</t>
+  </si>
+  <si>
+    <t>د راټولولو اپلیکیشن</t>
+  </si>
+  <si>
+    <t>د کلون تشکیلات</t>
+  </si>
+  <si>
+    <t>ایا تاسو ډاډه یاست چې غواړئ دا تشکیلات کلون کړئ؟</t>
+  </si>
+  <si>
+    <t>د دې تشکیلاتو سره کومه ټیم ټاکل شوې نه ده.</t>
+  </si>
+  <si>
+    <t>دا تشکیلات له ځان سره تړلی شمېرنیه ساحه نه لري.</t>
+  </si>
+  <si>
+    <t>دا تشکیلات له ځان سره تړلی مطالعه نه لري.</t>
+  </si>
+  <si>
+    <t>دا تشکیلات د راټولولو ټیم نلري.</t>
+  </si>
+  <si>
+    <t>د شمېرنې ساحې سمول</t>
+  </si>
+  <si>
+    <t>ټولې شمېرنې ساحې حذف کړئ</t>
+  </si>
+  <si>
+    <t>ایا تاسو ډاډه یاست چې غواړئ ټولې شمېرنې ساحې د تل لپاره حذف کړئ؟</t>
+  </si>
+  <si>
+    <t>په نقشه کې د ټیم پوله رسم کړئ</t>
+  </si>
+  <si>
+    <t>په نقشه کې د ټیم د پولې پر ټکو ټپ کړئ</t>
+  </si>
+  <si>
+    <t>اپلیکیشن کلکشن</t>
+  </si>
+  <si>
+    <t>کپی پیکربندی</t>
+  </si>
+  <si>
+    <t>آیا مطمئن هستید که می‌خواهید این پیکربندی را کپی کنید؟</t>
+  </si>
+  <si>
+    <t>این پیکربندی هیچ تیم جمع‌آوری مرتبطی ندارد.</t>
+  </si>
+  <si>
+    <t>این پیکربندی هیچ ناحیه شمارش مرتبطی ندارد.</t>
+  </si>
+  <si>
+    <t>این پیکربندی هیچ مطالعه مرتبطی ندارد.</t>
+  </si>
+  <si>
+    <t>این پیکربندی هیچ تیم شمارش مرتبطی ندارد.</t>
+  </si>
+  <si>
+    <t>ویرایش ناحیه شمارش</t>
+  </si>
+  <si>
+    <t>حذف تمام نواحی فهرست‌بندی</t>
+  </si>
+  <si>
+    <t>آیا مطمئن هستید که می‌خواهید تمام نواحی فهرست‌بندی را برای همیشه حذف کنید؟</t>
+  </si>
+  <si>
+    <t>کشیدن مرز تیم روی نقشه</t>
+  </si>
+  <si>
+    <t>روی نقاط مرزی تیم روی نقشه ضربه بزنید</t>
+  </si>
+  <si>
+    <t>Aplicación de recaudación</t>
+  </si>
+  <si>
+    <t>Clonar configuración</t>
+  </si>
+  <si>
+    <t>¿Estás seguro de que quieres clonar esta configuración?</t>
+  </si>
+  <si>
+    <t>Esta configuración no tiene ningún equipo de recaudación asociado.</t>
+  </si>
+  <si>
+    <t>Esta configuración no tiene ninguna zona de recuento asociada.</t>
+  </si>
+  <si>
+    <t>Esta configuración no tiene ningún estudio asociado.</t>
+  </si>
+  <si>
+    <t>Esta configuración no tiene ningún equipo de recogida asociado.</t>
+  </si>
+  <si>
+    <t>Editar área de enumeración</t>
+  </si>
+  <si>
+    <t>Eliminar todas las áreas de enumeración</t>
+  </si>
+  <si>
+    <t>¿Estás seguro de que quieres eliminar definitivamente todas las áreas de enumeración?</t>
+  </si>
+  <si>
+    <t>Dibuja los límites del equipo en el mapa</t>
+  </si>
+  <si>
+    <t>Toca los puntos que delimitan el equipo en el mapa</t>
+  </si>
+  <si>
+    <t>Modifiez une zone d'énumération</t>
+  </si>
+  <si>
+    <t>Supprimez toutes les zones d'énumération</t>
+  </si>
+  <si>
+    <t>Êtes-vous sûr de vouloir supprimer définitivement toutes les zones d'énumération ?</t>
+  </si>
+  <si>
+    <t>Tracez le périmètre de l'équipe sur la carte</t>
+  </si>
+  <si>
+    <t>Appuyez sur les points délimitant le périmètre de l'équipe sur la carte</t>
+  </si>
+  <si>
+    <t>Application de collecte</t>
+  </si>
+  <si>
+    <t>Clonez la configuration</t>
+  </si>
+  <si>
+    <t>Êtes-vous sûr de vouloir cloner cette configuration ?</t>
+  </si>
+  <si>
+    <t>Aucune équipe de collecte n'est associée à cette configuration.</t>
+  </si>
+  <si>
+    <t>Aucune zone de recensement n'est associée à cette configuration.</t>
+  </si>
+  <si>
+    <t>Aucune étude n'est associée à cette configuration.</t>
+  </si>
+  <si>
+    <t>Aucune équipe de recensement n'est associée à cette configuration.</t>
+  </si>
+  <si>
+    <t>Aplicação de Recolha</t>
+  </si>
+  <si>
+    <t>Clonar Configuração</t>
+  </si>
+  <si>
+    <t>Tem a certeza de que pretende clonar esta configuração?</t>
+  </si>
+  <si>
+    <t>Esta configuração não tem nenhuma equipa de recolha associada.</t>
+  </si>
+  <si>
+    <t>Esta configuração não tem nenhuma área de recenseamento associada.</t>
+  </si>
+  <si>
+    <t>Esta configuração não tem nenhum estudo associado.</t>
+  </si>
+  <si>
+    <t>Editar área de enumeração</t>
+  </si>
+  <si>
+    <t>Eliminar todas as áreas de enumeração</t>
+  </si>
+  <si>
+    <t>Tem a certeza de que pretende eliminar definitivamente todas as áreas de enumeração?</t>
+  </si>
+  <si>
+    <t>Desenhe o limite da equipa no mapa</t>
+  </si>
+  <si>
+    <t>Toque nos pontos que delimitam a equipa no mapa</t>
+  </si>
+  <si>
+    <t>Редактировать область перечисления</t>
+  </si>
+  <si>
+    <t>Удалить все области перечисления</t>
+  </si>
+  <si>
+    <t>Вы действительно хотите окончательно удалить все области перечисления?</t>
+  </si>
+  <si>
+    <t>Начертите границы команды на карте</t>
+  </si>
+  <si>
+    <t>Нажмите на точки границ команды на карте</t>
+  </si>
+  <si>
+    <t>Приложение для сбора данных</t>
+  </si>
+  <si>
+    <t>Клонирование конфигурации</t>
+  </si>
+  <si>
+    <t>Вы действительно хотите клонировать эту конфигурацию?</t>
+  </si>
+  <si>
+    <t>С этой конфигурацией не связана ни одна группа сбора данных.</t>
+  </si>
+  <si>
+    <t>С этой конфигурацией не связана ни одна зона переписи.</t>
+  </si>
+  <si>
+    <t>С этой конфигурацией не связано ни одно исследование.</t>
+  </si>
+  <si>
+    <t>С этой конфигурацией не связана ни одна группа переписи.</t>
+  </si>
+  <si>
+    <t>Aplikasi Pengumpulan Data</t>
+  </si>
+  <si>
+    <t>Kloning Konfigurasi</t>
+  </si>
+  <si>
+    <t>Apakah Anda yakin ingin mengkloning konfigurasi ini?</t>
+  </si>
+  <si>
+    <t>Konfigurasi ini tidak memiliki tim pengumpulan data yang terkait dengannya.</t>
+  </si>
+  <si>
+    <t>Konfigurasi ini tidak memiliki Area Enumerasi yang terkait dengannya.</t>
+  </si>
+  <si>
+    <t>Konfigurasi ini tidak memiliki Studi yang terkait dengannya.</t>
+  </si>
+  <si>
+    <t>Konfigurasi ini tidak memiliki Tim Enumerasi yang terkait dengannya.</t>
+  </si>
+  <si>
+    <t>Konfigurasi ini tidak memiliki Tim Pengumpulan Data yang terkait dengannya.</t>
+  </si>
+  <si>
+    <t>Edit Area Enumerasi</t>
+  </si>
+  <si>
+    <t>Hapus semua Area Enumerasi</t>
+  </si>
+  <si>
+    <t>Apakah Anda yakin ingin menghapus semua Area Enumerasi secara permanen?</t>
+  </si>
+  <si>
+    <t>Gambar batas tim pada peta</t>
+  </si>
+  <si>
+    <t>Ketuk titik-titik batas tim pada peta</t>
+  </si>
+  <si>
+    <t>App ng Koleksyon</t>
+  </si>
+  <si>
+    <t>Pag-clone ng Configuration</t>
+  </si>
+  <si>
+    <t>Sigurado ka bang gusto mong i-clone ang Configuration na ito?</t>
+  </si>
+  <si>
+    <t>Ang configuration na ito ay walang collection team na nauugnay dito.</t>
+  </si>
+  <si>
+    <t>Ang configuration na ito ay walang Enumeration Area na nauugnay dito.</t>
+  </si>
+  <si>
+    <t>Ang configuration na ito ay walang Study na nauugnay dito.</t>
+  </si>
+  <si>
+    <t>Ang configuration na ito ay walang Enumeration Team na nauugnay dito.</t>
+  </si>
+  <si>
+    <t>Ang configuration na ito ay walang Collection Team na nauugnay dito.</t>
+  </si>
+  <si>
+    <t>I-edit ang Enumeration Area</t>
+  </si>
+  <si>
+    <t>Burahin ang lahat ng Enumeration Area</t>
+  </si>
+  <si>
+    <t>Sigurado ka bang gusto mong permanenteng burahin ang lahat ng Enumeration Area?</t>
+  </si>
+  <si>
+    <t>Iguhit ang hangganan ng team sa mapa</t>
+  </si>
+  <si>
+    <t>I-tap ang mga punto ng hangganan ng team sa mapa</t>
+  </si>
+  <si>
+    <t>distance</t>
+  </si>
+  <si>
+    <t>Distance</t>
+  </si>
+  <si>
+    <t>enforce_geofence_boundary</t>
+  </si>
+  <si>
+    <t>enter_the_geofence_buffer_value</t>
+  </si>
+  <si>
+    <t>geofence_hint</t>
+  </si>
+  <si>
+    <t>geofence_error</t>
+  </si>
+  <si>
+    <t>begin_sample_review</t>
+  </si>
+  <si>
+    <t>review_sample</t>
+  </si>
+  <si>
+    <t>review_possible_duplicates</t>
+  </si>
+  <si>
+    <t>review_boundary_violations</t>
+  </si>
+  <si>
+    <t>save_sample</t>
+  </si>
+  <si>
+    <t>duplicate</t>
+  </si>
+  <si>
+    <t>outside_boundary</t>
+  </si>
+  <si>
+    <t>reason_is_required</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>keep_or_exclude_this_location</t>
+  </si>
+  <si>
+    <t>keep_this_location</t>
+  </si>
+  <si>
+    <t>exclude_this_location</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>Enforce Geofence Boundary</t>
+  </si>
+  <si>
+    <t>Enter the geofence buffer value</t>
+  </si>
+  <si>
+    <t>Placeholder for GeoFence Hint</t>
+  </si>
+  <si>
+    <t>You are currently outside of the Geofence</t>
+  </si>
+  <si>
+    <t>Begin Sample Review</t>
+  </si>
+  <si>
+    <t>Review Sample</t>
+  </si>
+  <si>
+    <t>Review Possible Duplicates</t>
+  </si>
+  <si>
+    <t>Review Boundary Violations</t>
+  </si>
+  <si>
+    <t>Save Sample</t>
+  </si>
+  <si>
+    <t>Duplicate</t>
+  </si>
+  <si>
+    <t>Outside Boundary</t>
+  </si>
+  <si>
+    <t>You must select a Reason for the exclusion.</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Keep or Exclude this location?</t>
+  </si>
+  <si>
+    <t>Keep this location</t>
+  </si>
+  <si>
+    <t>Exclude this location</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>collection_apps</t>
+  </si>
+  <si>
+    <t>ODK Collect</t>
+  </si>
+  <si>
+    <t>Kobo Collect</t>
+  </si>
+  <si>
+    <t>Ona</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -14354,6 +15035,23 @@
       <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF444746"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF444746"/>
+      <name val="Google Sans"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -14435,7 +15133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -14496,6 +15194,15 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14685,8 +15392,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}" name="Table1" displayName="Table1" ref="A1:J512" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J512" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}" name="Table1" displayName="Table1" ref="A1:J548" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J548" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{DE67F62A-9DCA-4DFE-8C98-83B024E5D946}" name="app_name" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{BCDA3AB5-7BB5-4A21-ABBB-4186B52D559D}" name="GPSSample::en" dataDxfId="8"/>
@@ -15012,19 +15719,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD3E6CC-854C-5841-9577-D3ADD2982DB6}">
-  <dimension ref="A1:J514"/>
+  <dimension ref="A1:J548"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" customWidth="1"/>
-    <col min="2" max="2" width="63" customWidth="1"/>
+    <col min="1" max="1" width="33.5" customWidth="1"/>
+    <col min="2" max="2" width="86.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.33203125" customWidth="1"/>
     <col min="4" max="4" width="31.1640625" customWidth="1"/>
     <col min="5" max="5" width="26.6640625" customWidth="1"/>
     <col min="6" max="6" width="29.1640625" customWidth="1"/>
     <col min="7" max="7" width="45" customWidth="1"/>
-    <col min="8" max="8" width="70.83203125" customWidth="1"/>
-    <col min="9" max="9" width="74.83203125" customWidth="1"/>
-    <col min="10" max="10" width="40.33203125" customWidth="1"/>
+    <col min="8" max="8" width="67.1640625" customWidth="1"/>
+    <col min="9" max="9" width="43.33203125" customWidth="1"/>
+    <col min="10" max="10" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -15053,10 +15760,10 @@
         <v>2884</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>4362</v>
+        <v>4345</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>4363</v>
+        <v>4346</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -15120,7 +15827,7 @@
         <v>3407</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>3849</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -15152,7 +15859,7 @@
         <v>3408</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>3850</v>
+        <v>3839</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -15184,7 +15891,7 @@
         <v>3409</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>3851</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -15248,7 +15955,7 @@
         <v>3411</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>3852</v>
+        <v>3841</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -15280,7 +15987,7 @@
         <v>3412</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>3853</v>
+        <v>3842</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -15312,7 +16019,7 @@
         <v>3413</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>3857</v>
+        <v>4784</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -15341,10 +16048,10 @@
         <v>2892</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>3414</v>
+        <v>4785</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>3856</v>
+        <v>4786</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -15373,10 +16080,10 @@
         <v>2893</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>3415</v>
+        <v>4787</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>3854</v>
+        <v>4788</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -15405,10 +16112,10 @@
         <v>2894</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>3416</v>
+        <v>3414</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>3855</v>
+        <v>4789</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -15437,10 +16144,10 @@
         <v>2895</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>3417</v>
+        <v>3415</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>3886</v>
+        <v>3871</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -15468,11 +16175,11 @@
       <c r="H14" s="4" t="s">
         <v>2896</v>
       </c>
-      <c r="I14" s="14" t="s">
-        <v>3418</v>
+      <c r="I14" s="3" t="s">
+        <v>4790</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>3887</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -15501,10 +16208,10 @@
         <v>2897</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>3419</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>3888</v>
+        <v>4791</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>4792</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -15533,10 +16240,10 @@
         <v>2898</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>3420</v>
+        <v>4793</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>3889</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -15565,10 +16272,10 @@
         <v>2899</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>3421</v>
+        <v>3416</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>3890</v>
+        <v>3874</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -15597,10 +16304,10 @@
         <v>2900</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>3422</v>
+        <v>3417</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>3891</v>
+        <v>3875</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -15629,10 +16336,10 @@
         <v>2901</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>3423</v>
+        <v>4794</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>3892</v>
+        <v>4795</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -15661,10 +16368,10 @@
         <v>2902</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>3424</v>
+        <v>3418</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>3893</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -15693,10 +16400,10 @@
         <v>2903</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>3425</v>
+        <v>4796</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>3894</v>
+        <v>3877</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -15725,10 +16432,10 @@
         <v>2904</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>3426</v>
+        <v>3419</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>3899</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -15757,10 +16464,10 @@
         <v>2905</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>3427</v>
+        <v>3420</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>3898</v>
+        <v>3881</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -15789,10 +16496,10 @@
         <v>2906</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>3428</v>
+        <v>3421</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>3897</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -15821,10 +16528,10 @@
         <v>2907</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>3429</v>
+        <v>3422</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>3896</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -15853,10 +16560,10 @@
         <v>2908</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>3430</v>
+        <v>3423</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>3895</v>
+        <v>3878</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -15885,10 +16592,10 @@
         <v>2909</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>3431</v>
+        <v>3424</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>3882</v>
+        <v>3867</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -15917,10 +16624,10 @@
         <v>2910</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>3432</v>
+        <v>3868</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>3883</v>
+        <v>3868</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -15949,10 +16656,10 @@
         <v>175</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>3433</v>
+        <v>3425</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>3884</v>
+        <v>3869</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -15981,10 +16688,10 @@
         <v>2911</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>3434</v>
+        <v>3426</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>3434</v>
+        <v>3426</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -16013,10 +16720,10 @@
         <v>2912</v>
       </c>
       <c r="I31" s="14" t="s">
-        <v>3435</v>
+        <v>3427</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>3885</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -16045,10 +16752,10 @@
         <v>190</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>3436</v>
+        <v>3428</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>3858</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -16077,10 +16784,10 @@
         <v>196</v>
       </c>
       <c r="I33" s="14" t="s">
-        <v>3437</v>
+        <v>3429</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>3859</v>
+        <v>3845</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -16109,10 +16816,10 @@
         <v>2913</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>3438</v>
+        <v>3686</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>3860</v>
+        <v>4797</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -16141,10 +16848,10 @@
         <v>2914</v>
       </c>
       <c r="I35" s="14" t="s">
-        <v>3439</v>
+        <v>3687</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>3861</v>
+        <v>4798</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -16173,10 +16880,10 @@
         <v>2916</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>3440</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>3862</v>
+        <v>3430</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>4799</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -16205,10 +16912,10 @@
         <v>2915</v>
       </c>
       <c r="I37" s="14" t="s">
-        <v>3441</v>
+        <v>3431</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>3863</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -16237,10 +16944,10 @@
         <v>2917</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>3442</v>
+        <v>4801</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>3864</v>
+        <v>4802</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -16269,10 +16976,10 @@
         <v>2918</v>
       </c>
       <c r="I39" s="14" t="s">
-        <v>3443</v>
+        <v>3433</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>3865</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -16301,10 +17008,10 @@
         <v>238</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>3444</v>
+        <v>3434</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>3444</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -16333,10 +17040,10 @@
         <v>2919</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>3445</v>
+        <v>4803</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>3445</v>
+        <v>4803</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -16365,10 +17072,10 @@
         <v>249</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>3446</v>
+        <v>3436</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>3866</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -16397,10 +17104,10 @@
         <v>255</v>
       </c>
       <c r="I43" s="14" t="s">
-        <v>3447</v>
+        <v>3437</v>
       </c>
       <c r="J43" s="14" t="s">
-        <v>3867</v>
+        <v>3853</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -16429,10 +17136,10 @@
         <v>2920</v>
       </c>
       <c r="I44" s="14" t="s">
-        <v>3448</v>
+        <v>3438</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>3868</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -16461,10 +17168,10 @@
         <v>267</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>3449</v>
+        <v>3439</v>
       </c>
       <c r="J45" s="14" t="s">
-        <v>3869</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -16525,10 +17232,10 @@
         <v>2922</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>3450</v>
+        <v>3440</v>
       </c>
       <c r="J47" s="14" t="s">
-        <v>3870</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -16557,10 +17264,10 @@
         <v>284</v>
       </c>
       <c r="I48" s="14" t="s">
-        <v>3451</v>
+        <v>3441</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>3871</v>
+        <v>3857</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -16589,10 +17296,10 @@
         <v>289</v>
       </c>
       <c r="I49" s="14" t="s">
-        <v>3452</v>
+        <v>3442</v>
       </c>
       <c r="J49" s="14" t="s">
-        <v>3872</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -16621,7 +17328,7 @@
         <v>2923</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>3453</v>
+        <v>3443</v>
       </c>
       <c r="J50" s="14" t="s">
         <v>3406</v>
@@ -16653,10 +17360,10 @@
         <v>2924</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>3454</v>
+        <v>3444</v>
       </c>
       <c r="J51" s="14" t="s">
-        <v>3873</v>
+        <v>3859</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -16685,10 +17392,10 @@
         <v>2925</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>3455</v>
+        <v>3445</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>3874</v>
+        <v>3860</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -16716,11 +17423,11 @@
       <c r="H53" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="I53" s="14" t="s">
-        <v>3456</v>
+      <c r="I53" s="3" t="s">
+        <v>4804</v>
       </c>
       <c r="J53" s="14" t="s">
-        <v>3875</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -16749,10 +17456,10 @@
         <v>2926</v>
       </c>
       <c r="I54" s="14" t="s">
-        <v>3457</v>
+        <v>3446</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>3876</v>
+        <v>4805</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -16781,10 +17488,10 @@
         <v>2927</v>
       </c>
       <c r="I55" s="14" t="s">
-        <v>3458</v>
+        <v>3447</v>
       </c>
       <c r="J55" s="14" t="s">
-        <v>3877</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -16813,10 +17520,10 @@
         <v>2928</v>
       </c>
       <c r="I56" s="14" t="s">
-        <v>3459</v>
+        <v>3448</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>3878</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -16845,10 +17552,10 @@
         <v>2929</v>
       </c>
       <c r="I57" s="14" t="s">
-        <v>3460</v>
+        <v>3449</v>
       </c>
       <c r="J57" s="14" t="s">
-        <v>3879</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -16877,10 +17584,10 @@
         <v>2930</v>
       </c>
       <c r="I58" s="14" t="s">
-        <v>3461</v>
+        <v>3450</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>3880</v>
+        <v>3865</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -16909,10 +17616,10 @@
         <v>2931</v>
       </c>
       <c r="I59" s="14" t="s">
-        <v>3462</v>
+        <v>3451</v>
       </c>
       <c r="J59" s="14" t="s">
-        <v>3881</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -16941,10 +17648,10 @@
         <v>2932</v>
       </c>
       <c r="I60" s="14" t="s">
-        <v>3463</v>
+        <v>3452</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>3958</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -16973,10 +17680,10 @@
         <v>2933</v>
       </c>
       <c r="I61" s="14" t="s">
-        <v>3464</v>
+        <v>3453</v>
       </c>
       <c r="J61" s="14" t="s">
-        <v>3959</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -17005,10 +17712,10 @@
         <v>2934</v>
       </c>
       <c r="I62" s="14" t="s">
-        <v>3465</v>
+        <v>3454</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>3960</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -17037,10 +17744,10 @@
         <v>2935</v>
       </c>
       <c r="I63" s="14" t="s">
-        <v>3466</v>
+        <v>3455</v>
       </c>
       <c r="J63" s="14" t="s">
-        <v>3961</v>
+        <v>3944</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -17054,7 +17761,7 @@
         <v>372</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>4518</v>
+        <v>4501</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>373</v>
@@ -17069,10 +17776,10 @@
         <v>2936</v>
       </c>
       <c r="I64" s="14" t="s">
-        <v>3467</v>
+        <v>3456</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>3962</v>
+        <v>3945</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -17101,10 +17808,10 @@
         <v>2937</v>
       </c>
       <c r="I65" s="14" t="s">
-        <v>3468</v>
+        <v>3457</v>
       </c>
       <c r="J65" s="14" t="s">
-        <v>3963</v>
+        <v>3946</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -17133,10 +17840,10 @@
         <v>2939</v>
       </c>
       <c r="I66" s="14" t="s">
-        <v>3469</v>
+        <v>3458</v>
       </c>
       <c r="J66" s="14" t="s">
-        <v>3964</v>
+        <v>3947</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -17165,10 +17872,10 @@
         <v>2938</v>
       </c>
       <c r="I67" s="14" t="s">
-        <v>3470</v>
+        <v>3459</v>
       </c>
       <c r="J67" s="14" t="s">
-        <v>3965</v>
+        <v>3948</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -17197,10 +17904,10 @@
         <v>2940</v>
       </c>
       <c r="I68" s="14" t="s">
-        <v>3471</v>
+        <v>3460</v>
       </c>
       <c r="J68" s="14" t="s">
-        <v>3966</v>
+        <v>3949</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -17229,10 +17936,10 @@
         <v>2941</v>
       </c>
       <c r="I69" s="14" t="s">
-        <v>3472</v>
+        <v>3461</v>
       </c>
       <c r="J69" s="14" t="s">
-        <v>3967</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -17261,10 +17968,10 @@
         <v>2942</v>
       </c>
       <c r="I70" s="14" t="s">
-        <v>3473</v>
+        <v>3462</v>
       </c>
       <c r="J70" s="14" t="s">
-        <v>3968</v>
+        <v>3951</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -17293,10 +18000,10 @@
         <v>2943</v>
       </c>
       <c r="I71" s="14" t="s">
-        <v>3474</v>
+        <v>3463</v>
       </c>
       <c r="J71" s="14" t="s">
-        <v>3969</v>
+        <v>3952</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -17325,10 +18032,10 @@
         <v>2944</v>
       </c>
       <c r="I72" s="14" t="s">
-        <v>3475</v>
+        <v>3464</v>
       </c>
       <c r="J72" s="14" t="s">
-        <v>3942</v>
+        <v>3925</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -17357,10 +18064,10 @@
         <v>2946</v>
       </c>
       <c r="I73" s="14" t="s">
-        <v>3476</v>
+        <v>3465</v>
       </c>
       <c r="J73" s="14" t="s">
-        <v>3943</v>
+        <v>3926</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -17392,7 +18099,7 @@
         <v>3407</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>3849</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -17421,10 +18128,10 @@
         <v>2947</v>
       </c>
       <c r="I75" s="14" t="s">
-        <v>3477</v>
+        <v>3466</v>
       </c>
       <c r="J75" s="14" t="s">
-        <v>3944</v>
+        <v>3927</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -17453,10 +18160,10 @@
         <v>2948</v>
       </c>
       <c r="I76" s="14" t="s">
-        <v>3478</v>
+        <v>3467</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>3945</v>
+        <v>3928</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -17485,10 +18192,10 @@
         <v>2949</v>
       </c>
       <c r="I77" s="14" t="s">
-        <v>3479</v>
+        <v>3468</v>
       </c>
       <c r="J77" s="14" t="s">
-        <v>3946</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -17517,10 +18224,10 @@
         <v>450</v>
       </c>
       <c r="I78" s="14" t="s">
-        <v>3480</v>
+        <v>3469</v>
       </c>
       <c r="J78" s="14" t="s">
-        <v>3947</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -17549,10 +18256,10 @@
         <v>2950</v>
       </c>
       <c r="I79" s="14" t="s">
-        <v>3481</v>
+        <v>3470</v>
       </c>
       <c r="J79" s="14" t="s">
-        <v>3948</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -17581,10 +18288,10 @@
         <v>2951</v>
       </c>
       <c r="I80" s="14" t="s">
-        <v>3482</v>
+        <v>3471</v>
       </c>
       <c r="J80" s="14" t="s">
-        <v>3949</v>
+        <v>3932</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -17613,10 +18320,10 @@
         <v>2952</v>
       </c>
       <c r="I81" s="14" t="s">
-        <v>3483</v>
+        <v>3472</v>
       </c>
       <c r="J81" s="14" t="s">
-        <v>3950</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -17645,10 +18352,10 @@
         <v>2953</v>
       </c>
       <c r="I82" s="14" t="s">
-        <v>3484</v>
+        <v>3473</v>
       </c>
       <c r="J82" s="14" t="s">
-        <v>3951</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -17677,10 +18384,10 @@
         <v>2954</v>
       </c>
       <c r="I83" s="14" t="s">
-        <v>3485</v>
+        <v>3474</v>
       </c>
       <c r="J83" s="14" t="s">
-        <v>3952</v>
+        <v>3935</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -17709,10 +18416,10 @@
         <v>2955</v>
       </c>
       <c r="I84" s="14" t="s">
-        <v>3486</v>
+        <v>3475</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>3953</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -17741,10 +18448,10 @@
         <v>2956</v>
       </c>
       <c r="I85" s="14" t="s">
-        <v>3487</v>
+        <v>3476</v>
       </c>
       <c r="J85" s="14" t="s">
-        <v>3954</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -17773,10 +18480,10 @@
         <v>2957</v>
       </c>
       <c r="I86" s="14" t="s">
-        <v>3488</v>
+        <v>3477</v>
       </c>
       <c r="J86" s="14" t="s">
-        <v>3955</v>
+        <v>3938</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -17805,10 +18512,10 @@
         <v>2958</v>
       </c>
       <c r="I87" s="14" t="s">
-        <v>3489</v>
+        <v>3478</v>
       </c>
       <c r="J87" s="14" t="s">
-        <v>3956</v>
+        <v>3939</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -17837,10 +18544,10 @@
         <v>2959</v>
       </c>
       <c r="I88" s="14" t="s">
-        <v>3490</v>
+        <v>3479</v>
       </c>
       <c r="J88" s="14" t="s">
-        <v>3957</v>
+        <v>3940</v>
       </c>
     </row>
     <row r="89" spans="1:10">
@@ -17869,10 +18576,10 @@
         <v>2960</v>
       </c>
       <c r="I89" s="14" t="s">
-        <v>3491</v>
+        <v>3480</v>
       </c>
       <c r="J89" s="14" t="s">
-        <v>4015</v>
+        <v>3998</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -17901,10 +18608,10 @@
         <v>2961</v>
       </c>
       <c r="I90" s="14" t="s">
-        <v>3492</v>
+        <v>3481</v>
       </c>
       <c r="J90" s="14" t="s">
-        <v>4016</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -17933,10 +18640,10 @@
         <v>2962</v>
       </c>
       <c r="I91" s="14" t="s">
-        <v>3493</v>
+        <v>3482</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>4017</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -17965,10 +18672,10 @@
         <v>2963</v>
       </c>
       <c r="I92" s="14" t="s">
-        <v>3494</v>
+        <v>3483</v>
       </c>
       <c r="J92" s="14" t="s">
-        <v>4018</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -17997,10 +18704,10 @@
         <v>2964</v>
       </c>
       <c r="I93" s="14" t="s">
-        <v>3495</v>
+        <v>3484</v>
       </c>
       <c r="J93" s="14" t="s">
-        <v>4012</v>
+        <v>3995</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -18029,10 +18736,10 @@
         <v>2965</v>
       </c>
       <c r="I94" s="14" t="s">
-        <v>3496</v>
+        <v>3485</v>
       </c>
       <c r="J94" s="14" t="s">
-        <v>4013</v>
+        <v>3996</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -18061,10 +18768,10 @@
         <v>2966</v>
       </c>
       <c r="I95" s="14" t="s">
-        <v>3497</v>
+        <v>3486</v>
       </c>
       <c r="J95" s="14" t="s">
-        <v>4014</v>
+        <v>3997</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -18093,10 +18800,10 @@
         <v>2967</v>
       </c>
       <c r="I96" s="14" t="s">
-        <v>3498</v>
+        <v>3487</v>
       </c>
       <c r="J96" s="14" t="s">
-        <v>4011</v>
+        <v>3994</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -18125,10 +18832,10 @@
         <v>2968</v>
       </c>
       <c r="I97" s="14" t="s">
-        <v>3499</v>
+        <v>3488</v>
       </c>
       <c r="J97" s="14" t="s">
-        <v>4009</v>
+        <v>3992</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -18157,10 +18864,10 @@
         <v>2969</v>
       </c>
       <c r="I98" s="14" t="s">
-        <v>3500</v>
+        <v>3489</v>
       </c>
       <c r="J98" s="14" t="s">
-        <v>4010</v>
+        <v>3993</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -18189,10 +18896,10 @@
         <v>2970</v>
       </c>
       <c r="I99" s="14" t="s">
-        <v>3501</v>
+        <v>3490</v>
       </c>
       <c r="J99" s="14" t="s">
-        <v>4008</v>
+        <v>3991</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -18221,10 +18928,10 @@
         <v>2971</v>
       </c>
       <c r="I100" s="14" t="s">
-        <v>3502</v>
+        <v>3491</v>
       </c>
       <c r="J100" s="14" t="s">
-        <v>4007</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -18253,10 +18960,10 @@
         <v>2972</v>
       </c>
       <c r="I101" s="14" t="s">
-        <v>3503</v>
+        <v>3492</v>
       </c>
       <c r="J101" s="14" t="s">
-        <v>4005</v>
+        <v>3988</v>
       </c>
     </row>
     <row r="102" spans="1:10">
@@ -18285,10 +18992,10 @@
         <v>2973</v>
       </c>
       <c r="I102" s="14" t="s">
-        <v>3504</v>
+        <v>3493</v>
       </c>
       <c r="J102" s="14" t="s">
-        <v>4006</v>
+        <v>3989</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -18317,10 +19024,10 @@
         <v>2974</v>
       </c>
       <c r="I103" s="14" t="s">
-        <v>3505</v>
+        <v>3494</v>
       </c>
       <c r="J103" s="14" t="s">
-        <v>4019</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="104" spans="1:10">
@@ -18349,10 +19056,10 @@
         <v>2975</v>
       </c>
       <c r="I104" s="14" t="s">
-        <v>3506</v>
+        <v>3495</v>
       </c>
       <c r="J104" s="14" t="s">
-        <v>4020</v>
+        <v>4003</v>
       </c>
     </row>
     <row r="105" spans="1:10">
@@ -18381,10 +19088,10 @@
         <v>2976</v>
       </c>
       <c r="I105" s="14" t="s">
-        <v>3507</v>
+        <v>3496</v>
       </c>
       <c r="J105" s="14" t="s">
-        <v>4021</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="106" spans="1:10">
@@ -18413,10 +19120,10 @@
         <v>2977</v>
       </c>
       <c r="I106" s="14" t="s">
-        <v>3508</v>
+        <v>3497</v>
       </c>
       <c r="J106" s="14" t="s">
-        <v>4022</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="107" spans="1:10">
@@ -18445,10 +19152,10 @@
         <v>2978</v>
       </c>
       <c r="I107" s="14" t="s">
-        <v>3509</v>
+        <v>3498</v>
       </c>
       <c r="J107" s="14" t="s">
-        <v>4023</v>
+        <v>4006</v>
       </c>
     </row>
     <row r="108" spans="1:10">
@@ -18477,10 +19184,10 @@
         <v>2979</v>
       </c>
       <c r="I108" s="14" t="s">
-        <v>3510</v>
+        <v>3499</v>
       </c>
       <c r="J108" s="14" t="s">
-        <v>3510</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="109" spans="1:10">
@@ -18509,10 +19216,10 @@
         <v>2980</v>
       </c>
       <c r="I109" s="14" t="s">
-        <v>3511</v>
+        <v>3500</v>
       </c>
       <c r="J109" s="14" t="s">
-        <v>4091</v>
+        <v>4074</v>
       </c>
     </row>
     <row r="110" spans="1:10">
@@ -18541,10 +19248,10 @@
         <v>2981</v>
       </c>
       <c r="I110" s="14" t="s">
-        <v>3512</v>
+        <v>3501</v>
       </c>
       <c r="J110" s="14" t="s">
-        <v>4092</v>
+        <v>4075</v>
       </c>
     </row>
     <row r="111" spans="1:10">
@@ -18573,10 +19280,10 @@
         <v>2982</v>
       </c>
       <c r="I111" s="14" t="s">
-        <v>3513</v>
+        <v>3502</v>
       </c>
       <c r="J111" s="14" t="s">
-        <v>4093</v>
+        <v>4076</v>
       </c>
     </row>
     <row r="112" spans="1:10">
@@ -18605,10 +19312,10 @@
         <v>2983</v>
       </c>
       <c r="I112" s="14" t="s">
-        <v>3514</v>
+        <v>3503</v>
       </c>
       <c r="J112" s="14" t="s">
-        <v>4094</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="113" spans="1:10">
@@ -18637,10 +19344,10 @@
         <v>2984</v>
       </c>
       <c r="I113" s="14" t="s">
-        <v>3515</v>
+        <v>3504</v>
       </c>
       <c r="J113" s="14" t="s">
-        <v>4095</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -18701,10 +19408,10 @@
         <v>2986</v>
       </c>
       <c r="I115" s="14" t="s">
-        <v>3516</v>
+        <v>3505</v>
       </c>
       <c r="J115" s="14" t="s">
-        <v>4143</v>
+        <v>4126</v>
       </c>
     </row>
     <row r="116" spans="1:10">
@@ -18733,10 +19440,10 @@
         <v>2987</v>
       </c>
       <c r="I116" s="14" t="s">
-        <v>3517</v>
+        <v>3506</v>
       </c>
       <c r="J116" s="14" t="s">
-        <v>4144</v>
+        <v>4127</v>
       </c>
     </row>
     <row r="117" spans="1:10">
@@ -18765,10 +19472,10 @@
         <v>2988</v>
       </c>
       <c r="I117" s="14" t="s">
-        <v>3518</v>
+        <v>3507</v>
       </c>
       <c r="J117" s="14" t="s">
-        <v>4145</v>
+        <v>4128</v>
       </c>
     </row>
     <row r="118" spans="1:10">
@@ -18797,10 +19504,10 @@
         <v>2989</v>
       </c>
       <c r="I118" s="14" t="s">
-        <v>3519</v>
+        <v>3508</v>
       </c>
       <c r="J118" s="14" t="s">
-        <v>4146</v>
+        <v>4129</v>
       </c>
     </row>
     <row r="119" spans="1:10">
@@ -18829,10 +19536,10 @@
         <v>2990</v>
       </c>
       <c r="I119" s="14" t="s">
-        <v>3520</v>
+        <v>3509</v>
       </c>
       <c r="J119" s="14" t="s">
-        <v>4147</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="120" spans="1:10">
@@ -18861,10 +19568,10 @@
         <v>2991</v>
       </c>
       <c r="I120" s="14" t="s">
-        <v>3521</v>
+        <v>3510</v>
       </c>
       <c r="J120" s="14" t="s">
-        <v>4148</v>
+        <v>4131</v>
       </c>
     </row>
     <row r="121" spans="1:10">
@@ -18893,10 +19600,10 @@
         <v>2992</v>
       </c>
       <c r="I121" s="14" t="s">
-        <v>3522</v>
+        <v>3511</v>
       </c>
       <c r="J121" s="14" t="s">
-        <v>4149</v>
+        <v>4132</v>
       </c>
     </row>
     <row r="122" spans="1:10">
@@ -18925,10 +19632,10 @@
         <v>2993</v>
       </c>
       <c r="I122" s="14" t="s">
-        <v>3523</v>
+        <v>3512</v>
       </c>
       <c r="J122" s="14" t="s">
-        <v>4150</v>
+        <v>4133</v>
       </c>
     </row>
     <row r="123" spans="1:10">
@@ -18957,10 +19664,10 @@
         <v>3004</v>
       </c>
       <c r="I123" s="14" t="s">
-        <v>3524</v>
+        <v>3513</v>
       </c>
       <c r="J123" s="14" t="s">
-        <v>4151</v>
+        <v>4134</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -18989,10 +19696,10 @@
         <v>3005</v>
       </c>
       <c r="I124" s="14" t="s">
-        <v>3525</v>
+        <v>3514</v>
       </c>
       <c r="J124" s="14" t="s">
-        <v>4152</v>
+        <v>4135</v>
       </c>
     </row>
     <row r="125" spans="1:10">
@@ -19021,10 +19728,10 @@
         <v>3006</v>
       </c>
       <c r="I125" s="14" t="s">
-        <v>3526</v>
+        <v>3515</v>
       </c>
       <c r="J125" s="14" t="s">
-        <v>4152</v>
+        <v>4135</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -19053,10 +19760,10 @@
         <v>3007</v>
       </c>
       <c r="I126" s="14" t="s">
-        <v>3527</v>
+        <v>3516</v>
       </c>
       <c r="J126" s="14" t="s">
-        <v>3854</v>
+        <v>3843</v>
       </c>
     </row>
     <row r="127" spans="1:10">
@@ -19085,10 +19792,10 @@
         <v>3000</v>
       </c>
       <c r="I127" s="14" t="s">
-        <v>3528</v>
+        <v>3517</v>
       </c>
       <c r="J127" s="14" t="s">
-        <v>4153</v>
+        <v>4136</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -19117,10 +19824,10 @@
         <v>3001</v>
       </c>
       <c r="I128" s="14" t="s">
-        <v>3529</v>
+        <v>3518</v>
       </c>
       <c r="J128" s="14" t="s">
-        <v>4154</v>
+        <v>4137</v>
       </c>
     </row>
     <row r="129" spans="1:10">
@@ -19149,10 +19856,10 @@
         <v>3002</v>
       </c>
       <c r="I129" s="14" t="s">
-        <v>3530</v>
+        <v>3519</v>
       </c>
       <c r="J129" s="14" t="s">
-        <v>4155</v>
+        <v>4138</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -19181,10 +19888,10 @@
         <v>3003</v>
       </c>
       <c r="I130" s="14" t="s">
-        <v>3531</v>
+        <v>3520</v>
       </c>
       <c r="J130" s="14" t="s">
-        <v>4156</v>
+        <v>4139</v>
       </c>
     </row>
     <row r="131" spans="1:10">
@@ -19213,10 +19920,10 @@
         <v>785</v>
       </c>
       <c r="I131" s="14" t="s">
-        <v>3532</v>
+        <v>3521</v>
       </c>
       <c r="J131" s="14" t="s">
-        <v>4173</v>
+        <v>4156</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -19245,10 +19952,10 @@
         <v>2994</v>
       </c>
       <c r="I132" s="14" t="s">
-        <v>3533</v>
+        <v>3522</v>
       </c>
       <c r="J132" s="14" t="s">
-        <v>4174</v>
+        <v>4157</v>
       </c>
     </row>
     <row r="133" spans="1:10">
@@ -19277,10 +19984,10 @@
         <v>2995</v>
       </c>
       <c r="I133" s="14" t="s">
-        <v>3534</v>
+        <v>3523</v>
       </c>
       <c r="J133" s="14" t="s">
-        <v>4175</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -19309,10 +20016,10 @@
         <v>2996</v>
       </c>
       <c r="I134" s="14" t="s">
-        <v>3535</v>
+        <v>3524</v>
       </c>
       <c r="J134" s="14" t="s">
-        <v>4176</v>
+        <v>4159</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -19341,10 +20048,10 @@
         <v>2997</v>
       </c>
       <c r="I135" s="14" t="s">
-        <v>3536</v>
+        <v>3525</v>
       </c>
       <c r="J135" s="14" t="s">
-        <v>4177</v>
+        <v>4160</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -19373,10 +20080,10 @@
         <v>2998</v>
       </c>
       <c r="I136" s="14" t="s">
-        <v>3537</v>
+        <v>3526</v>
       </c>
       <c r="J136" s="14" t="s">
-        <v>4161</v>
+        <v>4144</v>
       </c>
     </row>
     <row r="137" spans="1:10">
@@ -19405,10 +20112,10 @@
         <v>2999</v>
       </c>
       <c r="I137" s="14" t="s">
-        <v>3538</v>
+        <v>3527</v>
       </c>
       <c r="J137" s="14" t="s">
-        <v>4162</v>
+        <v>4145</v>
       </c>
     </row>
     <row r="138" spans="1:10">
@@ -19437,10 +20144,10 @@
         <v>3010</v>
       </c>
       <c r="I138" s="14" t="s">
-        <v>3539</v>
+        <v>3528</v>
       </c>
       <c r="J138" s="14" t="s">
-        <v>4163</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -19469,10 +20176,10 @@
         <v>3009</v>
       </c>
       <c r="I139" s="14" t="s">
-        <v>3540</v>
+        <v>3529</v>
       </c>
       <c r="J139" s="14" t="s">
-        <v>4164</v>
+        <v>4147</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -19501,10 +20208,10 @@
         <v>3008</v>
       </c>
       <c r="I140" s="14" t="s">
-        <v>3541</v>
+        <v>3530</v>
       </c>
       <c r="J140" s="14" t="s">
-        <v>4165</v>
+        <v>4148</v>
       </c>
     </row>
     <row r="141" spans="1:10">
@@ -19533,10 +20240,10 @@
         <v>3014</v>
       </c>
       <c r="I141" s="14" t="s">
-        <v>3542</v>
+        <v>3531</v>
       </c>
       <c r="J141" s="14" t="s">
-        <v>4166</v>
+        <v>4149</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -19565,10 +20272,10 @@
         <v>3004</v>
       </c>
       <c r="I142" s="14" t="s">
-        <v>3543</v>
+        <v>3532</v>
       </c>
       <c r="J142" s="14" t="s">
-        <v>4167</v>
+        <v>4150</v>
       </c>
     </row>
     <row r="143" spans="1:10">
@@ -19597,10 +20304,10 @@
         <v>3013</v>
       </c>
       <c r="I143" s="14" t="s">
-        <v>3544</v>
+        <v>3533</v>
       </c>
       <c r="J143" s="14" t="s">
-        <v>4168</v>
+        <v>4151</v>
       </c>
     </row>
     <row r="144" spans="1:10">
@@ -19629,10 +20336,10 @@
         <v>3012</v>
       </c>
       <c r="I144" s="14" t="s">
-        <v>3545</v>
+        <v>3534</v>
       </c>
       <c r="J144" s="14" t="s">
-        <v>4169</v>
+        <v>4152</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -19661,10 +20368,10 @@
         <v>3011</v>
       </c>
       <c r="I145" s="14" t="s">
-        <v>3546</v>
+        <v>3535</v>
       </c>
       <c r="J145" s="14" t="s">
-        <v>4170</v>
+        <v>4153</v>
       </c>
     </row>
     <row r="146" spans="1:10">
@@ -19693,10 +20400,10 @@
         <v>3015</v>
       </c>
       <c r="I146" s="14" t="s">
-        <v>3547</v>
+        <v>3536</v>
       </c>
       <c r="J146" s="14" t="s">
-        <v>4171</v>
+        <v>4154</v>
       </c>
     </row>
     <row r="147" spans="1:10">
@@ -19725,10 +20432,10 @@
         <v>3017</v>
       </c>
       <c r="I147" s="14" t="s">
-        <v>3548</v>
+        <v>3537</v>
       </c>
       <c r="J147" s="14" t="s">
-        <v>4172</v>
+        <v>4155</v>
       </c>
     </row>
     <row r="148" spans="1:10">
@@ -19757,10 +20464,10 @@
         <v>3016</v>
       </c>
       <c r="I148" s="14" t="s">
-        <v>3549</v>
+        <v>3538</v>
       </c>
       <c r="J148" s="14" t="s">
-        <v>4157</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="149" spans="1:10">
@@ -19789,10 +20496,10 @@
         <v>3018</v>
       </c>
       <c r="I149" s="14" t="s">
-        <v>3550</v>
+        <v>3539</v>
       </c>
       <c r="J149" s="14" t="s">
-        <v>4158</v>
+        <v>4141</v>
       </c>
     </row>
     <row r="150" spans="1:10">
@@ -19821,10 +20528,10 @@
         <v>3019</v>
       </c>
       <c r="I150" s="14" t="s">
-        <v>3551</v>
+        <v>3540</v>
       </c>
       <c r="J150" s="14" t="s">
-        <v>4159</v>
+        <v>4142</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -19853,10 +20560,10 @@
         <v>3020</v>
       </c>
       <c r="I151" s="14" t="s">
-        <v>3552</v>
+        <v>3541</v>
       </c>
       <c r="J151" s="14" t="s">
-        <v>4160</v>
+        <v>4143</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -19885,10 +20592,10 @@
         <v>3027</v>
       </c>
       <c r="I152" s="14" t="s">
-        <v>3553</v>
+        <v>3542</v>
       </c>
       <c r="J152" s="14" t="s">
-        <v>4096</v>
+        <v>4079</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -19917,10 +20624,10 @@
         <v>3028</v>
       </c>
       <c r="I153" s="14" t="s">
-        <v>3554</v>
+        <v>3543</v>
       </c>
       <c r="J153" s="14" t="s">
-        <v>4097</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="154" spans="1:10">
@@ -19949,10 +20656,10 @@
         <v>3029</v>
       </c>
       <c r="I154" s="14" t="s">
-        <v>3555</v>
+        <v>3544</v>
       </c>
       <c r="J154" s="14" t="s">
-        <v>4098</v>
+        <v>4081</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -19981,10 +20688,10 @@
         <v>3030</v>
       </c>
       <c r="I155" s="14" t="s">
-        <v>3556</v>
+        <v>3545</v>
       </c>
       <c r="J155" s="14" t="s">
-        <v>4099</v>
+        <v>4082</v>
       </c>
     </row>
     <row r="156" spans="1:10">
@@ -20013,10 +20720,10 @@
         <v>3031</v>
       </c>
       <c r="I156" s="14" t="s">
-        <v>3557</v>
+        <v>3546</v>
       </c>
       <c r="J156" s="14" t="s">
-        <v>4100</v>
+        <v>4083</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -20045,10 +20752,10 @@
         <v>3032</v>
       </c>
       <c r="I157" s="14" t="s">
-        <v>3558</v>
+        <v>3547</v>
       </c>
       <c r="J157" s="14" t="s">
-        <v>4101</v>
+        <v>4084</v>
       </c>
     </row>
     <row r="158" spans="1:10">
@@ -20077,10 +20784,10 @@
         <v>3033</v>
       </c>
       <c r="I158" s="14" t="s">
-        <v>3559</v>
+        <v>3548</v>
       </c>
       <c r="J158" s="14" t="s">
-        <v>4102</v>
+        <v>4085</v>
       </c>
     </row>
     <row r="159" spans="1:10">
@@ -20109,10 +20816,10 @@
         <v>3034</v>
       </c>
       <c r="I159" s="14" t="s">
-        <v>3560</v>
+        <v>3549</v>
       </c>
       <c r="J159" s="14" t="s">
-        <v>4103</v>
+        <v>4086</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -20141,10 +20848,10 @@
         <v>3035</v>
       </c>
       <c r="I160" s="14" t="s">
-        <v>3561</v>
+        <v>3550</v>
       </c>
       <c r="J160" s="14" t="s">
-        <v>4104</v>
+        <v>4087</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -20173,10 +20880,10 @@
         <v>3036</v>
       </c>
       <c r="I161" s="14" t="s">
-        <v>3562</v>
+        <v>3551</v>
       </c>
       <c r="J161" s="14" t="s">
-        <v>4105</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="162" spans="1:10">
@@ -20205,10 +20912,10 @@
         <v>3037</v>
       </c>
       <c r="I162" s="14" t="s">
-        <v>3563</v>
+        <v>3552</v>
       </c>
       <c r="J162" s="14" t="s">
-        <v>4106</v>
+        <v>4089</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -20237,10 +20944,10 @@
         <v>3038</v>
       </c>
       <c r="I163" s="14" t="s">
-        <v>3564</v>
+        <v>3553</v>
       </c>
       <c r="J163" s="14" t="s">
-        <v>4107</v>
+        <v>4090</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -20269,10 +20976,10 @@
         <v>3039</v>
       </c>
       <c r="I164" s="14" t="s">
-        <v>3565</v>
+        <v>3554</v>
       </c>
       <c r="J164" s="14" t="s">
-        <v>4073</v>
+        <v>4056</v>
       </c>
     </row>
     <row r="165" spans="1:10">
@@ -20301,10 +21008,10 @@
         <v>3040</v>
       </c>
       <c r="I165" s="14" t="s">
-        <v>3566</v>
+        <v>3555</v>
       </c>
       <c r="J165" s="14" t="s">
-        <v>4108</v>
+        <v>4091</v>
       </c>
     </row>
     <row r="166" spans="1:10">
@@ -20333,10 +21040,10 @@
         <v>3041</v>
       </c>
       <c r="I166" s="14" t="s">
-        <v>3567</v>
+        <v>3556</v>
       </c>
       <c r="J166" s="14" t="s">
-        <v>4109</v>
+        <v>4092</v>
       </c>
     </row>
     <row r="167" spans="1:10">
@@ -20365,10 +21072,10 @@
         <v>3026</v>
       </c>
       <c r="I167" s="14" t="s">
-        <v>3568</v>
+        <v>3557</v>
       </c>
       <c r="J167" s="14" t="s">
-        <v>4110</v>
+        <v>4093</v>
       </c>
     </row>
     <row r="168" spans="1:10">
@@ -20397,10 +21104,10 @@
         <v>3025</v>
       </c>
       <c r="I168" s="14" t="s">
-        <v>3569</v>
+        <v>3558</v>
       </c>
       <c r="J168" s="14" t="s">
-        <v>4111</v>
+        <v>4094</v>
       </c>
     </row>
     <row r="169" spans="1:10">
@@ -20429,10 +21136,10 @@
         <v>3024</v>
       </c>
       <c r="I169" s="14" t="s">
-        <v>3570</v>
+        <v>3559</v>
       </c>
       <c r="J169" s="14" t="s">
-        <v>4024</v>
+        <v>4007</v>
       </c>
     </row>
     <row r="170" spans="1:10">
@@ -20461,10 +21168,10 @@
         <v>3023</v>
       </c>
       <c r="I170" s="14" t="s">
-        <v>3571</v>
+        <v>3560</v>
       </c>
       <c r="J170" s="14" t="s">
-        <v>3445</v>
+        <v>3435</v>
       </c>
     </row>
     <row r="171" spans="1:10">
@@ -20493,10 +21200,10 @@
         <v>1045</v>
       </c>
       <c r="I171" s="14" t="s">
-        <v>3572</v>
+        <v>3561</v>
       </c>
       <c r="J171" s="14" t="s">
-        <v>4025</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="172" spans="1:10">
@@ -20525,10 +21232,10 @@
         <v>1051</v>
       </c>
       <c r="I172" s="14" t="s">
-        <v>3573</v>
+        <v>3562</v>
       </c>
       <c r="J172" s="14" t="s">
-        <v>4026</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="173" spans="1:10">
@@ -20557,10 +21264,10 @@
         <v>1057</v>
       </c>
       <c r="I173" s="14" t="s">
-        <v>3574</v>
+        <v>3563</v>
       </c>
       <c r="J173" s="14" t="s">
-        <v>4027</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="174" spans="1:10">
@@ -20589,10 +21296,10 @@
         <v>3022</v>
       </c>
       <c r="I174" s="14" t="s">
-        <v>3575</v>
+        <v>3564</v>
       </c>
       <c r="J174" s="14" t="s">
-        <v>4028</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="175" spans="1:10">
@@ -20621,10 +21328,10 @@
         <v>3021</v>
       </c>
       <c r="I175" s="14" t="s">
-        <v>3576</v>
+        <v>3565</v>
       </c>
       <c r="J175" s="14" t="s">
-        <v>4112</v>
+        <v>4095</v>
       </c>
     </row>
     <row r="176" spans="1:10">
@@ -20653,10 +21360,10 @@
         <v>3042</v>
       </c>
       <c r="I176" s="14" t="s">
-        <v>3577</v>
+        <v>3566</v>
       </c>
       <c r="J176" s="14" t="s">
-        <v>4113</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="177" spans="1:10">
@@ -20685,10 +21392,10 @@
         <v>3043</v>
       </c>
       <c r="I177" s="14" t="s">
-        <v>3578</v>
+        <v>3567</v>
       </c>
       <c r="J177" s="14" t="s">
-        <v>4114</v>
+        <v>4097</v>
       </c>
     </row>
     <row r="178" spans="1:10">
@@ -20717,10 +21424,10 @@
         <v>3035</v>
       </c>
       <c r="I178" s="14" t="s">
-        <v>3561</v>
+        <v>3550</v>
       </c>
       <c r="J178" s="14" t="s">
-        <v>4104</v>
+        <v>4087</v>
       </c>
     </row>
     <row r="179" spans="1:10">
@@ -20749,10 +21456,10 @@
         <v>3044</v>
       </c>
       <c r="I179" s="14" t="s">
-        <v>3610</v>
+        <v>3599</v>
       </c>
       <c r="J179" s="14" t="s">
-        <v>4115</v>
+        <v>4098</v>
       </c>
     </row>
     <row r="180" spans="1:10">
@@ -20781,10 +21488,10 @@
         <v>3045</v>
       </c>
       <c r="I180" s="14" t="s">
-        <v>3611</v>
+        <v>3600</v>
       </c>
       <c r="J180" s="14" t="s">
-        <v>4116</v>
+        <v>4099</v>
       </c>
     </row>
     <row r="181" spans="1:10">
@@ -20813,10 +21520,10 @@
         <v>3046</v>
       </c>
       <c r="I181" s="14" t="s">
-        <v>3612</v>
+        <v>3601</v>
       </c>
       <c r="J181" s="14" t="s">
-        <v>4117</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="182" spans="1:10">
@@ -20845,10 +21552,10 @@
         <v>3047</v>
       </c>
       <c r="I182" s="14" t="s">
-        <v>3613</v>
+        <v>3602</v>
       </c>
       <c r="J182" s="14" t="s">
-        <v>4118</v>
+        <v>4101</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -20877,10 +21584,10 @@
         <v>3048</v>
       </c>
       <c r="I183" s="14" t="s">
-        <v>3614</v>
+        <v>3603</v>
       </c>
       <c r="J183" s="14" t="s">
-        <v>4119</v>
+        <v>4102</v>
       </c>
     </row>
     <row r="184" spans="1:10">
@@ -20909,10 +21616,10 @@
         <v>3049</v>
       </c>
       <c r="I184" s="14" t="s">
-        <v>3616</v>
+        <v>3605</v>
       </c>
       <c r="J184" s="14" t="s">
-        <v>4029</v>
+        <v>4012</v>
       </c>
     </row>
     <row r="185" spans="1:10">
@@ -20941,10 +21648,10 @@
         <v>3050</v>
       </c>
       <c r="I185" s="14" t="s">
-        <v>3617</v>
+        <v>3606</v>
       </c>
       <c r="J185" s="14" t="s">
-        <v>4030</v>
+        <v>4013</v>
       </c>
     </row>
     <row r="186" spans="1:10">
@@ -20973,10 +21680,10 @@
         <v>3051</v>
       </c>
       <c r="I186" s="14" t="s">
-        <v>3615</v>
+        <v>3604</v>
       </c>
       <c r="J186" s="14" t="s">
-        <v>4031</v>
+        <v>4014</v>
       </c>
     </row>
     <row r="187" spans="1:10">
@@ -21005,10 +21712,10 @@
         <v>3052</v>
       </c>
       <c r="I187" s="14" t="s">
-        <v>3662</v>
+        <v>3651</v>
       </c>
       <c r="J187" s="14" t="s">
-        <v>4033</v>
+        <v>4016</v>
       </c>
     </row>
     <row r="188" spans="1:10">
@@ -21037,10 +21744,10 @@
         <v>3069</v>
       </c>
       <c r="I188" s="14" t="s">
-        <v>3663</v>
+        <v>3652</v>
       </c>
       <c r="J188" s="14" t="s">
-        <v>4032</v>
+        <v>4015</v>
       </c>
     </row>
     <row r="189" spans="1:10">
@@ -21069,10 +21776,10 @@
         <v>3068</v>
       </c>
       <c r="I189" s="14" t="s">
-        <v>3664</v>
+        <v>3653</v>
       </c>
       <c r="J189" s="14" t="s">
-        <v>4034</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="190" spans="1:10">
@@ -21101,10 +21808,10 @@
         <v>3070</v>
       </c>
       <c r="I190" s="14" t="s">
-        <v>3665</v>
+        <v>3654</v>
       </c>
       <c r="J190" s="14" t="s">
-        <v>4035</v>
+        <v>4018</v>
       </c>
     </row>
     <row r="191" spans="1:10">
@@ -21133,10 +21840,10 @@
         <v>2906</v>
       </c>
       <c r="I191" s="14" t="s">
-        <v>3666</v>
+        <v>3655</v>
       </c>
       <c r="J191" s="14" t="s">
-        <v>4036</v>
+        <v>4019</v>
       </c>
     </row>
     <row r="192" spans="1:10">
@@ -21165,10 +21872,10 @@
         <v>3071</v>
       </c>
       <c r="I192" s="14" t="s">
-        <v>3667</v>
+        <v>3656</v>
       </c>
       <c r="J192" s="14" t="s">
-        <v>4037</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="193" spans="1:10">
@@ -21197,10 +21904,10 @@
         <v>3072</v>
       </c>
       <c r="I193" s="14" t="s">
-        <v>3668</v>
+        <v>3657</v>
       </c>
       <c r="J193" s="14" t="s">
-        <v>4038</v>
+        <v>4021</v>
       </c>
     </row>
     <row r="194" spans="1:10">
@@ -21229,10 +21936,10 @@
         <v>3073</v>
       </c>
       <c r="I194" s="14" t="s">
-        <v>3669</v>
+        <v>3658</v>
       </c>
       <c r="J194" s="14" t="s">
-        <v>4039</v>
+        <v>4022</v>
       </c>
     </row>
     <row r="195" spans="1:10">
@@ -21261,10 +21968,10 @@
         <v>3074</v>
       </c>
       <c r="I195" s="14" t="s">
-        <v>3670</v>
+        <v>3659</v>
       </c>
       <c r="J195" s="14" t="s">
-        <v>4040</v>
+        <v>4023</v>
       </c>
     </row>
     <row r="196" spans="1:10">
@@ -21293,10 +22000,10 @@
         <v>3053</v>
       </c>
       <c r="I196" s="14" t="s">
-        <v>3671</v>
+        <v>3660</v>
       </c>
       <c r="J196" s="14" t="s">
-        <v>4041</v>
+        <v>4024</v>
       </c>
     </row>
     <row r="197" spans="1:10">
@@ -21325,10 +22032,10 @@
         <v>3054</v>
       </c>
       <c r="I197" s="14" t="s">
-        <v>3672</v>
+        <v>3661</v>
       </c>
       <c r="J197" s="14" t="s">
-        <v>4042</v>
+        <v>4025</v>
       </c>
     </row>
     <row r="198" spans="1:10">
@@ -21357,10 +22064,10 @@
         <v>1206</v>
       </c>
       <c r="I198" s="14" t="s">
-        <v>3673</v>
+        <v>3662</v>
       </c>
       <c r="J198" s="14" t="s">
-        <v>4043</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="199" spans="1:10">
@@ -21389,10 +22096,10 @@
         <v>3055</v>
       </c>
       <c r="I199" s="14" t="s">
-        <v>3674</v>
+        <v>3663</v>
       </c>
       <c r="J199" s="14" t="s">
-        <v>4044</v>
+        <v>4027</v>
       </c>
     </row>
     <row r="200" spans="1:10">
@@ -21421,10 +22128,10 @@
         <v>3056</v>
       </c>
       <c r="I200" s="14" t="s">
-        <v>3675</v>
+        <v>3664</v>
       </c>
       <c r="J200" s="14" t="s">
-        <v>4045</v>
+        <v>4028</v>
       </c>
     </row>
     <row r="201" spans="1:10">
@@ -21453,10 +22160,10 @@
         <v>3057</v>
       </c>
       <c r="I201" s="14" t="s">
-        <v>3676</v>
+        <v>3665</v>
       </c>
       <c r="J201" s="14" t="s">
-        <v>4046</v>
+        <v>4029</v>
       </c>
     </row>
     <row r="202" spans="1:10">
@@ -21485,10 +22192,10 @@
         <v>3058</v>
       </c>
       <c r="I202" s="14" t="s">
-        <v>3583</v>
+        <v>3572</v>
       </c>
       <c r="J202" s="14" t="s">
-        <v>3909</v>
+        <v>3892</v>
       </c>
     </row>
     <row r="203" spans="1:10">
@@ -21517,10 +22224,10 @@
         <v>3059</v>
       </c>
       <c r="I203" s="14" t="s">
-        <v>3677</v>
+        <v>3666</v>
       </c>
       <c r="J203" s="14" t="s">
-        <v>4047</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="204" spans="1:10">
@@ -21549,10 +22256,10 @@
         <v>3060</v>
       </c>
       <c r="I204" s="14" t="s">
-        <v>3678</v>
+        <v>3667</v>
       </c>
       <c r="J204" s="14" t="s">
-        <v>4048</v>
+        <v>4031</v>
       </c>
     </row>
     <row r="205" spans="1:10">
@@ -21581,10 +22288,10 @@
         <v>3061</v>
       </c>
       <c r="I205" s="14" t="s">
-        <v>3679</v>
+        <v>3668</v>
       </c>
       <c r="J205" s="14" t="s">
-        <v>4049</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="206" spans="1:10">
@@ -21613,10 +22320,10 @@
         <v>1256</v>
       </c>
       <c r="I206" s="14" t="s">
-        <v>3680</v>
+        <v>3669</v>
       </c>
       <c r="J206" s="14" t="s">
-        <v>3680</v>
+        <v>3669</v>
       </c>
     </row>
     <row r="207" spans="1:10">
@@ -21645,10 +22352,10 @@
         <v>3067</v>
       </c>
       <c r="I207" s="14" t="s">
-        <v>3681</v>
+        <v>3670</v>
       </c>
       <c r="J207" s="14" t="s">
-        <v>4050</v>
+        <v>4033</v>
       </c>
     </row>
     <row r="208" spans="1:10">
@@ -21677,10 +22384,10 @@
         <v>2911</v>
       </c>
       <c r="I208" s="14" t="s">
-        <v>3434</v>
+        <v>3426</v>
       </c>
       <c r="J208" s="14" t="s">
-        <v>3434</v>
+        <v>3426</v>
       </c>
     </row>
     <row r="209" spans="1:10">
@@ -21709,10 +22416,10 @@
         <v>175</v>
       </c>
       <c r="I209" s="14" t="s">
-        <v>3682</v>
+        <v>3671</v>
       </c>
       <c r="J209" s="14" t="s">
-        <v>3433</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="210" spans="1:10">
@@ -21741,10 +22448,10 @@
         <v>190</v>
       </c>
       <c r="I210" s="14" t="s">
-        <v>3683</v>
+        <v>3672</v>
       </c>
       <c r="J210" s="14" t="s">
-        <v>3858</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="211" spans="1:10">
@@ -21773,10 +22480,10 @@
         <v>3066</v>
       </c>
       <c r="I211" s="14" t="s">
-        <v>3685</v>
+        <v>3674</v>
       </c>
       <c r="J211" s="14" t="s">
-        <v>4051</v>
+        <v>4034</v>
       </c>
     </row>
     <row r="212" spans="1:10">
@@ -21805,10 +22512,10 @@
         <v>3065</v>
       </c>
       <c r="I212" s="14" t="s">
-        <v>3686</v>
+        <v>3675</v>
       </c>
       <c r="J212" s="14" t="s">
-        <v>4052</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="213" spans="1:10">
@@ -21837,10 +22544,10 @@
         <v>3064</v>
       </c>
       <c r="I213" s="14" t="s">
-        <v>3687</v>
+        <v>3676</v>
       </c>
       <c r="J213" s="14" t="s">
-        <v>4053</v>
+        <v>4036</v>
       </c>
     </row>
     <row r="214" spans="1:10">
@@ -21869,10 +22576,10 @@
         <v>3063</v>
       </c>
       <c r="I214" s="14" t="s">
-        <v>3684</v>
+        <v>3673</v>
       </c>
       <c r="J214" s="14" t="s">
-        <v>4122</v>
+        <v>4105</v>
       </c>
     </row>
     <row r="215" spans="1:10">
@@ -21901,10 +22608,10 @@
         <v>3062</v>
       </c>
       <c r="I215" s="14" t="s">
-        <v>3688</v>
+        <v>3677</v>
       </c>
       <c r="J215" s="14" t="s">
-        <v>4123</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -21933,10 +22640,10 @@
         <v>3217</v>
       </c>
       <c r="I216" s="14" t="s">
-        <v>3689</v>
+        <v>3678</v>
       </c>
       <c r="J216" s="14" t="s">
-        <v>4124</v>
+        <v>4107</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -21965,10 +22672,10 @@
         <v>3218</v>
       </c>
       <c r="I217" s="14" t="s">
-        <v>3690</v>
+        <v>3679</v>
       </c>
       <c r="J217" s="14" t="s">
-        <v>4125</v>
+        <v>4108</v>
       </c>
     </row>
     <row r="218" spans="1:10">
@@ -21997,10 +22704,10 @@
         <v>2912</v>
       </c>
       <c r="I218" s="14" t="s">
-        <v>3435</v>
+        <v>3427</v>
       </c>
       <c r="J218" s="14" t="s">
-        <v>3885</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="219" spans="1:10">
@@ -22029,10 +22736,10 @@
         <v>196</v>
       </c>
       <c r="I219" s="14" t="s">
-        <v>3691</v>
+        <v>3680</v>
       </c>
       <c r="J219" s="14" t="s">
-        <v>4126</v>
+        <v>4109</v>
       </c>
     </row>
     <row r="220" spans="1:10">
@@ -22061,10 +22768,10 @@
         <v>3219</v>
       </c>
       <c r="I220" s="14" t="s">
-        <v>3692</v>
+        <v>3681</v>
       </c>
       <c r="J220" s="14" t="s">
-        <v>4127</v>
+        <v>4110</v>
       </c>
     </row>
     <row r="221" spans="1:10">
@@ -22093,10 +22800,10 @@
         <v>3220</v>
       </c>
       <c r="I221" s="14" t="s">
-        <v>3693</v>
+        <v>3682</v>
       </c>
       <c r="J221" s="14" t="s">
-        <v>3693</v>
+        <v>3682</v>
       </c>
     </row>
     <row r="222" spans="1:10">
@@ -22125,10 +22832,10 @@
         <v>249</v>
       </c>
       <c r="I222" s="14" t="s">
-        <v>3446</v>
+        <v>3436</v>
       </c>
       <c r="J222" s="14" t="s">
-        <v>3866</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="223" spans="1:10">
@@ -22157,10 +22864,10 @@
         <v>255</v>
       </c>
       <c r="I223" s="14" t="s">
-        <v>3447</v>
+        <v>3437</v>
       </c>
       <c r="J223" s="14" t="s">
-        <v>3867</v>
+        <v>3853</v>
       </c>
     </row>
     <row r="224" spans="1:10">
@@ -22189,10 +22896,10 @@
         <v>2920</v>
       </c>
       <c r="I224" s="14" t="s">
-        <v>3448</v>
+        <v>3438</v>
       </c>
       <c r="J224" s="14" t="s">
-        <v>4120</v>
+        <v>4103</v>
       </c>
     </row>
     <row r="225" spans="1:10">
@@ -22221,10 +22928,10 @@
         <v>267</v>
       </c>
       <c r="I225" s="14" t="s">
-        <v>3449</v>
+        <v>3439</v>
       </c>
       <c r="J225" s="14" t="s">
-        <v>4121</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="226" spans="1:10">
@@ -22253,10 +22960,10 @@
         <v>3231</v>
       </c>
       <c r="I226" s="14" t="s">
-        <v>3694</v>
+        <v>3683</v>
       </c>
       <c r="J226" s="14" t="s">
-        <v>4054</v>
+        <v>4037</v>
       </c>
     </row>
     <row r="227" spans="1:10">
@@ -22285,10 +22992,10 @@
         <v>3232</v>
       </c>
       <c r="I227" s="14" t="s">
-        <v>3695</v>
+        <v>3684</v>
       </c>
       <c r="J227" s="14" t="s">
-        <v>4055</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="228" spans="1:10">
@@ -22317,10 +23024,10 @@
         <v>3233</v>
       </c>
       <c r="I228" s="14" t="s">
-        <v>3696</v>
+        <v>3685</v>
       </c>
       <c r="J228" s="14" t="s">
-        <v>4056</v>
+        <v>4039</v>
       </c>
     </row>
     <row r="229" spans="1:10">
@@ -22349,10 +23056,10 @@
         <v>2913</v>
       </c>
       <c r="I229" s="14" t="s">
-        <v>3697</v>
+        <v>3686</v>
       </c>
       <c r="J229" s="14" t="s">
-        <v>3860</v>
+        <v>3846</v>
       </c>
     </row>
     <row r="230" spans="1:10">
@@ -22381,10 +23088,10 @@
         <v>2914</v>
       </c>
       <c r="I230" s="14" t="s">
-        <v>3698</v>
+        <v>3687</v>
       </c>
       <c r="J230" s="14" t="s">
-        <v>3861</v>
+        <v>3847</v>
       </c>
     </row>
     <row r="231" spans="1:10">
@@ -22413,10 +23120,10 @@
         <v>2916</v>
       </c>
       <c r="I231" s="14" t="s">
-        <v>3440</v>
+        <v>3430</v>
       </c>
       <c r="J231" s="14" t="s">
-        <v>3862</v>
+        <v>3848</v>
       </c>
     </row>
     <row r="232" spans="1:10">
@@ -22445,10 +23152,10 @@
         <v>2915</v>
       </c>
       <c r="I232" s="14" t="s">
-        <v>3441</v>
+        <v>3431</v>
       </c>
       <c r="J232" s="14" t="s">
-        <v>3863</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="233" spans="1:10">
@@ -22477,10 +23184,10 @@
         <v>2917</v>
       </c>
       <c r="I233" s="14" t="s">
-        <v>3442</v>
+        <v>3432</v>
       </c>
       <c r="J233" s="14" t="s">
-        <v>3864</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="234" spans="1:10">
@@ -22509,10 +23216,10 @@
         <v>3238</v>
       </c>
       <c r="I234" s="14" t="s">
-        <v>3699</v>
+        <v>3688</v>
       </c>
       <c r="J234" s="14" t="s">
-        <v>4057</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -22541,10 +23248,10 @@
         <v>3237</v>
       </c>
       <c r="I235" s="14" t="s">
-        <v>3703</v>
+        <v>3692</v>
       </c>
       <c r="J235" s="14" t="s">
-        <v>4058</v>
+        <v>4041</v>
       </c>
     </row>
     <row r="236" spans="1:10">
@@ -22573,10 +23280,10 @@
         <v>3236</v>
       </c>
       <c r="I236" s="14" t="s">
-        <v>3702</v>
+        <v>3691</v>
       </c>
       <c r="J236" s="14" t="s">
-        <v>4059</v>
+        <v>4042</v>
       </c>
     </row>
     <row r="237" spans="1:10">
@@ -22605,10 +23312,10 @@
         <v>3235</v>
       </c>
       <c r="I237" s="14" t="s">
-        <v>3701</v>
+        <v>3690</v>
       </c>
       <c r="J237" s="14" t="s">
-        <v>4060</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="238" spans="1:10">
@@ -22637,10 +23344,10 @@
         <v>3234</v>
       </c>
       <c r="I238" s="14" t="s">
-        <v>3700</v>
+        <v>3689</v>
       </c>
       <c r="J238" s="14" t="s">
-        <v>4061</v>
+        <v>4044</v>
       </c>
     </row>
     <row r="239" spans="1:10">
@@ -22669,10 +23376,10 @@
         <v>3273</v>
       </c>
       <c r="I239" s="14" t="s">
-        <v>3704</v>
+        <v>3693</v>
       </c>
       <c r="J239" s="14" t="s">
-        <v>4134</v>
+        <v>4117</v>
       </c>
     </row>
     <row r="240" spans="1:10">
@@ -22701,10 +23408,10 @@
         <v>3274</v>
       </c>
       <c r="I240" s="14" t="s">
-        <v>3705</v>
+        <v>3694</v>
       </c>
       <c r="J240" s="14" t="s">
-        <v>3910</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="241" spans="1:10">
@@ -22733,10 +23440,10 @@
         <v>3275</v>
       </c>
       <c r="I241" s="14" t="s">
-        <v>3706</v>
+        <v>3695</v>
       </c>
       <c r="J241" s="14" t="s">
-        <v>4135</v>
+        <v>4118</v>
       </c>
     </row>
     <row r="242" spans="1:10">
@@ -22765,10 +23472,10 @@
         <v>3276</v>
       </c>
       <c r="I242" s="14" t="s">
-        <v>3707</v>
+        <v>3696</v>
       </c>
       <c r="J242" s="14" t="s">
-        <v>4136</v>
+        <v>4119</v>
       </c>
     </row>
     <row r="243" spans="1:10">
@@ -22797,10 +23504,10 @@
         <v>3277</v>
       </c>
       <c r="I243" s="14" t="s">
-        <v>3762</v>
+        <v>3751</v>
       </c>
       <c r="J243" s="14" t="s">
-        <v>4138</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="244" spans="1:10">
@@ -22829,10 +23536,10 @@
         <v>3278</v>
       </c>
       <c r="I244" s="14" t="s">
-        <v>3761</v>
+        <v>3750</v>
       </c>
       <c r="J244" s="14" t="s">
-        <v>4137</v>
+        <v>4120</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -22861,10 +23568,10 @@
         <v>3239</v>
       </c>
       <c r="I245" s="14" t="s">
-        <v>3743</v>
+        <v>3732</v>
       </c>
       <c r="J245" s="14" t="s">
-        <v>4139</v>
+        <v>4122</v>
       </c>
     </row>
     <row r="246" spans="1:10">
@@ -22893,10 +23600,10 @@
         <v>3240</v>
       </c>
       <c r="I246" s="14" t="s">
-        <v>3744</v>
+        <v>3733</v>
       </c>
       <c r="J246" s="14" t="s">
-        <v>4140</v>
+        <v>4123</v>
       </c>
     </row>
     <row r="247" spans="1:10">
@@ -22925,10 +23632,10 @@
         <v>3241</v>
       </c>
       <c r="I247" s="14" t="s">
-        <v>3745</v>
+        <v>3734</v>
       </c>
       <c r="J247" s="14" t="s">
-        <v>4141</v>
+        <v>4124</v>
       </c>
     </row>
     <row r="248" spans="1:10">
@@ -22957,10 +23664,10 @@
         <v>3242</v>
       </c>
       <c r="I248" s="14" t="s">
-        <v>3746</v>
+        <v>3735</v>
       </c>
       <c r="J248" s="14" t="s">
-        <v>4142</v>
+        <v>4125</v>
       </c>
     </row>
     <row r="249" spans="1:10">
@@ -22989,10 +23696,10 @@
         <v>3243</v>
       </c>
       <c r="I249" s="14" t="s">
-        <v>3747</v>
+        <v>3736</v>
       </c>
       <c r="J249" s="14" t="s">
-        <v>4185</v>
+        <v>4168</v>
       </c>
     </row>
     <row r="250" spans="1:10">
@@ -23021,10 +23728,10 @@
         <v>3244</v>
       </c>
       <c r="I250" s="14" t="s">
-        <v>3748</v>
+        <v>3737</v>
       </c>
       <c r="J250" s="14" t="s">
-        <v>4184</v>
+        <v>4167</v>
       </c>
     </row>
     <row r="251" spans="1:10">
@@ -23053,10 +23760,10 @@
         <v>3221</v>
       </c>
       <c r="I251" s="14" t="s">
-        <v>3749</v>
+        <v>3738</v>
       </c>
       <c r="J251" s="14" t="s">
-        <v>4183</v>
+        <v>4166</v>
       </c>
     </row>
     <row r="252" spans="1:10">
@@ -23085,10 +23792,10 @@
         <v>3222</v>
       </c>
       <c r="I252" s="14" t="s">
-        <v>3750</v>
+        <v>3739</v>
       </c>
       <c r="J252" s="14" t="s">
-        <v>4182</v>
+        <v>4165</v>
       </c>
     </row>
     <row r="253" spans="1:10">
@@ -23117,10 +23824,10 @@
         <v>3223</v>
       </c>
       <c r="I253" s="14" t="s">
-        <v>3617</v>
+        <v>3606</v>
       </c>
       <c r="J253" s="14" t="s">
-        <v>4178</v>
+        <v>4161</v>
       </c>
     </row>
     <row r="254" spans="1:10">
@@ -23149,10 +23856,10 @@
         <v>3224</v>
       </c>
       <c r="I254" s="14" t="s">
-        <v>3751</v>
+        <v>3740</v>
       </c>
       <c r="J254" s="14" t="s">
-        <v>4179</v>
+        <v>4162</v>
       </c>
     </row>
     <row r="255" spans="1:10">
@@ -23181,10 +23888,10 @@
         <v>3225</v>
       </c>
       <c r="I255" s="14" t="s">
-        <v>3752</v>
+        <v>3741</v>
       </c>
       <c r="J255" s="14" t="s">
-        <v>4180</v>
+        <v>4163</v>
       </c>
     </row>
     <row r="256" spans="1:10">
@@ -23213,10 +23920,10 @@
         <v>3226</v>
       </c>
       <c r="I256" s="14" t="s">
-        <v>3753</v>
+        <v>3742</v>
       </c>
       <c r="J256" s="14" t="s">
-        <v>4181</v>
+        <v>4164</v>
       </c>
     </row>
     <row r="257" spans="1:10">
@@ -23245,10 +23952,10 @@
         <v>3227</v>
       </c>
       <c r="I257" s="14" t="s">
-        <v>3754</v>
+        <v>3743</v>
       </c>
       <c r="J257" s="14" t="s">
-        <v>4190</v>
+        <v>4173</v>
       </c>
     </row>
     <row r="258" spans="1:10">
@@ -23277,10 +23984,10 @@
         <v>3228</v>
       </c>
       <c r="I258" s="14" t="s">
-        <v>3755</v>
+        <v>3744</v>
       </c>
       <c r="J258" s="14" t="s">
-        <v>4191</v>
+        <v>4174</v>
       </c>
     </row>
     <row r="259" spans="1:10">
@@ -23309,10 +24016,10 @@
         <v>3229</v>
       </c>
       <c r="I259" s="14" t="s">
-        <v>3756</v>
+        <v>3745</v>
       </c>
       <c r="J259" s="14" t="s">
-        <v>4192</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="260" spans="1:10">
@@ -23341,10 +24048,10 @@
         <v>3229</v>
       </c>
       <c r="I260" s="14" t="s">
-        <v>3756</v>
+        <v>3745</v>
       </c>
       <c r="J260" s="14" t="s">
-        <v>4192</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="261" spans="1:10">
@@ -23373,10 +24080,10 @@
         <v>3230</v>
       </c>
       <c r="I261" s="14" t="s">
-        <v>3757</v>
+        <v>3746</v>
       </c>
       <c r="J261" s="14" t="s">
-        <v>4193</v>
+        <v>4176</v>
       </c>
     </row>
     <row r="262" spans="1:10">
@@ -23408,7 +24115,7 @@
         <v>1534</v>
       </c>
       <c r="J262" s="14" t="s">
-        <v>4186</v>
+        <v>4169</v>
       </c>
     </row>
     <row r="263" spans="1:10">
@@ -23437,10 +24144,10 @@
         <v>1536</v>
       </c>
       <c r="I263" s="14" t="s">
-        <v>3758</v>
+        <v>3747</v>
       </c>
       <c r="J263" s="14" t="s">
-        <v>4187</v>
+        <v>4170</v>
       </c>
     </row>
     <row r="264" spans="1:10">
@@ -23469,10 +24176,10 @@
         <v>1541</v>
       </c>
       <c r="I264" s="14" t="s">
-        <v>3759</v>
+        <v>3748</v>
       </c>
       <c r="J264" s="14" t="s">
-        <v>4188</v>
+        <v>4171</v>
       </c>
     </row>
     <row r="265" spans="1:10">
@@ -23501,10 +24208,10 @@
         <v>3134</v>
       </c>
       <c r="I265" s="14" t="s">
-        <v>3760</v>
+        <v>3749</v>
       </c>
       <c r="J265" s="14" t="s">
-        <v>4189</v>
+        <v>4172</v>
       </c>
     </row>
     <row r="266" spans="1:10">
@@ -23533,10 +24240,10 @@
         <v>3135</v>
       </c>
       <c r="I266" s="14" t="s">
-        <v>3765</v>
+        <v>3754</v>
       </c>
       <c r="J266" s="14" t="s">
-        <v>4062</v>
+        <v>4045</v>
       </c>
     </row>
     <row r="267" spans="1:10">
@@ -23565,10 +24272,10 @@
         <v>3136</v>
       </c>
       <c r="I267" s="14" t="s">
-        <v>3763</v>
+        <v>3752</v>
       </c>
       <c r="J267" s="14" t="s">
-        <v>4063</v>
+        <v>4046</v>
       </c>
     </row>
     <row r="268" spans="1:10">
@@ -23597,10 +24304,10 @@
         <v>3137</v>
       </c>
       <c r="I268" s="14" t="s">
-        <v>3764</v>
+        <v>3753</v>
       </c>
       <c r="J268" s="14" t="s">
-        <v>4064</v>
+        <v>4047</v>
       </c>
     </row>
     <row r="269" spans="1:10">
@@ -23629,10 +24336,10 @@
         <v>3138</v>
       </c>
       <c r="I269" s="14" t="s">
-        <v>3766</v>
+        <v>3755</v>
       </c>
       <c r="J269" s="14" t="s">
-        <v>4065</v>
+        <v>4048</v>
       </c>
     </row>
     <row r="270" spans="1:10">
@@ -23661,10 +24368,10 @@
         <v>3139</v>
       </c>
       <c r="I270" s="14" t="s">
-        <v>3767</v>
+        <v>3756</v>
       </c>
       <c r="J270" s="14" t="s">
-        <v>4066</v>
+        <v>4049</v>
       </c>
     </row>
     <row r="271" spans="1:10">
@@ -23693,10 +24400,10 @@
         <v>3140</v>
       </c>
       <c r="I271" s="14" t="s">
-        <v>3768</v>
+        <v>3757</v>
       </c>
       <c r="J271" s="14" t="s">
-        <v>4067</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="272" spans="1:10">
@@ -23725,10 +24432,10 @@
         <v>3141</v>
       </c>
       <c r="I272" s="14" t="s">
-        <v>3844</v>
+        <v>3833</v>
       </c>
       <c r="J272" s="14" t="s">
-        <v>4068</v>
+        <v>4051</v>
       </c>
     </row>
     <row r="273" spans="1:10">
@@ -23757,10 +24464,10 @@
         <v>3142</v>
       </c>
       <c r="I273" s="14" t="s">
-        <v>3845</v>
+        <v>3834</v>
       </c>
       <c r="J273" s="14" t="s">
-        <v>4069</v>
+        <v>4052</v>
       </c>
     </row>
     <row r="274" spans="1:10">
@@ -23789,10 +24496,10 @@
         <v>3202</v>
       </c>
       <c r="I274" s="14" t="s">
-        <v>3843</v>
+        <v>3832</v>
       </c>
       <c r="J274" s="14" t="s">
-        <v>4070</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="275" spans="1:10">
@@ -23821,10 +24528,10 @@
         <v>3203</v>
       </c>
       <c r="I275" s="14" t="s">
-        <v>3846</v>
+        <v>3835</v>
       </c>
       <c r="J275" s="14" t="s">
-        <v>4071</v>
+        <v>4054</v>
       </c>
     </row>
     <row r="276" spans="1:10">
@@ -23853,10 +24560,10 @@
         <v>3204</v>
       </c>
       <c r="I276" s="14" t="s">
-        <v>3847</v>
+        <v>3836</v>
       </c>
       <c r="J276" s="14" t="s">
-        <v>4072</v>
+        <v>4055</v>
       </c>
     </row>
     <row r="277" spans="1:10">
@@ -23885,10 +24592,10 @@
         <v>3039</v>
       </c>
       <c r="I277" s="14" t="s">
-        <v>3848</v>
+        <v>3837</v>
       </c>
       <c r="J277" s="14" t="s">
-        <v>4073</v>
+        <v>4056</v>
       </c>
     </row>
     <row r="278" spans="1:10">
@@ -23917,10 +24624,10 @@
         <v>3205</v>
       </c>
       <c r="I278" s="14" t="s">
-        <v>3840</v>
+        <v>3829</v>
       </c>
       <c r="J278" s="14" t="s">
-        <v>4074</v>
+        <v>4057</v>
       </c>
     </row>
     <row r="279" spans="1:10">
@@ -23949,10 +24656,10 @@
         <v>3206</v>
       </c>
       <c r="I279" s="14" t="s">
-        <v>3841</v>
+        <v>3830</v>
       </c>
       <c r="J279" s="14" t="s">
-        <v>4075</v>
+        <v>4058</v>
       </c>
     </row>
     <row r="280" spans="1:10">
@@ -23981,10 +24688,10 @@
         <v>3207</v>
       </c>
       <c r="I280" s="14" t="s">
-        <v>3842</v>
+        <v>3831</v>
       </c>
       <c r="J280" s="14" t="s">
-        <v>4076</v>
+        <v>4059</v>
       </c>
     </row>
     <row r="281" spans="1:10">
@@ -24013,10 +24720,10 @@
         <v>1642</v>
       </c>
       <c r="I281" s="14" t="s">
-        <v>3832</v>
+        <v>3821</v>
       </c>
       <c r="J281" s="14" t="s">
-        <v>4077</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="282" spans="1:10">
@@ -24045,10 +24752,10 @@
         <v>3208</v>
       </c>
       <c r="I282" s="14" t="s">
-        <v>3833</v>
+        <v>3822</v>
       </c>
       <c r="J282" s="14" t="s">
-        <v>4078</v>
+        <v>4061</v>
       </c>
     </row>
     <row r="283" spans="1:10">
@@ -24077,10 +24784,10 @@
         <v>3209</v>
       </c>
       <c r="I283" s="14" t="s">
-        <v>3834</v>
+        <v>3823</v>
       </c>
       <c r="J283" s="14" t="s">
-        <v>4079</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="284" spans="1:10">
@@ -24109,10 +24816,10 @@
         <v>3210</v>
       </c>
       <c r="I284" s="14" t="s">
-        <v>3835</v>
+        <v>3824</v>
       </c>
       <c r="J284" s="14" t="s">
-        <v>4080</v>
+        <v>4063</v>
       </c>
     </row>
     <row r="285" spans="1:10">
@@ -24141,10 +24848,10 @@
         <v>3211</v>
       </c>
       <c r="I285" s="14" t="s">
-        <v>3836</v>
+        <v>3825</v>
       </c>
       <c r="J285" s="14" t="s">
-        <v>4085</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="286" spans="1:10">
@@ -24173,10 +24880,10 @@
         <v>3212</v>
       </c>
       <c r="I286" s="14" t="s">
-        <v>3837</v>
+        <v>3826</v>
       </c>
       <c r="J286" s="14" t="s">
-        <v>4086</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="287" spans="1:10">
@@ -24205,10 +24912,10 @@
         <v>3213</v>
       </c>
       <c r="I287" s="14" t="s">
-        <v>3839</v>
+        <v>3828</v>
       </c>
       <c r="J287" s="14" t="s">
-        <v>4087</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="288" spans="1:10">
@@ -24237,10 +24944,10 @@
         <v>3214</v>
       </c>
       <c r="I288" s="14" t="s">
-        <v>3838</v>
+        <v>3827</v>
       </c>
       <c r="J288" s="14" t="s">
-        <v>4090</v>
+        <v>4073</v>
       </c>
     </row>
     <row r="289" spans="1:10">
@@ -24269,10 +24976,10 @@
         <v>3215</v>
       </c>
       <c r="I289" s="14" t="s">
-        <v>3769</v>
+        <v>3758</v>
       </c>
       <c r="J289" s="14" t="s">
-        <v>4088</v>
+        <v>4071</v>
       </c>
     </row>
     <row r="290" spans="1:10">
@@ -24301,10 +25008,10 @@
         <v>3216</v>
       </c>
       <c r="I290" s="14" t="s">
-        <v>3770</v>
+        <v>3759</v>
       </c>
       <c r="J290" s="14" t="s">
-        <v>4089</v>
+        <v>4072</v>
       </c>
     </row>
     <row r="291" spans="1:10">
@@ -24333,10 +25040,10 @@
         <v>3186</v>
       </c>
       <c r="I291" s="14" t="s">
-        <v>3771</v>
+        <v>3760</v>
       </c>
       <c r="J291" s="14" t="s">
-        <v>4084</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="292" spans="1:10">
@@ -24365,10 +25072,10 @@
         <v>3187</v>
       </c>
       <c r="I292" s="14" t="s">
-        <v>3772</v>
+        <v>3761</v>
       </c>
       <c r="J292" s="14" t="s">
-        <v>4083</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="293" spans="1:10">
@@ -24397,10 +25104,10 @@
         <v>3189</v>
       </c>
       <c r="I293" s="14" t="s">
-        <v>3773</v>
+        <v>3762</v>
       </c>
       <c r="J293" s="14" t="s">
-        <v>4082</v>
+        <v>4065</v>
       </c>
     </row>
     <row r="294" spans="1:10">
@@ -24429,10 +25136,10 @@
         <v>3188</v>
       </c>
       <c r="I294" s="14" t="s">
-        <v>3775</v>
+        <v>3764</v>
       </c>
       <c r="J294" s="14" t="s">
-        <v>4081</v>
+        <v>4064</v>
       </c>
     </row>
     <row r="295" spans="1:10">
@@ -24461,10 +25168,10 @@
         <v>3014</v>
       </c>
       <c r="I295" s="14" t="s">
-        <v>3774</v>
+        <v>3763</v>
       </c>
       <c r="J295" s="14" t="s">
-        <v>4128</v>
+        <v>4111</v>
       </c>
     </row>
     <row r="296" spans="1:10">
@@ -24493,10 +25200,10 @@
         <v>3190</v>
       </c>
       <c r="I296" s="14" t="s">
-        <v>3776</v>
+        <v>3765</v>
       </c>
       <c r="J296" s="14" t="s">
-        <v>4129</v>
+        <v>4112</v>
       </c>
     </row>
     <row r="297" spans="1:10">
@@ -24525,10 +25232,10 @@
         <v>3191</v>
       </c>
       <c r="I297" s="14" t="s">
-        <v>3777</v>
+        <v>3766</v>
       </c>
       <c r="J297" s="14" t="s">
-        <v>4130</v>
+        <v>4113</v>
       </c>
     </row>
     <row r="298" spans="1:10">
@@ -24557,10 +25264,10 @@
         <v>3183</v>
       </c>
       <c r="I298" s="14" t="s">
-        <v>3778</v>
+        <v>3767</v>
       </c>
       <c r="J298" s="14" t="s">
-        <v>4131</v>
+        <v>4114</v>
       </c>
     </row>
     <row r="299" spans="1:10">
@@ -24589,10 +25296,10 @@
         <v>3184</v>
       </c>
       <c r="I299" s="14" t="s">
-        <v>3779</v>
+        <v>3768</v>
       </c>
       <c r="J299" s="14" t="s">
-        <v>4132</v>
+        <v>4115</v>
       </c>
     </row>
     <row r="300" spans="1:10">
@@ -24621,10 +25328,10 @@
         <v>3185</v>
       </c>
       <c r="I300" s="14" t="s">
-        <v>3780</v>
+        <v>3769</v>
       </c>
       <c r="J300" s="14" t="s">
-        <v>4133</v>
+        <v>4116</v>
       </c>
     </row>
     <row r="301" spans="1:10">
@@ -24653,10 +25360,10 @@
         <v>3245</v>
       </c>
       <c r="I301" s="14" t="s">
-        <v>3781</v>
+        <v>3770</v>
       </c>
       <c r="J301" s="14" t="s">
-        <v>4210</v>
+        <v>4193</v>
       </c>
     </row>
     <row r="302" spans="1:10">
@@ -24685,10 +25392,10 @@
         <v>3246</v>
       </c>
       <c r="I302" s="14" t="s">
-        <v>3782</v>
+        <v>3771</v>
       </c>
       <c r="J302" s="14" t="s">
-        <v>4211</v>
+        <v>4194</v>
       </c>
     </row>
     <row r="303" spans="1:10">
@@ -24717,10 +25424,10 @@
         <v>3247</v>
       </c>
       <c r="I303" s="14" t="s">
-        <v>3783</v>
+        <v>3772</v>
       </c>
       <c r="J303" s="14" t="s">
-        <v>4212</v>
+        <v>4195</v>
       </c>
     </row>
     <row r="304" spans="1:10">
@@ -24749,10 +25456,10 @@
         <v>3248</v>
       </c>
       <c r="I304" s="14" t="s">
-        <v>3784</v>
+        <v>3773</v>
       </c>
       <c r="J304" s="14" t="s">
-        <v>4213</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="305" spans="1:10">
@@ -24781,10 +25488,10 @@
         <v>3249</v>
       </c>
       <c r="I305" s="14" t="s">
-        <v>3797</v>
+        <v>3786</v>
       </c>
       <c r="J305" s="14" t="s">
-        <v>4214</v>
+        <v>4197</v>
       </c>
     </row>
     <row r="306" spans="1:10">
@@ -24813,10 +25520,10 @@
         <v>3250</v>
       </c>
       <c r="I306" s="14" t="s">
-        <v>3798</v>
+        <v>3787</v>
       </c>
       <c r="J306" s="14" t="s">
-        <v>4215</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="307" spans="1:10">
@@ -24845,10 +25552,10 @@
         <v>3266</v>
       </c>
       <c r="I307" s="14" t="s">
-        <v>3799</v>
+        <v>3788</v>
       </c>
       <c r="J307" s="14" t="s">
-        <v>4236</v>
+        <v>4219</v>
       </c>
     </row>
     <row r="308" spans="1:10">
@@ -24877,10 +25584,10 @@
         <v>3267</v>
       </c>
       <c r="I308" s="14" t="s">
-        <v>3800</v>
+        <v>3789</v>
       </c>
       <c r="J308" s="14" t="s">
-        <v>4237</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="309" spans="1:10">
@@ -24909,10 +25616,10 @@
         <v>3268</v>
       </c>
       <c r="I309" s="14" t="s">
-        <v>3801</v>
+        <v>3790</v>
       </c>
       <c r="J309" s="14" t="s">
-        <v>4234</v>
+        <v>4217</v>
       </c>
     </row>
     <row r="310" spans="1:10">
@@ -24941,10 +25648,10 @@
         <v>3269</v>
       </c>
       <c r="I310" s="14" t="s">
-        <v>3802</v>
+        <v>3791</v>
       </c>
       <c r="J310" s="14" t="s">
-        <v>4235</v>
+        <v>4218</v>
       </c>
     </row>
     <row r="311" spans="1:10">
@@ -24973,10 +25680,10 @@
         <v>3270</v>
       </c>
       <c r="I311" s="14" t="s">
-        <v>3803</v>
+        <v>3792</v>
       </c>
       <c r="J311" s="14" t="s">
-        <v>4240</v>
+        <v>4223</v>
       </c>
     </row>
     <row r="312" spans="1:10">
@@ -25005,10 +25712,10 @@
         <v>3271</v>
       </c>
       <c r="I312" s="14" t="s">
-        <v>3804</v>
+        <v>3793</v>
       </c>
       <c r="J312" s="14" t="s">
-        <v>4239</v>
+        <v>4222</v>
       </c>
     </row>
     <row r="313" spans="1:10">
@@ -25037,10 +25744,10 @@
         <v>3272</v>
       </c>
       <c r="I313" s="14" t="s">
-        <v>3805</v>
+        <v>3794</v>
       </c>
       <c r="J313" s="14" t="s">
-        <v>4238</v>
+        <v>4221</v>
       </c>
     </row>
     <row r="314" spans="1:10">
@@ -25069,10 +25776,10 @@
         <v>3251</v>
       </c>
       <c r="I314" s="14" t="s">
-        <v>3806</v>
+        <v>3795</v>
       </c>
       <c r="J314" s="14" t="s">
-        <v>4241</v>
+        <v>4224</v>
       </c>
     </row>
     <row r="315" spans="1:10">
@@ -25101,10 +25808,10 @@
         <v>3252</v>
       </c>
       <c r="I315" s="14" t="s">
-        <v>3807</v>
+        <v>3796</v>
       </c>
       <c r="J315" s="14" t="s">
-        <v>4242</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="316" spans="1:10">
@@ -25133,10 +25840,10 @@
         <v>3253</v>
       </c>
       <c r="I316" s="14" t="s">
-        <v>3808</v>
+        <v>3797</v>
       </c>
       <c r="J316" s="14" t="s">
-        <v>4217</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="317" spans="1:10">
@@ -25165,10 +25872,10 @@
         <v>3254</v>
       </c>
       <c r="I317" s="14" t="s">
-        <v>3809</v>
+        <v>3798</v>
       </c>
       <c r="J317" s="14" t="s">
-        <v>4218</v>
+        <v>4201</v>
       </c>
     </row>
     <row r="318" spans="1:10">
@@ -25197,10 +25904,10 @@
         <v>3256</v>
       </c>
       <c r="I318" s="14" t="s">
-        <v>3810</v>
+        <v>3799</v>
       </c>
       <c r="J318" s="14" t="s">
-        <v>3810</v>
+        <v>3799</v>
       </c>
     </row>
     <row r="319" spans="1:10">
@@ -25229,10 +25936,10 @@
         <v>3255</v>
       </c>
       <c r="I319" s="14" t="s">
-        <v>3811</v>
+        <v>3800</v>
       </c>
       <c r="J319" s="14" t="s">
-        <v>4216</v>
+        <v>4199</v>
       </c>
     </row>
     <row r="320" spans="1:10">
@@ -25261,10 +25968,10 @@
         <v>3258</v>
       </c>
       <c r="I320" s="14" t="s">
-        <v>3812</v>
+        <v>3801</v>
       </c>
       <c r="J320" s="14" t="s">
-        <v>4251</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="321" spans="1:10">
@@ -25293,10 +26000,10 @@
         <v>3257</v>
       </c>
       <c r="I321" s="14" t="s">
-        <v>3813</v>
+        <v>3802</v>
       </c>
       <c r="J321" s="14" t="s">
-        <v>4252</v>
+        <v>4235</v>
       </c>
     </row>
     <row r="322" spans="1:10">
@@ -25325,10 +26032,10 @@
         <v>3259</v>
       </c>
       <c r="I322" s="14" t="s">
-        <v>3814</v>
+        <v>3803</v>
       </c>
       <c r="J322" s="14" t="s">
-        <v>4253</v>
+        <v>4236</v>
       </c>
     </row>
     <row r="323" spans="1:10">
@@ -25357,10 +26064,10 @@
         <v>3260</v>
       </c>
       <c r="I323" s="14" t="s">
-        <v>3815</v>
+        <v>3804</v>
       </c>
       <c r="J323" s="14" t="s">
-        <v>4255</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="324" spans="1:10">
@@ -25389,10 +26096,10 @@
         <v>3261</v>
       </c>
       <c r="I324" s="14" t="s">
-        <v>3816</v>
+        <v>3805</v>
       </c>
       <c r="J324" s="14" t="s">
-        <v>4254</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="325" spans="1:10">
@@ -25421,10 +26128,10 @@
         <v>3262</v>
       </c>
       <c r="I325" s="14" t="s">
-        <v>3817</v>
+        <v>3806</v>
       </c>
       <c r="J325" s="14" t="s">
-        <v>4256</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="326" spans="1:10">
@@ -25453,10 +26160,10 @@
         <v>3263</v>
       </c>
       <c r="I326" s="14" t="s">
-        <v>3818</v>
+        <v>3807</v>
       </c>
       <c r="J326" s="14" t="s">
-        <v>4257</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="327" spans="1:10">
@@ -25485,10 +26192,10 @@
         <v>3264</v>
       </c>
       <c r="I327" s="14" t="s">
-        <v>3819</v>
+        <v>3808</v>
       </c>
       <c r="J327" s="14" t="s">
-        <v>4258</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="328" spans="1:10">
@@ -25517,10 +26224,10 @@
         <v>3265</v>
       </c>
       <c r="I328" s="14" t="s">
-        <v>3820</v>
+        <v>3809</v>
       </c>
       <c r="J328" s="14" t="s">
-        <v>4259</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="329" spans="1:10">
@@ -25549,10 +26256,10 @@
         <v>3192</v>
       </c>
       <c r="I329" s="14" t="s">
-        <v>3821</v>
+        <v>3810</v>
       </c>
       <c r="J329" s="14" t="s">
-        <v>4260</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="330" spans="1:10">
@@ -25581,10 +26288,10 @@
         <v>1950</v>
       </c>
       <c r="I330" s="14" t="s">
-        <v>3822</v>
+        <v>3811</v>
       </c>
       <c r="J330" s="14" t="s">
-        <v>4261</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="331" spans="1:10">
@@ -25613,10 +26320,10 @@
         <v>3193</v>
       </c>
       <c r="I331" s="14" t="s">
-        <v>3823</v>
+        <v>3812</v>
       </c>
       <c r="J331" s="14" t="s">
-        <v>4275</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="332" spans="1:10">
@@ -25645,10 +26352,10 @@
         <v>3194</v>
       </c>
       <c r="I332" s="14" t="s">
-        <v>3824</v>
+        <v>3813</v>
       </c>
       <c r="J332" s="14" t="s">
-        <v>4274</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="333" spans="1:10">
@@ -25677,10 +26384,10 @@
         <v>3195</v>
       </c>
       <c r="I333" s="14" t="s">
-        <v>3825</v>
+        <v>3814</v>
       </c>
       <c r="J333" s="14" t="s">
-        <v>4273</v>
+        <v>4256</v>
       </c>
     </row>
     <row r="334" spans="1:10">
@@ -25709,10 +26416,10 @@
         <v>3196</v>
       </c>
       <c r="I334" s="14" t="s">
-        <v>3826</v>
+        <v>3815</v>
       </c>
       <c r="J334" s="14" t="s">
-        <v>4269</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="335" spans="1:10">
@@ -25741,10 +26448,10 @@
         <v>3197</v>
       </c>
       <c r="I335" s="14" t="s">
-        <v>3827</v>
+        <v>3816</v>
       </c>
       <c r="J335" s="14" t="s">
-        <v>4270</v>
+        <v>4253</v>
       </c>
     </row>
     <row r="336" spans="1:10">
@@ -25773,10 +26480,10 @@
         <v>3198</v>
       </c>
       <c r="I336" s="14" t="s">
-        <v>3831</v>
+        <v>3820</v>
       </c>
       <c r="J336" s="14" t="s">
-        <v>4271</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="337" spans="1:10">
@@ -25805,10 +26512,10 @@
         <v>3201</v>
       </c>
       <c r="I337" s="14" t="s">
-        <v>3830</v>
+        <v>3819</v>
       </c>
       <c r="J337" s="14" t="s">
-        <v>4272</v>
+        <v>4255</v>
       </c>
     </row>
     <row r="338" spans="1:10">
@@ -25837,10 +26544,10 @@
         <v>3199</v>
       </c>
       <c r="I338" s="14" t="s">
-        <v>3829</v>
+        <v>3818</v>
       </c>
       <c r="J338" s="14" t="s">
-        <v>4265</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="339" spans="1:10">
@@ -25869,10 +26576,10 @@
         <v>2007</v>
       </c>
       <c r="I339" s="14" t="s">
-        <v>3828</v>
+        <v>3817</v>
       </c>
       <c r="J339" s="14" t="s">
-        <v>4266</v>
+        <v>4249</v>
       </c>
     </row>
     <row r="340" spans="1:10">
@@ -25901,10 +26608,10 @@
         <v>3200</v>
       </c>
       <c r="I340" s="14" t="s">
-        <v>3792</v>
+        <v>3781</v>
       </c>
       <c r="J340" s="14" t="s">
-        <v>4267</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="341" spans="1:10">
@@ -25933,10 +26640,10 @@
         <v>3143</v>
       </c>
       <c r="I341" s="14" t="s">
-        <v>3791</v>
+        <v>3780</v>
       </c>
       <c r="J341" s="14" t="s">
-        <v>4268</v>
+        <v>4251</v>
       </c>
     </row>
     <row r="342" spans="1:10">
@@ -25965,10 +26672,10 @@
         <v>3144</v>
       </c>
       <c r="I342" s="14" t="s">
-        <v>3790</v>
+        <v>3779</v>
       </c>
       <c r="J342" s="14" t="s">
-        <v>4264</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="343" spans="1:10">
@@ -25997,10 +26704,10 @@
         <v>3146</v>
       </c>
       <c r="I343" s="14" t="s">
-        <v>3789</v>
+        <v>3778</v>
       </c>
       <c r="J343" s="14" t="s">
-        <v>4263</v>
+        <v>4246</v>
       </c>
     </row>
     <row r="344" spans="1:10">
@@ -26029,10 +26736,10 @@
         <v>3145</v>
       </c>
       <c r="I344" s="14" t="s">
-        <v>3788</v>
+        <v>3777</v>
       </c>
       <c r="J344" s="14" t="s">
-        <v>4262</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="345" spans="1:10">
@@ -26061,10 +26768,10 @@
         <v>3148</v>
       </c>
       <c r="I345" s="14" t="s">
-        <v>3796</v>
+        <v>3785</v>
       </c>
       <c r="J345" s="14" t="s">
-        <v>4245</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="346" spans="1:10">
@@ -26093,10 +26800,10 @@
         <v>3147</v>
       </c>
       <c r="I346" s="14" t="s">
-        <v>3795</v>
+        <v>3784</v>
       </c>
       <c r="J346" s="14" t="s">
-        <v>4246</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="347" spans="1:10">
@@ -26125,10 +26832,10 @@
         <v>3153</v>
       </c>
       <c r="I347" s="14" t="s">
-        <v>3794</v>
+        <v>3783</v>
       </c>
       <c r="J347" s="14" t="s">
-        <v>4247</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="348" spans="1:10">
@@ -26157,10 +26864,10 @@
         <v>3152</v>
       </c>
       <c r="I348" s="14" t="s">
-        <v>3793</v>
+        <v>3782</v>
       </c>
       <c r="J348" s="14" t="s">
-        <v>4248</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="349" spans="1:10">
@@ -26189,10 +26896,10 @@
         <v>3150</v>
       </c>
       <c r="I349" s="14" t="s">
-        <v>3785</v>
+        <v>3774</v>
       </c>
       <c r="J349" s="14" t="s">
-        <v>4249</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="350" spans="1:10">
@@ -26221,10 +26928,10 @@
         <v>3151</v>
       </c>
       <c r="I350" s="14" t="s">
-        <v>3786</v>
+        <v>3775</v>
       </c>
       <c r="J350" s="14" t="s">
-        <v>4250</v>
+        <v>4233</v>
       </c>
     </row>
     <row r="351" spans="1:10">
@@ -26253,10 +26960,10 @@
         <v>3149</v>
       </c>
       <c r="I351" s="14" t="s">
-        <v>3787</v>
+        <v>3776</v>
       </c>
       <c r="J351" s="14" t="s">
-        <v>4244</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="352" spans="1:10">
@@ -26285,10 +26992,10 @@
         <v>3173</v>
       </c>
       <c r="I352" s="14" t="s">
-        <v>3730</v>
+        <v>3719</v>
       </c>
       <c r="J352" s="14" t="s">
-        <v>4243</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="353" spans="1:10">
@@ -26317,10 +27024,10 @@
         <v>3174</v>
       </c>
       <c r="I353" s="14" t="s">
-        <v>3731</v>
+        <v>3720</v>
       </c>
       <c r="J353" s="14" t="s">
-        <v>4219</v>
+        <v>4202</v>
       </c>
     </row>
     <row r="354" spans="1:10">
@@ -26349,10 +27056,10 @@
         <v>3177</v>
       </c>
       <c r="I354" s="14" t="s">
-        <v>3732</v>
+        <v>3721</v>
       </c>
       <c r="J354" s="14" t="s">
-        <v>4220</v>
+        <v>4203</v>
       </c>
     </row>
     <row r="355" spans="1:10">
@@ -26381,10 +27088,10 @@
         <v>3176</v>
       </c>
       <c r="I355" s="14" t="s">
-        <v>3733</v>
+        <v>3722</v>
       </c>
       <c r="J355" s="14" t="s">
-        <v>4221</v>
+        <v>4204</v>
       </c>
     </row>
     <row r="356" spans="1:10">
@@ -26413,10 +27120,10 @@
         <v>3175</v>
       </c>
       <c r="I356" s="14" t="s">
-        <v>3734</v>
+        <v>3723</v>
       </c>
       <c r="J356" s="14" t="s">
-        <v>4222</v>
+        <v>4205</v>
       </c>
     </row>
     <row r="357" spans="1:10">
@@ -26445,10 +27152,10 @@
         <v>3178</v>
       </c>
       <c r="I357" s="14" t="s">
-        <v>3735</v>
+        <v>3724</v>
       </c>
       <c r="J357" s="14" t="s">
-        <v>4223</v>
+        <v>4206</v>
       </c>
     </row>
     <row r="358" spans="1:10">
@@ -26477,10 +27184,10 @@
         <v>3179</v>
       </c>
       <c r="I358" s="14" t="s">
-        <v>3736</v>
+        <v>3725</v>
       </c>
       <c r="J358" s="14" t="s">
-        <v>4226</v>
+        <v>4209</v>
       </c>
     </row>
     <row r="359" spans="1:10">
@@ -26509,10 +27216,10 @@
         <v>3180</v>
       </c>
       <c r="I359" s="14" t="s">
-        <v>3737</v>
+        <v>3726</v>
       </c>
       <c r="J359" s="14" t="s">
-        <v>4225</v>
+        <v>4208</v>
       </c>
     </row>
     <row r="360" spans="1:10">
@@ -26541,10 +27248,10 @@
         <v>3181</v>
       </c>
       <c r="I360" s="14" t="s">
-        <v>3738</v>
+        <v>3727</v>
       </c>
       <c r="J360" s="14" t="s">
-        <v>4224</v>
+        <v>4207</v>
       </c>
     </row>
     <row r="361" spans="1:10">
@@ -26573,10 +27280,10 @@
         <v>3182</v>
       </c>
       <c r="I361" s="14" t="s">
-        <v>3739</v>
+        <v>3728</v>
       </c>
       <c r="J361" s="14" t="s">
-        <v>4229</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="362" spans="1:10">
@@ -26605,10 +27312,10 @@
         <v>3154</v>
       </c>
       <c r="I362" s="14" t="s">
-        <v>3740</v>
+        <v>3729</v>
       </c>
       <c r="J362" s="14" t="s">
-        <v>4227</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="363" spans="1:10">
@@ -26637,10 +27344,10 @@
         <v>2148</v>
       </c>
       <c r="I363" s="14" t="s">
-        <v>3741</v>
+        <v>3730</v>
       </c>
       <c r="J363" s="14" t="s">
-        <v>4228</v>
+        <v>4211</v>
       </c>
     </row>
     <row r="364" spans="1:10">
@@ -26669,10 +27376,10 @@
         <v>3155</v>
       </c>
       <c r="I364" s="14" t="s">
-        <v>3742</v>
+        <v>3731</v>
       </c>
       <c r="J364" s="14" t="s">
-        <v>4230</v>
+        <v>4213</v>
       </c>
     </row>
     <row r="365" spans="1:10">
@@ -26701,10 +27408,10 @@
         <v>3162</v>
       </c>
       <c r="I365" s="14" t="s">
-        <v>3727</v>
+        <v>3716</v>
       </c>
       <c r="J365" s="14" t="s">
-        <v>4231</v>
+        <v>4214</v>
       </c>
     </row>
     <row r="366" spans="1:10">
@@ -26733,10 +27440,10 @@
         <v>3161</v>
       </c>
       <c r="I366" s="14" t="s">
-        <v>3728</v>
+        <v>3717</v>
       </c>
       <c r="J366" s="14" t="s">
-        <v>4233</v>
+        <v>4216</v>
       </c>
     </row>
     <row r="367" spans="1:10">
@@ -26765,10 +27472,10 @@
         <v>3160</v>
       </c>
       <c r="I367" s="14" t="s">
-        <v>3729</v>
+        <v>3718</v>
       </c>
       <c r="J367" s="14" t="s">
-        <v>4233</v>
+        <v>4216</v>
       </c>
     </row>
     <row r="368" spans="1:10">
@@ -26797,10 +27504,10 @@
         <v>3159</v>
       </c>
       <c r="I368" s="14" t="s">
-        <v>3726</v>
+        <v>3715</v>
       </c>
       <c r="J368" s="14" t="s">
-        <v>4232</v>
+        <v>4215</v>
       </c>
     </row>
     <row r="369" spans="1:10">
@@ -26829,10 +27536,10 @@
         <v>2190</v>
       </c>
       <c r="I369" s="14" t="s">
-        <v>3716</v>
+        <v>3705</v>
       </c>
       <c r="J369" s="14" t="s">
-        <v>4202</v>
+        <v>4185</v>
       </c>
     </row>
     <row r="370" spans="1:10">
@@ -26861,10 +27568,10 @@
         <v>3156</v>
       </c>
       <c r="I370" s="14" t="s">
-        <v>3717</v>
+        <v>3706</v>
       </c>
       <c r="J370" s="14" t="s">
-        <v>4203</v>
+        <v>4186</v>
       </c>
     </row>
     <row r="371" spans="1:10">
@@ -26893,10 +27600,10 @@
         <v>3158</v>
       </c>
       <c r="I371" s="14" t="s">
-        <v>3718</v>
+        <v>3707</v>
       </c>
       <c r="J371" s="14" t="s">
-        <v>4204</v>
+        <v>4187</v>
       </c>
     </row>
     <row r="372" spans="1:10">
@@ -26925,10 +27632,10 @@
         <v>3157</v>
       </c>
       <c r="I372" s="14" t="s">
-        <v>3719</v>
+        <v>3708</v>
       </c>
       <c r="J372" s="14" t="s">
-        <v>4205</v>
+        <v>4188</v>
       </c>
     </row>
     <row r="373" spans="1:10">
@@ -26957,10 +27664,10 @@
         <v>3163</v>
       </c>
       <c r="I373" s="14" t="s">
-        <v>3720</v>
+        <v>3709</v>
       </c>
       <c r="J373" s="14" t="s">
-        <v>3720</v>
+        <v>3709</v>
       </c>
     </row>
     <row r="374" spans="1:10">
@@ -26989,10 +27696,10 @@
         <v>2222</v>
       </c>
       <c r="I374" s="14" t="s">
-        <v>3721</v>
+        <v>3710</v>
       </c>
       <c r="J374" s="14" t="s">
-        <v>4206</v>
+        <v>4189</v>
       </c>
     </row>
     <row r="375" spans="1:10">
@@ -27021,10 +27728,10 @@
         <v>3166</v>
       </c>
       <c r="I375" s="14" t="s">
-        <v>3722</v>
+        <v>3711</v>
       </c>
       <c r="J375" s="14" t="s">
-        <v>4207</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="376" spans="1:10">
@@ -27053,10 +27760,10 @@
         <v>3165</v>
       </c>
       <c r="I376" s="14" t="s">
-        <v>3723</v>
+        <v>3712</v>
       </c>
       <c r="J376" s="14" t="s">
-        <v>4208</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="377" spans="1:10">
@@ -27085,10 +27792,10 @@
         <v>3165</v>
       </c>
       <c r="I377" s="14" t="s">
-        <v>3724</v>
+        <v>3713</v>
       </c>
       <c r="J377" s="14" t="s">
-        <v>4209</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="378" spans="1:10">
@@ -27117,10 +27824,10 @@
         <v>3164</v>
       </c>
       <c r="I378" s="14" t="s">
-        <v>3725</v>
+        <v>3714</v>
       </c>
       <c r="J378" s="14" t="s">
-        <v>4198</v>
+        <v>4181</v>
       </c>
     </row>
     <row r="379" spans="1:10">
@@ -27149,10 +27856,10 @@
         <v>3167</v>
       </c>
       <c r="I379" s="14" t="s">
-        <v>3708</v>
+        <v>3697</v>
       </c>
       <c r="J379" s="14" t="s">
-        <v>4199</v>
+        <v>4182</v>
       </c>
     </row>
     <row r="380" spans="1:10">
@@ -27181,10 +27888,10 @@
         <v>3168</v>
       </c>
       <c r="I380" s="14" t="s">
-        <v>3709</v>
+        <v>3698</v>
       </c>
       <c r="J380" s="14" t="s">
-        <v>4200</v>
+        <v>4183</v>
       </c>
     </row>
     <row r="381" spans="1:10">
@@ -27213,10 +27920,10 @@
         <v>3169</v>
       </c>
       <c r="I381" s="14" t="s">
-        <v>3710</v>
+        <v>3699</v>
       </c>
       <c r="J381" s="14" t="s">
-        <v>4201</v>
+        <v>4184</v>
       </c>
     </row>
     <row r="382" spans="1:10">
@@ -27245,10 +27952,10 @@
         <v>3170</v>
       </c>
       <c r="I382" s="14" t="s">
-        <v>3711</v>
+        <v>3700</v>
       </c>
       <c r="J382" s="14" t="s">
-        <v>4197</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="383" spans="1:10">
@@ -27277,10 +27984,10 @@
         <v>3171</v>
       </c>
       <c r="I383" s="14" t="s">
-        <v>3712</v>
+        <v>3701</v>
       </c>
       <c r="J383" s="14" t="s">
-        <v>4196</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="384" spans="1:10">
@@ -27309,10 +28016,10 @@
         <v>3172</v>
       </c>
       <c r="I384" s="14" t="s">
-        <v>3713</v>
+        <v>3702</v>
       </c>
       <c r="J384" s="14" t="s">
-        <v>4194</v>
+        <v>4177</v>
       </c>
     </row>
     <row r="385" spans="1:10">
@@ -27341,10 +28048,10 @@
         <v>3097</v>
       </c>
       <c r="I385" s="14" t="s">
-        <v>3714</v>
+        <v>3703</v>
       </c>
       <c r="J385" s="14" t="s">
-        <v>4195</v>
+        <v>4178</v>
       </c>
     </row>
     <row r="386" spans="1:10">
@@ -27373,10 +28080,10 @@
         <v>3098</v>
       </c>
       <c r="I386" s="14" t="s">
-        <v>3715</v>
+        <v>3704</v>
       </c>
       <c r="J386" s="14" t="s">
-        <v>3976</v>
+        <v>3959</v>
       </c>
     </row>
     <row r="387" spans="1:10">
@@ -27405,10 +28112,10 @@
         <v>3099</v>
       </c>
       <c r="I387" s="14" t="s">
-        <v>3651</v>
+        <v>3640</v>
       </c>
       <c r="J387" s="14" t="s">
-        <v>3977</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="388" spans="1:10">
@@ -27437,10 +28144,10 @@
         <v>3100</v>
       </c>
       <c r="I388" s="14" t="s">
-        <v>3652</v>
+        <v>3641</v>
       </c>
       <c r="J388" s="14" t="s">
-        <v>3978</v>
+        <v>3961</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -27469,10 +28176,10 @@
         <v>3101</v>
       </c>
       <c r="I389" s="14" t="s">
-        <v>3653</v>
+        <v>3642</v>
       </c>
       <c r="J389" s="14" t="s">
-        <v>3979</v>
+        <v>3962</v>
       </c>
     </row>
     <row r="390" spans="1:10">
@@ -27501,10 +28208,10 @@
         <v>3102</v>
       </c>
       <c r="I390" s="14" t="s">
-        <v>3654</v>
+        <v>3643</v>
       </c>
       <c r="J390" s="14" t="s">
-        <v>3980</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="391" spans="1:10">
@@ -27533,10 +28240,10 @@
         <v>3103</v>
       </c>
       <c r="I391" s="14" t="s">
-        <v>3655</v>
+        <v>3644</v>
       </c>
       <c r="J391" s="14" t="s">
-        <v>3981</v>
+        <v>3964</v>
       </c>
     </row>
     <row r="392" spans="1:10">
@@ -27565,10 +28272,10 @@
         <v>3104</v>
       </c>
       <c r="I392" s="14" t="s">
-        <v>3656</v>
+        <v>3645</v>
       </c>
       <c r="J392" s="14" t="s">
-        <v>3982</v>
+        <v>3965</v>
       </c>
     </row>
     <row r="393" spans="1:10">
@@ -27597,10 +28304,10 @@
         <v>3105</v>
       </c>
       <c r="I393" s="14" t="s">
-        <v>3657</v>
+        <v>3646</v>
       </c>
       <c r="J393" s="14" t="s">
-        <v>3983</v>
+        <v>3966</v>
       </c>
     </row>
     <row r="394" spans="1:10">
@@ -27629,10 +28336,10 @@
         <v>3106</v>
       </c>
       <c r="I394" s="14" t="s">
-        <v>3658</v>
+        <v>3647</v>
       </c>
       <c r="J394" s="14" t="s">
-        <v>3984</v>
+        <v>3967</v>
       </c>
     </row>
     <row r="395" spans="1:10">
@@ -27661,10 +28368,10 @@
         <v>3108</v>
       </c>
       <c r="I395" s="14" t="s">
-        <v>3659</v>
+        <v>3648</v>
       </c>
       <c r="J395" s="14" t="s">
-        <v>3987</v>
+        <v>3970</v>
       </c>
     </row>
     <row r="396" spans="1:10">
@@ -27693,10 +28400,10 @@
         <v>3107</v>
       </c>
       <c r="I396" s="14" t="s">
-        <v>3660</v>
+        <v>3649</v>
       </c>
       <c r="J396" s="14" t="s">
-        <v>3986</v>
+        <v>3969</v>
       </c>
     </row>
     <row r="397" spans="1:10">
@@ -27725,10 +28432,10 @@
         <v>3109</v>
       </c>
       <c r="I397" s="14" t="s">
-        <v>3661</v>
+        <v>3650</v>
       </c>
       <c r="J397" s="14" t="s">
-        <v>3985</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="398" spans="1:10">
@@ -27757,10 +28464,10 @@
         <v>3111</v>
       </c>
       <c r="I398" s="14" t="s">
-        <v>3645</v>
+        <v>3634</v>
       </c>
       <c r="J398" s="14" t="s">
-        <v>3970</v>
+        <v>3953</v>
       </c>
     </row>
     <row r="399" spans="1:10">
@@ -27789,10 +28496,10 @@
         <v>3110</v>
       </c>
       <c r="I399" s="30" t="s">
-        <v>3646</v>
+        <v>3635</v>
       </c>
       <c r="J399" s="14" t="s">
-        <v>3971</v>
+        <v>3954</v>
       </c>
     </row>
     <row r="400" spans="1:10">
@@ -27821,10 +28528,10 @@
         <v>3112</v>
       </c>
       <c r="I400" s="30" t="s">
-        <v>3647</v>
+        <v>3636</v>
       </c>
       <c r="J400" s="14" t="s">
-        <v>3972</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="401" spans="1:10">
@@ -27853,10 +28560,10 @@
         <v>3113</v>
       </c>
       <c r="I401" s="14" t="s">
-        <v>3648</v>
+        <v>3637</v>
       </c>
       <c r="J401" s="14" t="s">
-        <v>3975</v>
+        <v>3958</v>
       </c>
     </row>
     <row r="402" spans="1:10">
@@ -27885,10 +28592,10 @@
         <v>3114</v>
       </c>
       <c r="I402" s="14" t="s">
-        <v>3649</v>
+        <v>3638</v>
       </c>
       <c r="J402" s="14" t="s">
-        <v>3974</v>
+        <v>3957</v>
       </c>
     </row>
     <row r="403" spans="1:10">
@@ -27917,10 +28624,10 @@
         <v>3115</v>
       </c>
       <c r="I403" s="14" t="s">
-        <v>3650</v>
+        <v>3639</v>
       </c>
       <c r="J403" s="14" t="s">
-        <v>3973</v>
+        <v>3956</v>
       </c>
     </row>
     <row r="404" spans="1:10">
@@ -27949,10 +28656,10 @@
         <v>3116</v>
       </c>
       <c r="I404" s="14" t="s">
-        <v>3623</v>
+        <v>3612</v>
       </c>
       <c r="J404" s="14" t="s">
-        <v>3988</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="405" spans="1:10">
@@ -27981,10 +28688,10 @@
         <v>3117</v>
       </c>
       <c r="I405" s="14" t="s">
-        <v>3624</v>
+        <v>3613</v>
       </c>
       <c r="J405" s="14" t="s">
-        <v>3989</v>
+        <v>3972</v>
       </c>
     </row>
     <row r="406" spans="1:10">
@@ -28013,10 +28720,10 @@
         <v>3118</v>
       </c>
       <c r="I406" s="14" t="s">
-        <v>3625</v>
+        <v>3614</v>
       </c>
       <c r="J406" s="14" t="s">
-        <v>3990</v>
+        <v>3973</v>
       </c>
     </row>
     <row r="407" spans="1:10">
@@ -28045,10 +28752,10 @@
         <v>3119</v>
       </c>
       <c r="I407" s="14" t="s">
-        <v>3626</v>
+        <v>3615</v>
       </c>
       <c r="J407" s="14" t="s">
-        <v>3991</v>
+        <v>3974</v>
       </c>
     </row>
     <row r="408" spans="1:10">
@@ -28077,10 +28784,10 @@
         <v>3120</v>
       </c>
       <c r="I408" s="14" t="s">
-        <v>3627</v>
+        <v>3616</v>
       </c>
       <c r="J408" s="14" t="s">
-        <v>3992</v>
+        <v>3975</v>
       </c>
     </row>
     <row r="409" spans="1:10">
@@ -28109,10 +28816,10 @@
         <v>3121</v>
       </c>
       <c r="I409" s="14" t="s">
-        <v>3628</v>
+        <v>3617</v>
       </c>
       <c r="J409" s="14" t="s">
-        <v>3995</v>
+        <v>3978</v>
       </c>
     </row>
     <row r="410" spans="1:10">
@@ -28141,10 +28848,10 @@
         <v>3122</v>
       </c>
       <c r="I410" s="14" t="s">
-        <v>3629</v>
+        <v>3618</v>
       </c>
       <c r="J410" s="14" t="s">
-        <v>3994</v>
+        <v>3977</v>
       </c>
     </row>
     <row r="411" spans="1:10">
@@ -28173,10 +28880,10 @@
         <v>3123</v>
       </c>
       <c r="I411" s="14" t="s">
-        <v>3630</v>
+        <v>3619</v>
       </c>
       <c r="J411" s="14" t="s">
-        <v>3993</v>
+        <v>3976</v>
       </c>
     </row>
     <row r="412" spans="1:10">
@@ -28205,10 +28912,10 @@
         <v>3124</v>
       </c>
       <c r="I412" s="14" t="s">
-        <v>3631</v>
+        <v>3620</v>
       </c>
       <c r="J412" s="14" t="s">
-        <v>4004</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="413" spans="1:10">
@@ -28237,10 +28944,10 @@
         <v>3125</v>
       </c>
       <c r="I413" s="14" t="s">
-        <v>3632</v>
+        <v>3621</v>
       </c>
       <c r="J413" s="14" t="s">
-        <v>3999</v>
+        <v>3982</v>
       </c>
     </row>
     <row r="414" spans="1:10">
@@ -28269,10 +28976,10 @@
         <v>3126</v>
       </c>
       <c r="I414" s="14" t="s">
-        <v>3633</v>
+        <v>3622</v>
       </c>
       <c r="J414" s="14" t="s">
-        <v>4000</v>
+        <v>3983</v>
       </c>
     </row>
     <row r="415" spans="1:10">
@@ -28301,10 +29008,10 @@
         <v>3127</v>
       </c>
       <c r="I415" s="14" t="s">
-        <v>3634</v>
+        <v>3623</v>
       </c>
       <c r="J415" s="14" t="s">
-        <v>4001</v>
+        <v>3984</v>
       </c>
     </row>
     <row r="416" spans="1:10">
@@ -28333,10 +29040,10 @@
         <v>3128</v>
       </c>
       <c r="I416" s="14" t="s">
-        <v>3635</v>
+        <v>3624</v>
       </c>
       <c r="J416" s="14" t="s">
-        <v>4002</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="417" spans="1:10">
@@ -28365,10 +29072,10 @@
         <v>3129</v>
       </c>
       <c r="I417" s="14" t="s">
-        <v>3636</v>
+        <v>3625</v>
       </c>
       <c r="J417" s="14" t="s">
-        <v>4003</v>
+        <v>3986</v>
       </c>
     </row>
     <row r="418" spans="1:10">
@@ -28397,10 +29104,10 @@
         <v>3130</v>
       </c>
       <c r="I418" s="14" t="s">
-        <v>3637</v>
+        <v>3626</v>
       </c>
       <c r="J418" s="14" t="s">
-        <v>3996</v>
+        <v>3979</v>
       </c>
     </row>
     <row r="419" spans="1:10">
@@ -28429,10 +29136,10 @@
         <v>3131</v>
       </c>
       <c r="I419" s="14" t="s">
-        <v>3638</v>
+        <v>3627</v>
       </c>
       <c r="J419" s="14" t="s">
-        <v>3997</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="420" spans="1:10">
@@ -28461,10 +29168,10 @@
         <v>3132</v>
       </c>
       <c r="I420" s="14" t="s">
-        <v>3639</v>
+        <v>3628</v>
       </c>
       <c r="J420" s="14" t="s">
-        <v>3998</v>
+        <v>3981</v>
       </c>
     </row>
     <row r="421" spans="1:10">
@@ -28493,10 +29200,10 @@
         <v>3133</v>
       </c>
       <c r="I421" s="14" t="s">
-        <v>3640</v>
+        <v>3629</v>
       </c>
       <c r="J421" s="14" t="s">
-        <v>3939</v>
+        <v>3922</v>
       </c>
     </row>
     <row r="422" spans="1:10">
@@ -28525,10 +29232,10 @@
         <v>3086</v>
       </c>
       <c r="I422" s="14" t="s">
-        <v>3641</v>
+        <v>3630</v>
       </c>
       <c r="J422" s="14" t="s">
-        <v>3940</v>
+        <v>3923</v>
       </c>
     </row>
     <row r="423" spans="1:10">
@@ -28557,10 +29264,10 @@
         <v>3091</v>
       </c>
       <c r="I423" s="14" t="s">
-        <v>3642</v>
+        <v>3631</v>
       </c>
       <c r="J423" s="14" t="s">
-        <v>3941</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="424" spans="1:10">
@@ -28589,10 +29296,10 @@
         <v>3092</v>
       </c>
       <c r="I424" s="14" t="s">
-        <v>3643</v>
+        <v>3632</v>
       </c>
       <c r="J424" s="14" t="s">
-        <v>3938</v>
+        <v>3921</v>
       </c>
     </row>
     <row r="425" spans="1:10">
@@ -28621,10 +29328,10 @@
         <v>3093</v>
       </c>
       <c r="I425" s="14" t="s">
-        <v>3644</v>
+        <v>3633</v>
       </c>
       <c r="J425" s="14" t="s">
-        <v>3937</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="426" spans="1:10">
@@ -28653,10 +29360,10 @@
         <v>3094</v>
       </c>
       <c r="I426" s="14" t="s">
-        <v>3620</v>
+        <v>3609</v>
       </c>
       <c r="J426" s="14" t="s">
-        <v>3934</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="427" spans="1:10">
@@ -28685,10 +29392,10 @@
         <v>3095</v>
       </c>
       <c r="I427" s="14" t="s">
-        <v>3621</v>
+        <v>3610</v>
       </c>
       <c r="J427" s="14" t="s">
-        <v>3935</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="428" spans="1:10">
@@ -28717,10 +29424,10 @@
         <v>3096</v>
       </c>
       <c r="I428" s="14" t="s">
-        <v>3622</v>
+        <v>3611</v>
       </c>
       <c r="J428" s="14" t="s">
-        <v>3936</v>
+        <v>3919</v>
       </c>
     </row>
     <row r="429" spans="1:10">
@@ -28749,10 +29456,10 @@
         <v>3090</v>
       </c>
       <c r="I429" s="14" t="s">
-        <v>3606</v>
+        <v>3595</v>
       </c>
       <c r="J429" s="14" t="s">
-        <v>3922</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -28781,10 +29488,10 @@
         <v>3089</v>
       </c>
       <c r="I430" s="14" t="s">
-        <v>3607</v>
+        <v>3596</v>
       </c>
       <c r="J430" s="14" t="s">
-        <v>3923</v>
+        <v>3906</v>
       </c>
     </row>
     <row r="431" spans="1:10">
@@ -28813,10 +29520,10 @@
         <v>3079</v>
       </c>
       <c r="I431" s="14" t="s">
-        <v>3608</v>
+        <v>3597</v>
       </c>
       <c r="J431" s="14" t="s">
-        <v>3924</v>
+        <v>3907</v>
       </c>
     </row>
     <row r="432" spans="1:10">
@@ -28845,10 +29552,10 @@
         <v>3080</v>
       </c>
       <c r="I432" s="14" t="s">
-        <v>3609</v>
+        <v>3598</v>
       </c>
       <c r="J432" s="14" t="s">
-        <v>3925</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="433" spans="1:10">
@@ -28877,10 +29584,10 @@
         <v>3081</v>
       </c>
       <c r="I433" s="14" t="s">
-        <v>3589</v>
+        <v>3578</v>
       </c>
       <c r="J433" s="14" t="s">
-        <v>3926</v>
+        <v>3909</v>
       </c>
     </row>
     <row r="434" spans="1:10">
@@ -28909,10 +29616,10 @@
         <v>3082</v>
       </c>
       <c r="I434" s="14" t="s">
-        <v>3590</v>
+        <v>3579</v>
       </c>
       <c r="J434" s="14" t="s">
-        <v>3927</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="435" spans="1:10">
@@ -28941,10 +29648,10 @@
         <v>3083</v>
       </c>
       <c r="I435" s="14" t="s">
-        <v>3591</v>
+        <v>3580</v>
       </c>
       <c r="J435" s="14" t="s">
-        <v>3928</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="436" spans="1:10">
@@ -28973,10 +29680,10 @@
         <v>2836</v>
       </c>
       <c r="I436" s="14" t="s">
-        <v>3592</v>
+        <v>3581</v>
       </c>
       <c r="J436" s="14" t="s">
-        <v>3929</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="437" spans="1:10">
@@ -29005,10 +29712,10 @@
         <v>3084</v>
       </c>
       <c r="I437" s="14" t="s">
-        <v>3593</v>
+        <v>3582</v>
       </c>
       <c r="J437" s="14" t="s">
-        <v>3930</v>
+        <v>3913</v>
       </c>
     </row>
     <row r="438" spans="1:10">
@@ -29037,10 +29744,10 @@
         <v>3085</v>
       </c>
       <c r="I438" s="14" t="s">
-        <v>3594</v>
+        <v>3583</v>
       </c>
       <c r="J438" s="14" t="s">
-        <v>3931</v>
+        <v>3914</v>
       </c>
     </row>
     <row r="439" spans="1:10">
@@ -29069,10 +29776,10 @@
         <v>3078</v>
       </c>
       <c r="I439" s="14" t="s">
-        <v>3595</v>
+        <v>3584</v>
       </c>
       <c r="J439" s="14" t="s">
-        <v>3932</v>
+        <v>3915</v>
       </c>
     </row>
     <row r="440" spans="1:10">
@@ -29101,10 +29808,10 @@
         <v>3077</v>
       </c>
       <c r="I440" s="14" t="s">
-        <v>3596</v>
+        <v>3585</v>
       </c>
       <c r="J440" s="14" t="s">
-        <v>3933</v>
+        <v>3916</v>
       </c>
     </row>
     <row r="441" spans="1:10">
@@ -29133,10 +29840,10 @@
         <v>3076</v>
       </c>
       <c r="I441" s="14" t="s">
-        <v>3597</v>
+        <v>3586</v>
       </c>
       <c r="J441" s="14" t="s">
-        <v>3915</v>
+        <v>3898</v>
       </c>
     </row>
     <row r="442" spans="1:10">
@@ -29165,10 +29872,10 @@
         <v>3075</v>
       </c>
       <c r="I442" s="14" t="s">
-        <v>3598</v>
+        <v>3587</v>
       </c>
       <c r="J442" s="14" t="s">
-        <v>3916</v>
+        <v>3899</v>
       </c>
     </row>
     <row r="443" spans="1:10">
@@ -29197,10 +29904,10 @@
         <v>3365</v>
       </c>
       <c r="I443" s="14" t="s">
-        <v>3599</v>
+        <v>3588</v>
       </c>
       <c r="J443" s="14" t="s">
-        <v>3917</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="444" spans="1:10">
@@ -29229,10 +29936,10 @@
         <v>3366</v>
       </c>
       <c r="I444" s="14" t="s">
-        <v>3600</v>
+        <v>3589</v>
       </c>
       <c r="J444" s="14" t="s">
-        <v>3918</v>
+        <v>3901</v>
       </c>
     </row>
     <row r="445" spans="1:10">
@@ -29261,10 +29968,10 @@
         <v>3367</v>
       </c>
       <c r="I445" s="14" t="s">
-        <v>3601</v>
+        <v>3590</v>
       </c>
       <c r="J445" s="14" t="s">
-        <v>3919</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="446" spans="1:10">
@@ -29293,10 +30000,10 @@
         <v>3368</v>
       </c>
       <c r="I446" s="14" t="s">
-        <v>3602</v>
+        <v>3591</v>
       </c>
       <c r="J446" s="14" t="s">
-        <v>3920</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="447" spans="1:10">
@@ -29325,10 +30032,10 @@
         <v>3369</v>
       </c>
       <c r="I447" s="14" t="s">
-        <v>3603</v>
+        <v>3592</v>
       </c>
       <c r="J447" s="14" t="s">
-        <v>3921</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="448" spans="1:10">
@@ -29357,10 +30064,10 @@
         <v>3370</v>
       </c>
       <c r="I448" s="14" t="s">
-        <v>3604</v>
+        <v>3593</v>
       </c>
       <c r="J448" s="14" t="s">
-        <v>3913</v>
+        <v>3896</v>
       </c>
     </row>
     <row r="449" spans="1:10">
@@ -29389,10 +30096,10 @@
         <v>3371</v>
       </c>
       <c r="I449" s="14" t="s">
-        <v>3605</v>
+        <v>3594</v>
       </c>
       <c r="J449" s="14" t="s">
-        <v>3914</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="450" spans="1:10">
@@ -29421,10 +30128,10 @@
         <v>3082</v>
       </c>
       <c r="I450" s="14" t="s">
-        <v>3579</v>
+        <v>3568</v>
       </c>
       <c r="J450" s="14" t="s">
-        <v>3912</v>
+        <v>3895</v>
       </c>
     </row>
     <row r="451" spans="1:10">
@@ -29453,10 +30160,10 @@
         <v>3293</v>
       </c>
       <c r="I451" s="14" t="s">
-        <v>3580</v>
+        <v>3569</v>
       </c>
       <c r="J451" s="14" t="s">
-        <v>3906</v>
+        <v>3889</v>
       </c>
     </row>
     <row r="452" spans="1:10">
@@ -29485,10 +30192,10 @@
         <v>3105</v>
       </c>
       <c r="I452" s="14" t="s">
-        <v>3581</v>
+        <v>3570</v>
       </c>
       <c r="J452" s="14" t="s">
-        <v>3907</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="453" spans="1:10">
@@ -29517,10 +30224,10 @@
         <v>3372</v>
       </c>
       <c r="I453" s="14" t="s">
-        <v>3582</v>
+        <v>3571</v>
       </c>
       <c r="J453" s="14" t="s">
-        <v>3908</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="454" spans="1:10">
@@ -29549,10 +30256,10 @@
         <v>3373</v>
       </c>
       <c r="I454" s="14" t="s">
-        <v>3583</v>
+        <v>3572</v>
       </c>
       <c r="J454" s="14" t="s">
-        <v>3909</v>
+        <v>3892</v>
       </c>
     </row>
     <row r="455" spans="1:10">
@@ -29581,10 +30288,10 @@
         <v>3274</v>
       </c>
       <c r="I455" s="14" t="s">
-        <v>3584</v>
+        <v>3573</v>
       </c>
       <c r="J455" s="14" t="s">
-        <v>3910</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="456" spans="1:10">
@@ -29613,10 +30320,10 @@
         <v>3374</v>
       </c>
       <c r="I456" s="14" t="s">
-        <v>3585</v>
+        <v>3574</v>
       </c>
       <c r="J456" s="14" t="s">
-        <v>3911</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="457" spans="1:10">
@@ -29645,10 +30352,10 @@
         <v>3375</v>
       </c>
       <c r="I457" s="14" t="s">
-        <v>3586</v>
+        <v>3575</v>
       </c>
       <c r="J457" s="14" t="s">
-        <v>3903</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="458" spans="1:10">
@@ -29677,10 +30384,10 @@
         <v>3376</v>
       </c>
       <c r="I458" s="14" t="s">
-        <v>3587</v>
+        <v>3576</v>
       </c>
       <c r="J458" s="14" t="s">
-        <v>3904</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="459" spans="1:10">
@@ -29709,36 +30416,36 @@
         <v>3377</v>
       </c>
       <c r="I459" s="14" t="s">
-        <v>3588</v>
+        <v>3577</v>
       </c>
       <c r="J459" s="14" t="s">
-        <v>3905</v>
-      </c>
-    </row>
-    <row r="460" spans="1:10" ht="205">
+        <v>3888</v>
+      </c>
+    </row>
+    <row r="460" spans="1:10" ht="193">
       <c r="A460" s="33" t="s">
         <v>3378</v>
       </c>
       <c r="B460" s="34" t="s">
-        <v>4688</v>
+        <v>4671</v>
       </c>
       <c r="C460" s="34" t="s">
-        <v>4689</v>
+        <v>4672</v>
       </c>
       <c r="D460" s="34" t="s">
-        <v>4690</v>
+        <v>4673</v>
       </c>
       <c r="E460" s="34" t="s">
-        <v>4691</v>
+        <v>4674</v>
       </c>
       <c r="F460" s="34" t="s">
-        <v>4692</v>
+        <v>4675</v>
       </c>
       <c r="G460" s="34" t="s">
-        <v>4693</v>
+        <v>4676</v>
       </c>
       <c r="H460" s="34" t="s">
-        <v>4694</v>
+        <v>4677</v>
       </c>
       <c r="I460" s="35"/>
       <c r="J460" s="35"/>
@@ -29748,25 +30455,25 @@
         <v>3379</v>
       </c>
       <c r="B461" s="34" t="s">
-        <v>4695</v>
+        <v>4678</v>
       </c>
       <c r="C461" s="34" t="s">
-        <v>4696</v>
+        <v>4679</v>
       </c>
       <c r="D461" s="30" t="s">
-        <v>4697</v>
+        <v>4680</v>
       </c>
       <c r="E461" s="34" t="s">
-        <v>4698</v>
+        <v>4681</v>
       </c>
       <c r="F461" s="34" t="s">
-        <v>4699</v>
+        <v>4682</v>
       </c>
       <c r="G461" s="30" t="s">
-        <v>4687</v>
+        <v>4670</v>
       </c>
       <c r="H461" s="34" t="s">
-        <v>4700</v>
+        <v>4683</v>
       </c>
       <c r="I461" s="14"/>
       <c r="J461" s="14"/>
@@ -29776,31 +30483,31 @@
         <v>3380</v>
       </c>
       <c r="B462" s="30" t="s">
-        <v>4701</v>
+        <v>4684</v>
       </c>
       <c r="C462" s="30" t="s">
-        <v>4702</v>
+        <v>4685</v>
       </c>
       <c r="D462" s="30" t="s">
-        <v>4703</v>
+        <v>4686</v>
       </c>
       <c r="E462" s="30" t="s">
-        <v>4704</v>
+        <v>4687</v>
       </c>
       <c r="F462" s="30" t="s">
-        <v>4705</v>
+        <v>4688</v>
       </c>
       <c r="G462" s="30" t="s">
         <v>3389</v>
       </c>
       <c r="H462" s="30" t="s">
-        <v>4706</v>
+        <v>4689</v>
       </c>
       <c r="I462" s="14" t="s">
-        <v>4707</v>
+        <v>4690</v>
       </c>
       <c r="J462" s="14" t="s">
-        <v>4708</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="463" spans="1:10">
@@ -29829,10 +30536,10 @@
         <v>3387</v>
       </c>
       <c r="I463" s="14" t="s">
-        <v>4276</v>
+        <v>4259</v>
       </c>
       <c r="J463" s="14" t="s">
-        <v>3902</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="464" spans="1:10">
@@ -29861,36 +30568,36 @@
         <v>3405</v>
       </c>
       <c r="I464" s="14" t="s">
-        <v>3618</v>
+        <v>3607</v>
       </c>
       <c r="J464" s="14" t="s">
-        <v>3901</v>
-      </c>
-    </row>
-    <row r="465" spans="1:10" ht="25">
+        <v>3884</v>
+      </c>
+    </row>
+    <row r="465" spans="1:10">
       <c r="A465" s="33" t="s">
         <v>3392</v>
       </c>
       <c r="B465" s="34" t="s">
-        <v>4709</v>
+        <v>4692</v>
       </c>
       <c r="C465" s="30" t="s">
-        <v>4710</v>
+        <v>4693</v>
       </c>
       <c r="D465" s="30" t="s">
-        <v>4711</v>
+        <v>4694</v>
       </c>
       <c r="E465" s="30" t="s">
-        <v>4712</v>
+        <v>4695</v>
       </c>
       <c r="F465" s="30" t="s">
-        <v>4713</v>
+        <v>4696</v>
       </c>
       <c r="G465" s="30" t="s">
-        <v>4714</v>
+        <v>4697</v>
       </c>
       <c r="H465" s="30" t="s">
-        <v>4715</v>
+        <v>4698</v>
       </c>
       <c r="I465" s="35"/>
       <c r="J465" s="35"/>
@@ -29921,1423 +30628,2295 @@
         <v>3404</v>
       </c>
       <c r="I466" s="14" t="s">
-        <v>3619</v>
+        <v>3608</v>
       </c>
       <c r="J466" s="14" t="s">
-        <v>3900</v>
+        <v>3883</v>
       </c>
     </row>
     <row r="467" spans="1:10">
       <c r="A467" s="33" t="s">
-        <v>4277</v>
+        <v>4260</v>
       </c>
       <c r="B467" s="30" t="s">
+        <v>4261</v>
+      </c>
+      <c r="C467" s="3" t="s">
+        <v>4272</v>
+      </c>
+      <c r="D467" s="3" t="s">
         <v>4278</v>
       </c>
-      <c r="C467" s="3" t="s">
+      <c r="E467" s="3" t="s">
+        <v>4272</v>
+      </c>
+      <c r="F467" s="3" t="s">
         <v>4289</v>
-      </c>
-      <c r="D467" s="3" t="s">
-        <v>4295</v>
-      </c>
-      <c r="E467" s="3" t="s">
-        <v>4289</v>
-      </c>
-      <c r="F467" s="3" t="s">
-        <v>4306</v>
       </c>
       <c r="G467" s="4" t="s">
         <v>1254</v>
       </c>
       <c r="H467" s="4" t="s">
-        <v>4332</v>
+        <v>4315</v>
       </c>
       <c r="I467" s="14" t="s">
-        <v>4312</v>
+        <v>4295</v>
       </c>
       <c r="J467" s="14" t="s">
-        <v>4318</v>
+        <v>4301</v>
       </c>
     </row>
     <row r="468" spans="1:10">
       <c r="A468" s="33" t="s">
-        <v>4279</v>
+        <v>4262</v>
       </c>
       <c r="B468" s="30" t="s">
-        <v>4280</v>
+        <v>4263</v>
       </c>
       <c r="C468" s="3" t="s">
+        <v>4273</v>
+      </c>
+      <c r="D468" s="3" t="s">
+        <v>4281</v>
+      </c>
+      <c r="E468" s="3" t="s">
+        <v>4284</v>
+      </c>
+      <c r="F468" s="3" t="s">
         <v>4290</v>
       </c>
-      <c r="D468" s="3" t="s">
-        <v>4298</v>
-      </c>
-      <c r="E468" s="3" t="s">
-        <v>4301</v>
-      </c>
-      <c r="F468" s="3" t="s">
+      <c r="G468" s="4" t="s">
         <v>4307</v>
       </c>
-      <c r="G468" s="4" t="s">
-        <v>4324</v>
-      </c>
       <c r="H468" s="4" t="s">
-        <v>4333</v>
+        <v>4316</v>
       </c>
       <c r="I468" s="14" t="s">
-        <v>4313</v>
+        <v>4296</v>
       </c>
       <c r="J468" s="14" t="s">
-        <v>4319</v>
+        <v>4302</v>
       </c>
     </row>
     <row r="469" spans="1:10">
       <c r="A469" s="33" t="s">
-        <v>4281</v>
+        <v>4264</v>
       </c>
       <c r="B469" s="30" t="s">
+        <v>4265</v>
+      </c>
+      <c r="C469" s="3" t="s">
+        <v>4274</v>
+      </c>
+      <c r="D469" s="3" t="s">
         <v>4282</v>
       </c>
-      <c r="C469" s="3" t="s">
+      <c r="E469" s="3" t="s">
+        <v>4285</v>
+      </c>
+      <c r="F469" s="3" t="s">
         <v>4291</v>
       </c>
-      <c r="D469" s="3" t="s">
-        <v>4299</v>
-      </c>
-      <c r="E469" s="3" t="s">
-        <v>4302</v>
-      </c>
-      <c r="F469" s="3" t="s">
+      <c r="G469" s="4" t="s">
         <v>4308</v>
       </c>
-      <c r="G469" s="4" t="s">
-        <v>4325</v>
-      </c>
       <c r="H469" s="4" t="s">
-        <v>4334</v>
+        <v>4317</v>
       </c>
       <c r="I469" s="14" t="s">
-        <v>4314</v>
+        <v>4297</v>
       </c>
       <c r="J469" s="14" t="s">
-        <v>4320</v>
+        <v>4303</v>
       </c>
     </row>
     <row r="470" spans="1:10">
       <c r="A470" s="33" t="s">
-        <v>4283</v>
+        <v>4266</v>
       </c>
       <c r="B470" s="30" t="s">
-        <v>4284</v>
+        <v>4267</v>
       </c>
       <c r="C470" s="3" t="s">
+        <v>4275</v>
+      </c>
+      <c r="D470" s="3" t="s">
+        <v>4279</v>
+      </c>
+      <c r="E470" s="3" t="s">
+        <v>4286</v>
+      </c>
+      <c r="F470" s="3" t="s">
         <v>4292</v>
       </c>
-      <c r="D470" s="3" t="s">
-        <v>4296</v>
-      </c>
-      <c r="E470" s="3" t="s">
-        <v>4303</v>
-      </c>
-      <c r="F470" s="3" t="s">
-        <v>4309</v>
-      </c>
       <c r="G470" s="4" t="s">
-        <v>4328</v>
+        <v>4311</v>
       </c>
       <c r="H470" s="4" t="s">
-        <v>4335</v>
+        <v>4318</v>
       </c>
       <c r="I470" s="14" t="s">
-        <v>4315</v>
+        <v>4298</v>
       </c>
       <c r="J470" s="14" t="s">
-        <v>4321</v>
+        <v>4304</v>
       </c>
     </row>
     <row r="471" spans="1:10">
       <c r="A471" s="33" t="s">
-        <v>4285</v>
+        <v>4268</v>
       </c>
       <c r="B471" s="30" t="s">
-        <v>4286</v>
+        <v>4269</v>
       </c>
       <c r="C471" s="3" t="s">
+        <v>4276</v>
+      </c>
+      <c r="D471" s="3" t="s">
+        <v>4280</v>
+      </c>
+      <c r="E471" s="3" t="s">
+        <v>4287</v>
+      </c>
+      <c r="F471" s="3" t="s">
         <v>4293</v>
       </c>
-      <c r="D471" s="3" t="s">
-        <v>4297</v>
-      </c>
-      <c r="E471" s="3" t="s">
-        <v>4304</v>
-      </c>
-      <c r="F471" s="3" t="s">
-        <v>4310</v>
-      </c>
       <c r="G471" s="4" t="s">
-        <v>4326</v>
+        <v>4309</v>
       </c>
       <c r="H471" s="4" t="s">
-        <v>4336</v>
+        <v>4319</v>
       </c>
       <c r="I471" s="14" t="s">
-        <v>4316</v>
+        <v>4299</v>
       </c>
       <c r="J471" s="14" t="s">
-        <v>4322</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="472" spans="1:10">
       <c r="A472" s="33" t="s">
-        <v>4287</v>
+        <v>4270</v>
       </c>
       <c r="B472" s="30" t="s">
+        <v>4271</v>
+      </c>
+      <c r="C472" s="3" t="s">
+        <v>4277</v>
+      </c>
+      <c r="D472" s="3" t="s">
+        <v>4283</v>
+      </c>
+      <c r="E472" s="3" t="s">
         <v>4288</v>
       </c>
-      <c r="C472" s="3" t="s">
+      <c r="F472" s="3" t="s">
         <v>4294</v>
       </c>
-      <c r="D472" s="3" t="s">
+      <c r="G472" s="4" t="s">
+        <v>4310</v>
+      </c>
+      <c r="H472" s="4" t="s">
+        <v>4320</v>
+      </c>
+      <c r="I472" s="14" t="s">
         <v>4300</v>
       </c>
-      <c r="E472" s="3" t="s">
-        <v>4305</v>
-      </c>
-      <c r="F472" s="3" t="s">
-        <v>4311</v>
-      </c>
-      <c r="G472" s="4" t="s">
-        <v>4327</v>
-      </c>
-      <c r="H472" s="4" t="s">
-        <v>4337</v>
-      </c>
-      <c r="I472" s="14" t="s">
-        <v>4317</v>
-      </c>
       <c r="J472" s="14" t="s">
-        <v>4323</v>
+        <v>4306</v>
       </c>
     </row>
     <row r="473" spans="1:10">
       <c r="A473" s="33" t="s">
-        <v>4329</v>
+        <v>4312</v>
       </c>
       <c r="B473" s="30" t="s">
-        <v>4330</v>
+        <v>4313</v>
       </c>
       <c r="C473" s="3" t="s">
-        <v>4344</v>
+        <v>4327</v>
       </c>
       <c r="D473" s="3" t="s">
-        <v>4343</v>
+        <v>4326</v>
       </c>
       <c r="E473" s="3" t="s">
-        <v>4342</v>
+        <v>4325</v>
       </c>
       <c r="F473" s="3" t="s">
-        <v>4341</v>
+        <v>4324</v>
       </c>
       <c r="G473" s="4" t="s">
-        <v>4331</v>
+        <v>4314</v>
       </c>
       <c r="H473" s="4" t="s">
-        <v>4338</v>
+        <v>4321</v>
       </c>
       <c r="I473" s="14" t="s">
-        <v>4340</v>
+        <v>4323</v>
       </c>
       <c r="J473" s="14" t="s">
-        <v>4339</v>
+        <v>4322</v>
       </c>
     </row>
     <row r="474" spans="1:10">
       <c r="A474" s="33" t="s">
-        <v>4345</v>
+        <v>4328</v>
       </c>
       <c r="B474" s="30" t="s">
-        <v>4346</v>
+        <v>4329</v>
       </c>
       <c r="C474" s="3" t="s">
-        <v>4347</v>
+        <v>4330</v>
       </c>
       <c r="D474" s="3" t="s">
-        <v>4348</v>
+        <v>4331</v>
       </c>
       <c r="E474" s="3" t="s">
-        <v>4349</v>
+        <v>4332</v>
       </c>
       <c r="F474" s="3" t="s">
-        <v>4350</v>
+        <v>4333</v>
       </c>
       <c r="G474" s="4" t="s">
-        <v>4352</v>
+        <v>4335</v>
       </c>
       <c r="H474" s="4" t="s">
-        <v>4351</v>
+        <v>4334</v>
       </c>
       <c r="I474" s="14" t="s">
-        <v>4354</v>
+        <v>4337</v>
       </c>
       <c r="J474" s="14" t="s">
-        <v>4353</v>
+        <v>4336</v>
       </c>
     </row>
     <row r="475" spans="1:10">
       <c r="A475" s="33" t="s">
-        <v>4356</v>
+        <v>4339</v>
       </c>
       <c r="B475" s="30" t="s">
-        <v>4355</v>
+        <v>4338</v>
       </c>
       <c r="C475" s="3" t="s">
-        <v>4360</v>
+        <v>4343</v>
       </c>
       <c r="D475" s="3" t="s">
-        <v>4355</v>
+        <v>4338</v>
       </c>
       <c r="E475" s="3" t="s">
-        <v>4360</v>
+        <v>4343</v>
       </c>
       <c r="F475" s="3" t="s">
-        <v>4357</v>
+        <v>4340</v>
       </c>
       <c r="G475" s="4" t="s">
-        <v>4361</v>
+        <v>4344</v>
       </c>
       <c r="H475" s="3" t="s">
-        <v>4355</v>
+        <v>4338</v>
       </c>
       <c r="I475" s="14" t="s">
-        <v>4358</v>
+        <v>4341</v>
       </c>
       <c r="J475" s="14" t="s">
-        <v>4359</v>
+        <v>4342</v>
       </c>
     </row>
     <row r="476" spans="1:10">
       <c r="A476" s="33" t="s">
-        <v>4364</v>
+        <v>4347</v>
       </c>
       <c r="B476" s="30" t="s">
-        <v>4365</v>
+        <v>4348</v>
       </c>
       <c r="C476" s="10" t="s">
-        <v>4398</v>
+        <v>4381</v>
       </c>
       <c r="D476" s="3" t="s">
-        <v>4408</v>
+        <v>4391</v>
       </c>
       <c r="E476" s="3" t="s">
-        <v>4403</v>
+        <v>4386</v>
       </c>
       <c r="F476" s="10" t="s">
-        <v>4412</v>
+        <v>4395</v>
       </c>
       <c r="G476" s="7" t="s">
-        <v>4427</v>
+        <v>4410</v>
       </c>
       <c r="H476" s="11" t="s">
-        <v>4432</v>
+        <v>4415</v>
       </c>
       <c r="I476" s="14" t="s">
-        <v>4422</v>
+        <v>4405</v>
       </c>
       <c r="J476" s="14" t="s">
-        <v>4417</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="477" spans="1:10" ht="49">
       <c r="A477" s="33" t="s">
-        <v>4366</v>
+        <v>4349</v>
       </c>
       <c r="B477" s="34" t="s">
-        <v>4367</v>
+        <v>4350</v>
       </c>
       <c r="C477" s="10" t="s">
-        <v>4399</v>
+        <v>4382</v>
       </c>
       <c r="D477" s="10" t="s">
-        <v>4409</v>
+        <v>4392</v>
       </c>
       <c r="E477" s="10" t="s">
-        <v>4404</v>
+        <v>4387</v>
       </c>
       <c r="F477" s="10" t="s">
-        <v>4413</v>
+        <v>4396</v>
       </c>
       <c r="G477" s="7" t="s">
-        <v>4428</v>
+        <v>4411</v>
       </c>
       <c r="H477" s="10" t="s">
-        <v>4433</v>
+        <v>4416</v>
       </c>
       <c r="I477" s="35" t="s">
-        <v>4423</v>
+        <v>4406</v>
       </c>
       <c r="J477" s="35" t="s">
-        <v>4418</v>
+        <v>4401</v>
       </c>
     </row>
     <row r="478" spans="1:10" ht="97">
       <c r="A478" s="33" t="s">
-        <v>4368</v>
+        <v>4351</v>
       </c>
       <c r="B478" s="34" t="s">
-        <v>4369</v>
+        <v>4352</v>
       </c>
       <c r="C478" s="10" t="s">
-        <v>4400</v>
+        <v>4383</v>
       </c>
       <c r="D478" s="10" t="s">
-        <v>4672</v>
+        <v>4655</v>
       </c>
       <c r="E478" s="10" t="s">
-        <v>4405</v>
+        <v>4388</v>
       </c>
       <c r="F478" s="10" t="s">
-        <v>4414</v>
+        <v>4397</v>
       </c>
       <c r="G478" s="7" t="s">
-        <v>4429</v>
+        <v>4412</v>
       </c>
       <c r="H478" s="10" t="s">
-        <v>4434</v>
+        <v>4417</v>
       </c>
       <c r="I478" s="35" t="s">
-        <v>4424</v>
+        <v>4407</v>
       </c>
       <c r="J478" s="35" t="s">
-        <v>4419</v>
+        <v>4402</v>
       </c>
     </row>
     <row r="479" spans="1:10" ht="97">
       <c r="A479" s="33" t="s">
-        <v>4390</v>
+        <v>4373</v>
       </c>
       <c r="B479" s="34" t="s">
-        <v>4391</v>
+        <v>4374</v>
       </c>
       <c r="C479" s="10" t="s">
-        <v>4401</v>
+        <v>4384</v>
       </c>
       <c r="D479" s="10" t="s">
-        <v>4410</v>
+        <v>4393</v>
       </c>
       <c r="E479" s="10" t="s">
-        <v>4406</v>
+        <v>4389</v>
       </c>
       <c r="F479" s="10" t="s">
-        <v>4415</v>
+        <v>4398</v>
       </c>
       <c r="G479" s="8" t="s">
-        <v>4430</v>
+        <v>4413</v>
       </c>
       <c r="H479" s="10" t="s">
-        <v>4435</v>
+        <v>4418</v>
       </c>
       <c r="I479" s="35" t="s">
-        <v>4425</v>
+        <v>4408</v>
       </c>
       <c r="J479" s="35" t="s">
-        <v>4420</v>
+        <v>4403</v>
       </c>
     </row>
     <row r="480" spans="1:10" ht="61">
       <c r="A480" s="33" t="s">
-        <v>4392</v>
+        <v>4375</v>
       </c>
       <c r="B480" s="34" t="s">
-        <v>4393</v>
+        <v>4376</v>
       </c>
       <c r="C480" s="10" t="s">
-        <v>4402</v>
+        <v>4385</v>
       </c>
       <c r="D480" s="10" t="s">
-        <v>4411</v>
+        <v>4394</v>
       </c>
       <c r="E480" s="10" t="s">
-        <v>4407</v>
+        <v>4390</v>
       </c>
       <c r="F480" s="10" t="s">
-        <v>4416</v>
+        <v>4399</v>
       </c>
       <c r="G480" s="8" t="s">
-        <v>4431</v>
+        <v>4414</v>
       </c>
       <c r="H480" s="10" t="s">
-        <v>4436</v>
+        <v>4419</v>
       </c>
       <c r="I480" s="35" t="s">
-        <v>4426</v>
+        <v>4409</v>
       </c>
       <c r="J480" s="35" t="s">
-        <v>4421</v>
+        <v>4404</v>
       </c>
     </row>
     <row r="481" spans="1:10" ht="61">
       <c r="A481" s="33" t="s">
-        <v>4394</v>
+        <v>4377</v>
       </c>
       <c r="B481" s="34" t="s">
-        <v>4395</v>
+        <v>4378</v>
       </c>
       <c r="C481" s="10" t="s">
-        <v>4437</v>
+        <v>4420</v>
       </c>
       <c r="D481" s="10" t="s">
-        <v>4444</v>
+        <v>4427</v>
       </c>
       <c r="E481" s="10" t="s">
-        <v>4446</v>
+        <v>4429</v>
       </c>
       <c r="F481" s="10" t="s">
-        <v>4453</v>
+        <v>4436</v>
       </c>
       <c r="G481" s="8" t="s">
-        <v>4479</v>
+        <v>4462</v>
       </c>
       <c r="H481" s="11" t="s">
-        <v>4472</v>
+        <v>4455</v>
       </c>
       <c r="I481" s="35" t="s">
-        <v>4466</v>
+        <v>4449</v>
       </c>
       <c r="J481" s="35" t="s">
-        <v>4460</v>
+        <v>4443</v>
       </c>
     </row>
     <row r="482" spans="1:10" ht="85">
       <c r="A482" s="33" t="s">
-        <v>4370</v>
+        <v>4353</v>
       </c>
       <c r="B482" s="34" t="s">
-        <v>4371</v>
+        <v>4354</v>
       </c>
       <c r="C482" s="10" t="s">
-        <v>4438</v>
+        <v>4421</v>
       </c>
       <c r="D482" s="10" t="s">
-        <v>4683</v>
+        <v>4666</v>
       </c>
       <c r="E482" s="10" t="s">
-        <v>4447</v>
+        <v>4430</v>
       </c>
       <c r="F482" s="10" t="s">
-        <v>4454</v>
+        <v>4437</v>
       </c>
       <c r="G482" s="7" t="s">
-        <v>4480</v>
+        <v>4463</v>
       </c>
       <c r="H482" s="11" t="s">
-        <v>4473</v>
+        <v>4456</v>
       </c>
       <c r="I482" s="35" t="s">
-        <v>4467</v>
+        <v>4450</v>
       </c>
       <c r="J482" s="35" t="s">
-        <v>4461</v>
+        <v>4444</v>
       </c>
     </row>
     <row r="483" spans="1:10" ht="49">
       <c r="A483" s="33" t="s">
-        <v>4372</v>
+        <v>4355</v>
       </c>
       <c r="B483" s="34" t="s">
-        <v>4373</v>
+        <v>4356</v>
       </c>
       <c r="C483" s="10" t="s">
-        <v>4439</v>
+        <v>4422</v>
       </c>
       <c r="D483" s="10" t="s">
-        <v>4673</v>
+        <v>4656</v>
       </c>
       <c r="E483" s="10" t="s">
-        <v>4448</v>
+        <v>4431</v>
       </c>
       <c r="F483" s="10" t="s">
-        <v>4455</v>
+        <v>4438</v>
       </c>
       <c r="G483" s="7" t="s">
-        <v>4481</v>
+        <v>4464</v>
       </c>
       <c r="H483" s="11" t="s">
-        <v>4474</v>
+        <v>4457</v>
       </c>
       <c r="I483" s="35" t="s">
-        <v>4468</v>
+        <v>4451</v>
       </c>
       <c r="J483" s="35" t="s">
-        <v>4462</v>
+        <v>4445</v>
       </c>
     </row>
     <row r="484" spans="1:10" ht="85">
       <c r="A484" s="33" t="s">
-        <v>4374</v>
+        <v>4357</v>
       </c>
       <c r="B484" s="34" t="s">
-        <v>4375</v>
+        <v>4358</v>
       </c>
       <c r="C484" s="10" t="s">
-        <v>4440</v>
+        <v>4423</v>
       </c>
       <c r="D484" s="10" t="s">
-        <v>4684</v>
+        <v>4667</v>
       </c>
       <c r="E484" s="10" t="s">
-        <v>4449</v>
+        <v>4432</v>
       </c>
       <c r="F484" s="10" t="s">
-        <v>4456</v>
+        <v>4439</v>
       </c>
       <c r="G484" s="7" t="s">
-        <v>4482</v>
+        <v>4465</v>
       </c>
       <c r="H484" s="10" t="s">
-        <v>4475</v>
+        <v>4458</v>
       </c>
       <c r="I484" s="35"/>
       <c r="J484" s="35"/>
     </row>
     <row r="485" spans="1:10" ht="85">
       <c r="A485" s="33" t="s">
-        <v>4378</v>
+        <v>4361</v>
       </c>
       <c r="B485" s="34" t="s">
-        <v>4379</v>
+        <v>4362</v>
       </c>
       <c r="C485" s="10" t="s">
-        <v>4441</v>
+        <v>4424</v>
       </c>
       <c r="D485" s="10" t="s">
-        <v>4685</v>
+        <v>4668</v>
       </c>
       <c r="E485" s="10" t="s">
-        <v>4450</v>
+        <v>4433</v>
       </c>
       <c r="F485" s="10" t="s">
-        <v>4457</v>
+        <v>4440</v>
       </c>
       <c r="G485" s="8" t="s">
-        <v>4483</v>
+        <v>4466</v>
       </c>
       <c r="H485" s="10" t="s">
-        <v>4476</v>
+        <v>4459</v>
       </c>
       <c r="I485" s="35" t="s">
-        <v>4469</v>
+        <v>4452</v>
       </c>
       <c r="J485" s="35" t="s">
-        <v>4463</v>
+        <v>4446</v>
       </c>
     </row>
     <row r="486" spans="1:10" ht="61">
       <c r="A486" s="33" t="s">
-        <v>4376</v>
+        <v>4359</v>
       </c>
       <c r="B486" s="34" t="s">
-        <v>4377</v>
+        <v>4360</v>
       </c>
       <c r="C486" s="10" t="s">
-        <v>4442</v>
+        <v>4425</v>
       </c>
       <c r="D486" s="10" t="s">
-        <v>4674</v>
+        <v>4657</v>
       </c>
       <c r="E486" s="10" t="s">
-        <v>4451</v>
+        <v>4434</v>
       </c>
       <c r="F486" s="10" t="s">
-        <v>4458</v>
+        <v>4441</v>
       </c>
       <c r="G486" s="7" t="s">
-        <v>4484</v>
+        <v>4467</v>
       </c>
       <c r="H486" s="10" t="s">
-        <v>4477</v>
+        <v>4460</v>
       </c>
       <c r="I486" s="35" t="s">
-        <v>4470</v>
+        <v>4453</v>
       </c>
       <c r="J486" s="35" t="s">
-        <v>4464</v>
+        <v>4447</v>
       </c>
     </row>
     <row r="487" spans="1:10" ht="37">
       <c r="A487" s="33" t="s">
-        <v>4380</v>
+        <v>4363</v>
       </c>
       <c r="B487" s="34" t="s">
-        <v>4381</v>
+        <v>4364</v>
       </c>
       <c r="C487" s="10" t="s">
-        <v>4443</v>
+        <v>4426</v>
       </c>
       <c r="D487" s="10" t="s">
-        <v>4445</v>
+        <v>4428</v>
       </c>
       <c r="E487" s="10" t="s">
-        <v>4452</v>
+        <v>4435</v>
       </c>
       <c r="F487" s="10" t="s">
-        <v>4459</v>
+        <v>4442</v>
       </c>
       <c r="G487" s="7" t="s">
-        <v>4485</v>
+        <v>4468</v>
       </c>
       <c r="H487" s="10" t="s">
-        <v>4478</v>
+        <v>4461</v>
       </c>
       <c r="I487" s="35" t="s">
-        <v>4471</v>
+        <v>4454</v>
       </c>
       <c r="J487" s="35" t="s">
-        <v>4465</v>
+        <v>4448</v>
       </c>
     </row>
     <row r="488" spans="1:10" ht="73">
       <c r="A488" s="33" t="s">
-        <v>4382</v>
+        <v>4365</v>
       </c>
       <c r="B488" s="34" t="s">
-        <v>4383</v>
+        <v>4366</v>
       </c>
       <c r="C488" s="3" t="s">
-        <v>4494</v>
+        <v>4477</v>
       </c>
       <c r="D488" s="3" t="s">
-        <v>4498</v>
+        <v>4481</v>
       </c>
       <c r="E488" s="3" t="s">
-        <v>4502</v>
+        <v>4485</v>
       </c>
       <c r="F488" s="10" t="s">
-        <v>4506</v>
+        <v>4489</v>
       </c>
       <c r="G488" s="7" t="s">
-        <v>4510</v>
+        <v>4493</v>
       </c>
       <c r="H488" s="9" t="s">
-        <v>4514</v>
+        <v>4497</v>
       </c>
       <c r="I488" s="35" t="s">
-        <v>4489</v>
+        <v>4472</v>
       </c>
       <c r="J488" s="35" t="s">
-        <v>4490</v>
+        <v>4473</v>
       </c>
     </row>
     <row r="489" spans="1:10">
       <c r="A489" s="33" t="s">
-        <v>4384</v>
+        <v>4367</v>
       </c>
       <c r="B489" s="30" t="s">
-        <v>4385</v>
+        <v>4368</v>
       </c>
       <c r="C489" s="3" t="s">
-        <v>4495</v>
+        <v>4478</v>
       </c>
       <c r="D489" s="3" t="s">
-        <v>4499</v>
+        <v>4482</v>
       </c>
       <c r="E489" s="3" t="s">
-        <v>4503</v>
+        <v>4486</v>
       </c>
       <c r="F489" s="10" t="s">
-        <v>4507</v>
+        <v>4490</v>
       </c>
       <c r="G489" s="7" t="s">
-        <v>4511</v>
+        <v>4494</v>
       </c>
       <c r="H489" s="9" t="s">
-        <v>4515</v>
+        <v>4498</v>
       </c>
       <c r="I489" s="35" t="s">
-        <v>4488</v>
+        <v>4471</v>
       </c>
       <c r="J489" s="35" t="s">
-        <v>4491</v>
+        <v>4474</v>
       </c>
     </row>
     <row r="490" spans="1:10" ht="49">
       <c r="A490" s="33" t="s">
-        <v>4386</v>
+        <v>4369</v>
       </c>
       <c r="B490" s="34" t="s">
-        <v>4387</v>
+        <v>4370</v>
       </c>
       <c r="C490" s="3" t="s">
-        <v>4496</v>
+        <v>4479</v>
       </c>
       <c r="D490" s="3" t="s">
-        <v>4500</v>
+        <v>4483</v>
       </c>
       <c r="E490" s="3" t="s">
-        <v>4504</v>
+        <v>4487</v>
       </c>
       <c r="F490" s="10" t="s">
-        <v>4508</v>
+        <v>4491</v>
       </c>
       <c r="G490" s="9" t="s">
-        <v>4512</v>
+        <v>4495</v>
       </c>
       <c r="H490" s="9" t="s">
-        <v>4516</v>
+        <v>4499</v>
       </c>
       <c r="I490" s="35" t="s">
-        <v>4487</v>
+        <v>4470</v>
       </c>
       <c r="J490" s="35" t="s">
-        <v>4492</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="491" spans="1:10" ht="25">
       <c r="A491" s="33" t="s">
-        <v>4388</v>
+        <v>4371</v>
       </c>
       <c r="B491" s="30" t="s">
-        <v>4389</v>
+        <v>4372</v>
       </c>
       <c r="C491" s="3" t="s">
-        <v>4497</v>
+        <v>4480</v>
       </c>
       <c r="D491" s="3" t="s">
-        <v>4501</v>
+        <v>4484</v>
       </c>
       <c r="E491" s="3" t="s">
-        <v>4505</v>
+        <v>4488</v>
       </c>
       <c r="F491" s="10" t="s">
-        <v>4509</v>
+        <v>4492</v>
       </c>
       <c r="G491" s="9" t="s">
-        <v>4513</v>
+        <v>4496</v>
       </c>
       <c r="H491" s="10" t="s">
-        <v>4517</v>
+        <v>4500</v>
       </c>
       <c r="I491" s="35" t="s">
-        <v>4486</v>
+        <v>4469</v>
       </c>
       <c r="J491" s="35" t="s">
-        <v>4493</v>
+        <v>4476</v>
       </c>
     </row>
     <row r="492" spans="1:10" ht="25">
       <c r="A492" s="33" t="s">
-        <v>4519</v>
+        <v>4502</v>
       </c>
       <c r="B492" s="30" t="s">
-        <v>4524</v>
+        <v>4507</v>
       </c>
       <c r="C492" s="3" t="s">
-        <v>4525</v>
+        <v>4508</v>
       </c>
       <c r="D492" s="3" t="s">
-        <v>4528</v>
+        <v>4511</v>
       </c>
       <c r="E492" s="3" t="s">
-        <v>4531</v>
+        <v>4514</v>
       </c>
       <c r="F492" s="3" t="s">
-        <v>4534</v>
+        <v>4517</v>
       </c>
       <c r="G492" s="11" t="s">
-        <v>4543</v>
+        <v>4526</v>
       </c>
       <c r="H492" s="11" t="s">
-        <v>4546</v>
+        <v>4529</v>
       </c>
       <c r="I492" s="14" t="s">
-        <v>4537</v>
+        <v>4520</v>
       </c>
       <c r="J492" s="14" t="s">
-        <v>4540</v>
+        <v>4523</v>
       </c>
     </row>
     <row r="493" spans="1:10">
       <c r="A493" s="33" t="s">
-        <v>4520</v>
+        <v>4503</v>
       </c>
       <c r="B493" s="30" t="s">
+        <v>4504</v>
+      </c>
+      <c r="C493" s="3" t="s">
+        <v>4509</v>
+      </c>
+      <c r="D493" s="3" t="s">
+        <v>4512</v>
+      </c>
+      <c r="E493" s="3" t="s">
+        <v>4515</v>
+      </c>
+      <c r="F493" s="3" t="s">
+        <v>4518</v>
+      </c>
+      <c r="G493" s="11" t="s">
+        <v>4527</v>
+      </c>
+      <c r="H493" s="11" t="s">
+        <v>4530</v>
+      </c>
+      <c r="I493" s="14" t="s">
         <v>4521</v>
       </c>
-      <c r="C493" s="3" t="s">
-        <v>4526</v>
-      </c>
-      <c r="D493" s="3" t="s">
-        <v>4529</v>
-      </c>
-      <c r="E493" s="3" t="s">
-        <v>4532</v>
-      </c>
-      <c r="F493" s="3" t="s">
-        <v>4535</v>
-      </c>
-      <c r="G493" s="11" t="s">
-        <v>4544</v>
-      </c>
-      <c r="H493" s="11" t="s">
-        <v>4547</v>
-      </c>
-      <c r="I493" s="14" t="s">
-        <v>4538</v>
-      </c>
       <c r="J493" s="14" t="s">
-        <v>4541</v>
+        <v>4524</v>
       </c>
     </row>
     <row r="494" spans="1:10">
       <c r="A494" s="33" t="s">
+        <v>4505</v>
+      </c>
+      <c r="B494" s="30" t="s">
+        <v>4506</v>
+      </c>
+      <c r="C494" s="3" t="s">
+        <v>4510</v>
+      </c>
+      <c r="D494" s="3" t="s">
+        <v>4513</v>
+      </c>
+      <c r="E494" s="3" t="s">
+        <v>4516</v>
+      </c>
+      <c r="F494" s="3" t="s">
+        <v>4519</v>
+      </c>
+      <c r="G494" s="11" t="s">
+        <v>4528</v>
+      </c>
+      <c r="H494" s="11" t="s">
+        <v>4531</v>
+      </c>
+      <c r="I494" s="14" t="s">
         <v>4522</v>
       </c>
-      <c r="B494" s="30" t="s">
-        <v>4523</v>
-      </c>
-      <c r="C494" s="3" t="s">
-        <v>4527</v>
-      </c>
-      <c r="D494" s="3" t="s">
-        <v>4530</v>
-      </c>
-      <c r="E494" s="3" t="s">
-        <v>4533</v>
-      </c>
-      <c r="F494" s="3" t="s">
-        <v>4536</v>
-      </c>
-      <c r="G494" s="11" t="s">
-        <v>4545</v>
-      </c>
-      <c r="H494" s="11" t="s">
-        <v>4548</v>
-      </c>
-      <c r="I494" s="14" t="s">
-        <v>4539</v>
-      </c>
       <c r="J494" s="14" t="s">
-        <v>4542</v>
+        <v>4525</v>
       </c>
     </row>
     <row r="495" spans="1:10">
       <c r="A495" s="33" t="s">
-        <v>4549</v>
+        <v>4532</v>
       </c>
       <c r="B495" s="36" t="s">
-        <v>4562</v>
+        <v>4545</v>
       </c>
       <c r="C495" s="3" t="s">
-        <v>4575</v>
+        <v>4558</v>
       </c>
       <c r="D495" s="3" t="s">
-        <v>4587</v>
+        <v>4570</v>
       </c>
       <c r="E495" s="3" t="s">
-        <v>4598</v>
+        <v>4581</v>
       </c>
       <c r="F495" s="3" t="s">
         <v>2852</v>
       </c>
       <c r="G495" s="5" t="s">
-        <v>4652</v>
+        <v>4635</v>
       </c>
       <c r="H495" s="3" t="s">
-        <v>4640</v>
+        <v>4623</v>
       </c>
       <c r="I495" s="14" t="s">
-        <v>4619</v>
+        <v>4602</v>
       </c>
       <c r="J495" s="14" t="s">
-        <v>3933</v>
+        <v>3916</v>
       </c>
     </row>
     <row r="496" spans="1:10">
       <c r="A496" s="33" t="s">
-        <v>4550</v>
+        <v>4533</v>
       </c>
       <c r="B496" s="36" t="s">
-        <v>4563</v>
+        <v>4546</v>
       </c>
       <c r="C496" s="3" t="s">
-        <v>4576</v>
+        <v>4559</v>
       </c>
       <c r="D496" s="3" t="s">
-        <v>4588</v>
+        <v>4571</v>
       </c>
       <c r="E496" s="3" t="s">
-        <v>4599</v>
+        <v>4582</v>
       </c>
       <c r="F496" s="3" t="s">
-        <v>4609</v>
+        <v>4592</v>
       </c>
       <c r="G496" s="5" t="s">
-        <v>4653</v>
+        <v>4636</v>
       </c>
       <c r="H496" s="3" t="s">
-        <v>4641</v>
+        <v>4624</v>
       </c>
       <c r="I496" s="14" t="s">
-        <v>4620</v>
+        <v>4603</v>
       </c>
       <c r="J496" s="14" t="s">
-        <v>4630</v>
+        <v>4613</v>
       </c>
     </row>
     <row r="497" spans="1:10">
       <c r="A497" s="33" t="s">
-        <v>4551</v>
+        <v>4534</v>
       </c>
       <c r="B497" s="30" t="s">
-        <v>4564</v>
+        <v>4547</v>
       </c>
       <c r="C497" s="3" t="s">
-        <v>4577</v>
+        <v>4560</v>
       </c>
       <c r="D497" s="3" t="s">
-        <v>4589</v>
+        <v>4572</v>
       </c>
       <c r="E497" s="3" t="s">
-        <v>4577</v>
+        <v>4560</v>
       </c>
       <c r="F497" s="3" t="s">
-        <v>4610</v>
+        <v>4593</v>
       </c>
       <c r="G497" s="5" t="s">
-        <v>4654</v>
+        <v>4637</v>
       </c>
       <c r="H497" s="3" t="s">
-        <v>4642</v>
+        <v>4625</v>
       </c>
       <c r="I497" s="14" t="s">
-        <v>4621</v>
+        <v>4604</v>
       </c>
       <c r="J497" s="14" t="s">
-        <v>4631</v>
+        <v>4614</v>
       </c>
     </row>
     <row r="498" spans="1:10">
       <c r="A498" s="33" t="s">
-        <v>4552</v>
+        <v>4535</v>
       </c>
       <c r="B498" s="36" t="s">
-        <v>4565</v>
+        <v>4548</v>
       </c>
       <c r="C498" s="3" t="s">
-        <v>4578</v>
+        <v>4561</v>
       </c>
       <c r="D498" s="3" t="s">
-        <v>4590</v>
+        <v>4573</v>
       </c>
       <c r="E498" s="3" t="s">
-        <v>4600</v>
+        <v>4583</v>
       </c>
       <c r="F498" s="3" t="s">
-        <v>4611</v>
+        <v>4594</v>
       </c>
       <c r="G498" s="5" t="s">
-        <v>4655</v>
+        <v>4638</v>
       </c>
       <c r="H498" s="3" t="s">
-        <v>4643</v>
+        <v>4626</v>
       </c>
       <c r="I498" s="14" t="s">
-        <v>4622</v>
+        <v>4605</v>
       </c>
       <c r="J498" s="14" t="s">
-        <v>4632</v>
+        <v>4615</v>
       </c>
     </row>
     <row r="499" spans="1:10">
       <c r="A499" s="33" t="s">
-        <v>4553</v>
+        <v>4536</v>
       </c>
       <c r="B499" s="36" t="s">
-        <v>4566</v>
+        <v>4549</v>
       </c>
       <c r="C499" s="3" t="s">
-        <v>4579</v>
+        <v>4562</v>
       </c>
       <c r="D499" s="3" t="s">
-        <v>4588</v>
+        <v>4571</v>
       </c>
       <c r="E499" s="3" t="s">
-        <v>4601</v>
+        <v>4584</v>
       </c>
       <c r="F499" s="3" t="s">
-        <v>4609</v>
+        <v>4592</v>
       </c>
       <c r="G499" s="5" t="s">
-        <v>4656</v>
+        <v>4639</v>
       </c>
       <c r="H499" s="3" t="s">
-        <v>4644</v>
+        <v>4627</v>
       </c>
       <c r="I499" s="14" t="s">
-        <v>4620</v>
+        <v>4603</v>
       </c>
       <c r="J499" s="14" t="s">
-        <v>4630</v>
+        <v>4613</v>
       </c>
     </row>
     <row r="500" spans="1:10">
       <c r="A500" s="33" t="s">
-        <v>4554</v>
+        <v>4537</v>
       </c>
       <c r="B500" s="36" t="s">
-        <v>4567</v>
+        <v>4550</v>
       </c>
       <c r="C500" s="3" t="s">
-        <v>4580</v>
+        <v>4563</v>
       </c>
       <c r="D500" s="3" t="s">
-        <v>4591</v>
+        <v>4574</v>
       </c>
       <c r="E500" s="3" t="s">
-        <v>4602</v>
+        <v>4585</v>
       </c>
       <c r="F500" s="3" t="s">
-        <v>4612</v>
+        <v>4595</v>
       </c>
       <c r="G500" s="5" t="s">
-        <v>4657</v>
+        <v>4640</v>
       </c>
       <c r="H500" s="3" t="s">
-        <v>4645</v>
+        <v>4628</v>
       </c>
       <c r="I500" s="14" t="s">
-        <v>4623</v>
+        <v>4606</v>
       </c>
       <c r="J500" s="14" t="s">
-        <v>4633</v>
+        <v>4616</v>
       </c>
     </row>
     <row r="501" spans="1:10">
       <c r="A501" s="33" t="s">
-        <v>4555</v>
+        <v>4538</v>
       </c>
       <c r="B501" s="36" t="s">
-        <v>4568</v>
+        <v>4551</v>
       </c>
       <c r="C501" s="3" t="s">
-        <v>4581</v>
+        <v>4564</v>
       </c>
       <c r="D501" s="3" t="s">
-        <v>4592</v>
+        <v>4575</v>
       </c>
       <c r="E501" s="3" t="s">
-        <v>4603</v>
+        <v>4586</v>
       </c>
       <c r="F501" s="3" t="s">
-        <v>4613</v>
+        <v>4596</v>
       </c>
       <c r="G501" s="5" t="s">
-        <v>4658</v>
+        <v>4641</v>
       </c>
       <c r="H501" s="3" t="s">
-        <v>4646</v>
+        <v>4629</v>
       </c>
       <c r="I501" s="14" t="s">
-        <v>4624</v>
+        <v>4607</v>
       </c>
       <c r="J501" s="14" t="s">
-        <v>4634</v>
+        <v>4617</v>
       </c>
     </row>
     <row r="502" spans="1:10">
       <c r="A502" s="33" t="s">
-        <v>4556</v>
+        <v>4539</v>
       </c>
       <c r="B502" s="36" t="s">
-        <v>4569</v>
+        <v>4552</v>
       </c>
       <c r="C502" s="3" t="s">
-        <v>4582</v>
+        <v>4565</v>
       </c>
       <c r="D502" s="3" t="s">
-        <v>4593</v>
+        <v>4576</v>
       </c>
       <c r="E502" s="3" t="s">
-        <v>4604</v>
+        <v>4587</v>
       </c>
       <c r="F502" s="3" t="s">
-        <v>4614</v>
+        <v>4597</v>
       </c>
       <c r="G502" s="5" t="s">
-        <v>4659</v>
+        <v>4642</v>
       </c>
       <c r="H502" s="3" t="s">
-        <v>4647</v>
+        <v>4630</v>
       </c>
       <c r="I502" s="14" t="s">
-        <v>4625</v>
+        <v>4608</v>
       </c>
       <c r="J502" s="14" t="s">
-        <v>4635</v>
+        <v>4618</v>
       </c>
     </row>
     <row r="503" spans="1:10">
       <c r="A503" s="33" t="s">
-        <v>4557</v>
+        <v>4540</v>
       </c>
       <c r="B503" s="36" t="s">
-        <v>4570</v>
+        <v>4553</v>
       </c>
       <c r="C503" s="3" t="s">
-        <v>4583</v>
+        <v>4566</v>
       </c>
       <c r="D503" s="3" t="s">
-        <v>4594</v>
+        <v>4577</v>
       </c>
       <c r="E503" s="3" t="s">
-        <v>4605</v>
+        <v>4588</v>
       </c>
       <c r="F503" s="3" t="s">
-        <v>4615</v>
+        <v>4598</v>
       </c>
       <c r="G503" s="5" t="s">
-        <v>4660</v>
+        <v>4643</v>
       </c>
       <c r="H503" s="3" t="s">
-        <v>4648</v>
+        <v>4631</v>
       </c>
       <c r="I503" s="14" t="s">
-        <v>4626</v>
+        <v>4609</v>
       </c>
       <c r="J503" s="14" t="s">
-        <v>4636</v>
+        <v>4619</v>
       </c>
     </row>
     <row r="504" spans="1:10">
       <c r="A504" s="33" t="s">
-        <v>4558</v>
+        <v>4541</v>
       </c>
       <c r="B504" s="36" t="s">
-        <v>4571</v>
+        <v>4554</v>
       </c>
       <c r="C504" s="3" t="s">
-        <v>4584</v>
+        <v>4567</v>
       </c>
       <c r="D504" s="3" t="s">
-        <v>4595</v>
+        <v>4578</v>
       </c>
       <c r="E504" s="3" t="s">
-        <v>4606</v>
+        <v>4589</v>
       </c>
       <c r="F504" s="3" t="s">
-        <v>4616</v>
+        <v>4599</v>
       </c>
       <c r="G504" s="5" t="s">
-        <v>4661</v>
+        <v>4644</v>
       </c>
       <c r="H504" s="3" t="s">
-        <v>4649</v>
+        <v>4632</v>
       </c>
       <c r="I504" s="14" t="s">
-        <v>4627</v>
+        <v>4610</v>
       </c>
       <c r="J504" s="14" t="s">
-        <v>4637</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="505" spans="1:10">
       <c r="A505" s="33" t="s">
-        <v>4559</v>
+        <v>4542</v>
       </c>
       <c r="B505" s="30" t="s">
-        <v>4572</v>
+        <v>4555</v>
       </c>
       <c r="C505" s="3" t="s">
-        <v>4585</v>
+        <v>4568</v>
       </c>
       <c r="D505" s="3" t="s">
-        <v>4596</v>
+        <v>4579</v>
       </c>
       <c r="E505" s="3" t="s">
-        <v>4607</v>
+        <v>4590</v>
       </c>
       <c r="F505" s="3" t="s">
-        <v>4617</v>
+        <v>4600</v>
       </c>
       <c r="G505" s="5" t="s">
-        <v>4662</v>
+        <v>4645</v>
       </c>
       <c r="H505" s="3" t="s">
-        <v>4650</v>
+        <v>4633</v>
       </c>
       <c r="I505" s="14" t="s">
-        <v>4628</v>
+        <v>4611</v>
       </c>
       <c r="J505" s="14" t="s">
-        <v>4638</v>
+        <v>4621</v>
       </c>
     </row>
     <row r="506" spans="1:10">
       <c r="A506" s="33" t="s">
-        <v>4560</v>
+        <v>4543</v>
       </c>
       <c r="B506" s="30" t="s">
-        <v>4573</v>
+        <v>4556</v>
       </c>
       <c r="C506" s="3" t="s">
-        <v>4664</v>
+        <v>4647</v>
       </c>
       <c r="D506" s="3" t="s">
-        <v>4665</v>
+        <v>4648</v>
       </c>
       <c r="E506" s="3" t="s">
-        <v>4666</v>
+        <v>4649</v>
       </c>
       <c r="F506" s="3" t="s">
-        <v>4667</v>
+        <v>4650</v>
       </c>
       <c r="G506" s="9" t="s">
-        <v>4670</v>
+        <v>4653</v>
       </c>
       <c r="H506" s="9" t="s">
-        <v>4671</v>
+        <v>4654</v>
       </c>
       <c r="I506" s="14" t="s">
-        <v>4668</v>
+        <v>4651</v>
       </c>
       <c r="J506" s="14" t="s">
-        <v>4669</v>
+        <v>4652</v>
       </c>
     </row>
     <row r="507" spans="1:10">
       <c r="A507" s="33" t="s">
-        <v>4561</v>
+        <v>4544</v>
       </c>
       <c r="B507" s="36" t="s">
-        <v>4574</v>
+        <v>4557</v>
       </c>
       <c r="C507" s="3" t="s">
-        <v>4586</v>
+        <v>4569</v>
       </c>
       <c r="D507" s="3" t="s">
-        <v>4597</v>
+        <v>4580</v>
       </c>
       <c r="E507" s="3" t="s">
-        <v>4608</v>
+        <v>4591</v>
       </c>
       <c r="F507" s="3" t="s">
-        <v>4618</v>
+        <v>4601</v>
       </c>
       <c r="G507" s="5" t="s">
+        <v>4646</v>
+      </c>
+      <c r="H507" s="3" t="s">
+        <v>4634</v>
+      </c>
+      <c r="I507" s="14" t="s">
+        <v>4612</v>
+      </c>
+      <c r="J507" s="14" t="s">
+        <v>4622</v>
+      </c>
+    </row>
+    <row r="508" spans="1:10" ht="37">
+      <c r="A508" s="33" t="s">
+        <v>4658</v>
+      </c>
+      <c r="B508" s="34" t="s">
+        <v>4662</v>
+      </c>
+      <c r="C508" s="10" t="s">
+        <v>4728</v>
+      </c>
+      <c r="D508" s="3" t="s">
+        <v>4729</v>
+      </c>
+      <c r="E508" s="3" t="s">
+        <v>4730</v>
+      </c>
+      <c r="F508" s="3" t="s">
+        <v>4731</v>
+      </c>
+      <c r="G508" s="5" t="s">
+        <v>4732</v>
+      </c>
+      <c r="H508" s="39" t="s">
+        <v>4733</v>
+      </c>
+      <c r="I508" s="35" t="s">
+        <v>4734</v>
+      </c>
+      <c r="J508" s="14" t="s">
+        <v>4735</v>
+      </c>
+    </row>
+    <row r="509" spans="1:10" ht="25">
+      <c r="A509" s="33" t="s">
+        <v>4659</v>
+      </c>
+      <c r="B509" s="34" t="s">
         <v>4663</v>
       </c>
-      <c r="H507" s="3" t="s">
-        <v>4651</v>
-      </c>
-      <c r="I507" s="14" t="s">
-        <v>4629</v>
-      </c>
-      <c r="J507" s="14" t="s">
-        <v>4639</v>
-      </c>
-    </row>
-    <row r="508" spans="1:10">
-      <c r="A508" s="33" t="s">
-        <v>4675</v>
-      </c>
-      <c r="B508" s="30" t="s">
-        <v>4679</v>
-      </c>
-      <c r="C508" s="3"/>
-      <c r="D508" s="3"/>
-      <c r="E508" s="3"/>
-      <c r="F508" s="3"/>
-      <c r="G508" s="5"/>
-      <c r="H508" s="3"/>
-      <c r="I508" s="14"/>
-      <c r="J508" s="14"/>
-    </row>
-    <row r="509" spans="1:10">
-      <c r="A509" s="33" t="s">
-        <v>4676</v>
-      </c>
-      <c r="B509" s="30" t="s">
-        <v>4680</v>
-      </c>
-      <c r="C509" s="3"/>
-      <c r="D509" s="3"/>
-      <c r="E509" s="3"/>
-      <c r="F509" s="3"/>
-      <c r="G509" s="5"/>
-      <c r="H509" s="3"/>
-      <c r="I509" s="14"/>
-      <c r="J509" s="14"/>
-    </row>
-    <row r="510" spans="1:10">
+      <c r="C509" s="10" t="s">
+        <v>4736</v>
+      </c>
+      <c r="D509" s="3" t="s">
+        <v>4737</v>
+      </c>
+      <c r="E509" s="3" t="s">
+        <v>4738</v>
+      </c>
+      <c r="F509" s="3" t="s">
+        <v>4739</v>
+      </c>
+      <c r="G509" s="40" t="s">
+        <v>4740</v>
+      </c>
+      <c r="H509" s="39" t="s">
+        <v>4741</v>
+      </c>
+      <c r="I509" s="35" t="s">
+        <v>4742</v>
+      </c>
+      <c r="J509" s="14" t="s">
+        <v>4743</v>
+      </c>
+    </row>
+    <row r="510" spans="1:10" ht="25">
       <c r="A510" s="33" t="s">
-        <v>4677</v>
-      </c>
-      <c r="B510" s="30" t="s">
-        <v>4681</v>
-      </c>
-      <c r="C510" s="3"/>
-      <c r="D510" s="3"/>
-      <c r="E510" s="3"/>
-      <c r="F510" s="3"/>
-      <c r="G510" s="5"/>
-      <c r="H510" s="3"/>
-      <c r="I510" s="14"/>
-      <c r="J510" s="14"/>
-    </row>
-    <row r="511" spans="1:10">
+        <v>4660</v>
+      </c>
+      <c r="B510" s="34" t="s">
+        <v>4664</v>
+      </c>
+      <c r="C510" s="10" t="s">
+        <v>4744</v>
+      </c>
+      <c r="D510" s="3" t="s">
+        <v>4745</v>
+      </c>
+      <c r="E510" s="3" t="s">
+        <v>4746</v>
+      </c>
+      <c r="F510" s="3" t="s">
+        <v>4747</v>
+      </c>
+      <c r="G510" s="40" t="s">
+        <v>4748</v>
+      </c>
+      <c r="H510" s="39" t="s">
+        <v>4749</v>
+      </c>
+      <c r="I510" s="35" t="s">
+        <v>4750</v>
+      </c>
+      <c r="J510" s="14" t="s">
+        <v>4751</v>
+      </c>
+    </row>
+    <row r="511" spans="1:10" ht="37">
       <c r="A511" s="33" t="s">
-        <v>4678</v>
-      </c>
-      <c r="B511" s="30" t="s">
-        <v>4686</v>
-      </c>
-      <c r="C511" s="3"/>
-      <c r="D511" s="3"/>
-      <c r="E511" s="3"/>
-      <c r="F511" s="3"/>
-      <c r="G511" s="5"/>
-      <c r="H511" s="3"/>
-      <c r="I511" s="14"/>
-      <c r="J511" s="14"/>
-    </row>
-    <row r="512" spans="1:10">
+        <v>4661</v>
+      </c>
+      <c r="B511" s="34" t="s">
+        <v>4669</v>
+      </c>
+      <c r="C511" s="10" t="s">
+        <v>4752</v>
+      </c>
+      <c r="D511" s="3" t="s">
+        <v>4753</v>
+      </c>
+      <c r="E511" s="3" t="s">
+        <v>4754</v>
+      </c>
+      <c r="F511" s="3" t="s">
+        <v>4755</v>
+      </c>
+      <c r="G511" s="40" t="s">
+        <v>4756</v>
+      </c>
+      <c r="H511" s="39" t="s">
+        <v>4757</v>
+      </c>
+      <c r="I511" s="35" t="s">
+        <v>4758</v>
+      </c>
+      <c r="J511" s="14" t="s">
+        <v>4759</v>
+      </c>
+    </row>
+    <row r="512" spans="1:10" ht="109">
       <c r="A512" s="33" t="s">
-        <v>4397</v>
-      </c>
-      <c r="B512" s="30" t="s">
-        <v>4682</v>
-      </c>
-      <c r="C512" s="3"/>
-      <c r="D512" s="3"/>
-      <c r="E512" s="3"/>
-      <c r="F512" s="3"/>
-      <c r="G512" s="5"/>
-      <c r="H512" s="3"/>
-      <c r="I512" s="14"/>
-      <c r="J512" s="14"/>
-    </row>
-    <row r="513" spans="1:10">
+        <v>4380</v>
+      </c>
+      <c r="B512" s="34" t="s">
+        <v>4665</v>
+      </c>
+      <c r="C512" s="10" t="s">
+        <v>4760</v>
+      </c>
+      <c r="D512" s="3" t="s">
+        <v>4761</v>
+      </c>
+      <c r="E512" s="10" t="s">
+        <v>4762</v>
+      </c>
+      <c r="F512" s="10" t="s">
+        <v>4763</v>
+      </c>
+      <c r="G512" s="7" t="s">
+        <v>4764</v>
+      </c>
+      <c r="H512" s="10" t="s">
+        <v>4765</v>
+      </c>
+      <c r="I512" s="35" t="s">
+        <v>4766</v>
+      </c>
+      <c r="J512" s="14" t="s">
+        <v>4767</v>
+      </c>
+    </row>
+    <row r="513" spans="1:10" ht="145">
       <c r="A513" s="33" t="s">
-        <v>4396</v>
-      </c>
-      <c r="B513" s="30" t="s">
+        <v>4379</v>
+      </c>
+      <c r="B513" s="34" t="s">
+        <v>4699</v>
+      </c>
+      <c r="C513" s="10" t="s">
+        <v>4768</v>
+      </c>
+      <c r="D513" s="3" t="s">
+        <v>4769</v>
+      </c>
+      <c r="E513" s="10" t="s">
+        <v>4770</v>
+      </c>
+      <c r="F513" s="10" t="s">
+        <v>4771</v>
+      </c>
+      <c r="G513" s="8" t="s">
+        <v>4772</v>
+      </c>
+      <c r="H513" s="10" t="s">
+        <v>4773</v>
+      </c>
+      <c r="I513" s="35" t="s">
+        <v>4774</v>
+      </c>
+      <c r="J513" s="35" t="s">
+        <v>4775</v>
+      </c>
+    </row>
+    <row r="514" spans="1:10" ht="25">
+      <c r="A514" s="37" t="s">
+        <v>4700</v>
+      </c>
+      <c r="B514" s="38" t="s">
+        <v>4701</v>
+      </c>
+      <c r="C514" s="10" t="s">
+        <v>4776</v>
+      </c>
+      <c r="D514" s="3" t="s">
+        <v>4777</v>
+      </c>
+      <c r="E514" s="10" t="s">
+        <v>4778</v>
+      </c>
+      <c r="F514" s="3" t="s">
+        <v>4779</v>
+      </c>
+      <c r="G514" s="5" t="s">
+        <v>4780</v>
+      </c>
+      <c r="H514" s="39" t="s">
+        <v>4781</v>
+      </c>
+      <c r="I514" s="14" t="s">
+        <v>4782</v>
+      </c>
+      <c r="J514" s="14" t="s">
+        <v>4783</v>
+      </c>
+    </row>
+    <row r="515" spans="1:10">
+      <c r="A515" t="s">
+        <v>4702</v>
+      </c>
+      <c r="B515" s="38" t="s">
+        <v>4727</v>
+      </c>
+      <c r="C515" s="3" t="s">
+        <v>4830</v>
+      </c>
+      <c r="D515" s="3" t="s">
+        <v>4847</v>
+      </c>
+      <c r="E515" s="3" t="s">
+        <v>4854</v>
+      </c>
+      <c r="F515" s="3" t="s">
+        <v>4870</v>
+      </c>
+      <c r="G515" s="40" t="s">
+        <v>4877</v>
+      </c>
+      <c r="H515" s="40" t="s">
+        <v>4890</v>
+      </c>
+      <c r="I515" s="14" t="s">
+        <v>4818</v>
+      </c>
+      <c r="J515" s="14" t="s">
+        <v>4806</v>
+      </c>
+    </row>
+    <row r="516" spans="1:10">
+      <c r="A516" t="s">
+        <v>4703</v>
+      </c>
+      <c r="B516" s="38" t="s">
+        <v>4726</v>
+      </c>
+      <c r="C516" s="3" t="s">
+        <v>4831</v>
+      </c>
+      <c r="D516" s="3" t="s">
+        <v>4848</v>
+      </c>
+      <c r="E516" s="3" t="s">
+        <v>4855</v>
+      </c>
+      <c r="F516" s="3" t="s">
+        <v>4871</v>
+      </c>
+      <c r="G516" s="40" t="s">
+        <v>4878</v>
+      </c>
+      <c r="H516" s="40" t="s">
+        <v>4891</v>
+      </c>
+      <c r="I516" s="14" t="s">
+        <v>4819</v>
+      </c>
+      <c r="J516" s="14" t="s">
+        <v>4807</v>
+      </c>
+    </row>
+    <row r="517" spans="1:10">
+      <c r="A517" t="s">
+        <v>4704</v>
+      </c>
+      <c r="B517" s="38" t="s">
+        <v>4725</v>
+      </c>
+      <c r="C517" s="3" t="s">
+        <v>4832</v>
+      </c>
+      <c r="D517" s="3" t="s">
+        <v>4849</v>
+      </c>
+      <c r="E517" s="3" t="s">
+        <v>4856</v>
+      </c>
+      <c r="F517" s="3" t="s">
+        <v>4872</v>
+      </c>
+      <c r="G517" s="40" t="s">
+        <v>4879</v>
+      </c>
+      <c r="H517" s="40" t="s">
+        <v>4892</v>
+      </c>
+      <c r="I517" s="14" t="s">
+        <v>4820</v>
+      </c>
+      <c r="J517" s="14" t="s">
+        <v>4808</v>
+      </c>
+    </row>
+    <row r="518" spans="1:10">
+      <c r="A518" t="s">
+        <v>4705</v>
+      </c>
+      <c r="B518" s="38" t="s">
+        <v>4724</v>
+      </c>
+      <c r="C518" s="3" t="s">
+        <v>4833</v>
+      </c>
+      <c r="D518" s="3" t="s">
+        <v>4850</v>
+      </c>
+      <c r="E518" s="3" t="s">
+        <v>4857</v>
+      </c>
+      <c r="F518" s="3" t="s">
+        <v>4873</v>
+      </c>
+      <c r="G518" s="40" t="s">
+        <v>4880</v>
+      </c>
+      <c r="H518" s="40" t="s">
+        <v>4893</v>
+      </c>
+      <c r="I518" s="14" t="s">
+        <v>4821</v>
+      </c>
+      <c r="J518" s="14" t="s">
+        <v>4809</v>
+      </c>
+    </row>
+    <row r="519" spans="1:10">
+      <c r="A519" t="s">
+        <v>4706</v>
+      </c>
+      <c r="B519" s="38" t="s">
+        <v>4723</v>
+      </c>
+      <c r="C519" s="3" t="s">
+        <v>4834</v>
+      </c>
+      <c r="D519" s="3" t="s">
+        <v>4851</v>
+      </c>
+      <c r="E519" s="3" t="s">
+        <v>4858</v>
+      </c>
+      <c r="F519" s="3" t="s">
+        <v>4874</v>
+      </c>
+      <c r="G519" s="40" t="s">
+        <v>4881</v>
+      </c>
+      <c r="H519" s="40" t="s">
+        <v>4894</v>
+      </c>
+      <c r="I519" s="14" t="s">
+        <v>4822</v>
+      </c>
+      <c r="J519" s="14" t="s">
+        <v>4810</v>
+      </c>
+    </row>
+    <row r="520" spans="1:10">
+      <c r="A520" t="s">
+        <v>4707</v>
+      </c>
+      <c r="B520" s="38" t="s">
+        <v>4722</v>
+      </c>
+      <c r="C520" s="3" t="s">
+        <v>4835</v>
+      </c>
+      <c r="D520" s="3" t="s">
+        <v>4852</v>
+      </c>
+      <c r="E520" s="3" t="s">
+        <v>4859</v>
+      </c>
+      <c r="F520" s="3" t="s">
+        <v>4875</v>
+      </c>
+      <c r="G520" s="40" t="s">
+        <v>4882</v>
+      </c>
+      <c r="H520" s="40" t="s">
+        <v>4895</v>
+      </c>
+      <c r="I520" s="14" t="s">
+        <v>4823</v>
+      </c>
+      <c r="J520" s="14" t="s">
+        <v>4811</v>
+      </c>
+    </row>
+    <row r="521" spans="1:10">
+      <c r="A521" t="s">
+        <v>4708</v>
+      </c>
+      <c r="B521" s="38" t="s">
+        <v>4721</v>
+      </c>
+      <c r="C521" s="3" t="s">
+        <v>4509</v>
+      </c>
+      <c r="D521" s="3" t="s">
+        <v>4853</v>
+      </c>
+      <c r="E521" s="3" t="s">
+        <v>4515</v>
+      </c>
+      <c r="F521" s="3" t="s">
+        <v>4876</v>
+      </c>
+      <c r="G521" s="40" t="s">
+        <v>4883</v>
+      </c>
+      <c r="H521" s="40" t="s">
+        <v>4896</v>
+      </c>
+      <c r="I521" s="14" t="s">
+        <v>4824</v>
+      </c>
+      <c r="J521" s="14" t="s">
+        <v>4524</v>
+      </c>
+    </row>
+    <row r="522" spans="1:10">
+      <c r="A522" t="s">
+        <v>4709</v>
+      </c>
+      <c r="B522" s="38" t="s">
+        <v>4720</v>
+      </c>
+      <c r="C522" s="3" t="s">
+        <v>4836</v>
+      </c>
+      <c r="D522" s="3" t="s">
+        <v>4850</v>
+      </c>
+      <c r="E522" s="3" t="s">
+        <v>4857</v>
+      </c>
+      <c r="F522" s="3" t="s">
+        <v>4873</v>
+      </c>
+      <c r="G522" s="40" t="s">
+        <v>4884</v>
+      </c>
+      <c r="H522" s="40" t="s">
+        <v>4897</v>
+      </c>
+      <c r="I522" s="14" t="s">
+        <v>4821</v>
+      </c>
+      <c r="J522" s="14" t="s">
+        <v>4812</v>
+      </c>
+    </row>
+    <row r="523" spans="1:10">
+      <c r="A523" t="s">
+        <v>4710</v>
+      </c>
+      <c r="B523" s="38" t="s">
+        <v>4719</v>
+      </c>
+      <c r="C523" s="3" t="s">
+        <v>4837</v>
+      </c>
+      <c r="D523" s="3" t="s">
+        <v>4842</v>
+      </c>
+      <c r="E523" s="3" t="s">
+        <v>4860</v>
+      </c>
+      <c r="F523" s="3" t="s">
+        <v>4865</v>
+      </c>
+      <c r="G523" s="40" t="s">
+        <v>4885</v>
+      </c>
+      <c r="H523" s="40" t="s">
+        <v>4898</v>
+      </c>
+      <c r="I523" s="14" t="s">
+        <v>4825</v>
+      </c>
+      <c r="J523" s="14" t="s">
+        <v>4813</v>
+      </c>
+    </row>
+    <row r="524" spans="1:10">
+      <c r="A524" t="s">
+        <v>4711</v>
+      </c>
+      <c r="B524" s="38" t="s">
+        <v>4718</v>
+      </c>
+      <c r="C524" s="3" t="s">
+        <v>4838</v>
+      </c>
+      <c r="D524" s="3" t="s">
+        <v>4843</v>
+      </c>
+      <c r="E524" s="3" t="s">
+        <v>4861</v>
+      </c>
+      <c r="F524" s="3" t="s">
+        <v>4866</v>
+      </c>
+      <c r="G524" s="40" t="s">
+        <v>4886</v>
+      </c>
+      <c r="H524" s="40" t="s">
+        <v>4899</v>
+      </c>
+      <c r="I524" s="14" t="s">
+        <v>4826</v>
+      </c>
+      <c r="J524" s="14" t="s">
+        <v>4814</v>
+      </c>
+    </row>
+    <row r="525" spans="1:10">
+      <c r="A525" t="s">
+        <v>4712</v>
+      </c>
+      <c r="B525" s="38" t="s">
+        <v>4717</v>
+      </c>
+      <c r="C525" s="3" t="s">
+        <v>4839</v>
+      </c>
+      <c r="D525" s="3" t="s">
+        <v>4844</v>
+      </c>
+      <c r="E525" s="3" t="s">
+        <v>4862</v>
+      </c>
+      <c r="F525" s="3" t="s">
+        <v>4867</v>
+      </c>
+      <c r="G525" s="40" t="s">
+        <v>4887</v>
+      </c>
+      <c r="H525" s="40" t="s">
+        <v>4900</v>
+      </c>
+      <c r="I525" s="14" t="s">
+        <v>4827</v>
+      </c>
+      <c r="J525" s="14" t="s">
+        <v>4815</v>
+      </c>
+    </row>
+    <row r="526" spans="1:10">
+      <c r="A526" s="33" t="s">
+        <v>4713</v>
+      </c>
+      <c r="B526" s="38" t="s">
         <v>4716</v>
       </c>
-      <c r="C513" s="3"/>
-      <c r="D513" s="3"/>
-      <c r="E513" s="3"/>
-      <c r="F513" s="3"/>
-      <c r="G513" s="5"/>
-      <c r="H513" s="3"/>
-      <c r="I513" s="14"/>
-      <c r="J513" s="14"/>
-    </row>
-    <row r="514" spans="1:10">
-      <c r="A514" s="37" t="s">
-        <v>4717</v>
-      </c>
-      <c r="B514" t="s">
-        <v>4718</v>
-      </c>
+      <c r="C526" s="3" t="s">
+        <v>4840</v>
+      </c>
+      <c r="D526" s="3" t="s">
+        <v>4845</v>
+      </c>
+      <c r="E526" s="3" t="s">
+        <v>4863</v>
+      </c>
+      <c r="F526" s="3" t="s">
+        <v>4868</v>
+      </c>
+      <c r="G526" s="40" t="s">
+        <v>4888</v>
+      </c>
+      <c r="H526" s="40" t="s">
+        <v>4901</v>
+      </c>
+      <c r="I526" s="14" t="s">
+        <v>4828</v>
+      </c>
+      <c r="J526" s="14" t="s">
+        <v>4816</v>
+      </c>
+    </row>
+    <row r="527" spans="1:10">
+      <c r="A527" s="33" t="s">
+        <v>4714</v>
+      </c>
+      <c r="B527" s="38" t="s">
+        <v>4715</v>
+      </c>
+      <c r="C527" s="3" t="s">
+        <v>4841</v>
+      </c>
+      <c r="D527" s="3" t="s">
+        <v>4846</v>
+      </c>
+      <c r="E527" s="3" t="s">
+        <v>4864</v>
+      </c>
+      <c r="F527" s="3" t="s">
+        <v>4869</v>
+      </c>
+      <c r="G527" s="40" t="s">
+        <v>4889</v>
+      </c>
+      <c r="H527" s="40" t="s">
+        <v>4902</v>
+      </c>
+      <c r="I527" s="14" t="s">
+        <v>4829</v>
+      </c>
+      <c r="J527" s="14" t="s">
+        <v>4817</v>
+      </c>
+    </row>
+    <row r="528" spans="1:10">
+      <c r="A528" s="33" t="s">
+        <v>4903</v>
+      </c>
+      <c r="B528" s="38" t="s">
+        <v>4904</v>
+      </c>
+      <c r="C528" s="3"/>
+      <c r="D528" s="3"/>
+      <c r="E528" s="3"/>
+      <c r="F528" s="3"/>
+      <c r="G528" s="5"/>
+      <c r="H528" s="3"/>
+      <c r="I528" s="14"/>
+      <c r="J528" s="14"/>
+    </row>
+    <row r="529" spans="1:10">
+      <c r="A529" s="33" t="s">
+        <v>4905</v>
+      </c>
+      <c r="B529" s="38" t="s">
+        <v>4922</v>
+      </c>
+      <c r="C529" s="3"/>
+      <c r="D529" s="3"/>
+      <c r="E529" s="3"/>
+      <c r="F529" s="3"/>
+      <c r="G529" s="5"/>
+      <c r="H529" s="3"/>
+      <c r="I529" s="14"/>
+      <c r="J529" s="14"/>
+    </row>
+    <row r="530" spans="1:10">
+      <c r="A530" s="33" t="s">
+        <v>4906</v>
+      </c>
+      <c r="B530" s="38" t="s">
+        <v>4923</v>
+      </c>
+      <c r="C530" s="3"/>
+      <c r="D530" s="3"/>
+      <c r="E530" s="3"/>
+      <c r="F530" s="3"/>
+      <c r="G530" s="5"/>
+      <c r="H530" s="3"/>
+      <c r="I530" s="14"/>
+      <c r="J530" s="14"/>
+    </row>
+    <row r="531" spans="1:10">
+      <c r="A531" s="33" t="s">
+        <v>4907</v>
+      </c>
+      <c r="B531" s="38" t="s">
+        <v>4924</v>
+      </c>
+      <c r="C531" s="3"/>
+      <c r="D531" s="3"/>
+      <c r="E531" s="3"/>
+      <c r="F531" s="3"/>
+      <c r="G531" s="5"/>
+      <c r="H531" s="3"/>
+      <c r="I531" s="14"/>
+      <c r="J531" s="14"/>
+    </row>
+    <row r="532" spans="1:10">
+      <c r="A532" s="33" t="s">
+        <v>4908</v>
+      </c>
+      <c r="B532" s="38" t="s">
+        <v>4925</v>
+      </c>
+      <c r="C532" s="3"/>
+      <c r="D532" s="3"/>
+      <c r="E532" s="3"/>
+      <c r="F532" s="3"/>
+      <c r="G532" s="5"/>
+      <c r="H532" s="3"/>
+      <c r="I532" s="14"/>
+      <c r="J532" s="14"/>
+    </row>
+    <row r="533" spans="1:10">
+      <c r="A533" s="33" t="s">
+        <v>4909</v>
+      </c>
+      <c r="B533" s="38" t="s">
+        <v>4926</v>
+      </c>
+      <c r="C533" s="3"/>
+      <c r="D533" s="3"/>
+      <c r="E533" s="3"/>
+      <c r="F533" s="3"/>
+      <c r="G533" s="5"/>
+      <c r="H533" s="3"/>
+      <c r="I533" s="14"/>
+      <c r="J533" s="14"/>
+    </row>
+    <row r="534" spans="1:10">
+      <c r="A534" s="33" t="s">
+        <v>4910</v>
+      </c>
+      <c r="B534" s="38" t="s">
+        <v>4927</v>
+      </c>
+      <c r="C534" s="3"/>
+      <c r="D534" s="3"/>
+      <c r="E534" s="3"/>
+      <c r="F534" s="3"/>
+      <c r="G534" s="5"/>
+      <c r="H534" s="3"/>
+      <c r="I534" s="14"/>
+      <c r="J534" s="14"/>
+    </row>
+    <row r="535" spans="1:10">
+      <c r="A535" s="33" t="s">
+        <v>4911</v>
+      </c>
+      <c r="B535" s="38" t="s">
+        <v>4928</v>
+      </c>
+      <c r="C535" s="3"/>
+      <c r="D535" s="3"/>
+      <c r="E535" s="3"/>
+      <c r="F535" s="3"/>
+      <c r="G535" s="5"/>
+      <c r="H535" s="3"/>
+      <c r="I535" s="14"/>
+      <c r="J535" s="14"/>
+    </row>
+    <row r="536" spans="1:10">
+      <c r="A536" s="33" t="s">
+        <v>4912</v>
+      </c>
+      <c r="B536" s="38" t="s">
+        <v>4929</v>
+      </c>
+      <c r="C536" s="3"/>
+      <c r="D536" s="3"/>
+      <c r="E536" s="3"/>
+      <c r="F536" s="3"/>
+      <c r="G536" s="5"/>
+      <c r="H536" s="3"/>
+      <c r="I536" s="14"/>
+      <c r="J536" s="14"/>
+    </row>
+    <row r="537" spans="1:10">
+      <c r="A537" s="33" t="s">
+        <v>4913</v>
+      </c>
+      <c r="B537" s="38" t="s">
+        <v>4930</v>
+      </c>
+      <c r="C537" s="3"/>
+      <c r="D537" s="3"/>
+      <c r="E537" s="3"/>
+      <c r="F537" s="3"/>
+      <c r="G537" s="5"/>
+      <c r="H537" s="3"/>
+      <c r="I537" s="14"/>
+      <c r="J537" s="14"/>
+    </row>
+    <row r="538" spans="1:10">
+      <c r="A538" s="33" t="s">
+        <v>4914</v>
+      </c>
+      <c r="B538" s="38" t="s">
+        <v>4931</v>
+      </c>
+      <c r="C538" s="3"/>
+      <c r="D538" s="3"/>
+      <c r="E538" s="3"/>
+      <c r="F538" s="3"/>
+      <c r="G538" s="5"/>
+      <c r="H538" s="3"/>
+      <c r="I538" s="14"/>
+      <c r="J538" s="14"/>
+    </row>
+    <row r="539" spans="1:10">
+      <c r="A539" s="33" t="s">
+        <v>4915</v>
+      </c>
+      <c r="B539" s="38" t="s">
+        <v>4932</v>
+      </c>
+      <c r="C539" s="3"/>
+      <c r="D539" s="3"/>
+      <c r="E539" s="3"/>
+      <c r="F539" s="3"/>
+      <c r="G539" s="5"/>
+      <c r="H539" s="3"/>
+      <c r="I539" s="14"/>
+      <c r="J539" s="14"/>
+    </row>
+    <row r="540" spans="1:10">
+      <c r="A540" s="33" t="s">
+        <v>4916</v>
+      </c>
+      <c r="B540" s="38" t="s">
+        <v>4933</v>
+      </c>
+      <c r="C540" s="3"/>
+      <c r="D540" s="3"/>
+      <c r="E540" s="3"/>
+      <c r="F540" s="3"/>
+      <c r="G540" s="5"/>
+      <c r="H540" s="3"/>
+      <c r="I540" s="14"/>
+      <c r="J540" s="14"/>
+    </row>
+    <row r="541" spans="1:10">
+      <c r="A541" s="33" t="s">
+        <v>4917</v>
+      </c>
+      <c r="B541" s="38" t="s">
+        <v>4934</v>
+      </c>
+      <c r="C541" s="3"/>
+      <c r="D541" s="3"/>
+      <c r="E541" s="3"/>
+      <c r="F541" s="3"/>
+      <c r="G541" s="5"/>
+      <c r="H541" s="3"/>
+      <c r="I541" s="14"/>
+      <c r="J541" s="14"/>
+    </row>
+    <row r="542" spans="1:10">
+      <c r="A542" s="33" t="s">
+        <v>4918</v>
+      </c>
+      <c r="B542" s="38" t="s">
+        <v>4935</v>
+      </c>
+      <c r="C542" s="3"/>
+      <c r="D542" s="3"/>
+      <c r="E542" s="3"/>
+      <c r="F542" s="3"/>
+      <c r="G542" s="5"/>
+      <c r="H542" s="3"/>
+      <c r="I542" s="14"/>
+      <c r="J542" s="14"/>
+    </row>
+    <row r="543" spans="1:10">
+      <c r="A543" s="33" t="s">
+        <v>4919</v>
+      </c>
+      <c r="B543" s="38" t="s">
+        <v>4936</v>
+      </c>
+      <c r="C543" s="3"/>
+      <c r="D543" s="3"/>
+      <c r="E543" s="3"/>
+      <c r="F543" s="3"/>
+      <c r="G543" s="5"/>
+      <c r="H543" s="3"/>
+      <c r="I543" s="14"/>
+      <c r="J543" s="14"/>
+    </row>
+    <row r="544" spans="1:10">
+      <c r="A544" s="33" t="s">
+        <v>4920</v>
+      </c>
+      <c r="B544" s="38" t="s">
+        <v>4937</v>
+      </c>
+      <c r="C544" s="3"/>
+      <c r="D544" s="3"/>
+      <c r="E544" s="3"/>
+      <c r="F544" s="3"/>
+      <c r="G544" s="5"/>
+      <c r="H544" s="3"/>
+      <c r="I544" s="14"/>
+      <c r="J544" s="14"/>
+    </row>
+    <row r="545" spans="1:10">
+      <c r="A545" s="33" t="s">
+        <v>4921</v>
+      </c>
+      <c r="B545" s="38" t="s">
+        <v>4938</v>
+      </c>
+      <c r="C545" s="3"/>
+      <c r="D545" s="3"/>
+      <c r="E545" s="3"/>
+      <c r="F545" s="3"/>
+      <c r="G545" s="5"/>
+      <c r="H545" s="3"/>
+      <c r="I545" s="14"/>
+      <c r="J545" s="14"/>
+    </row>
+    <row r="546" spans="1:10">
+      <c r="A546" s="41" t="s">
+        <v>4939</v>
+      </c>
+      <c r="B546" s="42" t="s">
+        <v>4940</v>
+      </c>
+      <c r="C546" s="43"/>
+      <c r="D546" s="43"/>
+      <c r="E546" s="43"/>
+      <c r="F546" s="43"/>
+      <c r="G546" s="5"/>
+      <c r="H546" s="43"/>
+      <c r="I546" s="44"/>
+      <c r="J546" s="44"/>
+    </row>
+    <row r="547" spans="1:10">
+      <c r="A547" s="41" t="s">
+        <v>4939</v>
+      </c>
+      <c r="B547" s="42" t="s">
+        <v>4941</v>
+      </c>
+      <c r="C547" s="43"/>
+      <c r="D547" s="43"/>
+      <c r="E547" s="43"/>
+      <c r="F547" s="43"/>
+      <c r="G547" s="5"/>
+      <c r="H547" s="43"/>
+      <c r="I547" s="44"/>
+      <c r="J547" s="44"/>
+    </row>
+    <row r="548" spans="1:10">
+      <c r="A548" s="41" t="s">
+        <v>4939</v>
+      </c>
+      <c r="B548" s="42" t="s">
+        <v>4942</v>
+      </c>
+      <c r="C548" s="43"/>
+      <c r="D548" s="43"/>
+      <c r="E548" s="43"/>
+      <c r="F548" s="43"/>
+      <c r="G548" s="5"/>
+      <c r="H548" s="43"/>
+      <c r="I548" s="44"/>
+      <c r="J548" s="44"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -31592,6 +33171,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="6e0cf07b-8188-4b76-8f54-3cda03d37414" xsi:nil="true"/>
@@ -31600,15 +33188,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31631,26 +33210,26 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E20926E-9EFB-4B7E-90D4-905B08F8E59C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E20926E-9EFB-4B7E-90D4-905B08F8E59C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/translations/translations.xlsx
+++ b/translations/translations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/russell/Projects/GPS-Sample/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA50984F-0FEC-C647-98EA-C7F2787C525F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A635388-648A-9747-9F79-1D938214358B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25140" yWindow="2220" windowWidth="29040" windowHeight="20340" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5304" uniqueCount="4943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5306" uniqueCount="4945">
   <si>
     <t>app_name</t>
   </si>
@@ -14924,12 +14924,18 @@
   <si>
     <t>Ona</t>
   </si>
+  <si>
+    <t>delete_location_message</t>
+  </si>
+  <si>
+    <t>Would you also like to permanently delete this location?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -15052,6 +15058,20 @@
       <color rgb="FF444746"/>
       <name val="Google Sans"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF080808"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF067D17"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -15133,7 +15153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -15197,12 +15217,14 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15392,8 +15414,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}" name="Table1" displayName="Table1" ref="A1:J548" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J548" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}" name="Table1" displayName="Table1" ref="A1:J549" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J549" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{DE67F62A-9DCA-4DFE-8C98-83B024E5D946}" name="app_name" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{BCDA3AB5-7BB5-4A21-ABBB-4186B52D559D}" name="GPSSample::en" dataDxfId="8"/>
@@ -15719,7 +15741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD3E6CC-854C-5841-9577-D3ADD2982DB6}">
-  <dimension ref="A1:J548"/>
+  <dimension ref="A1:J549"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="33.5" customWidth="1"/>
@@ -32519,7 +32541,7 @@
       </c>
     </row>
     <row r="526" spans="1:10">
-      <c r="A526" s="33" t="s">
+      <c r="A526" s="45" t="s">
         <v>4713</v>
       </c>
       <c r="B526" s="38" t="s">
@@ -32551,7 +32573,7 @@
       </c>
     </row>
     <row r="527" spans="1:10">
-      <c r="A527" s="33" t="s">
+      <c r="A527" s="45" t="s">
         <v>4714</v>
       </c>
       <c r="B527" s="38" t="s">
@@ -32583,7 +32605,7 @@
       </c>
     </row>
     <row r="528" spans="1:10">
-      <c r="A528" s="33" t="s">
+      <c r="A528" s="45" t="s">
         <v>4903</v>
       </c>
       <c r="B528" s="38" t="s">
@@ -32599,7 +32621,7 @@
       <c r="J528" s="14"/>
     </row>
     <row r="529" spans="1:10">
-      <c r="A529" s="33" t="s">
+      <c r="A529" s="45" t="s">
         <v>4905</v>
       </c>
       <c r="B529" s="38" t="s">
@@ -32615,7 +32637,7 @@
       <c r="J529" s="14"/>
     </row>
     <row r="530" spans="1:10">
-      <c r="A530" s="33" t="s">
+      <c r="A530" s="45" t="s">
         <v>4906</v>
       </c>
       <c r="B530" s="38" t="s">
@@ -32631,7 +32653,7 @@
       <c r="J530" s="14"/>
     </row>
     <row r="531" spans="1:10">
-      <c r="A531" s="33" t="s">
+      <c r="A531" s="45" t="s">
         <v>4907</v>
       </c>
       <c r="B531" s="38" t="s">
@@ -32647,7 +32669,7 @@
       <c r="J531" s="14"/>
     </row>
     <row r="532" spans="1:10">
-      <c r="A532" s="33" t="s">
+      <c r="A532" s="45" t="s">
         <v>4908</v>
       </c>
       <c r="B532" s="38" t="s">
@@ -32663,7 +32685,7 @@
       <c r="J532" s="14"/>
     </row>
     <row r="533" spans="1:10">
-      <c r="A533" s="33" t="s">
+      <c r="A533" s="45" t="s">
         <v>4909</v>
       </c>
       <c r="B533" s="38" t="s">
@@ -32679,7 +32701,7 @@
       <c r="J533" s="14"/>
     </row>
     <row r="534" spans="1:10">
-      <c r="A534" s="33" t="s">
+      <c r="A534" s="45" t="s">
         <v>4910</v>
       </c>
       <c r="B534" s="38" t="s">
@@ -32695,7 +32717,7 @@
       <c r="J534" s="14"/>
     </row>
     <row r="535" spans="1:10">
-      <c r="A535" s="33" t="s">
+      <c r="A535" s="45" t="s">
         <v>4911</v>
       </c>
       <c r="B535" s="38" t="s">
@@ -32711,7 +32733,7 @@
       <c r="J535" s="14"/>
     </row>
     <row r="536" spans="1:10">
-      <c r="A536" s="33" t="s">
+      <c r="A536" s="45" t="s">
         <v>4912</v>
       </c>
       <c r="B536" s="38" t="s">
@@ -32727,7 +32749,7 @@
       <c r="J536" s="14"/>
     </row>
     <row r="537" spans="1:10">
-      <c r="A537" s="33" t="s">
+      <c r="A537" s="45" t="s">
         <v>4913</v>
       </c>
       <c r="B537" s="38" t="s">
@@ -32743,7 +32765,7 @@
       <c r="J537" s="14"/>
     </row>
     <row r="538" spans="1:10">
-      <c r="A538" s="33" t="s">
+      <c r="A538" s="45" t="s">
         <v>4914</v>
       </c>
       <c r="B538" s="38" t="s">
@@ -32759,7 +32781,7 @@
       <c r="J538" s="14"/>
     </row>
     <row r="539" spans="1:10">
-      <c r="A539" s="33" t="s">
+      <c r="A539" s="45" t="s">
         <v>4915</v>
       </c>
       <c r="B539" s="38" t="s">
@@ -32775,7 +32797,7 @@
       <c r="J539" s="14"/>
     </row>
     <row r="540" spans="1:10">
-      <c r="A540" s="33" t="s">
+      <c r="A540" s="45" t="s">
         <v>4916</v>
       </c>
       <c r="B540" s="38" t="s">
@@ -32791,7 +32813,7 @@
       <c r="J540" s="14"/>
     </row>
     <row r="541" spans="1:10">
-      <c r="A541" s="33" t="s">
+      <c r="A541" s="45" t="s">
         <v>4917</v>
       </c>
       <c r="B541" s="38" t="s">
@@ -32807,7 +32829,7 @@
       <c r="J541" s="14"/>
     </row>
     <row r="542" spans="1:10">
-      <c r="A542" s="33" t="s">
+      <c r="A542" s="45" t="s">
         <v>4918</v>
       </c>
       <c r="B542" s="38" t="s">
@@ -32823,7 +32845,7 @@
       <c r="J542" s="14"/>
     </row>
     <row r="543" spans="1:10">
-      <c r="A543" s="33" t="s">
+      <c r="A543" s="45" t="s">
         <v>4919</v>
       </c>
       <c r="B543" s="38" t="s">
@@ -32839,7 +32861,7 @@
       <c r="J543" s="14"/>
     </row>
     <row r="544" spans="1:10">
-      <c r="A544" s="33" t="s">
+      <c r="A544" s="45" t="s">
         <v>4920</v>
       </c>
       <c r="B544" s="38" t="s">
@@ -32855,7 +32877,7 @@
       <c r="J544" s="14"/>
     </row>
     <row r="545" spans="1:10">
-      <c r="A545" s="33" t="s">
+      <c r="A545" s="45" t="s">
         <v>4921</v>
       </c>
       <c r="B545" s="38" t="s">
@@ -32871,52 +32893,68 @@
       <c r="J545" s="14"/>
     </row>
     <row r="546" spans="1:10">
-      <c r="A546" s="41" t="s">
+      <c r="A546" s="45" t="s">
         <v>4939</v>
       </c>
-      <c r="B546" s="42" t="s">
+      <c r="B546" s="43" t="s">
         <v>4940</v>
       </c>
-      <c r="C546" s="43"/>
-      <c r="D546" s="43"/>
-      <c r="E546" s="43"/>
-      <c r="F546" s="43"/>
+      <c r="C546" s="3"/>
+      <c r="D546" s="3"/>
+      <c r="E546" s="3"/>
+      <c r="F546" s="3"/>
       <c r="G546" s="5"/>
-      <c r="H546" s="43"/>
-      <c r="I546" s="44"/>
-      <c r="J546" s="44"/>
+      <c r="H546" s="3"/>
+      <c r="I546" s="14"/>
+      <c r="J546" s="14"/>
     </row>
     <row r="547" spans="1:10">
-      <c r="A547" s="41" t="s">
+      <c r="A547" s="45" t="s">
         <v>4939</v>
       </c>
-      <c r="B547" s="42" t="s">
+      <c r="B547" s="43" t="s">
         <v>4941</v>
       </c>
-      <c r="C547" s="43"/>
-      <c r="D547" s="43"/>
-      <c r="E547" s="43"/>
-      <c r="F547" s="43"/>
+      <c r="C547" s="3"/>
+      <c r="D547" s="3"/>
+      <c r="E547" s="3"/>
+      <c r="F547" s="3"/>
       <c r="G547" s="5"/>
-      <c r="H547" s="43"/>
-      <c r="I547" s="44"/>
-      <c r="J547" s="44"/>
+      <c r="H547" s="3"/>
+      <c r="I547" s="14"/>
+      <c r="J547" s="14"/>
     </row>
     <row r="548" spans="1:10">
-      <c r="A548" s="41" t="s">
+      <c r="A548" s="45" t="s">
         <v>4939</v>
       </c>
-      <c r="B548" s="42" t="s">
+      <c r="B548" s="43" t="s">
         <v>4942</v>
       </c>
-      <c r="C548" s="43"/>
-      <c r="D548" s="43"/>
-      <c r="E548" s="43"/>
-      <c r="F548" s="43"/>
+      <c r="C548" s="3"/>
+      <c r="D548" s="3"/>
+      <c r="E548" s="3"/>
+      <c r="F548" s="3"/>
       <c r="G548" s="5"/>
-      <c r="H548" s="43"/>
-      <c r="I548" s="44"/>
-      <c r="J548" s="44"/>
+      <c r="H548" s="3"/>
+      <c r="I548" s="14"/>
+      <c r="J548" s="14"/>
+    </row>
+    <row r="549" spans="1:10">
+      <c r="A549" s="46" t="s">
+        <v>4943</v>
+      </c>
+      <c r="B549" s="44" t="s">
+        <v>4944</v>
+      </c>
+      <c r="C549" s="41"/>
+      <c r="D549" s="41"/>
+      <c r="E549" s="41"/>
+      <c r="F549" s="41"/>
+      <c r="G549" s="5"/>
+      <c r="H549" s="41"/>
+      <c r="I549" s="42"/>
+      <c r="J549" s="42"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -32930,6 +32968,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e0cf07b-8188-4b76-8f54-3cda03d37414" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="43e153a8-5ef1-4f65-aac7-dc4685f18eaa">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F12BE0DB4A3DF641BF113FBF1C7EA261" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c6b4b409d6b6c81c2874e5a51d11715e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="43e153a8-5ef1-4f65-aac7-dc4685f18eaa" xmlns:ns3="6e0cf07b-8188-4b76-8f54-3cda03d37414" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0521fade2ab7bf037697e8e8677cb864" ns2:_="" ns3:_="">
     <xsd:import namespace="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
@@ -33170,27 +33228,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E20926E-9EFB-4B7E-90D4-905B08F8E59C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e0cf07b-8188-4b76-8f54-3cda03d37414" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="43e153a8-5ef1-4f65-aac7-dc4685f18eaa">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6201EF1-2938-4925-833A-11BB4654F7B4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -33207,29 +33270,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E20926E-9EFB-4B7E-90D4-905B08F8E59C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/translations/translations.xlsx
+++ b/translations/translations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/russell/Projects/GPS-Sample/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1114FC5-7AEF-4844-9F4C-A5580B57DC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A62F6D-B106-AC40-9AA4-C84BCFCDBDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17740" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
+    <workbookView xWindow="7960" yWindow="800" windowWidth="30240" windowHeight="22740" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5430" uniqueCount="5068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5474" uniqueCount="5112">
   <si>
     <t>app_name</t>
   </si>
@@ -15271,13 +15271,145 @@
   </si>
   <si>
     <t>واټن</t>
+  </si>
+  <si>
+    <t>enforce_geofence_boundary</t>
+  </si>
+  <si>
+    <t>enter_the_geofence_buffer_value</t>
+  </si>
+  <si>
+    <t>geofence_hint</t>
+  </si>
+  <si>
+    <t>geofence_error</t>
+  </si>
+  <si>
+    <t>begin_sample_review</t>
+  </si>
+  <si>
+    <t>review_sample</t>
+  </si>
+  <si>
+    <t>review_possible_duplicates</t>
+  </si>
+  <si>
+    <t>review_boundary_violations</t>
+  </si>
+  <si>
+    <t>save_sample</t>
+  </si>
+  <si>
+    <t>duplicate</t>
+  </si>
+  <si>
+    <t>outside_boundary</t>
+  </si>
+  <si>
+    <t>reason_is_required</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>keep_or_exclude_this_location</t>
+  </si>
+  <si>
+    <t>keep_this_location</t>
+  </si>
+  <si>
+    <t>exclude_this_location</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>delete_location_message</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>edit</t>
+  </si>
+  <si>
+    <t>clone</t>
+  </si>
+  <si>
+    <t>configuration</t>
+  </si>
+  <si>
+    <t>Enforce Geofence Boundary</t>
+  </si>
+  <si>
+    <t>Enter the geofence buffer value</t>
+  </si>
+  <si>
+    <t>Placeholder for GeoFence Hint</t>
+  </si>
+  <si>
+    <t>You are currently outside of the Geofence</t>
+  </si>
+  <si>
+    <t>Begin Sample Review</t>
+  </si>
+  <si>
+    <t>Review Sample</t>
+  </si>
+  <si>
+    <t>Review Possible Duplicates</t>
+  </si>
+  <si>
+    <t>Review Boundary Violations</t>
+  </si>
+  <si>
+    <t>Save Sample</t>
+  </si>
+  <si>
+    <t>Duplicate</t>
+  </si>
+  <si>
+    <t>Outside Boundary</t>
+  </si>
+  <si>
+    <t>You must select a Reason for the exclusion.</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Keep or Exclude this location?</t>
+  </si>
+  <si>
+    <t>Keep this location</t>
+  </si>
+  <si>
+    <t>Exclude this location</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>Would you also like to permanently delete this location?</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Edit</t>
+  </si>
+  <si>
+    <t>Clone</t>
+  </si>
+  <si>
+    <t>Configuration</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -15360,6 +15492,13 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -15405,7 +15544,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -15437,11 +15576,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -15525,6 +15673,20 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15746,8 +15908,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}" name="Table1" displayName="Table1" ref="A1:J543" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J543" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}" name="Table1" displayName="Table1" ref="A1:J565" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J565" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{DE67F62A-9DCA-4DFE-8C98-83B024E5D946}" name="app_name" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{BCDA3AB5-7BB5-4A21-ABBB-4186B52D559D}" name="GPSSample::en" dataDxfId="8"/>
@@ -16073,7 +16235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD3E6CC-854C-5841-9577-D3ADD2982DB6}">
-  <dimension ref="A1:J543"/>
+  <dimension ref="A1:J565"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="33.5" customWidth="1"/>
@@ -33461,6 +33623,358 @@
       <c r="J543" s="12" t="s">
         <v>5067</v>
       </c>
+    </row>
+    <row r="544" spans="1:10">
+      <c r="A544" s="33" t="s">
+        <v>5068</v>
+      </c>
+      <c r="B544" s="34" t="s">
+        <v>5090</v>
+      </c>
+      <c r="C544" s="35"/>
+      <c r="D544" s="35"/>
+      <c r="E544" s="35"/>
+      <c r="F544" s="35"/>
+      <c r="G544" s="36"/>
+      <c r="H544" s="35"/>
+      <c r="I544" s="37"/>
+      <c r="J544" s="37"/>
+    </row>
+    <row r="545" spans="1:10">
+      <c r="A545" s="33" t="s">
+        <v>5069</v>
+      </c>
+      <c r="B545" s="34" t="s">
+        <v>5091</v>
+      </c>
+      <c r="C545" s="35"/>
+      <c r="D545" s="35"/>
+      <c r="E545" s="35"/>
+      <c r="F545" s="35"/>
+      <c r="G545" s="36"/>
+      <c r="H545" s="35"/>
+      <c r="I545" s="37"/>
+      <c r="J545" s="37"/>
+    </row>
+    <row r="546" spans="1:10">
+      <c r="A546" s="33" t="s">
+        <v>5070</v>
+      </c>
+      <c r="B546" s="34" t="s">
+        <v>5092</v>
+      </c>
+      <c r="C546" s="35"/>
+      <c r="D546" s="35"/>
+      <c r="E546" s="35"/>
+      <c r="F546" s="35"/>
+      <c r="G546" s="36"/>
+      <c r="H546" s="35"/>
+      <c r="I546" s="37"/>
+      <c r="J546" s="37"/>
+    </row>
+    <row r="547" spans="1:10">
+      <c r="A547" s="33" t="s">
+        <v>5071</v>
+      </c>
+      <c r="B547" s="38" t="s">
+        <v>5093</v>
+      </c>
+      <c r="C547" s="35"/>
+      <c r="D547" s="35"/>
+      <c r="E547" s="35"/>
+      <c r="F547" s="35"/>
+      <c r="G547" s="36"/>
+      <c r="H547" s="35"/>
+      <c r="I547" s="37"/>
+      <c r="J547" s="37"/>
+    </row>
+    <row r="548" spans="1:10">
+      <c r="A548" s="33" t="s">
+        <v>5072</v>
+      </c>
+      <c r="B548" s="38" t="s">
+        <v>5094</v>
+      </c>
+      <c r="C548" s="35"/>
+      <c r="D548" s="35"/>
+      <c r="E548" s="35"/>
+      <c r="F548" s="35"/>
+      <c r="G548" s="36"/>
+      <c r="H548" s="35"/>
+      <c r="I548" s="37"/>
+      <c r="J548" s="37"/>
+    </row>
+    <row r="549" spans="1:10">
+      <c r="A549" s="33" t="s">
+        <v>5073</v>
+      </c>
+      <c r="B549" s="38" t="s">
+        <v>5095</v>
+      </c>
+      <c r="C549" s="35"/>
+      <c r="D549" s="35"/>
+      <c r="E549" s="35"/>
+      <c r="F549" s="35"/>
+      <c r="G549" s="36"/>
+      <c r="H549" s="35"/>
+      <c r="I549" s="37"/>
+      <c r="J549" s="37"/>
+    </row>
+    <row r="550" spans="1:10">
+      <c r="A550" s="33" t="s">
+        <v>5074</v>
+      </c>
+      <c r="B550" s="38" t="s">
+        <v>5096</v>
+      </c>
+      <c r="C550" s="35"/>
+      <c r="D550" s="35"/>
+      <c r="E550" s="35"/>
+      <c r="F550" s="35"/>
+      <c r="G550" s="36"/>
+      <c r="H550" s="35"/>
+      <c r="I550" s="37"/>
+      <c r="J550" s="37"/>
+    </row>
+    <row r="551" spans="1:10">
+      <c r="A551" s="33" t="s">
+        <v>5075</v>
+      </c>
+      <c r="B551" s="38" t="s">
+        <v>5097</v>
+      </c>
+      <c r="C551" s="35"/>
+      <c r="D551" s="35"/>
+      <c r="E551" s="35"/>
+      <c r="F551" s="35"/>
+      <c r="G551" s="36"/>
+      <c r="H551" s="35"/>
+      <c r="I551" s="37"/>
+      <c r="J551" s="37"/>
+    </row>
+    <row r="552" spans="1:10">
+      <c r="A552" s="33" t="s">
+        <v>5076</v>
+      </c>
+      <c r="B552" s="38" t="s">
+        <v>5098</v>
+      </c>
+      <c r="C552" s="35"/>
+      <c r="D552" s="35"/>
+      <c r="E552" s="35"/>
+      <c r="F552" s="35"/>
+      <c r="G552" s="36"/>
+      <c r="H552" s="35"/>
+      <c r="I552" s="37"/>
+      <c r="J552" s="37"/>
+    </row>
+    <row r="553" spans="1:10">
+      <c r="A553" s="33" t="s">
+        <v>5077</v>
+      </c>
+      <c r="B553" s="34" t="s">
+        <v>5099</v>
+      </c>
+      <c r="C553" s="35"/>
+      <c r="D553" s="35"/>
+      <c r="E553" s="35"/>
+      <c r="F553" s="35"/>
+      <c r="G553" s="36"/>
+      <c r="H553" s="35"/>
+      <c r="I553" s="37"/>
+      <c r="J553" s="37"/>
+    </row>
+    <row r="554" spans="1:10">
+      <c r="A554" s="33" t="s">
+        <v>5078</v>
+      </c>
+      <c r="B554" s="34" t="s">
+        <v>5100</v>
+      </c>
+      <c r="C554" s="35"/>
+      <c r="D554" s="35"/>
+      <c r="E554" s="35"/>
+      <c r="F554" s="35"/>
+      <c r="G554" s="36"/>
+      <c r="H554" s="35"/>
+      <c r="I554" s="37"/>
+      <c r="J554" s="37"/>
+    </row>
+    <row r="555" spans="1:10">
+      <c r="A555" s="33" t="s">
+        <v>5079</v>
+      </c>
+      <c r="B555" s="38" t="s">
+        <v>5101</v>
+      </c>
+      <c r="C555" s="35"/>
+      <c r="D555" s="35"/>
+      <c r="E555" s="35"/>
+      <c r="F555" s="35"/>
+      <c r="G555" s="36"/>
+      <c r="H555" s="35"/>
+      <c r="I555" s="37"/>
+      <c r="J555" s="37"/>
+    </row>
+    <row r="556" spans="1:10">
+      <c r="A556" s="33" t="s">
+        <v>5080</v>
+      </c>
+      <c r="B556" s="34" t="s">
+        <v>5102</v>
+      </c>
+      <c r="C556" s="35"/>
+      <c r="D556" s="35"/>
+      <c r="E556" s="35"/>
+      <c r="F556" s="35"/>
+      <c r="G556" s="36"/>
+      <c r="H556" s="35"/>
+      <c r="I556" s="37"/>
+      <c r="J556" s="37"/>
+    </row>
+    <row r="557" spans="1:10">
+      <c r="A557" s="33" t="s">
+        <v>5081</v>
+      </c>
+      <c r="B557" s="34" t="s">
+        <v>5103</v>
+      </c>
+      <c r="C557" s="35"/>
+      <c r="D557" s="35"/>
+      <c r="E557" s="35"/>
+      <c r="F557" s="35"/>
+      <c r="G557" s="36"/>
+      <c r="H557" s="35"/>
+      <c r="I557" s="37"/>
+      <c r="J557" s="37"/>
+    </row>
+    <row r="558" spans="1:10">
+      <c r="A558" s="33" t="s">
+        <v>5082</v>
+      </c>
+      <c r="B558" s="34" t="s">
+        <v>5104</v>
+      </c>
+      <c r="C558" s="35"/>
+      <c r="D558" s="35"/>
+      <c r="E558" s="35"/>
+      <c r="F558" s="35"/>
+      <c r="G558" s="36"/>
+      <c r="H558" s="35"/>
+      <c r="I558" s="37"/>
+      <c r="J558" s="37"/>
+    </row>
+    <row r="559" spans="1:10">
+      <c r="A559" s="33" t="s">
+        <v>5083</v>
+      </c>
+      <c r="B559" s="34" t="s">
+        <v>5105</v>
+      </c>
+      <c r="C559" s="35"/>
+      <c r="D559" s="35"/>
+      <c r="E559" s="35"/>
+      <c r="F559" s="35"/>
+      <c r="G559" s="36"/>
+      <c r="H559" s="35"/>
+      <c r="I559" s="37"/>
+      <c r="J559" s="37"/>
+    </row>
+    <row r="560" spans="1:10">
+      <c r="A560" s="33" t="s">
+        <v>5084</v>
+      </c>
+      <c r="B560" s="34" t="s">
+        <v>5106</v>
+      </c>
+      <c r="C560" s="35"/>
+      <c r="D560" s="35"/>
+      <c r="E560" s="35"/>
+      <c r="F560" s="35"/>
+      <c r="G560" s="36"/>
+      <c r="H560" s="35"/>
+      <c r="I560" s="37"/>
+      <c r="J560" s="37"/>
+    </row>
+    <row r="561" spans="1:10">
+      <c r="A561" s="33" t="s">
+        <v>5085</v>
+      </c>
+      <c r="B561" s="38" t="s">
+        <v>5107</v>
+      </c>
+      <c r="C561" s="35"/>
+      <c r="D561" s="35"/>
+      <c r="E561" s="35"/>
+      <c r="F561" s="35"/>
+      <c r="G561" s="36"/>
+      <c r="H561" s="35"/>
+      <c r="I561" s="37"/>
+      <c r="J561" s="37"/>
+    </row>
+    <row r="562" spans="1:10">
+      <c r="A562" s="33" t="s">
+        <v>5086</v>
+      </c>
+      <c r="B562" s="34" t="s">
+        <v>5108</v>
+      </c>
+      <c r="C562" s="35"/>
+      <c r="D562" s="35"/>
+      <c r="E562" s="35"/>
+      <c r="F562" s="35"/>
+      <c r="G562" s="36"/>
+      <c r="H562" s="35"/>
+      <c r="I562" s="37"/>
+      <c r="J562" s="37"/>
+    </row>
+    <row r="563" spans="1:10">
+      <c r="A563" s="33" t="s">
+        <v>5087</v>
+      </c>
+      <c r="B563" s="34" t="s">
+        <v>5109</v>
+      </c>
+      <c r="C563" s="35"/>
+      <c r="D563" s="35"/>
+      <c r="E563" s="35"/>
+      <c r="F563" s="35"/>
+      <c r="G563" s="36"/>
+      <c r="H563" s="35"/>
+      <c r="I563" s="37"/>
+      <c r="J563" s="37"/>
+    </row>
+    <row r="564" spans="1:10">
+      <c r="A564" s="33" t="s">
+        <v>5088</v>
+      </c>
+      <c r="B564" s="34" t="s">
+        <v>5110</v>
+      </c>
+      <c r="C564" s="35"/>
+      <c r="D564" s="35"/>
+      <c r="E564" s="35"/>
+      <c r="F564" s="35"/>
+      <c r="G564" s="36"/>
+      <c r="H564" s="35"/>
+      <c r="I564" s="37"/>
+      <c r="J564" s="37"/>
+    </row>
+    <row r="565" spans="1:10">
+      <c r="A565" s="33" t="s">
+        <v>5089</v>
+      </c>
+      <c r="B565" s="34" t="s">
+        <v>5111</v>
+      </c>
+      <c r="C565" s="35"/>
+      <c r="D565" s="35"/>
+      <c r="E565" s="35"/>
+      <c r="F565" s="35"/>
+      <c r="G565" s="36"/>
+      <c r="H565" s="35"/>
+      <c r="I565" s="37"/>
+      <c r="J565" s="37"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -33485,6 +33999,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F12BE0DB4A3DF641BF113FBF1C7EA261" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c6b4b409d6b6c81c2874e5a51d11715e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="43e153a8-5ef1-4f65-aac7-dc4685f18eaa" xmlns:ns3="6e0cf07b-8188-4b76-8f54-3cda03d37414" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0521fade2ab7bf037697e8e8677cb864" ns2:_="" ns3:_="">
     <xsd:import namespace="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
@@ -33725,15 +34248,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E20926E-9EFB-4B7E-90D4-905B08F8E59C}">
   <ds:schemaRefs>
@@ -33752,6 +34266,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6201EF1-2938-4925-833A-11BB4654F7B4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -33768,12 +34290,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/translations/translations.xlsx
+++ b/translations/translations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/russell/Projects/GPS-Sample/translations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdc.sharepoint.com/teams/CGH-GPSSample/Shared Documents/General/2026/Strings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A62F6D-B106-AC40-9AA4-C84BCFCDBDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="13_ncr:1_{21A62F6D-B106-AC40-9AA4-C84BCFCDBDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F78D713D-C2B8-443E-9639-9C6A480ABF78}"/>
   <bookViews>
-    <workbookView xWindow="7960" yWindow="800" windowWidth="30240" windowHeight="22740" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5474" uniqueCount="5112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5649" uniqueCount="5274">
   <si>
     <t>app_name</t>
   </si>
@@ -15345,9 +15345,6 @@
     <t>Enter the geofence buffer value</t>
   </si>
   <si>
-    <t>Placeholder for GeoFence Hint</t>
-  </si>
-  <si>
     <t>You are currently outside of the Geofence</t>
   </si>
   <si>
@@ -15403,6 +15400,495 @@
   </si>
   <si>
     <t>Configuration</t>
+  </si>
+  <si>
+    <t>Aplicar los límites de la zona restringida</t>
+  </si>
+  <si>
+    <t>Introduce el valor del margen de la zona restringida</t>
+  </si>
+  <si>
+    <t>Actualmente te encuentras fuera de la zona geolocalizada</t>
+  </si>
+  <si>
+    <t>Iniciar revisión de la muestra</t>
+  </si>
+  <si>
+    <t>Revisar muestra</t>
+  </si>
+  <si>
+    <t>Revisar posibles duplicados</t>
+  </si>
+  <si>
+    <t>Revisar infracciones de límites</t>
+  </si>
+  <si>
+    <t>Guardar muestra</t>
+  </si>
+  <si>
+    <t>Duplicado</t>
+  </si>
+  <si>
+    <t>Fuera de los límites</t>
+  </si>
+  <si>
+    <t>Debes seleccionar un motivo para la exclusión.</t>
+  </si>
+  <si>
+    <t>Ubicación</t>
+  </si>
+  <si>
+    <t>¿Mantener o excluir esta ubicación?</t>
+  </si>
+  <si>
+    <t>Mantener esta ubicación</t>
+  </si>
+  <si>
+    <t>Excluir esta ubicación</t>
+  </si>
+  <si>
+    <t>Motivo</t>
+  </si>
+  <si>
+    <t>¿Deseas también eliminar definitivamente esta ubicación?</t>
+  </si>
+  <si>
+    <t>Abrir</t>
+  </si>
+  <si>
+    <t>Editar</t>
+  </si>
+  <si>
+    <t>Clonar</t>
+  </si>
+  <si>
+    <t>Vous vous trouvez actuellement en dehors de la zone de géorepérage</t>
+  </si>
+  <si>
+    <t>Lancez la révision des échantillons</t>
+  </si>
+  <si>
+    <t>Révisez l'échantillon</t>
+  </si>
+  <si>
+    <t>Révisez les doublons potentiels</t>
+  </si>
+  <si>
+    <t>Révisez les violations de périmètre</t>
+  </si>
+  <si>
+    <t>Enregistrez l'échantillon</t>
+  </si>
+  <si>
+    <t>Doublon</t>
+  </si>
+  <si>
+    <t>Hors périmètre</t>
+  </si>
+  <si>
+    <t>Vous devez sélectionner un motif d'exclusion.</t>
+  </si>
+  <si>
+    <t>Emplacement</t>
+  </si>
+  <si>
+    <t>Conservez ou exclurez cet emplacement ?</t>
+  </si>
+  <si>
+    <t>Conservez cet emplacement</t>
+  </si>
+  <si>
+    <t>Exclurez cet emplacement</t>
+  </si>
+  <si>
+    <t>Motif</t>
+  </si>
+  <si>
+    <t>Souhaitez-vous également supprimer définitivement cet emplacement ?</t>
+  </si>
+  <si>
+    <t>Ouvrissez</t>
+  </si>
+  <si>
+    <t>Modifiez</t>
+  </si>
+  <si>
+    <t>Clonez</t>
+  </si>
+  <si>
+    <t>Appliquez les limites de la zone de géorepérage</t>
+  </si>
+  <si>
+    <t>Saisissez la valeur de la zone tampon de la zone de géorepérage</t>
+  </si>
+  <si>
+    <t>Aplicar os limites da zona de restrição geográfica</t>
+  </si>
+  <si>
+    <t>Introduza o valor da zona tampão da zona de restrição geográfica</t>
+  </si>
+  <si>
+    <t>De momento, encontra-se fora da zona de geofence</t>
+  </si>
+  <si>
+    <t>Iniciar revisão da amostra</t>
+  </si>
+  <si>
+    <t>Revisar amostra</t>
+  </si>
+  <si>
+    <t>Revisar possíveis duplicados</t>
+  </si>
+  <si>
+    <t>Revisar violações dos limites</t>
+  </si>
+  <si>
+    <t>Guardar amostra</t>
+  </si>
+  <si>
+    <t>Fora dos limites</t>
+  </si>
+  <si>
+    <t>Tem de selecionar um motivo para a exclusão.</t>
+  </si>
+  <si>
+    <t>Localização</t>
+  </si>
+  <si>
+    <t>Manter ou excluir esta localização?</t>
+  </si>
+  <si>
+    <t>Manter esta localização</t>
+  </si>
+  <si>
+    <t>Excluir esta localização</t>
+  </si>
+  <si>
+    <t>Gostaria também de eliminar definitivamente esta localização?</t>
+  </si>
+  <si>
+    <t>В данный момент вы находитесь за пределами геозоны</t>
+  </si>
+  <si>
+    <t>Начать проверку выборки</t>
+  </si>
+  <si>
+    <t>Проверить выборку</t>
+  </si>
+  <si>
+    <t>Проверить возможные дубликаты</t>
+  </si>
+  <si>
+    <t>Проверить нарушения границ</t>
+  </si>
+  <si>
+    <t>Сохранить выборку</t>
+  </si>
+  <si>
+    <t>Дубликат</t>
+  </si>
+  <si>
+    <t>За пределами границ</t>
+  </si>
+  <si>
+    <t>Необходимо выбрать причину исключения.</t>
+  </si>
+  <si>
+    <t>Местоположение</t>
+  </si>
+  <si>
+    <t>Сохранить или исключить это местоположение?</t>
+  </si>
+  <si>
+    <t>Сохранить это местоположение</t>
+  </si>
+  <si>
+    <t>Исключить это местоположение</t>
+  </si>
+  <si>
+    <t>Причина</t>
+  </si>
+  <si>
+    <t>Хотите также окончательно удалить это местоположение?</t>
+  </si>
+  <si>
+    <t>Открыть</t>
+  </si>
+  <si>
+    <t>Редактировать</t>
+  </si>
+  <si>
+    <t>Клонировать</t>
+  </si>
+  <si>
+    <t>Применить границы геозоны</t>
+  </si>
+  <si>
+    <t>Введите значение буфера геозоны</t>
+  </si>
+  <si>
+    <t>اجرای مرز فنس جغرافیایی</t>
+  </si>
+  <si>
+    <t>مقدار بافر فنس جغرافیایی را وارد کنید</t>
+  </si>
+  <si>
+    <t>شما در حال حاضر خارج از حصار جغرافیایی هستید</t>
+  </si>
+  <si>
+    <t>شروع بازبینی نمونه</t>
+  </si>
+  <si>
+    <t>بازبینی موارد تکراری احتمالی</t>
+  </si>
+  <si>
+    <t>بازبینی موارد نقض مرز</t>
+  </si>
+  <si>
+    <t>ذخیره نمونه</t>
+  </si>
+  <si>
+    <t>تکرار</t>
+  </si>
+  <si>
+    <t>خارج از مرز</t>
+  </si>
+  <si>
+    <t>مکان</t>
+  </si>
+  <si>
+    <t>حذف این مکان</t>
+  </si>
+  <si>
+    <t>دلیل</t>
+  </si>
+  <si>
+    <t>باز کردن</t>
+  </si>
+  <si>
+    <t>ویرایش</t>
+  </si>
+  <si>
+    <t>آیا همچنین می‌خواهید این مکان را به‌طور دائم حذف کنید؟</t>
+  </si>
+  <si>
+    <t>کپی</t>
+  </si>
+  <si>
+    <t>پیکربندی</t>
+  </si>
+  <si>
+    <t>نگهداری این مکان</t>
+  </si>
+  <si>
+    <t>نگهداری یا حذف این مکان؟</t>
+  </si>
+  <si>
+    <t>شما باید یک دلیل برای حذف انتخاب کنید.</t>
+  </si>
+  <si>
+    <t>تاسو اوسمهال له جیوفینس څخه بهر یاست</t>
+  </si>
+  <si>
+    <t>د نمونې بیاکتنه پیل کړئ</t>
+  </si>
+  <si>
+    <t>د نمونې بیاکتنه</t>
+  </si>
+  <si>
+    <t>د احتمالي دوه ګونو بیاکتنه</t>
+  </si>
+  <si>
+    <t>د پولې څخه د سرغړونو بیاکتنه</t>
+  </si>
+  <si>
+    <t>نمونې خوندي کړئ</t>
+  </si>
+  <si>
+    <t>دوه ګونی</t>
+  </si>
+  <si>
+    <t>له پولې بهر</t>
+  </si>
+  <si>
+    <t>تاسو باید د ایستلو لپاره یو دلیل وټاکئ.</t>
+  </si>
+  <si>
+    <t>موقعیت</t>
+  </si>
+  <si>
+    <t>دا موقعیت وساتئ که یې وباسئ؟</t>
+  </si>
+  <si>
+    <t>دا موقعیت وساتئ</t>
+  </si>
+  <si>
+    <t>دا موقعیت وباسئ</t>
+  </si>
+  <si>
+    <t>ایا تاسو غواړئ دا موقعیت د تل لپاره هم حذف کړئ؟</t>
+  </si>
+  <si>
+    <t>پرانیستل</t>
+  </si>
+  <si>
+    <t>سمول</t>
+  </si>
+  <si>
+    <t>کاپي کول</t>
+  </si>
+  <si>
+    <t>د جیوفینس پولې پلي کړئ</t>
+  </si>
+  <si>
+    <t>د جیوفینس بفر ارزښت داخل کړئ</t>
+  </si>
+  <si>
+    <t>Terapkan Batas Geofence</t>
+  </si>
+  <si>
+    <t>Masukkan nilai buffer geofence</t>
+  </si>
+  <si>
+    <t>Anda saat ini berada di luar Geofence</t>
+  </si>
+  <si>
+    <t>Mulailah Tinjauan Sampel</t>
+  </si>
+  <si>
+    <t>Tinjau Sampel</t>
+  </si>
+  <si>
+    <t>Tinjau Kemungkinan Duplikat</t>
+  </si>
+  <si>
+    <t>Tinjau Pelanggaran Batas</t>
+  </si>
+  <si>
+    <t>Simpan Sampel</t>
+  </si>
+  <si>
+    <t>Duplikat</t>
+  </si>
+  <si>
+    <t>Di Luar Batas</t>
+  </si>
+  <si>
+    <t>Anda harus memilih Alasan pengecualian.</t>
+  </si>
+  <si>
+    <t>Lokasi</t>
+  </si>
+  <si>
+    <t>Pertahankan atau Kecualikan lokasi ini?</t>
+  </si>
+  <si>
+    <t>Pertahankan lokasi ini</t>
+  </si>
+  <si>
+    <t>Kecualikan lokasi ini</t>
+  </si>
+  <si>
+    <t>Alasan</t>
+  </si>
+  <si>
+    <t>Apakah Anda juga ingin menghapus lokasi ini secara permanen?</t>
+  </si>
+  <si>
+    <t>Buka</t>
+  </si>
+  <si>
+    <t>Sunting</t>
+  </si>
+  <si>
+    <t>Klon</t>
+  </si>
+  <si>
+    <t>Kasalukuyan kang nasa labas ng Geofence</t>
+  </si>
+  <si>
+    <t>Simulan ang Sample na Pagsusuri</t>
+  </si>
+  <si>
+    <t>Suriin ang Sample</t>
+  </si>
+  <si>
+    <t>Suriin ang Mga Posibleng Duplicate</t>
+  </si>
+  <si>
+    <t>Suriin ang Mga Paglabag sa Hangganan</t>
+  </si>
+  <si>
+    <t>I-save ang Sample</t>
+  </si>
+  <si>
+    <t>Sa Labas ng Hangganan</t>
+  </si>
+  <si>
+    <t>Dapat kang pumili ng Dahilan para sa pagbubukod.</t>
+  </si>
+  <si>
+    <t>Lokasyon</t>
+  </si>
+  <si>
+    <t>Panatilihin o Ibukod ang lokasyong ito?</t>
+  </si>
+  <si>
+    <t>Panatilihin ang lokasyong ito</t>
+  </si>
+  <si>
+    <t>Bukod ang lokasyong ito</t>
+  </si>
+  <si>
+    <t>Dahilan</t>
+  </si>
+  <si>
+    <t>Gusto mo rin bang permanenteng burahin ang lokasyong ito?</t>
+  </si>
+  <si>
+    <t>Buksan</t>
+  </si>
+  <si>
+    <t>I-edit</t>
+  </si>
+  <si>
+    <t>I-clone</t>
+  </si>
+  <si>
+    <t>Pag-configure</t>
+  </si>
+  <si>
+    <t>Ipatupad ang Hangganan ng Geofence</t>
+  </si>
+  <si>
+    <t>Ilagay ang halaga ng geofence buffer</t>
+  </si>
+  <si>
+    <t>A geofence is an error buffer around your enumeration areas. Teams are able to collect data outside the geofence, but anything beyond the error buffer will be flagged for review by the supervisors. Ex. For a 5m geofence, any location collected at 6m+ will be flagged for the supervisor to review.</t>
+  </si>
+  <si>
+    <t>Une « geofence » est une zone tampon d'erreur délimitée autour de vos zones de recensement. Les équipes peuvent collecter des données en dehors de la « geofence », mais toute donnée située au-delà de la zone tampon d'erreur sera signalée pour être examinée par les superviseurs. Exemple : pour une « geofence » de 5 m, toute localisation enregistrée à 6 m ou plus sera signalée pour être examinée par le superviseur.</t>
+  </si>
+  <si>
+    <t>Una geovalla es un margen de error que rodea las áreas de recuento. Los equipos pueden recopilar datos fuera de la geovalla, pero cualquier dato que se encuentre más allá del margen de error se marcará para que lo revisen los supervisores. Por ejemplo: en el caso de una geovalla de 5 m, cualquier ubicación registrada a 6 m o más se marcará para que la revise el supervisor.</t>
+  </si>
+  <si>
+    <t>Uma geofence é uma zona de tolerância em torno das suas áreas de recenseamento. As equipas podem recolher dados fora da geofence, mas qualquer localização fora da zona de tolerância será assinalada para revisão pelos supervisores. Ex.: No caso de uma geofence de 5 m, qualquer localização registada a 6 m ou mais será assinalada para que o supervisor a reveja.</t>
+  </si>
+  <si>
+    <t>Геозона — это буфер погрешности вокруг ваших зон переписи. Команды могут собирать данные за пределами геозоны, но все данные, полученные за пределами буфера погрешности, будут помечены для проверки руководителями. Например, при геозоне 5 м любые координаты, зафиксированные на расстоянии 6 м и более, будут помечены для проверки руководителем.</t>
+  </si>
+  <si>
+    <t>جیوفینس ستاسو د شمېرنې سیمو شاوخوا د تېروتنې لپاره یو حدمحسوبېږي. ټیمونه کولی شي د جیوفینس څخه بهر معلومات راټول کړي، خو هر هغه څه چې د تېروتنې له حدمحسوبې څخه واوړي، د څارونکو لخوا د بیاکتنې لپاره به په نښه شي. د بېلګې په توګه: د ۵ متره جیوفینس لپاره، هر هغه موقعیت چې په ۶ متره یا ډېر واټن کې راټول شي، د څارونکي د بیاکتنې لپاره به په نښه شي.</t>
+  </si>
+  <si>
+    <t>حصار جغرافیایی یک حاشیه خطا در اطراف مناطق سرشماری شما است. تیم‌ها می‌توانند در خارج از حصار جغرافیایی داده‌ها را جمع‌آوری کنند، اما هر داده‌ای که از حاشیه خطا فراتر رود برای بازبینی توسط سرپرستان علامت‌گذاری می‌شود. مثال: برای یک حصار جغرافیایی ۵ متری، هر موقعیتی که در فاصله ۶ متری یا بیشتر جمع‌آوری شود برای بازبینی سرپرست علامت‌گذاری خواهد شد.</t>
+  </si>
+  <si>
+    <t>Ang geofence ay isang error buffer sa paligid ng iyong mga enumeration area. Ang mga team ay makakakolekta ng data sa labas ng geofence, ngunit ang anumang bagay na lampas sa error buffer ay ifa-flag para sa pagsusuri ng mga superbisor. Hal. Para sa isang 5m geofence, ang anumang lokasyon na nakolekta sa 6m+ ay ifa-flag para sa pagsusuri ng superbisor.</t>
+  </si>
+  <si>
+    <t>Geofence adalah batas toleransi kesalahan di sekeliling wilayah pencacahan Anda. Tim dapat mengumpulkan data di luar geofence, namun data yang berada di luar batas toleransi tersebut akan ditandai untuk ditinjau oleh supervisor. Contoh: Untuk geofence sebesar 5 meter, lokasi mana pun yang tercatat pada jarak 6 meter atau lebih akan ditandai agar dapat ditinjau oleh supervisor.</t>
   </si>
 </sst>
 </file>
@@ -15589,7 +16075,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -15673,20 +16159,14 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1" readingOrder="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16236,19 +16716,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD3E6CC-854C-5841-9577-D3ADD2982DB6}">
   <dimension ref="A1:J565"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="33.5" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="29.33203125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="31.1640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="26.6640625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="29.1640625" style="5" customWidth="1"/>
-    <col min="7" max="8" width="31.33203125" customWidth="1"/>
-    <col min="9" max="10" width="24.33203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="25.875" customWidth="1"/>
+    <col min="3" max="3" width="29.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.375" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="9" max="9" width="24.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -16696,7 +17178,7 @@
         <v>3814</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="23.25">
       <c r="A15" s="6" t="s">
         <v>92</v>
       </c>
@@ -16856,7 +17338,7 @@
         <v>4654</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" ht="23.25">
       <c r="A20" s="6" t="s">
         <v>110</v>
       </c>
@@ -16888,7 +17370,7 @@
         <v>3818</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="25">
+    <row r="21" spans="1:10" ht="23.25">
       <c r="A21" s="6" t="s">
         <v>110</v>
       </c>
@@ -17848,7 +18330,7 @@
         <v>3401</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" ht="23.25">
       <c r="A51" s="6" t="s">
         <v>300</v>
       </c>
@@ -17880,7 +18362,7 @@
         <v>3801</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="25">
+    <row r="52" spans="1:10" ht="23.25">
       <c r="A52" s="6" t="s">
         <v>306</v>
       </c>
@@ -17976,7 +18458,7 @@
         <v>4664</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" ht="23.25">
       <c r="A55" s="6" t="s">
         <v>326</v>
       </c>
@@ -18456,7 +18938,7 @@
         <v>3889</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" ht="23.25">
       <c r="A70" s="6" t="s">
         <v>407</v>
       </c>
@@ -19544,7 +20026,7 @@
         <v>3937</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" ht="23.25">
       <c r="A104" s="6" t="s">
         <v>613</v>
       </c>
@@ -19640,7 +20122,7 @@
         <v>3939</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" ht="23.25">
       <c r="A107" s="6" t="s">
         <v>631</v>
       </c>
@@ -19768,7 +20250,7 @@
         <v>3996</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" ht="23.25">
       <c r="A111" s="6" t="s">
         <v>658</v>
       </c>
@@ -19800,7 +20282,7 @@
         <v>3997</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" ht="23.25">
       <c r="A112" s="6" t="s">
         <v>664</v>
       </c>
@@ -19992,7 +20474,7 @@
         <v>4039</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="25">
+    <row r="118" spans="1:10">
       <c r="A118" s="6" t="s">
         <v>699</v>
       </c>
@@ -20024,7 +20506,7 @@
         <v>4040</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" ht="23.25">
       <c r="A119" s="6" t="s">
         <v>706</v>
       </c>
@@ -20728,7 +21210,7 @@
         <v>4056</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="25">
+    <row r="141" spans="1:10" ht="23.25">
       <c r="A141" s="6" t="s">
         <v>849</v>
       </c>
@@ -21016,7 +21498,7 @@
         <v>4050</v>
       </c>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" spans="1:10" ht="23.25">
       <c r="A150" s="17" t="s">
         <v>908</v>
       </c>
@@ -21080,7 +21562,7 @@
         <v>4770</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="25">
+    <row r="152" spans="1:10" ht="34.5">
       <c r="A152" s="17" t="s">
         <v>919</v>
       </c>
@@ -21112,7 +21594,7 @@
         <v>3999</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="25">
+    <row r="153" spans="1:10" ht="34.5">
       <c r="A153" s="17" t="s">
         <v>925</v>
       </c>
@@ -21144,7 +21626,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="25">
+    <row r="154" spans="1:10" ht="34.5">
       <c r="A154" s="17" t="s">
         <v>931</v>
       </c>
@@ -21176,7 +21658,7 @@
         <v>4772</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="25">
+    <row r="155" spans="1:10" ht="34.5">
       <c r="A155" s="17" t="s">
         <v>938</v>
       </c>
@@ -21208,7 +21690,7 @@
         <v>4001</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="25">
+    <row r="156" spans="1:10" ht="34.5">
       <c r="A156" s="17" t="s">
         <v>945</v>
       </c>
@@ -21240,7 +21722,7 @@
         <v>4002</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="25">
+    <row r="157" spans="1:10" ht="34.5">
       <c r="A157" s="17" t="s">
         <v>952</v>
       </c>
@@ -21272,7 +21754,7 @@
         <v>4003</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="25">
+    <row r="158" spans="1:10" ht="34.5">
       <c r="A158" s="17" t="s">
         <v>959</v>
       </c>
@@ -21304,7 +21786,7 @@
         <v>4004</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="25">
+    <row r="159" spans="1:10" ht="34.5">
       <c r="A159" s="17" t="s">
         <v>966</v>
       </c>
@@ -21400,7 +21882,7 @@
         <v>4007</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="25">
+    <row r="162" spans="1:10" ht="23.25">
       <c r="A162" s="17" t="s">
         <v>986</v>
       </c>
@@ -21432,7 +21914,7 @@
         <v>4008</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" spans="1:10" ht="23.25">
       <c r="A163" s="17" t="s">
         <v>993</v>
       </c>
@@ -21464,7 +21946,7 @@
         <v>4009</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="25">
+    <row r="164" spans="1:10" ht="23.25">
       <c r="A164" s="17" t="s">
         <v>1000</v>
       </c>
@@ -21496,7 +21978,7 @@
         <v>3983</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="25">
+    <row r="165" spans="1:10" ht="34.5">
       <c r="A165" s="17" t="s">
         <v>1006</v>
       </c>
@@ -21528,7 +22010,7 @@
         <v>4775</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="25">
+    <row r="166" spans="1:10" ht="23.25">
       <c r="A166" s="17" t="s">
         <v>1012</v>
       </c>
@@ -21560,7 +22042,7 @@
         <v>4010</v>
       </c>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" spans="1:10" ht="23.25">
       <c r="A167" s="17" t="s">
         <v>1018</v>
       </c>
@@ -21848,7 +22330,7 @@
         <v>4013</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="25">
+    <row r="176" spans="1:10" ht="23.25">
       <c r="A176" s="17" t="s">
         <v>1077</v>
       </c>
@@ -22008,7 +22490,7 @@
         <v>4015</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="25">
+    <row r="181" spans="1:10" ht="23.25">
       <c r="A181" s="17" t="s">
         <v>1103</v>
       </c>
@@ -22040,7 +22522,7 @@
         <v>4016</v>
       </c>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" spans="1:10" ht="23.25">
       <c r="A182" s="17" t="s">
         <v>1109</v>
       </c>
@@ -22200,7 +22682,7 @@
         <v>3947</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="25">
+    <row r="187" spans="1:10" ht="23.25">
       <c r="A187" s="17" t="s">
         <v>1138</v>
       </c>
@@ -22424,7 +22906,7 @@
         <v>4787</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" ht="23.25">
       <c r="A194" s="6" t="s">
         <v>1179</v>
       </c>
@@ -22488,7 +22970,7 @@
         <v>3954</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" ht="23.25">
       <c r="A196" s="6" t="s">
         <v>1193</v>
       </c>
@@ -22520,7 +23002,7 @@
         <v>4789</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="25">
+    <row r="197" spans="1:10" ht="34.5">
       <c r="A197" s="6" t="s">
         <v>1199</v>
       </c>
@@ -22616,7 +23098,7 @@
         <v>3956</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="25">
+    <row r="200" spans="1:10" ht="23.25">
       <c r="A200" s="6" t="s">
         <v>1216</v>
       </c>
@@ -23064,7 +23546,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" spans="1:10" ht="23.25">
       <c r="A214" s="17" t="s">
         <v>1290</v>
       </c>
@@ -23864,7 +24346,7 @@
         <v>3971</v>
       </c>
     </row>
-    <row r="239" spans="1:10" ht="25">
+    <row r="239" spans="1:10" ht="23.25">
       <c r="A239" s="6" t="s">
         <v>1407</v>
       </c>
@@ -23992,7 +24474,7 @@
         <v>4032</v>
       </c>
     </row>
-    <row r="243" spans="1:10" ht="49">
+    <row r="243" spans="1:10" ht="45.75">
       <c r="A243" s="6" t="s">
         <v>1432</v>
       </c>
@@ -24024,7 +24506,7 @@
         <v>4034</v>
       </c>
     </row>
-    <row r="244" spans="1:10" ht="25">
+    <row r="244" spans="1:10" ht="23.25">
       <c r="A244" s="6" t="s">
         <v>1437</v>
       </c>
@@ -24152,7 +24634,7 @@
         <v>4807</v>
       </c>
     </row>
-    <row r="248" spans="1:10">
+    <row r="248" spans="1:10" ht="23.25">
       <c r="A248" s="24" t="s">
         <v>1460</v>
       </c>
@@ -24184,7 +24666,7 @@
         <v>4809</v>
       </c>
     </row>
-    <row r="249" spans="1:10">
+    <row r="249" spans="1:10" ht="23.25">
       <c r="A249" s="24" t="s">
         <v>1466</v>
       </c>
@@ -25016,7 +25498,7 @@
         <v>3980</v>
       </c>
     </row>
-    <row r="275" spans="1:10" ht="25">
+    <row r="275" spans="1:10" ht="23.25">
       <c r="A275" s="24" t="s">
         <v>1610</v>
       </c>
@@ -25048,7 +25530,7 @@
         <v>3981</v>
       </c>
     </row>
-    <row r="276" spans="1:10" ht="25">
+    <row r="276" spans="1:10" ht="23.25">
       <c r="A276" s="24" t="s">
         <v>1616</v>
       </c>
@@ -25080,7 +25562,7 @@
         <v>3982</v>
       </c>
     </row>
-    <row r="277" spans="1:10" ht="25">
+    <row r="277" spans="1:10" ht="23.25">
       <c r="A277" s="24" t="s">
         <v>1621</v>
       </c>
@@ -25176,7 +25658,7 @@
         <v>3984</v>
       </c>
     </row>
-    <row r="280" spans="1:10" ht="25">
+    <row r="280" spans="1:10" ht="34.5">
       <c r="A280" s="6" t="s">
         <v>1635</v>
       </c>
@@ -25400,7 +25882,7 @@
         <v>4831</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" ht="23.25">
       <c r="A287" s="6" t="s">
         <v>1678</v>
       </c>
@@ -25432,7 +25914,7 @@
         <v>3991</v>
       </c>
     </row>
-    <row r="288" spans="1:10">
+    <row r="288" spans="1:10" ht="23.25">
       <c r="A288" s="6" t="s">
         <v>1685</v>
       </c>
@@ -25496,7 +25978,7 @@
         <v>3992</v>
       </c>
     </row>
-    <row r="290" spans="1:10" ht="25">
+    <row r="290" spans="1:10" ht="34.5">
       <c r="A290" s="6" t="s">
         <v>1697</v>
       </c>
@@ -25560,7 +26042,7 @@
         <v>3990</v>
       </c>
     </row>
-    <row r="292" spans="1:10">
+    <row r="292" spans="1:10" ht="23.25">
       <c r="A292" s="6" t="s">
         <v>1709</v>
       </c>
@@ -25592,7 +26074,7 @@
         <v>3989</v>
       </c>
     </row>
-    <row r="293" spans="1:10" ht="25">
+    <row r="293" spans="1:10" ht="23.25">
       <c r="A293" s="6" t="s">
         <v>1716</v>
       </c>
@@ -25624,7 +26106,7 @@
         <v>3988</v>
       </c>
     </row>
-    <row r="294" spans="1:10">
+    <row r="294" spans="1:10" ht="23.25">
       <c r="A294" s="6" t="s">
         <v>1722</v>
       </c>
@@ -25656,7 +26138,7 @@
         <v>3987</v>
       </c>
     </row>
-    <row r="295" spans="1:10" ht="25">
+    <row r="295" spans="1:10" ht="23.25">
       <c r="A295" s="6" t="s">
         <v>1729</v>
       </c>
@@ -25752,7 +26234,7 @@
         <v>4026</v>
       </c>
     </row>
-    <row r="298" spans="1:10">
+    <row r="298" spans="1:10" ht="23.25">
       <c r="A298" s="6" t="s">
         <v>1744</v>
       </c>
@@ -25784,7 +26266,7 @@
         <v>4027</v>
       </c>
     </row>
-    <row r="299" spans="1:10">
+    <row r="299" spans="1:10" ht="23.25">
       <c r="A299" s="6" t="s">
         <v>1751</v>
       </c>
@@ -25816,7 +26298,7 @@
         <v>4028</v>
       </c>
     </row>
-    <row r="300" spans="1:10">
+    <row r="300" spans="1:10" ht="23.25">
       <c r="A300" s="6" t="s">
         <v>1758</v>
       </c>
@@ -25848,7 +26330,7 @@
         <v>4029</v>
       </c>
     </row>
-    <row r="301" spans="1:10" ht="25">
+    <row r="301" spans="1:10" ht="23.25">
       <c r="A301" s="21" t="s">
         <v>1765</v>
       </c>
@@ -25912,7 +26394,7 @@
         <v>4094</v>
       </c>
     </row>
-    <row r="303" spans="1:10" ht="25">
+    <row r="303" spans="1:10" ht="23.25">
       <c r="A303" s="21" t="s">
         <v>1777</v>
       </c>
@@ -25944,7 +26426,7 @@
         <v>4095</v>
       </c>
     </row>
-    <row r="304" spans="1:10" ht="25">
+    <row r="304" spans="1:10" ht="23.25">
       <c r="A304" s="21" t="s">
         <v>1784</v>
       </c>
@@ -25976,7 +26458,7 @@
         <v>4096</v>
       </c>
     </row>
-    <row r="305" spans="1:10" ht="25">
+    <row r="305" spans="1:10" ht="23.25">
       <c r="A305" s="21" t="s">
         <v>1791</v>
       </c>
@@ -26008,7 +26490,7 @@
         <v>4097</v>
       </c>
     </row>
-    <row r="306" spans="1:10" ht="25">
+    <row r="306" spans="1:10" ht="23.25">
       <c r="A306" s="21" t="s">
         <v>1798</v>
       </c>
@@ -26040,7 +26522,7 @@
         <v>4098</v>
       </c>
     </row>
-    <row r="307" spans="1:10">
+    <row r="307" spans="1:10" ht="23.25">
       <c r="A307" s="21" t="s">
         <v>1804</v>
       </c>
@@ -26136,7 +26618,7 @@
         <v>4117</v>
       </c>
     </row>
-    <row r="310" spans="1:10">
+    <row r="310" spans="1:10" ht="23.25">
       <c r="A310" s="21" t="s">
         <v>1822</v>
       </c>
@@ -26264,7 +26746,7 @@
         <v>4121</v>
       </c>
     </row>
-    <row r="314" spans="1:10" ht="25">
+    <row r="314" spans="1:10" ht="34.5">
       <c r="A314" s="21" t="s">
         <v>1844</v>
       </c>
@@ -26296,7 +26778,7 @@
         <v>4124</v>
       </c>
     </row>
-    <row r="315" spans="1:10" ht="25">
+    <row r="315" spans="1:10" ht="23.25">
       <c r="A315" s="21" t="s">
         <v>1851</v>
       </c>
@@ -26520,7 +27002,7 @@
         <v>4135</v>
       </c>
     </row>
-    <row r="322" spans="1:10" ht="25">
+    <row r="322" spans="1:10" ht="23.25">
       <c r="A322" s="21" t="s">
         <v>1899</v>
       </c>
@@ -26552,7 +27034,7 @@
         <v>4136</v>
       </c>
     </row>
-    <row r="323" spans="1:10" ht="25">
+    <row r="323" spans="1:10" ht="23.25">
       <c r="A323" s="21" t="s">
         <v>1905</v>
       </c>
@@ -26744,7 +27226,7 @@
         <v>4142</v>
       </c>
     </row>
-    <row r="329" spans="1:10" ht="25">
+    <row r="329" spans="1:10" ht="23.25">
       <c r="A329" s="29" t="s">
         <v>1943</v>
       </c>
@@ -26808,7 +27290,7 @@
         <v>4144</v>
       </c>
     </row>
-    <row r="331" spans="1:10">
+    <row r="331" spans="1:10" ht="23.25">
       <c r="A331" s="29" t="s">
         <v>1956</v>
       </c>
@@ -26840,7 +27322,7 @@
         <v>4158</v>
       </c>
     </row>
-    <row r="332" spans="1:10" ht="25">
+    <row r="332" spans="1:10" ht="23.25">
       <c r="A332" s="29" t="s">
         <v>1962</v>
       </c>
@@ -26904,7 +27386,7 @@
         <v>4156</v>
       </c>
     </row>
-    <row r="334" spans="1:10">
+    <row r="334" spans="1:10" ht="23.25">
       <c r="A334" s="29" t="s">
         <v>1973</v>
       </c>
@@ -26936,7 +27418,7 @@
         <v>4152</v>
       </c>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" spans="1:10" ht="23.25">
       <c r="A335" s="29" t="s">
         <v>1980</v>
       </c>
@@ -27032,7 +27514,7 @@
         <v>4155</v>
       </c>
     </row>
-    <row r="338" spans="1:10" ht="25">
+    <row r="338" spans="1:10" ht="23.25">
       <c r="A338" s="29" t="s">
         <v>2001</v>
       </c>
@@ -27320,7 +27802,7 @@
         <v>4129</v>
       </c>
     </row>
-    <row r="347" spans="1:10" ht="25">
+    <row r="347" spans="1:10" ht="23.25">
       <c r="A347" s="29" t="s">
         <v>2053</v>
       </c>
@@ -27512,7 +27994,7 @@
         <v>4126</v>
       </c>
     </row>
-    <row r="353" spans="1:10">
+    <row r="353" spans="1:10" ht="23.25">
       <c r="A353" s="29" t="s">
         <v>2091</v>
       </c>
@@ -27544,7 +28026,7 @@
         <v>4102</v>
       </c>
     </row>
-    <row r="354" spans="1:10">
+    <row r="354" spans="1:10" ht="23.25">
       <c r="A354" s="29" t="s">
         <v>2096</v>
       </c>
@@ -27576,7 +28058,7 @@
         <v>4103</v>
       </c>
     </row>
-    <row r="355" spans="1:10">
+    <row r="355" spans="1:10" ht="23.25">
       <c r="A355" s="29" t="s">
         <v>2101</v>
       </c>
@@ -27608,7 +28090,7 @@
         <v>4104</v>
       </c>
     </row>
-    <row r="356" spans="1:10">
+    <row r="356" spans="1:10" ht="23.25">
       <c r="A356" s="29" t="s">
         <v>2106</v>
       </c>
@@ -27640,7 +28122,7 @@
         <v>4105</v>
       </c>
     </row>
-    <row r="357" spans="1:10">
+    <row r="357" spans="1:10" ht="23.25">
       <c r="A357" s="29" t="s">
         <v>2111</v>
       </c>
@@ -27672,7 +28154,7 @@
         <v>4106</v>
       </c>
     </row>
-    <row r="358" spans="1:10" ht="25">
+    <row r="358" spans="1:10" ht="23.25">
       <c r="A358" s="29" t="s">
         <v>2116</v>
       </c>
@@ -27704,7 +28186,7 @@
         <v>4109</v>
       </c>
     </row>
-    <row r="359" spans="1:10" ht="25">
+    <row r="359" spans="1:10" ht="34.5">
       <c r="A359" s="29" t="s">
         <v>2123</v>
       </c>
@@ -27768,7 +28250,7 @@
         <v>4107</v>
       </c>
     </row>
-    <row r="361" spans="1:10" ht="25">
+    <row r="361" spans="1:10" ht="23.25">
       <c r="A361" s="29" t="s">
         <v>2136</v>
       </c>
@@ -27896,7 +28378,7 @@
         <v>4113</v>
       </c>
     </row>
-    <row r="365" spans="1:10">
+    <row r="365" spans="1:10" ht="23.25">
       <c r="A365" s="29" t="s">
         <v>2161</v>
       </c>
@@ -27928,7 +28410,7 @@
         <v>4114</v>
       </c>
     </row>
-    <row r="366" spans="1:10" ht="25">
+    <row r="366" spans="1:10" ht="34.5">
       <c r="A366" s="29" t="s">
         <v>2167</v>
       </c>
@@ -27960,7 +28442,7 @@
         <v>4116</v>
       </c>
     </row>
-    <row r="367" spans="1:10" ht="25">
+    <row r="367" spans="1:10" ht="34.5">
       <c r="A367" s="29" t="s">
         <v>2174</v>
       </c>
@@ -28248,7 +28730,7 @@
         <v>4091</v>
       </c>
     </row>
-    <row r="376" spans="1:10" ht="25">
+    <row r="376" spans="1:10" ht="34.5">
       <c r="A376" s="29" t="s">
         <v>2234</v>
       </c>
@@ -28280,7 +28762,7 @@
         <v>4092</v>
       </c>
     </row>
-    <row r="377" spans="1:10" ht="25">
+    <row r="377" spans="1:10" ht="34.5">
       <c r="A377" s="29" t="s">
         <v>2241</v>
       </c>
@@ -28312,7 +28794,7 @@
         <v>4093</v>
       </c>
     </row>
-    <row r="378" spans="1:10" ht="25">
+    <row r="378" spans="1:10" ht="34.5">
       <c r="A378" s="29" t="s">
         <v>2248</v>
       </c>
@@ -28376,7 +28858,7 @@
         <v>4083</v>
       </c>
     </row>
-    <row r="380" spans="1:10">
+    <row r="380" spans="1:10" ht="23.25">
       <c r="A380" s="29" t="s">
         <v>2261</v>
       </c>
@@ -28440,7 +28922,7 @@
         <v>4085</v>
       </c>
     </row>
-    <row r="382" spans="1:10">
+    <row r="382" spans="1:10" ht="23.25">
       <c r="A382" s="29" t="s">
         <v>2275</v>
       </c>
@@ -28472,7 +28954,7 @@
         <v>4081</v>
       </c>
     </row>
-    <row r="383" spans="1:10" ht="49">
+    <row r="383" spans="1:10" ht="57">
       <c r="A383" s="29" t="s">
         <v>2282</v>
       </c>
@@ -28504,7 +28986,7 @@
         <v>4080</v>
       </c>
     </row>
-    <row r="384" spans="1:10">
+    <row r="384" spans="1:10" ht="23.25">
       <c r="A384" s="29" t="s">
         <v>2289</v>
       </c>
@@ -28856,7 +29338,7 @@
         <v>3906</v>
       </c>
     </row>
-    <row r="395" spans="1:10" ht="37">
+    <row r="395" spans="1:10" ht="45.75">
       <c r="A395" s="29" t="s">
         <v>2356</v>
       </c>
@@ -28888,7 +29370,7 @@
         <v>3909</v>
       </c>
     </row>
-    <row r="396" spans="1:10">
+    <row r="396" spans="1:10" ht="23.25">
       <c r="A396" s="29" t="s">
         <v>2391</v>
       </c>
@@ -28920,7 +29402,7 @@
         <v>3908</v>
       </c>
     </row>
-    <row r="397" spans="1:10" ht="25">
+    <row r="397" spans="1:10" ht="23.25">
       <c r="A397" s="29" t="s">
         <v>2392</v>
       </c>
@@ -29400,7 +29882,7 @@
         <v>3915</v>
       </c>
     </row>
-    <row r="412" spans="1:10" ht="25">
+    <row r="412" spans="1:10" ht="34.5">
       <c r="A412" s="29" t="s">
         <v>2540</v>
       </c>
@@ -29496,7 +29978,7 @@
         <v>3922</v>
       </c>
     </row>
-    <row r="415" spans="1:10">
+    <row r="415" spans="1:10" ht="23.25">
       <c r="A415" s="29" t="s">
         <v>2543</v>
       </c>
@@ -29528,7 +30010,7 @@
         <v>3923</v>
       </c>
     </row>
-    <row r="416" spans="1:10">
+    <row r="416" spans="1:10" ht="23.25">
       <c r="A416" s="29" t="s">
         <v>2544</v>
       </c>
@@ -29784,7 +30266,7 @@
         <v>3866</v>
       </c>
     </row>
-    <row r="424" spans="1:10" ht="25">
+    <row r="424" spans="1:10" ht="34.5">
       <c r="A424" s="29" t="s">
         <v>2552</v>
       </c>
@@ -29816,7 +30298,7 @@
         <v>3863</v>
       </c>
     </row>
-    <row r="425" spans="1:10" ht="25">
+    <row r="425" spans="1:10" ht="23.25">
       <c r="A425" s="29" t="s">
         <v>2553</v>
       </c>
@@ -30072,7 +30554,7 @@
         <v>3850</v>
       </c>
     </row>
-    <row r="433" spans="1:10" ht="25">
+    <row r="433" spans="1:10" ht="23.25">
       <c r="A433" s="29" t="s">
         <v>2737</v>
       </c>
@@ -30200,7 +30682,7 @@
         <v>3854</v>
       </c>
     </row>
-    <row r="437" spans="1:10" ht="25">
+    <row r="437" spans="1:10" ht="23.25">
       <c r="A437" s="29" t="s">
         <v>2828</v>
       </c>
@@ -30232,7 +30714,7 @@
         <v>3855</v>
       </c>
     </row>
-    <row r="438" spans="1:10" ht="25">
+    <row r="438" spans="1:10" ht="23.25">
       <c r="A438" s="29" t="s">
         <v>2829</v>
       </c>
@@ -30584,7 +31066,7 @@
         <v>3838</v>
       </c>
     </row>
-    <row r="449" spans="1:10" ht="25">
+    <row r="449" spans="1:10" ht="34.5">
       <c r="A449" s="29" t="s">
         <v>2154</v>
       </c>
@@ -30936,7 +31418,7 @@
         <v>3830</v>
       </c>
     </row>
-    <row r="460" spans="1:10" ht="37">
+    <row r="460" spans="1:10" ht="57">
       <c r="A460" s="29" t="s">
         <v>4838</v>
       </c>
@@ -30968,7 +31450,7 @@
         <v>4847</v>
       </c>
     </row>
-    <row r="461" spans="1:10" ht="49">
+    <row r="461" spans="1:10" ht="57">
       <c r="A461" s="29" t="s">
         <v>4848</v>
       </c>
@@ -31000,7 +31482,7 @@
         <v>4857</v>
       </c>
     </row>
-    <row r="462" spans="1:10" ht="49">
+    <row r="462" spans="1:10" ht="45.75">
       <c r="A462" s="29" t="s">
         <v>4858</v>
       </c>
@@ -31032,7 +31514,7 @@
         <v>4867</v>
       </c>
     </row>
-    <row r="463" spans="1:10" ht="37">
+    <row r="463" spans="1:10" ht="45.75">
       <c r="A463" s="29" t="s">
         <v>4868</v>
       </c>
@@ -31064,7 +31546,7 @@
         <v>4877</v>
       </c>
     </row>
-    <row r="464" spans="1:10" ht="37">
+    <row r="464" spans="1:10" ht="34.5">
       <c r="A464" s="29" t="s">
         <v>4878</v>
       </c>
@@ -31096,7 +31578,7 @@
         <v>4887</v>
       </c>
     </row>
-    <row r="465" spans="1:10">
+    <row r="465" spans="1:10" ht="23.25">
       <c r="A465" s="29" t="s">
         <v>4888</v>
       </c>
@@ -31192,7 +31674,7 @@
         <v>4917</v>
       </c>
     </row>
-    <row r="468" spans="1:10" ht="25">
+    <row r="468" spans="1:10" ht="23.25">
       <c r="A468" s="29" t="s">
         <v>4918</v>
       </c>
@@ -31224,7 +31706,7 @@
         <v>4927</v>
       </c>
     </row>
-    <row r="469" spans="1:10">
+    <row r="469" spans="1:10" ht="23.25">
       <c r="A469" s="29" t="s">
         <v>3378</v>
       </c>
@@ -31256,7 +31738,7 @@
         <v>3827</v>
       </c>
     </row>
-    <row r="470" spans="1:10">
+    <row r="470" spans="1:10" ht="23.25">
       <c r="A470" s="29" t="s">
         <v>3386</v>
       </c>
@@ -31288,7 +31770,7 @@
         <v>3826</v>
       </c>
     </row>
-    <row r="471" spans="1:10">
+    <row r="471" spans="1:10" ht="23.25">
       <c r="A471" s="29" t="s">
         <v>4928</v>
       </c>
@@ -31320,7 +31802,7 @@
         <v>4937</v>
       </c>
     </row>
-    <row r="472" spans="1:10">
+    <row r="472" spans="1:10" ht="23.25">
       <c r="A472" s="29" t="s">
         <v>4938</v>
       </c>
@@ -31352,7 +31834,7 @@
         <v>4947</v>
       </c>
     </row>
-    <row r="473" spans="1:10" ht="25">
+    <row r="473" spans="1:10" ht="23.25">
       <c r="A473" s="29" t="s">
         <v>4948</v>
       </c>
@@ -31544,7 +32026,7 @@
         <v>4203</v>
       </c>
     </row>
-    <row r="479" spans="1:10" ht="25">
+    <row r="479" spans="1:10" ht="34.5">
       <c r="A479" s="29" t="s">
         <v>4166</v>
       </c>
@@ -31576,7 +32058,7 @@
         <v>4204</v>
       </c>
     </row>
-    <row r="480" spans="1:10">
+    <row r="480" spans="1:10" ht="23.25">
       <c r="A480" s="29" t="s">
         <v>4168</v>
       </c>
@@ -31608,7 +32090,7 @@
         <v>4205</v>
       </c>
     </row>
-    <row r="481" spans="1:10">
+    <row r="481" spans="1:10" ht="23.25">
       <c r="A481" s="29" t="s">
         <v>4170</v>
       </c>
@@ -31768,7 +32250,7 @@
         <v>4299</v>
       </c>
     </row>
-    <row r="486" spans="1:10" ht="49">
+    <row r="486" spans="1:10" ht="68.25">
       <c r="A486" s="29" t="s">
         <v>4249</v>
       </c>
@@ -31800,7 +32282,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="487" spans="1:10" ht="97">
+    <row r="487" spans="1:10" ht="124.5">
       <c r="A487" s="29" t="s">
         <v>4251</v>
       </c>
@@ -31832,7 +32314,7 @@
         <v>4301</v>
       </c>
     </row>
-    <row r="488" spans="1:10" ht="97">
+    <row r="488" spans="1:10" ht="124.5">
       <c r="A488" s="29" t="s">
         <v>4273</v>
       </c>
@@ -31864,7 +32346,7 @@
         <v>4302</v>
       </c>
     </row>
-    <row r="489" spans="1:10" ht="61">
+    <row r="489" spans="1:10" ht="79.5">
       <c r="A489" s="29" t="s">
         <v>4275</v>
       </c>
@@ -31896,7 +32378,7 @@
         <v>4303</v>
       </c>
     </row>
-    <row r="490" spans="1:10" ht="61">
+    <row r="490" spans="1:10" ht="79.5">
       <c r="A490" s="29" t="s">
         <v>4277</v>
       </c>
@@ -31928,7 +32410,7 @@
         <v>4342</v>
       </c>
     </row>
-    <row r="491" spans="1:10" ht="85">
+    <row r="491" spans="1:10" ht="102">
       <c r="A491" s="29" t="s">
         <v>4253</v>
       </c>
@@ -31960,7 +32442,7 @@
         <v>4343</v>
       </c>
     </row>
-    <row r="492" spans="1:10" ht="49">
+    <row r="492" spans="1:10" ht="68.25">
       <c r="A492" s="29" t="s">
         <v>4255</v>
       </c>
@@ -31992,7 +32474,7 @@
         <v>4344</v>
       </c>
     </row>
-    <row r="493" spans="1:10" ht="85">
+    <row r="493" spans="1:10" ht="113.25">
       <c r="A493" s="29" t="s">
         <v>4257</v>
       </c>
@@ -32024,7 +32506,7 @@
         <v>4968</v>
       </c>
     </row>
-    <row r="494" spans="1:10" ht="85">
+    <row r="494" spans="1:10" ht="102">
       <c r="A494" s="29" t="s">
         <v>4261</v>
       </c>
@@ -32056,7 +32538,7 @@
         <v>4345</v>
       </c>
     </row>
-    <row r="495" spans="1:10" ht="73">
+    <row r="495" spans="1:10" ht="90.75">
       <c r="A495" s="29" t="s">
         <v>4259</v>
       </c>
@@ -32088,7 +32570,7 @@
         <v>4346</v>
       </c>
     </row>
-    <row r="496" spans="1:10" ht="37">
+    <row r="496" spans="1:10" ht="45.75">
       <c r="A496" s="29" t="s">
         <v>4263</v>
       </c>
@@ -32120,7 +32602,7 @@
         <v>4347</v>
       </c>
     </row>
-    <row r="497" spans="1:10" ht="73">
+    <row r="497" spans="1:10" ht="79.5">
       <c r="A497" s="29" t="s">
         <v>4265</v>
       </c>
@@ -32184,7 +32666,7 @@
         <v>4373</v>
       </c>
     </row>
-    <row r="499" spans="1:10" ht="49">
+    <row r="499" spans="1:10" ht="45.75">
       <c r="A499" s="29" t="s">
         <v>4269</v>
       </c>
@@ -32216,7 +32698,7 @@
         <v>4374</v>
       </c>
     </row>
-    <row r="500" spans="1:10" ht="25">
+    <row r="500" spans="1:10" ht="34.5">
       <c r="A500" s="29" t="s">
         <v>4271</v>
       </c>
@@ -32248,7 +32730,7 @@
         <v>4375</v>
       </c>
     </row>
-    <row r="501" spans="1:10" ht="37">
+    <row r="501" spans="1:10" ht="34.5">
       <c r="A501" s="29" t="s">
         <v>4400</v>
       </c>
@@ -32280,7 +32762,7 @@
         <v>4421</v>
       </c>
     </row>
-    <row r="502" spans="1:10" ht="25">
+    <row r="502" spans="1:10" ht="34.5">
       <c r="A502" s="29" t="s">
         <v>4401</v>
       </c>
@@ -32504,7 +32986,7 @@
         <v>4511</v>
       </c>
     </row>
-    <row r="509" spans="1:10">
+    <row r="509" spans="1:10" ht="23.25">
       <c r="A509" s="29" t="s">
         <v>4435</v>
       </c>
@@ -32696,7 +33178,7 @@
         <v>4519</v>
       </c>
     </row>
-    <row r="515" spans="1:10" ht="37">
+    <row r="515" spans="1:10" ht="34.5">
       <c r="A515" s="6" t="s">
         <v>4441</v>
       </c>
@@ -32760,7 +33242,7 @@
         <v>4520</v>
       </c>
     </row>
-    <row r="517" spans="1:10" ht="37">
+    <row r="517" spans="1:10" ht="45.75">
       <c r="A517" s="6" t="s">
         <v>4556</v>
       </c>
@@ -32792,7 +33274,7 @@
         <v>4603</v>
       </c>
     </row>
-    <row r="518" spans="1:10" ht="25">
+    <row r="518" spans="1:10" ht="34.5">
       <c r="A518" s="6" t="s">
         <v>4557</v>
       </c>
@@ -32824,7 +33306,7 @@
         <v>4611</v>
       </c>
     </row>
-    <row r="519" spans="1:10" ht="25">
+    <row r="519" spans="1:10" ht="34.5">
       <c r="A519" s="6" t="s">
         <v>4558</v>
       </c>
@@ -32856,7 +33338,7 @@
         <v>4619</v>
       </c>
     </row>
-    <row r="520" spans="1:10" ht="25">
+    <row r="520" spans="1:10" ht="34.5">
       <c r="A520" s="6" t="s">
         <v>4559</v>
       </c>
@@ -32888,7 +33370,7 @@
         <v>4627</v>
       </c>
     </row>
-    <row r="521" spans="1:10" ht="109">
+    <row r="521" spans="1:10" ht="135.75">
       <c r="A521" s="6" t="s">
         <v>4279</v>
       </c>
@@ -32984,7 +33466,7 @@
         <v>4976</v>
       </c>
     </row>
-    <row r="524" spans="1:10" ht="25">
+    <row r="524" spans="1:10" ht="23.25">
       <c r="A524" s="6" t="s">
         <v>4977</v>
       </c>
@@ -33016,7 +33498,7 @@
         <v>4980</v>
       </c>
     </row>
-    <row r="525" spans="1:10" ht="25">
+    <row r="525" spans="1:10" ht="23.25">
       <c r="A525" s="29" t="s">
         <v>4981</v>
       </c>
@@ -33048,7 +33530,7 @@
         <v>4984</v>
       </c>
     </row>
-    <row r="526" spans="1:10" ht="25">
+    <row r="526" spans="1:10" ht="34.5">
       <c r="A526" s="29" t="s">
         <v>4985</v>
       </c>
@@ -33080,7 +33562,7 @@
         <v>4988</v>
       </c>
     </row>
-    <row r="527" spans="1:10" ht="25">
+    <row r="527" spans="1:10" ht="23.25">
       <c r="A527" s="29" t="s">
         <v>4989</v>
       </c>
@@ -33112,7 +33594,7 @@
         <v>4992</v>
       </c>
     </row>
-    <row r="528" spans="1:10" ht="25">
+    <row r="528" spans="1:10" ht="23.25">
       <c r="A528" s="29" t="s">
         <v>4993</v>
       </c>
@@ -33144,7 +33626,7 @@
         <v>4996</v>
       </c>
     </row>
-    <row r="529" spans="1:10">
+    <row r="529" spans="1:10" ht="23.25">
       <c r="A529" s="29" t="s">
         <v>4568</v>
       </c>
@@ -33240,7 +33722,7 @@
         <v>4666</v>
       </c>
     </row>
-    <row r="532" spans="1:10" ht="25">
+    <row r="532" spans="1:10" ht="23.25">
       <c r="A532" s="29" t="s">
         <v>4572</v>
       </c>
@@ -33272,7 +33754,7 @@
         <v>4667</v>
       </c>
     </row>
-    <row r="533" spans="1:10" ht="25">
+    <row r="533" spans="1:10" ht="23.25">
       <c r="A533" s="29" t="s">
         <v>4573</v>
       </c>
@@ -33304,7 +33786,7 @@
         <v>4668</v>
       </c>
     </row>
-    <row r="534" spans="1:10" ht="25">
+    <row r="534" spans="1:10" ht="23.25">
       <c r="A534" s="29" t="s">
         <v>4574</v>
       </c>
@@ -33336,7 +33818,7 @@
         <v>4669</v>
       </c>
     </row>
-    <row r="535" spans="1:10" ht="25">
+    <row r="535" spans="1:10" ht="23.25">
       <c r="A535" s="29" t="s">
         <v>4575</v>
       </c>
@@ -33368,7 +33850,7 @@
         <v>4670</v>
       </c>
     </row>
-    <row r="536" spans="1:10" ht="25">
+    <row r="536" spans="1:10" ht="23.25">
       <c r="A536" s="29" t="s">
         <v>4576</v>
       </c>
@@ -33400,7 +33882,7 @@
         <v>4422</v>
       </c>
     </row>
-    <row r="537" spans="1:10" ht="25">
+    <row r="537" spans="1:10" ht="23.25">
       <c r="A537" s="29" t="s">
         <v>4577</v>
       </c>
@@ -33496,7 +33978,7 @@
         <v>4673</v>
       </c>
     </row>
-    <row r="540" spans="1:10" ht="37">
+    <row r="540" spans="1:10" ht="34.5">
       <c r="A540" s="29" t="s">
         <v>4580</v>
       </c>
@@ -33560,7 +34042,7 @@
         <v>4675</v>
       </c>
     </row>
-    <row r="542" spans="1:10" ht="25">
+    <row r="542" spans="1:10" ht="23.25">
       <c r="A542" s="29" t="s">
         <v>4582</v>
       </c>
@@ -33624,357 +34106,707 @@
         <v>5067</v>
       </c>
     </row>
-    <row r="544" spans="1:10">
-      <c r="A544" s="33" t="s">
+    <row r="544" spans="1:10" ht="23.25">
+      <c r="A544" s="29" t="s">
         <v>5068</v>
       </c>
-      <c r="B544" s="34" t="s">
+      <c r="B544" s="27" t="s">
         <v>5090</v>
       </c>
-      <c r="C544" s="35"/>
-      <c r="D544" s="35"/>
-      <c r="E544" s="35"/>
-      <c r="F544" s="35"/>
-      <c r="G544" s="36"/>
-      <c r="H544" s="35"/>
-      <c r="I544" s="37"/>
-      <c r="J544" s="37"/>
-    </row>
-    <row r="545" spans="1:10">
-      <c r="A545" s="33" t="s">
+      <c r="C544" s="9" t="s">
+        <v>5111</v>
+      </c>
+      <c r="D544" s="9" t="s">
+        <v>5149</v>
+      </c>
+      <c r="E544" s="9" t="s">
+        <v>5151</v>
+      </c>
+      <c r="F544" s="9" t="s">
+        <v>5184</v>
+      </c>
+      <c r="G544" s="31" t="s">
+        <v>5225</v>
+      </c>
+      <c r="H544" s="36" t="s">
+        <v>5263</v>
+      </c>
+      <c r="I544" s="12" t="s">
+        <v>5186</v>
+      </c>
+      <c r="J544" s="12" t="s">
+        <v>5223</v>
+      </c>
+    </row>
+    <row r="545" spans="1:10" ht="23.25">
+      <c r="A545" s="29" t="s">
         <v>5069</v>
       </c>
-      <c r="B545" s="34" t="s">
+      <c r="B545" s="27" t="s">
         <v>5091</v>
       </c>
-      <c r="C545" s="35"/>
-      <c r="D545" s="35"/>
-      <c r="E545" s="35"/>
-      <c r="F545" s="35"/>
-      <c r="G545" s="36"/>
-      <c r="H545" s="35"/>
-      <c r="I545" s="37"/>
-      <c r="J545" s="37"/>
-    </row>
-    <row r="546" spans="1:10">
-      <c r="A546" s="33" t="s">
+      <c r="C545" s="9" t="s">
+        <v>5112</v>
+      </c>
+      <c r="D545" s="9" t="s">
+        <v>5150</v>
+      </c>
+      <c r="E545" s="9" t="s">
+        <v>5152</v>
+      </c>
+      <c r="F545" s="9" t="s">
+        <v>5185</v>
+      </c>
+      <c r="G545" s="31" t="s">
+        <v>5226</v>
+      </c>
+      <c r="H545" s="36" t="s">
+        <v>5264</v>
+      </c>
+      <c r="I545" s="12" t="s">
+        <v>5187</v>
+      </c>
+      <c r="J545" s="12" t="s">
+        <v>5224</v>
+      </c>
+    </row>
+    <row r="546" spans="1:10" ht="135.75">
+      <c r="A546" s="29" t="s">
         <v>5070</v>
       </c>
-      <c r="B546" s="34" t="s">
+      <c r="B546" s="35" t="s">
+        <v>5265</v>
+      </c>
+      <c r="C546" s="9" t="s">
+        <v>5267</v>
+      </c>
+      <c r="D546" s="9" t="s">
+        <v>5266</v>
+      </c>
+      <c r="E546" s="9" t="s">
+        <v>5268</v>
+      </c>
+      <c r="F546" s="9" t="s">
+        <v>5269</v>
+      </c>
+      <c r="G546" s="33" t="s">
+        <v>5273</v>
+      </c>
+      <c r="H546" s="9" t="s">
+        <v>5272</v>
+      </c>
+      <c r="I546" s="12" t="s">
+        <v>5271</v>
+      </c>
+      <c r="J546" s="12" t="s">
+        <v>5270</v>
+      </c>
+    </row>
+    <row r="547" spans="1:10" ht="23.25">
+      <c r="A547" s="29" t="s">
+        <v>5071</v>
+      </c>
+      <c r="B547" s="34" t="s">
         <v>5092</v>
       </c>
-      <c r="C546" s="35"/>
-      <c r="D546" s="35"/>
-      <c r="E546" s="35"/>
-      <c r="F546" s="35"/>
-      <c r="G546" s="36"/>
-      <c r="H546" s="35"/>
-      <c r="I546" s="37"/>
-      <c r="J546" s="37"/>
-    </row>
-    <row r="547" spans="1:10">
-      <c r="A547" s="33" t="s">
-        <v>5071</v>
-      </c>
-      <c r="B547" s="38" t="s">
+      <c r="C547" s="9" t="s">
+        <v>5113</v>
+      </c>
+      <c r="D547" s="9" t="s">
+        <v>5131</v>
+      </c>
+      <c r="E547" s="9" t="s">
+        <v>5153</v>
+      </c>
+      <c r="F547" s="9" t="s">
+        <v>5166</v>
+      </c>
+      <c r="G547" s="31" t="s">
+        <v>5227</v>
+      </c>
+      <c r="H547" s="36" t="s">
+        <v>5245</v>
+      </c>
+      <c r="I547" s="12"/>
+      <c r="J547" s="12" t="s">
+        <v>5206</v>
+      </c>
+    </row>
+    <row r="548" spans="1:10">
+      <c r="A548" s="29" t="s">
+        <v>5072</v>
+      </c>
+      <c r="B548" s="34" t="s">
         <v>5093</v>
       </c>
-      <c r="C547" s="35"/>
-      <c r="D547" s="35"/>
-      <c r="E547" s="35"/>
-      <c r="F547" s="35"/>
-      <c r="G547" s="36"/>
-      <c r="H547" s="35"/>
-      <c r="I547" s="37"/>
-      <c r="J547" s="37"/>
-    </row>
-    <row r="548" spans="1:10">
-      <c r="A548" s="33" t="s">
-        <v>5072</v>
-      </c>
-      <c r="B548" s="38" t="s">
+      <c r="C548" s="9" t="s">
+        <v>5114</v>
+      </c>
+      <c r="D548" s="9" t="s">
+        <v>5132</v>
+      </c>
+      <c r="E548" s="9" t="s">
+        <v>5154</v>
+      </c>
+      <c r="F548" s="9" t="s">
+        <v>5167</v>
+      </c>
+      <c r="G548" s="31" t="s">
+        <v>5228</v>
+      </c>
+      <c r="H548" s="36" t="s">
+        <v>5246</v>
+      </c>
+      <c r="I548" s="12" t="s">
+        <v>5188</v>
+      </c>
+      <c r="J548" s="12" t="s">
+        <v>5207</v>
+      </c>
+    </row>
+    <row r="549" spans="1:10">
+      <c r="A549" s="29" t="s">
+        <v>5073</v>
+      </c>
+      <c r="B549" s="34" t="s">
         <v>5094</v>
       </c>
-      <c r="C548" s="35"/>
-      <c r="D548" s="35"/>
-      <c r="E548" s="35"/>
-      <c r="F548" s="35"/>
-      <c r="G548" s="36"/>
-      <c r="H548" s="35"/>
-      <c r="I548" s="37"/>
-      <c r="J548" s="37"/>
-    </row>
-    <row r="549" spans="1:10">
-      <c r="A549" s="33" t="s">
-        <v>5073</v>
-      </c>
-      <c r="B549" s="38" t="s">
+      <c r="C549" s="9" t="s">
+        <v>5115</v>
+      </c>
+      <c r="D549" s="9" t="s">
+        <v>5133</v>
+      </c>
+      <c r="E549" s="9" t="s">
+        <v>5155</v>
+      </c>
+      <c r="F549" s="9" t="s">
+        <v>5168</v>
+      </c>
+      <c r="G549" s="31" t="s">
+        <v>5229</v>
+      </c>
+      <c r="H549" s="36" t="s">
+        <v>5247</v>
+      </c>
+      <c r="I549" s="12" t="s">
+        <v>5189</v>
+      </c>
+      <c r="J549" s="12" t="s">
+        <v>5208</v>
+      </c>
+    </row>
+    <row r="550" spans="1:10">
+      <c r="A550" s="29" t="s">
+        <v>5074</v>
+      </c>
+      <c r="B550" s="34" t="s">
         <v>5095</v>
       </c>
-      <c r="C549" s="35"/>
-      <c r="D549" s="35"/>
-      <c r="E549" s="35"/>
-      <c r="F549" s="35"/>
-      <c r="G549" s="36"/>
-      <c r="H549" s="35"/>
-      <c r="I549" s="37"/>
-      <c r="J549" s="37"/>
-    </row>
-    <row r="550" spans="1:10">
-      <c r="A550" s="33" t="s">
-        <v>5074</v>
-      </c>
-      <c r="B550" s="38" t="s">
+      <c r="C550" s="9" t="s">
+        <v>5116</v>
+      </c>
+      <c r="D550" s="9" t="s">
+        <v>5134</v>
+      </c>
+      <c r="E550" s="9" t="s">
+        <v>5156</v>
+      </c>
+      <c r="F550" s="9" t="s">
+        <v>5169</v>
+      </c>
+      <c r="G550" s="31" t="s">
+        <v>5230</v>
+      </c>
+      <c r="H550" s="36" t="s">
+        <v>5248</v>
+      </c>
+      <c r="I550" s="12" t="s">
+        <v>5190</v>
+      </c>
+      <c r="J550" s="12" t="s">
+        <v>5209</v>
+      </c>
+    </row>
+    <row r="551" spans="1:10">
+      <c r="A551" s="29" t="s">
+        <v>5075</v>
+      </c>
+      <c r="B551" s="34" t="s">
         <v>5096</v>
       </c>
-      <c r="C550" s="35"/>
-      <c r="D550" s="35"/>
-      <c r="E550" s="35"/>
-      <c r="F550" s="35"/>
-      <c r="G550" s="36"/>
-      <c r="H550" s="35"/>
-      <c r="I550" s="37"/>
-      <c r="J550" s="37"/>
-    </row>
-    <row r="551" spans="1:10">
-      <c r="A551" s="33" t="s">
-        <v>5075</v>
-      </c>
-      <c r="B551" s="38" t="s">
+      <c r="C551" s="9" t="s">
+        <v>5117</v>
+      </c>
+      <c r="D551" s="9" t="s">
+        <v>5135</v>
+      </c>
+      <c r="E551" s="9" t="s">
+        <v>5157</v>
+      </c>
+      <c r="F551" s="9" t="s">
+        <v>5170</v>
+      </c>
+      <c r="G551" s="31" t="s">
+        <v>5231</v>
+      </c>
+      <c r="H551" s="36" t="s">
+        <v>5249</v>
+      </c>
+      <c r="I551" s="12" t="s">
+        <v>5191</v>
+      </c>
+      <c r="J551" s="12" t="s">
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="552" spans="1:10">
+      <c r="A552" s="29" t="s">
+        <v>5076</v>
+      </c>
+      <c r="B552" s="34" t="s">
         <v>5097</v>
       </c>
-      <c r="C551" s="35"/>
-      <c r="D551" s="35"/>
-      <c r="E551" s="35"/>
-      <c r="F551" s="35"/>
-      <c r="G551" s="36"/>
-      <c r="H551" s="35"/>
-      <c r="I551" s="37"/>
-      <c r="J551" s="37"/>
-    </row>
-    <row r="552" spans="1:10">
-      <c r="A552" s="33" t="s">
-        <v>5076</v>
-      </c>
-      <c r="B552" s="38" t="s">
+      <c r="C552" s="9" t="s">
+        <v>5118</v>
+      </c>
+      <c r="D552" s="9" t="s">
+        <v>5136</v>
+      </c>
+      <c r="E552" s="9" t="s">
+        <v>5158</v>
+      </c>
+      <c r="F552" s="9" t="s">
+        <v>5171</v>
+      </c>
+      <c r="G552" s="31" t="s">
+        <v>5232</v>
+      </c>
+      <c r="H552" s="36" t="s">
+        <v>5250</v>
+      </c>
+      <c r="I552" s="12" t="s">
+        <v>5192</v>
+      </c>
+      <c r="J552" s="12" t="s">
+        <v>5211</v>
+      </c>
+    </row>
+    <row r="553" spans="1:10">
+      <c r="A553" s="29" t="s">
+        <v>5077</v>
+      </c>
+      <c r="B553" s="27" t="s">
         <v>5098</v>
       </c>
-      <c r="C552" s="35"/>
-      <c r="D552" s="35"/>
-      <c r="E552" s="35"/>
-      <c r="F552" s="35"/>
-      <c r="G552" s="36"/>
-      <c r="H552" s="35"/>
-      <c r="I552" s="37"/>
-      <c r="J552" s="37"/>
-    </row>
-    <row r="553" spans="1:10">
-      <c r="A553" s="33" t="s">
-        <v>5077</v>
-      </c>
-      <c r="B553" s="34" t="s">
+      <c r="C553" s="9" t="s">
+        <v>5119</v>
+      </c>
+      <c r="D553" s="9" t="s">
+        <v>5137</v>
+      </c>
+      <c r="E553" s="9" t="s">
+        <v>5119</v>
+      </c>
+      <c r="F553" s="9" t="s">
+        <v>5172</v>
+      </c>
+      <c r="G553" s="31" t="s">
+        <v>5233</v>
+      </c>
+      <c r="H553" s="36" t="s">
+        <v>5098</v>
+      </c>
+      <c r="I553" s="12" t="s">
+        <v>5193</v>
+      </c>
+      <c r="J553" s="12" t="s">
+        <v>5212</v>
+      </c>
+    </row>
+    <row r="554" spans="1:10">
+      <c r="A554" s="29" t="s">
+        <v>5078</v>
+      </c>
+      <c r="B554" s="27" t="s">
         <v>5099</v>
       </c>
-      <c r="C553" s="35"/>
-      <c r="D553" s="35"/>
-      <c r="E553" s="35"/>
-      <c r="F553" s="35"/>
-      <c r="G553" s="36"/>
-      <c r="H553" s="35"/>
-      <c r="I553" s="37"/>
-      <c r="J553" s="37"/>
-    </row>
-    <row r="554" spans="1:10">
-      <c r="A554" s="33" t="s">
-        <v>5078</v>
-      </c>
-      <c r="B554" s="34" t="s">
+      <c r="C554" s="9" t="s">
+        <v>5120</v>
+      </c>
+      <c r="D554" s="9" t="s">
+        <v>5138</v>
+      </c>
+      <c r="E554" s="9" t="s">
+        <v>5159</v>
+      </c>
+      <c r="F554" s="9" t="s">
+        <v>5173</v>
+      </c>
+      <c r="G554" s="31" t="s">
+        <v>5234</v>
+      </c>
+      <c r="H554" s="36" t="s">
+        <v>5251</v>
+      </c>
+      <c r="I554" s="12" t="s">
+        <v>5194</v>
+      </c>
+      <c r="J554" s="12" t="s">
+        <v>5213</v>
+      </c>
+    </row>
+    <row r="555" spans="1:10" ht="23.25">
+      <c r="A555" s="29" t="s">
+        <v>5079</v>
+      </c>
+      <c r="B555" s="34" t="s">
         <v>5100</v>
       </c>
-      <c r="C554" s="35"/>
-      <c r="D554" s="35"/>
-      <c r="E554" s="35"/>
-      <c r="F554" s="35"/>
-      <c r="G554" s="36"/>
-      <c r="H554" s="35"/>
-      <c r="I554" s="37"/>
-      <c r="J554" s="37"/>
-    </row>
-    <row r="555" spans="1:10">
-      <c r="A555" s="33" t="s">
-        <v>5079</v>
-      </c>
-      <c r="B555" s="38" t="s">
+      <c r="C555" s="9" t="s">
+        <v>5121</v>
+      </c>
+      <c r="D555" s="9" t="s">
+        <v>5139</v>
+      </c>
+      <c r="E555" s="9" t="s">
+        <v>5160</v>
+      </c>
+      <c r="F555" s="9" t="s">
+        <v>5174</v>
+      </c>
+      <c r="G555" s="31" t="s">
+        <v>5235</v>
+      </c>
+      <c r="H555" s="36" t="s">
+        <v>5252</v>
+      </c>
+      <c r="I555" s="12" t="s">
+        <v>5205</v>
+      </c>
+      <c r="J555" s="12" t="s">
+        <v>5214</v>
+      </c>
+    </row>
+    <row r="556" spans="1:10">
+      <c r="A556" s="29" t="s">
+        <v>5080</v>
+      </c>
+      <c r="B556" s="27" t="s">
         <v>5101</v>
       </c>
-      <c r="C555" s="35"/>
-      <c r="D555" s="35"/>
-      <c r="E555" s="35"/>
-      <c r="F555" s="35"/>
-      <c r="G555" s="36"/>
-      <c r="H555" s="35"/>
-      <c r="I555" s="37"/>
-      <c r="J555" s="37"/>
-    </row>
-    <row r="556" spans="1:10">
-      <c r="A556" s="33" t="s">
-        <v>5080</v>
-      </c>
-      <c r="B556" s="34" t="s">
+      <c r="C556" s="9" t="s">
+        <v>5122</v>
+      </c>
+      <c r="D556" s="9" t="s">
+        <v>5140</v>
+      </c>
+      <c r="E556" s="9" t="s">
+        <v>5161</v>
+      </c>
+      <c r="F556" s="9" t="s">
+        <v>5175</v>
+      </c>
+      <c r="G556" s="31" t="s">
+        <v>5236</v>
+      </c>
+      <c r="H556" s="36" t="s">
+        <v>5253</v>
+      </c>
+      <c r="I556" s="12" t="s">
+        <v>5195</v>
+      </c>
+      <c r="J556" s="12" t="s">
+        <v>5215</v>
+      </c>
+    </row>
+    <row r="557" spans="1:10" ht="23.25">
+      <c r="A557" s="29" t="s">
+        <v>5081</v>
+      </c>
+      <c r="B557" s="27" t="s">
         <v>5102</v>
       </c>
-      <c r="C556" s="35"/>
-      <c r="D556" s="35"/>
-      <c r="E556" s="35"/>
-      <c r="F556" s="35"/>
-      <c r="G556" s="36"/>
-      <c r="H556" s="35"/>
-      <c r="I556" s="37"/>
-      <c r="J556" s="37"/>
-    </row>
-    <row r="557" spans="1:10">
-      <c r="A557" s="33" t="s">
-        <v>5081</v>
-      </c>
-      <c r="B557" s="34" t="s">
+      <c r="C557" s="9" t="s">
+        <v>5123</v>
+      </c>
+      <c r="D557" s="9" t="s">
+        <v>5141</v>
+      </c>
+      <c r="E557" s="9" t="s">
+        <v>5162</v>
+      </c>
+      <c r="F557" s="9" t="s">
+        <v>5176</v>
+      </c>
+      <c r="G557" s="31" t="s">
+        <v>5237</v>
+      </c>
+      <c r="H557" s="36" t="s">
+        <v>5254</v>
+      </c>
+      <c r="I557" s="12" t="s">
+        <v>5204</v>
+      </c>
+      <c r="J557" s="12" t="s">
+        <v>5216</v>
+      </c>
+    </row>
+    <row r="558" spans="1:10">
+      <c r="A558" s="29" t="s">
+        <v>5082</v>
+      </c>
+      <c r="B558" s="27" t="s">
         <v>5103</v>
       </c>
-      <c r="C557" s="35"/>
-      <c r="D557" s="35"/>
-      <c r="E557" s="35"/>
-      <c r="F557" s="35"/>
-      <c r="G557" s="36"/>
-      <c r="H557" s="35"/>
-      <c r="I557" s="37"/>
-      <c r="J557" s="37"/>
-    </row>
-    <row r="558" spans="1:10">
-      <c r="A558" s="33" t="s">
-        <v>5082</v>
-      </c>
-      <c r="B558" s="34" t="s">
+      <c r="C558" s="9" t="s">
+        <v>5124</v>
+      </c>
+      <c r="D558" s="9" t="s">
+        <v>5142</v>
+      </c>
+      <c r="E558" s="9" t="s">
+        <v>5163</v>
+      </c>
+      <c r="F558" s="9" t="s">
+        <v>5177</v>
+      </c>
+      <c r="G558" s="31" t="s">
+        <v>5238</v>
+      </c>
+      <c r="H558" s="36" t="s">
+        <v>5255</v>
+      </c>
+      <c r="I558" s="12" t="s">
+        <v>5203</v>
+      </c>
+      <c r="J558" s="12" t="s">
+        <v>5217</v>
+      </c>
+    </row>
+    <row r="559" spans="1:10">
+      <c r="A559" s="29" t="s">
+        <v>5083</v>
+      </c>
+      <c r="B559" s="27" t="s">
         <v>5104</v>
       </c>
-      <c r="C558" s="35"/>
-      <c r="D558" s="35"/>
-      <c r="E558" s="35"/>
-      <c r="F558" s="35"/>
-      <c r="G558" s="36"/>
-      <c r="H558" s="35"/>
-      <c r="I558" s="37"/>
-      <c r="J558" s="37"/>
-    </row>
-    <row r="559" spans="1:10">
-      <c r="A559" s="33" t="s">
-        <v>5083</v>
-      </c>
-      <c r="B559" s="34" t="s">
+      <c r="C559" s="9" t="s">
+        <v>5125</v>
+      </c>
+      <c r="D559" s="9" t="s">
+        <v>5143</v>
+      </c>
+      <c r="E559" s="9" t="s">
+        <v>5164</v>
+      </c>
+      <c r="F559" s="9" t="s">
+        <v>5178</v>
+      </c>
+      <c r="G559" s="31" t="s">
+        <v>5239</v>
+      </c>
+      <c r="H559" s="36" t="s">
+        <v>5256</v>
+      </c>
+      <c r="I559" s="12" t="s">
+        <v>5196</v>
+      </c>
+      <c r="J559" s="12" t="s">
+        <v>5218</v>
+      </c>
+    </row>
+    <row r="560" spans="1:10">
+      <c r="A560" s="29" t="s">
+        <v>5084</v>
+      </c>
+      <c r="B560" s="27" t="s">
         <v>5105</v>
       </c>
-      <c r="C559" s="35"/>
-      <c r="D559" s="35"/>
-      <c r="E559" s="35"/>
-      <c r="F559" s="35"/>
-      <c r="G559" s="36"/>
-      <c r="H559" s="35"/>
-      <c r="I559" s="37"/>
-      <c r="J559" s="37"/>
-    </row>
-    <row r="560" spans="1:10">
-      <c r="A560" s="33" t="s">
-        <v>5084</v>
-      </c>
-      <c r="B560" s="34" t="s">
+      <c r="C560" s="9" t="s">
+        <v>5126</v>
+      </c>
+      <c r="D560" s="9" t="s">
+        <v>5144</v>
+      </c>
+      <c r="E560" s="9" t="s">
+        <v>5126</v>
+      </c>
+      <c r="F560" s="9" t="s">
+        <v>5179</v>
+      </c>
+      <c r="G560" s="31" t="s">
+        <v>5240</v>
+      </c>
+      <c r="H560" s="36" t="s">
+        <v>5257</v>
+      </c>
+      <c r="I560" s="12" t="s">
+        <v>5197</v>
+      </c>
+      <c r="J560" s="12" t="s">
+        <v>5197</v>
+      </c>
+    </row>
+    <row r="561" spans="1:10" ht="23.25">
+      <c r="A561" s="29" t="s">
+        <v>5085</v>
+      </c>
+      <c r="B561" s="34" t="s">
         <v>5106</v>
       </c>
-      <c r="C560" s="35"/>
-      <c r="D560" s="35"/>
-      <c r="E560" s="35"/>
-      <c r="F560" s="35"/>
-      <c r="G560" s="36"/>
-      <c r="H560" s="35"/>
-      <c r="I560" s="37"/>
-      <c r="J560" s="37"/>
-    </row>
-    <row r="561" spans="1:10">
-      <c r="A561" s="33" t="s">
-        <v>5085</v>
-      </c>
-      <c r="B561" s="38" t="s">
+      <c r="C561" s="9" t="s">
+        <v>5127</v>
+      </c>
+      <c r="D561" s="9" t="s">
+        <v>5145</v>
+      </c>
+      <c r="E561" s="9" t="s">
+        <v>5165</v>
+      </c>
+      <c r="F561" s="9" t="s">
+        <v>5180</v>
+      </c>
+      <c r="G561" s="31" t="s">
+        <v>5241</v>
+      </c>
+      <c r="H561" s="36" t="s">
+        <v>5258</v>
+      </c>
+      <c r="I561" s="12" t="s">
+        <v>5200</v>
+      </c>
+      <c r="J561" s="12" t="s">
+        <v>5219</v>
+      </c>
+    </row>
+    <row r="562" spans="1:10">
+      <c r="A562" s="29" t="s">
+        <v>5086</v>
+      </c>
+      <c r="B562" s="27" t="s">
         <v>5107</v>
       </c>
-      <c r="C561" s="35"/>
-      <c r="D561" s="35"/>
-      <c r="E561" s="35"/>
-      <c r="F561" s="35"/>
-      <c r="G561" s="36"/>
-      <c r="H561" s="35"/>
-      <c r="I561" s="37"/>
-      <c r="J561" s="37"/>
-    </row>
-    <row r="562" spans="1:10">
-      <c r="A562" s="33" t="s">
-        <v>5086</v>
-      </c>
-      <c r="B562" s="34" t="s">
+      <c r="C562" s="9" t="s">
+        <v>5128</v>
+      </c>
+      <c r="D562" s="9" t="s">
+        <v>5146</v>
+      </c>
+      <c r="E562" s="9" t="s">
+        <v>5128</v>
+      </c>
+      <c r="F562" s="9" t="s">
+        <v>5181</v>
+      </c>
+      <c r="G562" s="31" t="s">
+        <v>5242</v>
+      </c>
+      <c r="H562" s="36" t="s">
+        <v>5259</v>
+      </c>
+      <c r="I562" s="12" t="s">
+        <v>5198</v>
+      </c>
+      <c r="J562" s="12" t="s">
+        <v>5220</v>
+      </c>
+    </row>
+    <row r="563" spans="1:10">
+      <c r="A563" s="29" t="s">
+        <v>5087</v>
+      </c>
+      <c r="B563" s="27" t="s">
         <v>5108</v>
       </c>
-      <c r="C562" s="35"/>
-      <c r="D562" s="35"/>
-      <c r="E562" s="35"/>
-      <c r="F562" s="35"/>
-      <c r="G562" s="36"/>
-      <c r="H562" s="35"/>
-      <c r="I562" s="37"/>
-      <c r="J562" s="37"/>
-    </row>
-    <row r="563" spans="1:10">
-      <c r="A563" s="33" t="s">
-        <v>5087</v>
-      </c>
-      <c r="B563" s="34" t="s">
+      <c r="C563" s="9" t="s">
+        <v>5129</v>
+      </c>
+      <c r="D563" s="9" t="s">
+        <v>5147</v>
+      </c>
+      <c r="E563" s="9" t="s">
+        <v>5129</v>
+      </c>
+      <c r="F563" s="9" t="s">
+        <v>5182</v>
+      </c>
+      <c r="G563" s="31" t="s">
+        <v>5243</v>
+      </c>
+      <c r="H563" s="36" t="s">
+        <v>5260</v>
+      </c>
+      <c r="I563" s="12" t="s">
+        <v>5199</v>
+      </c>
+      <c r="J563" s="12" t="s">
+        <v>5221</v>
+      </c>
+    </row>
+    <row r="564" spans="1:10">
+      <c r="A564" s="29" t="s">
+        <v>5088</v>
+      </c>
+      <c r="B564" s="27" t="s">
         <v>5109</v>
       </c>
-      <c r="C563" s="35"/>
-      <c r="D563" s="35"/>
-      <c r="E563" s="35"/>
-      <c r="F563" s="35"/>
-      <c r="G563" s="36"/>
-      <c r="H563" s="35"/>
-      <c r="I563" s="37"/>
-      <c r="J563" s="37"/>
-    </row>
-    <row r="564" spans="1:10">
-      <c r="A564" s="33" t="s">
-        <v>5088</v>
-      </c>
-      <c r="B564" s="34" t="s">
+      <c r="C564" s="9" t="s">
+        <v>5130</v>
+      </c>
+      <c r="D564" s="9" t="s">
+        <v>5148</v>
+      </c>
+      <c r="E564" s="9" t="s">
+        <v>5130</v>
+      </c>
+      <c r="F564" s="9" t="s">
+        <v>5183</v>
+      </c>
+      <c r="G564" s="31" t="s">
+        <v>5244</v>
+      </c>
+      <c r="H564" s="36" t="s">
+        <v>5261</v>
+      </c>
+      <c r="I564" s="12" t="s">
+        <v>5201</v>
+      </c>
+      <c r="J564" s="12" t="s">
+        <v>5222</v>
+      </c>
+    </row>
+    <row r="565" spans="1:10">
+      <c r="A565" s="29" t="s">
+        <v>5089</v>
+      </c>
+      <c r="B565" s="27" t="s">
         <v>5110</v>
       </c>
-      <c r="C564" s="35"/>
-      <c r="D564" s="35"/>
-      <c r="E564" s="35"/>
-      <c r="F564" s="35"/>
-      <c r="G564" s="36"/>
-      <c r="H564" s="35"/>
-      <c r="I564" s="37"/>
-      <c r="J564" s="37"/>
-    </row>
-    <row r="565" spans="1:10">
-      <c r="A565" s="33" t="s">
-        <v>5089</v>
-      </c>
-      <c r="B565" s="34" t="s">
-        <v>5111</v>
-      </c>
-      <c r="C565" s="35"/>
-      <c r="D565" s="35"/>
-      <c r="E565" s="35"/>
-      <c r="F565" s="35"/>
-      <c r="G565" s="36"/>
-      <c r="H565" s="35"/>
-      <c r="I565" s="37"/>
-      <c r="J565" s="37"/>
+      <c r="C565" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D565" s="9" t="s">
+        <v>5110</v>
+      </c>
+      <c r="E565" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="F565" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G565" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="H565" s="36" t="s">
+        <v>5262</v>
+      </c>
+      <c r="I565" s="12" t="s">
+        <v>5202</v>
+      </c>
+      <c r="J565" s="12" t="s">
+        <v>3401</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -34251,16 +35083,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E20926E-9EFB-4B7E-90D4-905B08F8E59C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
     <ds:schemaRef ds:uri="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/translations/translations.xlsx
+++ b/translations/translations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/russell/Projects/GPS-Sample/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A93F00-41D8-6846-BB2C-CF6E74189822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D486B6-3C5F-544C-9611-6C8C84290E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39520" yWindow="5180" windowWidth="29040" windowHeight="15720" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17740" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5723" uniqueCount="5354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5725" uniqueCount="5356">
   <si>
     <t>app_name</t>
   </si>
@@ -16129,13 +16129,19 @@
   </si>
   <si>
     <t>Allow Supervisors to edit this configuration.</t>
+  </si>
+  <si>
+    <t>name_already_exists</t>
+  </si>
+  <si>
+    <t>That configuration name already exists.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -16257,6 +16263,12 @@
       <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri Light (Headings)"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FFBCBEC4"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="9">
@@ -16477,18 +16489,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16710,8 +16720,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}" name="Table1" displayName="Table1" ref="A1:J582" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J582" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}" name="Table1" displayName="Table1" ref="A1:J583" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J583" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{DE67F62A-9DCA-4DFE-8C98-83B024E5D946}" name="app_name" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{BCDA3AB5-7BB5-4A21-ABBB-4186B52D559D}" name="GPSSample::en" dataDxfId="8"/>
@@ -17037,7 +17047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD3E6CC-854C-5841-9577-D3ADD2982DB6}">
-  <dimension ref="A1:J582"/>
+  <dimension ref="A1:J583"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="33.5" customWidth="1"/>
@@ -35291,196 +35301,212 @@
       </c>
     </row>
     <row r="571" spans="1:10">
-      <c r="A571" s="45" t="s">
+      <c r="A571" s="29" t="s">
         <v>5330</v>
       </c>
       <c r="B571" s="6" t="s">
         <v>5342</v>
       </c>
-      <c r="C571" s="47"/>
-      <c r="D571" s="47"/>
-      <c r="E571" s="47"/>
-      <c r="F571" s="47"/>
+      <c r="C571" s="9"/>
+      <c r="D571" s="9"/>
+      <c r="E571" s="9"/>
+      <c r="F571" s="9"/>
       <c r="G571" s="33"/>
-      <c r="H571" s="47"/>
-      <c r="I571" s="48"/>
-      <c r="J571" s="48"/>
+      <c r="H571" s="9"/>
+      <c r="I571" s="12"/>
+      <c r="J571" s="12"/>
     </row>
     <row r="572" spans="1:10">
-      <c r="A572" s="45" t="s">
+      <c r="A572" s="29" t="s">
         <v>5331</v>
       </c>
-      <c r="B572" s="46" t="s">
+      <c r="B572" s="27" t="s">
         <v>5343</v>
       </c>
-      <c r="C572" s="47"/>
-      <c r="D572" s="47"/>
-      <c r="E572" s="47"/>
-      <c r="F572" s="47"/>
+      <c r="C572" s="9"/>
+      <c r="D572" s="9"/>
+      <c r="E572" s="9"/>
+      <c r="F572" s="9"/>
       <c r="G572" s="33"/>
-      <c r="H572" s="47"/>
-      <c r="I572" s="48"/>
-      <c r="J572" s="48"/>
+      <c r="H572" s="9"/>
+      <c r="I572" s="12"/>
+      <c r="J572" s="12"/>
     </row>
     <row r="573" spans="1:10">
-      <c r="A573" s="45" t="s">
+      <c r="A573" s="29" t="s">
         <v>5332</v>
       </c>
-      <c r="B573" s="50" t="s">
+      <c r="B573" s="46" t="s">
         <v>5344</v>
       </c>
-      <c r="C573" s="47"/>
-      <c r="D573" s="47"/>
-      <c r="E573" s="47"/>
-      <c r="F573" s="47"/>
+      <c r="C573" s="9"/>
+      <c r="D573" s="9"/>
+      <c r="E573" s="9"/>
+      <c r="F573" s="9"/>
       <c r="G573" s="33"/>
-      <c r="H573" s="47"/>
-      <c r="I573" s="48"/>
-      <c r="J573" s="48"/>
+      <c r="H573" s="9"/>
+      <c r="I573" s="12"/>
+      <c r="J573" s="12"/>
     </row>
     <row r="574" spans="1:10">
-      <c r="A574" s="45" t="s">
+      <c r="A574" s="29" t="s">
         <v>5333</v>
       </c>
-      <c r="B574" s="46" t="s">
+      <c r="B574" s="27" t="s">
         <v>5345</v>
       </c>
-      <c r="C574" s="47"/>
-      <c r="D574" s="47"/>
-      <c r="E574" s="47"/>
-      <c r="F574" s="47"/>
+      <c r="C574" s="9"/>
+      <c r="D574" s="9"/>
+      <c r="E574" s="9"/>
+      <c r="F574" s="9"/>
       <c r="G574" s="33"/>
-      <c r="H574" s="47"/>
-      <c r="I574" s="48"/>
-      <c r="J574" s="48"/>
+      <c r="H574" s="9"/>
+      <c r="I574" s="12"/>
+      <c r="J574" s="12"/>
     </row>
     <row r="575" spans="1:10">
-      <c r="A575" s="45" t="s">
+      <c r="A575" s="29" t="s">
         <v>5334</v>
       </c>
-      <c r="B575" s="50" t="s">
+      <c r="B575" s="46" t="s">
         <v>5346</v>
       </c>
-      <c r="C575" s="47"/>
-      <c r="D575" s="47"/>
-      <c r="E575" s="47"/>
-      <c r="F575" s="47"/>
+      <c r="C575" s="9"/>
+      <c r="D575" s="9"/>
+      <c r="E575" s="9"/>
+      <c r="F575" s="9"/>
       <c r="G575" s="33"/>
-      <c r="H575" s="47"/>
-      <c r="I575" s="48"/>
-      <c r="J575" s="48"/>
+      <c r="H575" s="9"/>
+      <c r="I575" s="12"/>
+      <c r="J575" s="12"/>
     </row>
     <row r="576" spans="1:10">
-      <c r="A576" s="45" t="s">
+      <c r="A576" s="29" t="s">
         <v>5335</v>
       </c>
-      <c r="B576" s="46" t="s">
+      <c r="B576" s="27" t="s">
         <v>5347</v>
       </c>
-      <c r="C576" s="47"/>
-      <c r="D576" s="47"/>
-      <c r="E576" s="47"/>
-      <c r="F576" s="47"/>
+      <c r="C576" s="9"/>
+      <c r="D576" s="9"/>
+      <c r="E576" s="9"/>
+      <c r="F576" s="9"/>
       <c r="G576" s="33"/>
-      <c r="H576" s="47"/>
-      <c r="I576" s="48"/>
-      <c r="J576" s="48"/>
+      <c r="H576" s="9"/>
+      <c r="I576" s="12"/>
+      <c r="J576" s="12"/>
     </row>
     <row r="577" spans="1:10">
-      <c r="A577" s="45" t="s">
+      <c r="A577" s="29" t="s">
         <v>5336</v>
       </c>
-      <c r="B577" s="46" t="s">
+      <c r="B577" s="27" t="s">
         <v>5348</v>
       </c>
-      <c r="C577" s="47"/>
-      <c r="D577" s="47"/>
-      <c r="E577" s="47"/>
-      <c r="F577" s="47"/>
+      <c r="C577" s="9"/>
+      <c r="D577" s="9"/>
+      <c r="E577" s="9"/>
+      <c r="F577" s="9"/>
       <c r="G577" s="33"/>
-      <c r="H577" s="47"/>
-      <c r="I577" s="48"/>
-      <c r="J577" s="48"/>
+      <c r="H577" s="9"/>
+      <c r="I577" s="12"/>
+      <c r="J577" s="12"/>
     </row>
     <row r="578" spans="1:10">
-      <c r="A578" s="45" t="s">
+      <c r="A578" s="29" t="s">
         <v>5337</v>
       </c>
-      <c r="B578" s="46" t="s">
+      <c r="B578" s="27" t="s">
         <v>5349</v>
       </c>
-      <c r="C578" s="47"/>
-      <c r="D578" s="47"/>
-      <c r="E578" s="47"/>
-      <c r="F578" s="47"/>
+      <c r="C578" s="9"/>
+      <c r="D578" s="9"/>
+      <c r="E578" s="9"/>
+      <c r="F578" s="9"/>
       <c r="G578" s="33"/>
-      <c r="H578" s="47"/>
-      <c r="I578" s="48"/>
-      <c r="J578" s="48"/>
+      <c r="H578" s="9"/>
+      <c r="I578" s="12"/>
+      <c r="J578" s="12"/>
     </row>
     <row r="579" spans="1:10">
-      <c r="A579" s="45" t="s">
+      <c r="A579" s="29" t="s">
         <v>5338</v>
       </c>
-      <c r="B579" s="50" t="s">
+      <c r="B579" s="46" t="s">
         <v>5350</v>
       </c>
-      <c r="C579" s="47"/>
-      <c r="D579" s="47"/>
-      <c r="E579" s="47"/>
-      <c r="F579" s="47"/>
+      <c r="C579" s="9"/>
+      <c r="D579" s="9"/>
+      <c r="E579" s="9"/>
+      <c r="F579" s="9"/>
       <c r="G579" s="33"/>
-      <c r="H579" s="47"/>
-      <c r="I579" s="48"/>
-      <c r="J579" s="48"/>
+      <c r="H579" s="9"/>
+      <c r="I579" s="12"/>
+      <c r="J579" s="12"/>
     </row>
     <row r="580" spans="1:10" ht="25">
-      <c r="A580" s="45" t="s">
+      <c r="A580" s="29" t="s">
         <v>5339</v>
       </c>
-      <c r="B580" s="46" t="s">
+      <c r="B580" s="27" t="s">
         <v>5351</v>
       </c>
-      <c r="C580" s="47"/>
-      <c r="D580" s="47"/>
-      <c r="E580" s="47"/>
-      <c r="F580" s="47"/>
+      <c r="C580" s="9"/>
+      <c r="D580" s="9"/>
+      <c r="E580" s="9"/>
+      <c r="F580" s="9"/>
       <c r="G580" s="33"/>
-      <c r="H580" s="47"/>
-      <c r="I580" s="48"/>
-      <c r="J580" s="48"/>
+      <c r="H580" s="9"/>
+      <c r="I580" s="12"/>
+      <c r="J580" s="12"/>
     </row>
     <row r="581" spans="1:10">
-      <c r="A581" s="45" t="s">
+      <c r="A581" s="29" t="s">
         <v>5340</v>
       </c>
-      <c r="B581" s="49" t="s">
+      <c r="B581" s="45" t="s">
         <v>5352</v>
       </c>
-      <c r="C581" s="47"/>
-      <c r="D581" s="47"/>
-      <c r="E581" s="47"/>
-      <c r="F581" s="47"/>
+      <c r="C581" s="9"/>
+      <c r="D581" s="9"/>
+      <c r="E581" s="9"/>
+      <c r="F581" s="9"/>
       <c r="G581" s="33"/>
-      <c r="H581" s="47"/>
-      <c r="I581" s="48"/>
-      <c r="J581" s="48"/>
+      <c r="H581" s="9"/>
+      <c r="I581" s="12"/>
+      <c r="J581" s="12"/>
     </row>
     <row r="582" spans="1:10">
-      <c r="A582" s="45" t="s">
+      <c r="A582" s="29" t="s">
         <v>5341</v>
       </c>
-      <c r="B582" s="46" t="s">
+      <c r="B582" s="27" t="s">
         <v>5353</v>
       </c>
-      <c r="C582" s="47"/>
-      <c r="D582" s="47"/>
-      <c r="E582" s="47"/>
-      <c r="F582" s="47"/>
+      <c r="C582" s="9"/>
+      <c r="D582" s="9"/>
+      <c r="E582" s="9"/>
+      <c r="F582" s="9"/>
       <c r="G582" s="33"/>
-      <c r="H582" s="47"/>
-      <c r="I582" s="48"/>
-      <c r="J582" s="48"/>
+      <c r="H582" s="9"/>
+      <c r="I582" s="12"/>
+      <c r="J582" s="12"/>
+    </row>
+    <row r="583" spans="1:10">
+      <c r="A583" s="47" t="s">
+        <v>5354</v>
+      </c>
+      <c r="B583" s="50" t="s">
+        <v>5355</v>
+      </c>
+      <c r="C583" s="48"/>
+      <c r="D583" s="48"/>
+      <c r="E583" s="48"/>
+      <c r="F583" s="48"/>
+      <c r="G583" s="33"/>
+      <c r="H583" s="48"/>
+      <c r="I583" s="49"/>
+      <c r="J583" s="49"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -35494,14 +35520,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e0cf07b-8188-4b76-8f54-3cda03d37414" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="43e153a8-5ef1-4f65-aac7-dc4685f18eaa">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -35746,27 +35770,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e0cf07b-8188-4b76-8f54-3cda03d37414" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="43e153a8-5ef1-4f65-aac7-dc4685f18eaa">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E20926E-9EFB-4B7E-90D4-905B08F8E59C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
-    <ds:schemaRef ds:uri="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -35791,9 +35808,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E20926E-9EFB-4B7E-90D4-905B08F8E59C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
+    <ds:schemaRef ds:uri="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>